--- a/tests/traces/h100/Falconsai_nsfw_image_detection__1016002_perf_report.xlsx
+++ b/tests/traces/h100/Falconsai_nsfw_image_detection__1016002_perf_report.xlsx
@@ -11,10 +11,12 @@
     <sheet name="ops_summary_by_category" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="ops_summary" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="ops_unique_args" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="GEMM" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="SDPA_fwd" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="CONV_fwd" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="BinaryElementwise" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="unified_perf_summary" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="GEMM" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="SDPA_fwd" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="CONV_fwd" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="BinaryElementwise" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Normalization" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -561,13 +563,504 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AK3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>param: op_shape</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>param: dtype_in_out</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>param: stride_input</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>param: stride_output</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>param: num_channels</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>param: has_bias</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>param: is_affine</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>param: is_training</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>GFLOPS_first</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Data Moved (MB)_first</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>FLOPS/Byte_first</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>TB/s_mean</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>TB/s_median</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>TB/s_std</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>TB/s_min</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>TB/s_max</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>TFLOPS/s_mean</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>TFLOPS/s_median</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>TFLOPS/s_std</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>TFLOPS/s_min</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>TFLOPS/s_max</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Compute Spec</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>kernel_details__summarize_kernel_stats</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>trunc_kernel_details</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Input Dims_first</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Input type_first</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Input Strides_first</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Concrete Inputs_first</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel Time (µs)_mean</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel Time (µs)_median</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel Time (µs)_std</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel Time (µs)_min</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel Time (µs)_max</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel Time (µs)_sum</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>name_count</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>UID_first</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>aten::layer_norm</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>(4, 197, 768)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>('c10::BFloat16', None)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>(151296, 768, 1)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>768</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>0.003030528</v>
+      </c>
+      <c r="K2" t="n">
+        <v>2.3173828125</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.247155499367889</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.5466261436434106</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.5463023981557714</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.0136524750083966</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.5237086762430939</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.5709334820168646</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.6817278011431411</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.6813240401778364</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.01702675928670446</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.6531461556432518</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.7120428318705904</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>vector_bf16</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 7, 'count': 25, 'total_duration_us': np.float64(111.20100000000001), 'mean_duration_us': np.float64(4.448040000000001), 'median_duration_us': np.float64(4.448), 'std_dev_duration_us': np.float64(0.10934037863479323), 'min_duration_us': np.float64(4.256), 'max_duration_us': np.float64(4.64)}]</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_ke...', 'stream': 7, 'mean_duration_us': np.float64(4.45)}]</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>[[4, 197, 768], [], [768], [768], [], []]</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>['c10::BFloat16', 'ScalarList', 'c10::BFloat16', 'c10::BFloat16', 'Scalar', 'Scalar']</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>[[151296, 768, 1], [], [1], [1], [], []]</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>['', '[768]', '', '', '9.9999999999999998e-13', 'True']</t>
+        </is>
+      </c>
+      <c r="AD2" t="n">
+        <v>4.448037109375</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>4.447998046875</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0.1115342775722907</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>4.256103515625</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>4.639892578125</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>111.200927734375</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>aten::native_layer_norm</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>(4, 197, 768)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>('c10::BFloat16', None)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>(151296, 768, 1)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>768</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>0.003030528</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2.3173828125</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.247155499367889</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.5466261436434106</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.5463023981557714</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.0136524750083966</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.5237086762430939</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.5709334820168646</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.6817278011431411</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.6813240401778364</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.01702675928670446</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.6531461556432518</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.7120428318705904</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>vector_bf16</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 7, 'count': 25, 'total_duration_us': np.float64(111.20100000000001), 'mean_duration_us': np.float64(4.448040000000001), 'median_duration_us': np.float64(4.448), 'std_dev_duration_us': np.float64(0.10934037863479323), 'min_duration_us': np.float64(4.256), 'max_duration_us': np.float64(4.64)}]</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_ke...', 'stream': 7, 'mean_duration_us': np.float64(4.45)}]</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>[[4, 197, 768], [], [768], [768], []]</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>['c10::BFloat16', 'ScalarList', 'c10::BFloat16', 'c10::BFloat16', 'Scalar']</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>[[151296, 768, 1], [], [1], [1], []]</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>['', '[768]', '', '', '9.9999999999999998e-13']</t>
+        </is>
+      </c>
+      <c r="AD3" t="n">
+        <v>4.448037109375</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>4.447998046875</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0.1115342775722907</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>4.256103515625</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>4.639892578125</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>111.200927734375</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>18</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -610,10 +1103,10 @@
         <v>0.73503662109375</v>
       </c>
       <c r="D2" t="n">
-        <v>59.98786578240298</v>
+        <v>59.98786578240299</v>
       </c>
       <c r="E2" t="n">
-        <v>59.98786578240298</v>
+        <v>59.98786578240299</v>
       </c>
     </row>
     <row r="3">
@@ -623,16 +1116,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="C3" t="n">
-        <v>0.24131298828125</v>
+        <v>0.130112060546875</v>
       </c>
       <c r="D3" t="n">
-        <v>19.69405433300158</v>
+        <v>10.61871558609367</v>
       </c>
       <c r="E3" t="n">
-        <v>79.68192011540457</v>
+        <v>70.60658136849666</v>
       </c>
     </row>
     <row r="4">
@@ -651,7 +1144,7 @@
         <v>10.25309507229224</v>
       </c>
       <c r="E4" t="n">
-        <v>89.93501518769681</v>
+        <v>80.8596764407889</v>
       </c>
     </row>
     <row r="5">
@@ -670,7 +1163,26 @@
         <v>10.06498481230318</v>
       </c>
       <c r="E5" t="n">
-        <v>99.99999999999999</v>
+        <v>90.92466125309208</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>NORM_fwd</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>25</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.111200927734375</v>
+      </c>
+      <c r="D6" t="n">
+        <v>9.075338746907917</v>
+      </c>
+      <c r="E6" t="n">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -684,7 +1196,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -705,15 +1217,20 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Categories</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>total_direct_kernel_time_ms</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Percentage (%)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Cumulative Percentage (%)</t>
         </is>
@@ -731,15 +1248,20 @@
       <c r="C2" t="n">
         <v>73</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>{'GEMM'}</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
         <v>0.73503662109375</v>
-      </c>
-      <c r="E2" t="n">
-        <v>59.98786578240299</v>
       </c>
       <c r="F2" t="n">
         <v>59.98786578240299</v>
       </c>
+      <c r="G2" t="n">
+        <v>59.98786578240299</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -753,13 +1275,18 @@
       <c r="C3" t="n">
         <v>1</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>{'CONV_fwd'}</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
         <v>0.125632080078125</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>10.25309507229224</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>70.24096085469523</v>
       </c>
     </row>
@@ -775,13 +1302,18 @@
       <c r="C4" t="n">
         <v>12</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>{'other'}</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
         <v>0.12284814453125</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>10.02589230832071</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>80.26685316301594</v>
       </c>
     </row>
@@ -797,13 +1329,18 @@
       <c r="C5" t="n">
         <v>25</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>{'NORM_fwd'}</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
         <v>0.111200927734375</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>9.075338746907917</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>89.34219190992386</v>
       </c>
     </row>
@@ -819,13 +1356,18 @@
       <c r="C6" t="n">
         <v>12</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>{'elementwise'}</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
         <v>0.060541259765625</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>4.94089799187665</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>94.28308990180051</v>
       </c>
     </row>
@@ -841,13 +1383,18 @@
       <c r="C7" t="n">
         <v>25</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>{'elementwise'}</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
         <v>0.05731298828125</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>4.677432048879577</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>98.96052195068009</v>
       </c>
     </row>
@@ -863,13 +1410,18 @@
       <c r="C8" t="n">
         <v>1</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>{'other'}</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
         <v>0.007263916015625</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>0.5928232777729626</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>99.55334522845305</v>
       </c>
     </row>
@@ -885,13 +1437,18 @@
       <c r="C9" t="n">
         <v>1</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>{'elementwise'}</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
         <v>0.003968017578125</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>0.3238381586274984</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>99.87718338708055</v>
       </c>
     </row>
@@ -907,13 +1464,18 @@
       <c r="C10" t="n">
         <v>1</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>{'elementwise'}</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
         <v>0.0015048828125</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>0.1228166129194549</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>100</v>
       </c>
     </row>
@@ -928,7 +1490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q14"/>
+  <dimension ref="A1:R14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -939,80 +1501,85 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>op category</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Input Dims</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Input type</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Input Strides</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Concrete Inputs</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>operation_count</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>total_direct_kernel_time_mean</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>total_direct_kernel_time_median</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>total_direct_kernel_time_std</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>total_direct_kernel_time_min</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>total_direct_kernel_time_max</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>total_direct_kernel_time_sum</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>ex_UID</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>kernel_details_summary</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>trunc_kernel_details</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Percentage (%)</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Cumulative Percentage (%)</t>
         </is>
@@ -1026,64 +1593,69 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>GEMM</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>((768,), (788, 768), (768, 768), (), ())</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>('c10::BFloat16', 'c10::BFloat16', 'c10::BFloat16', 'Scalar', 'Scalar')</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>((1,), (768, 1), (1, 768), (), ())</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>('', '', '', '1', '1')</t>
         </is>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>48</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>8.315348307291666</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>8.256103515625</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>0.1344482499064346</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>8.1279296875</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>8.639892578125</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>399.13671875</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>30</v>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_128x64_64x6_tn_align8&gt;(cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_128x64_64x6_tn_align8::Params)', 'stream': 7, 'count': 48, 'total_duration_us': np.float64(399.136), 'mean_duration_us': np.float64(8.315333333333333), 'median_duration_us': np.float64(8.256), 'std_dev_duration_us': np.float64(0.13305517861231703), 'min_duration_us': np.float64(8.128), 'max_duration_us': np.float64(8.64)}]</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_80_tensorop_bf16_s16816gemm_relu_b...', 'stream': 7, 'mean_duration_us': np.float64(8.32)}]</t>
         </is>
-      </c>
-      <c r="P2" t="n">
-        <v>32.57437687604667</v>
       </c>
       <c r="Q2" t="n">
         <v>32.57437687604667</v>
       </c>
+      <c r="R2" t="n">
+        <v>32.57437687604667</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1093,62 +1665,67 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>GEMM</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>((3072,), (788, 768), (768, 3072), (), ())</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>('c10::BFloat16', 'c10::BFloat16', 'c10::BFloat16', 'Scalar', 'Scalar')</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>((1,), (768, 1), (1, 768), (), ())</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>('', '', '', '1', '1')</t>
         </is>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>12</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>13.88246663411458</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>13.887451171875</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>0.1063651301764554</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>13.760009765625</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>14.176025390625</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>166.589599609375</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>104</v>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>[{'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'count': 12, 'total_duration_us': np.float64(166.59), 'mean_duration_us': np.float64(13.8825), 'median_duration_us': np.float64(13.8875), 'std_dev_duration_us': np.float64(0.10183278777813505), 'min_duration_us': np.float64(13.76), 'max_duration_us': np.float64(14.176)}]</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>[{'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warp...', 'stream': 7, 'mean_duration_us': np.float64(13.88)}]</t>
         </is>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>13.59572333585382</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>46.1701002119005</v>
       </c>
     </row>
@@ -1160,62 +1737,67 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>GEMM</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>((768,), (788, 3072), (3072, 768), (), ())</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>('c10::BFloat16', 'c10::BFloat16', 'c10::BFloat16', 'Scalar', 'Scalar')</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>((1,), (3072, 1), (1, 3072), (), ())</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>('', '', '', '1', '1')</t>
         </is>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>12</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>13.53594970703125</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>13.4879150390625</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>0.1773776572326171</v>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>13.343994140625</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>13.951904296875</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>162.431396484375</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>114</v>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>[{'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x64x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'count': 12, 'total_duration_us': np.float64(162.43200000000002), 'mean_duration_us': np.float64(13.536000000000001), 'median_duration_us': np.float64(13.488), 'std_dev_duration_us': np.float64(0.16983128883296716), 'min_duration_us': np.float64(13.344), 'max_duration_us': np.float64(13.952)}]</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>[{'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x64x64_warpg...', 'stream': 7, 'mean_duration_us': np.float64(13.54)}]</t>
         </is>
       </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
         <v>13.25636373961045</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>59.42646395151095</v>
       </c>
     </row>
@@ -1227,37 +1809,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>CONV_fwd</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
           <t>((4, 3, 224, 224), (768, 3, 16, 16), (), (), (), (), (), (), ())</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>('c10::BFloat16', 'c10::BFloat16', 'ScalarList', 'ScalarList', 'ScalarList', 'Scalar', 'Scalar', 'Scalar', 'Scalar')</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>((150528, 50176, 224, 1), (768, 256, 16, 1), (), (), (), (), (), (), ())</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>('', '', '[0, 0]', '[16, 16]', '[1, 1]', '1', 'False', 'False', 'True')</t>
         </is>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>1</v>
-      </c>
-      <c r="G5" t="n">
-        <v>125.632080078125</v>
       </c>
       <c r="H5" t="n">
         <v>125.632080078125</v>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="n">
+      <c r="I5" t="n">
         <v>125.632080078125</v>
       </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
         <v>125.632080078125</v>
       </c>
@@ -1265,22 +1849,25 @@
         <v>125.632080078125</v>
       </c>
       <c r="M5" t="n">
+        <v>125.632080078125</v>
+      </c>
+      <c r="N5" t="n">
         <v>4</v>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>[{'name': 'Memset (Device)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(2.272), 'mean_duration_us': np.float64(2.272), 'median_duration_us': np.float64(2.272), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(2.272), 'max_duration_us': np.float64(2.272)}, {'name': 'void cudnn::engines_precompiled::nchwToNhwcKernel&lt;__nv_bfloat16, __nv_bfloat16, float, false, true, (cudnnKernelDataType_t)0&gt;(cudnn::engines_precompiled::nchw2nhwc_params_t&lt;float&gt;, __nv_bfloat16 const*, __nv_bfloat16*)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(10.464), 'mean_duration_us': np.float64(10.464), 'median_duration_us': np.float64(10.464), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(10.464), 'max_duration_us': np.float64(10.464)}, {'name': 'Memset (Device)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(2.112), 'mean_duration_us': np.float64(2.112), 'median_duration_us': np.float64(2.112), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(2.112), 'max_duration_us': np.float64(2.112)}, {'name': 'void cudnn::engines_precompiled::nchwToNhwcKernel&lt;__nv_bfloat16, __nv_bfloat16, float, false, true, (cudnnKernelDataType_t)0&gt;(cudnn::engines_precompiled::nchw2nhwc_params_t&lt;float&gt;, __nv_bfloat16 const*, __nv_bfloat16*)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(10.4), 'mean_duration_us': np.float64(10.4), 'median_duration_us': np.float64(10.4), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(10.4), 'max_duration_us': np.float64(10.4)}, {'name': 'void cutlass__5x_cudnn::Kernel&lt;cutlass_tensorop_bf16_s16816fprop_optimized_bf16_256x64_32x4_nhwc_align8&gt;(cutlass_tensorop_bf16_s16816fprop_optimized_bf16_256x64_32x4_nhwc_align8::Params)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(98.176), 'mean_duration_us': np.float64(98.176), 'median_duration_us': np.float64(98.176), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(98.176), 'max_duration_us': np.float64(98.176)}, {'name': 'void cudnn::engines_precompiled::nhwcToNchwKernel&lt;__nv_bfloat16, __nv_bfloat16, float, true, false, (cudnnKernelDataType_t)0&gt;(cudnn::engines_precompiled::nhwc2nchw_params_t&lt;float&gt;, __nv_bfloat16 const*, __nv_bfloat16*)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(2.208), 'mean_duration_us': np.float64(2.208), 'median_duration_us': np.float64(2.208), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(2.208), 'max_duration_us': np.float64(2.208)}]</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>[{'name': 'Memset (Device)', 'stream': 7, 'mean_duration_us': np.float64(2.27)}, {'name': 'void cudnn::engines_precompiled::nchwToNhwcKernel&lt;__nv_bfloat16,...', 'stream': 7, 'mean_duration_us': np.float64(10.46)}, {'name': 'Memset (Device)', 'stream': 7, 'mean_duration_us': np.float64(2.11)}, {'name': 'void cudnn::engines_precompiled::nchwToNhwcKernel&lt;__nv_bfloat16,...', 'stream': 7, 'mean_duration_us': np.float64(10.4)}, {'name': 'void cutlass__5x_cudnn::Kernel&lt;cutlass_tensorop_bf16_s16816fprop...', 'stream': 7, 'mean_duration_us': np.float64(98.18)}, {'name': 'void cudnn::engines_precompiled::nhwcToNchwKernel&lt;__nv_bfloat16,...', 'stream': 7, 'mean_duration_us': np.float64(2.21)}]</t>
         </is>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
         <v>10.25309507229224</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>69.67955902380319</v>
       </c>
     </row>
@@ -1292,62 +1879,67 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
           <t>((4, 197, 12, 64), (4, 197, 12, 64), (4, 197, 12, 64), (), (), (), (), (), (), (), (), (), (), (), ())</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>('c10::BFloat16', 'c10::BFloat16', 'c10::BFloat16', '', '', 'Scalar', 'Scalar', 'Scalar', 'Scalar', 'Scalar', 'Scalar', '', '', '', '')</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>((151296, 768, 64, 1), (151296, 768, 64, 1), (151296, 768, 64, 1), (), (), (), (), (), (), (), (), (), (), (), ())</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>('', '', '', '', '', '197', '197', '0.', 'False', 'False', '0.125', '', '', '', '')</t>
         </is>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>12</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>10.23734537760417</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>10.2239990234375</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>0.228442528412397</v>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>10.01611328125</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>10.847900390625</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>122.84814453125</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>68</v>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>[{'name': 'void pytorch_flash::flash_fwd_kernel&lt;pytorch_flash::Flash_fwd_kernel_traits&lt;64, 128, 128, 4, false, false, cutlass::bfloat16_t, pytorch_flash::Flash_kernel_traits&lt;64, 128, 128, 4, cutlass::bfloat16_t&gt; &gt;, false, false, false, false, false, true, false&gt;(pytorch_flash::Flash_fwd_params)', 'stream': 7, 'count': 12, 'total_duration_us': np.float64(122.848), 'mean_duration_us': np.float64(10.237333333333334), 'median_duration_us': np.float64(10.224), 'std_dev_duration_us': np.float64(0.21878045819699932), 'min_duration_us': np.float64(10.016), 'max_duration_us': np.float64(10.848)}]</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>[{'name': 'void pytorch_flash::flash_fwd_kernel&lt;pytorch_flash::Flash_fwd_ke...', 'stream': 7, 'mean_duration_us': np.float64(10.24)}]</t>
         </is>
       </c>
-      <c r="P6" t="n">
+      <c r="Q6" t="n">
         <v>10.02589230832071</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>79.7054513321239</v>
       </c>
     </row>
@@ -1359,62 +1951,67 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>NORM_fwd</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
           <t>((4, 197, 768), (), (768,), (768,), ())</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>('c10::BFloat16', 'ScalarList', 'c10::BFloat16', 'c10::BFloat16', 'Scalar')</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>((151296, 768, 1), (), (1,), (1,), ())</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>('', '[768]', '', '', '9.9999999999999998e-13')</t>
         </is>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>25</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>4.448037109375</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>4.447998046875</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>0.1115342775722907</v>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>4.256103515625</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>4.639892578125</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>111.200927734375</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>18</v>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 7, 'count': 25, 'total_duration_us': np.float64(111.20100000000001), 'mean_duration_us': np.float64(4.448040000000001), 'median_duration_us': np.float64(4.448), 'std_dev_duration_us': np.float64(0.10934037863479323), 'min_duration_us': np.float64(4.256), 'max_duration_us': np.float64(4.64)}]</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_ke...', 'stream': 7, 'mean_duration_us': np.float64(4.45)}]</t>
         </is>
       </c>
-      <c r="P7" t="n">
+      <c r="Q7" t="n">
         <v>9.075338746907917</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>88.78079007903182</v>
       </c>
     </row>
@@ -1426,62 +2023,67 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
           <t>((4, 197, 3072), ())</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>('c10::BFloat16', '')</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>((605184, 3072, 1), ())</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>('', '')</t>
         </is>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>12</v>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>5.04510498046875</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>5.055419921875</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>0.03943788318148379</v>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>4.990966796875</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>5.1201171875</v>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
         <v>60.541259765625</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>107</v>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::GeluCUDAKernelImpl(at::TensorIteratorBase&amp;, at::native::GeluType)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::GeluCUDAKernelImpl(at::TensorIteratorBase&amp;, at::native::GeluType)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 12, 'total_duration_us': np.float64(60.541999999999994), 'mean_duration_us': np.float64(5.045166666666666), 'median_duration_us': np.float64(5.0555), 'std_dev_duration_us': np.float64(0.037739972914080884), 'min_duration_us': np.float64(4.991), 'max_duration_us': np.float64(5.12)}]</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::Ge...', 'stream': 7, 'mean_duration_us': np.float64(5.05)}]</t>
         </is>
       </c>
-      <c r="P8" t="n">
+      <c r="Q8" t="n">
         <v>4.940897991876649</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>93.72168807090847</v>
       </c>
     </row>
@@ -1493,62 +2095,67 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
           <t>((4, 197, 768), (4, 197, 768), ())</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>('c10::BFloat16', 'c10::BFloat16', 'Scalar')</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>((151296, 768, 1), (151296, 768, 1), ())</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>('', '', '1')</t>
         </is>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>24</v>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>2.230662027994792</v>
       </c>
-      <c r="H9" t="n">
+      <c r="I9" t="n">
         <v>2.2244873046875</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>0.03450867810431143</v>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>2.176025390625</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>2.303955078125</v>
       </c>
-      <c r="L9" t="n">
+      <c r="M9" t="n">
         <v>53.535888671875</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>90</v>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 7, 'count': 24, 'total_duration_us': np.float64(53.536), 'mean_duration_us': np.float64(2.2306666666666666), 'median_duration_us': np.float64(2.2245), 'std_dev_duration_us': np.float64(0.033798011118341686), 'min_duration_us': np.float64(2.176), 'max_duration_us': np.float64(2.304)}]</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CU...', 'stream': 7, 'mean_duration_us': np.float64(2.23)}]</t>
         </is>
       </c>
-      <c r="P9" t="n">
+      <c r="Q9" t="n">
         <v>4.369175102338875</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>98.09086317324734</v>
       </c>
     </row>
@@ -1560,37 +2167,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
           <t>(((4, 1, 768), (4, 196, 768)), ())</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>('TensorList', 'Scalar')</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>(((0, 768, 1), (150528, 1, 196)), ())</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>('', '1')</t>
         </is>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>1</v>
-      </c>
-      <c r="G10" t="n">
-        <v>7.263916015625</v>
       </c>
       <c r="H10" t="n">
         <v>7.263916015625</v>
       </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="n">
+      <c r="I10" t="n">
         <v>7.263916015625</v>
       </c>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="n">
         <v>7.263916015625</v>
       </c>
@@ -1598,22 +2207,25 @@
         <v>7.263916015625</v>
       </c>
       <c r="M10" t="n">
+        <v>7.263916015625</v>
+      </c>
+      <c r="N10" t="n">
         <v>14</v>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::(anonymous namespace)::CatArrayBatchedCopy&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 3, 64, 64&gt;(at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;*, at::native::(anonymous namespace)::CatArrInputTensorMetadata&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 64, 64&gt;, at::native::(anonymous namespace)::TensorSizeStride&lt;unsigned int, 4u&gt;, int, unsigned int)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(7.264), 'mean_duration_us': np.float64(7.264), 'median_duration_us': np.float64(7.264), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(7.264), 'max_duration_us': np.float64(7.264)}]</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::(anonymous namespace)::CatArrayBatchedCopy&lt;at::...', 'stream': 7, 'mean_duration_us': np.float64(7.26)}]</t>
         </is>
       </c>
-      <c r="P10" t="n">
+      <c r="Q10" t="n">
         <v>0.5928232777729626</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>98.68368645102031</v>
       </c>
     </row>
@@ -1625,37 +2237,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>GEMM</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
           <t>((768,), (4, 768), (768, 768), (), ())</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>('c10::BFloat16', 'c10::BFloat16', 'c10::BFloat16', 'Scalar', 'Scalar')</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>((1,), (151296, 1), (1, 768), (), ())</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>('', '', '', '1', '1')</t>
         </is>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>1</v>
-      </c>
-      <c r="G11" t="n">
-        <v>6.87890625</v>
       </c>
       <c r="H11" t="n">
         <v>6.87890625</v>
       </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="n">
+      <c r="I11" t="n">
         <v>6.87890625</v>
       </c>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="n">
         <v>6.87890625</v>
       </c>
@@ -1663,22 +2277,25 @@
         <v>6.87890625</v>
       </c>
       <c r="M11" t="n">
+        <v>6.87890625</v>
+      </c>
+      <c r="N11" t="n">
         <v>1256</v>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_64x64_64x6_tn_align8&gt;(cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_64x64_64x6_tn_align8::Params)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(6.879), 'mean_duration_us': np.float64(6.879), 'median_duration_us': np.float64(6.879), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(6.879), 'max_duration_us': np.float64(6.879)}]</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_80_tensorop_bf16_s16816gemm_relu_b...', 'stream': 7, 'mean_duration_us': np.float64(6.88)}]</t>
         </is>
       </c>
-      <c r="P11" t="n">
+      <c r="Q11" t="n">
         <v>0.5614018308920443</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>99.24508828191234</v>
       </c>
     </row>
@@ -1690,37 +2307,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
           <t>((4, 768, 14, 14), (1, 768, 1, 1), ())</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>('c10::BFloat16', 'c10::BFloat16', 'Scalar')</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>((150528, 196, 14, 1), (768, 1, 1, 1), ())</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>('', '', '1')</t>
         </is>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>1</v>
-      </c>
-      <c r="G12" t="n">
-        <v>3.968017578125</v>
       </c>
       <c r="H12" t="n">
         <v>3.968017578125</v>
       </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="n">
+      <c r="I12" t="n">
         <v>3.968017578125</v>
       </c>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="n">
         <v>3.968017578125</v>
       </c>
@@ -1728,22 +2347,25 @@
         <v>3.968017578125</v>
       </c>
       <c r="M12" t="n">
+        <v>3.968017578125</v>
+      </c>
+      <c r="N12" t="n">
         <v>7</v>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(3.968), 'mean_duration_us': np.float64(3.968), 'median_duration_us': np.float64(3.968), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(3.968), 'max_duration_us': np.float64(3.968)}]</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(3.97)}]</t>
         </is>
       </c>
-      <c r="P12" t="n">
+      <c r="Q12" t="n">
         <v>0.3238381586274984</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>99.56892644053984</v>
       </c>
     </row>
@@ -1755,37 +2377,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
           <t>((4, 197, 768), (1, 197, 768), ())</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>('c10::BFloat16', 'c10::BFloat16', 'Scalar')</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>((151296, 768, 1), (151296, 768, 1), ())</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>('', '', '1')</t>
         </is>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
         <v>1</v>
-      </c>
-      <c r="G13" t="n">
-        <v>3.777099609375</v>
       </c>
       <c r="H13" t="n">
         <v>3.777099609375</v>
       </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="n">
+      <c r="I13" t="n">
         <v>3.777099609375</v>
       </c>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="n">
         <v>3.777099609375</v>
       </c>
@@ -1793,22 +2417,25 @@
         <v>3.777099609375</v>
       </c>
       <c r="M13" t="n">
+        <v>3.777099609375</v>
+      </c>
+      <c r="N13" t="n">
         <v>15</v>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(3.777), 'mean_duration_us': np.float64(3.777), 'median_duration_us': np.float64(3.777), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(3.777), 'max_duration_us': np.float64(3.777)}]</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(3.78)}]</t>
         </is>
       </c>
-      <c r="P13" t="n">
+      <c r="Q13" t="n">
         <v>0.3082569465407019</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>99.87718338708055</v>
       </c>
     </row>
@@ -1820,37 +2447,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
           <t>((4, 768),)</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>('c10::BFloat16',)</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>((768, 1),)</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>('',)</t>
         </is>
       </c>
-      <c r="F14" t="n">
+      <c r="G14" t="n">
         <v>1</v>
-      </c>
-      <c r="G14" t="n">
-        <v>1.5048828125</v>
       </c>
       <c r="H14" t="n">
         <v>1.5048828125</v>
       </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="n">
+      <c r="I14" t="n">
         <v>1.5048828125</v>
       </c>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="n">
         <v>1.5048828125</v>
       </c>
@@ -1858,22 +2487,25 @@
         <v>1.5048828125</v>
       </c>
       <c r="M14" t="n">
+        <v>1.5048828125</v>
+      </c>
+      <c r="N14" t="n">
         <v>1258</v>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::tanh_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::tanh_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(1.505), 'mean_duration_us': np.float64(1.505), 'median_duration_us': np.float64(1.505), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(1.505), 'max_duration_us': np.float64(1.505)}]</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::ta...', 'stream': 7, 'mean_duration_us': np.float64(1.5)}]</t>
         </is>
       </c>
-      <c r="P14" t="n">
+      <c r="Q14" t="n">
         <v>0.1228166129194549</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>100</v>
       </c>
     </row>
@@ -1888,7 +2520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ5"/>
+  <dimension ref="A1:AN13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1899,177 +2531,197 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>param: M</t>
+          <t>op category</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>param: N</t>
+          <t>Input Dims</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>param: K</t>
+          <t>Input type</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>param: bias</t>
+          <t>Input Strides</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>param: stride_A</t>
+          <t>Concrete Inputs</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>param: stride_B</t>
+          <t>ex_UID</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>param: dtype_A_B</t>
+          <t>operation_count</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>param: B</t>
+          <t>total_duration_us</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>GFLOPS_first</t>
+          <t>mean_duration_us</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Data Moved (MB)_first</t>
+          <t>std_duration_us</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>FLOPS/Byte_first</t>
+          <t>GFLOPS</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>Data Moved (MB)</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>FLOPS/Byte</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Compute Spec</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
           <t>TB/s_mean</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>TB/s_std</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>TFLOPS/s_mean</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>TFLOPS/s_std</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel Time (µs)_mean</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel Time (µs)_std</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel Time (µs)_sum</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>duration_us_median</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>duration_us_min</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>duration_us_max</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>TB/s_median</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>TB/s_std</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>TB/s_min</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>TB/s_max</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>TFLOPS/s_mean</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>TFLOPS/s_median</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>TFLOPS/s_std</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>TFLOPS/s_min</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>TFLOPS/s_max</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>kernel_details__summarize_kernel_stats</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel Time (µs)_median</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel Time (µs)_min</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel Time (µs)_max</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>kernel_details_summary</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>trunc_kernel_details</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>Input Dims_first</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>Input type_first</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>Input Strides_first</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>Concrete Inputs_first</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>Kernel Time (µs)_mean</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>Kernel Time (µs)_median</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>Kernel Time (µs)_std</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>Kernel Time (µs)_min</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>Kernel Time (µs)_max</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>Kernel Time (µs)_sum</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>name_count</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>UID_first</t>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>perf_params</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>has_perf_model</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>Percentage (%)</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>Cumulative Percentage (%)</t>
         </is>
       </c>
     </row>
@@ -2079,128 +2731,140 @@
           <t>aten::addmm</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>788</v>
-      </c>
-      <c r="C2" t="n">
-        <v>768</v>
-      </c>
-      <c r="D2" t="n">
-        <v>768</v>
-      </c>
-      <c r="E2" t="b">
-        <v>1</v>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>GEMM</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>((768,), (788, 768), (768, 768), (), ())</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>('c10::BFloat16', 'c10::BFloat16', 'c10::BFloat16', 'Scalar', 'Scalar')</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>((1,), (768, 1), (1, 768), (), ())</t>
+        </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>(768, 1)</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>(1, 768)</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>('c10::BFloat16', 'c10::BFloat16')</t>
-        </is>
+          <t>('', '', '', '1', '1')</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H2" t="n">
+        <v>48</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>1154.879</v>
       </c>
       <c r="J2" t="n">
+        <v>24.05997916666666</v>
+      </c>
+      <c r="K2" t="n">
+        <v>3.557746534509176</v>
+      </c>
+      <c r="L2" t="n">
         <v>0.930167808</v>
       </c>
-      <c r="K2" t="n">
+      <c r="M2" t="n">
         <v>3.43505859375</v>
       </c>
-      <c r="L2" t="n">
+      <c r="N2" t="n">
         <v>258.2422174840085</v>
       </c>
-      <c r="M2" t="n">
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>matrix_bf16</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
         <v>0.4332748290550287</v>
       </c>
-      <c r="N2" t="n">
-        <v>0.4362735996688056</v>
-      </c>
-      <c r="O2" t="n">
+      <c r="Q2" t="n">
         <v>0.006921872667601486</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0.4168940721693182</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0.4431534398654331</v>
       </c>
       <c r="R2" t="n">
         <v>111.8898526351753</v>
       </c>
       <c r="S2" t="n">
+        <v>1.78751974682336</v>
+      </c>
+      <c r="T2" t="n">
+        <v>8.315348307291666</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.1344482499064346</v>
+      </c>
+      <c r="V2" t="n">
+        <v>399.13671875</v>
+      </c>
+      <c r="W2" t="n">
+        <v>25.2705</v>
+      </c>
+      <c r="X2" t="n">
+        <v>19.16</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>34.53</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.4362735996688056</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0.4168940721693182</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.4431534398654331</v>
+      </c>
+      <c r="AC2" t="n">
         <v>112.664261808203</v>
       </c>
-      <c r="T2" t="n">
-        <v>1.78751974682336</v>
-      </c>
-      <c r="U2" t="n">
+      <c r="AD2" t="n">
         <v>107.659649652943</v>
       </c>
-      <c r="V2" t="n">
+      <c r="AE2" t="n">
         <v>114.4409269965157</v>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="AF2" t="n">
+        <v>8.256103515625</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>8.1279296875</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>8.639892578125</v>
+      </c>
+      <c r="AI2" t="inlineStr">
         <is>
           <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_128x64_64x6_tn_align8&gt;(cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_128x64_64x6_tn_align8::Params)', 'stream': 7, 'count': 48, 'total_duration_us': np.float64(399.136), 'mean_duration_us': np.float64(8.315333333333333), 'median_duration_us': np.float64(8.256), 'std_dev_duration_us': np.float64(0.13305517861231703), 'min_duration_us': np.float64(8.128), 'max_duration_us': np.float64(8.64)}]</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="AJ2" t="inlineStr">
         <is>
           <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_80_tensorop_bf16_s16816gemm_relu_b...', 'stream': 7, 'mean_duration_us': np.float64(8.32)}]</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>[[768], [788, 768], [768, 768], [], []]</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>['c10::BFloat16', 'c10::BFloat16', 'c10::BFloat16', 'Scalar', 'Scalar']</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>[[1], [768, 1], [1, 768], [], []]</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>['', '', '', '1', '1']</t>
-        </is>
-      </c>
-      <c r="AC2" t="n">
-        <v>8.315348307291666</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>8.256103515625</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>0.1344482499064346</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>8.1279296875</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>8.639892578125</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>399.13671875</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>48</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>30</v>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>{'M': 788, 'N': 768, 'K': 768, 'bias': True, 'stride_A': (768, 1), 'stride_B': (1, 768), 'dtype_A_B': ('c10::BFloat16', 'c10::BFloat16'), 'B': 1}</t>
+        </is>
+      </c>
+      <c r="AL2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>32.57437687604667</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>32.57437687604667</v>
       </c>
     </row>
     <row r="3">
@@ -2209,128 +2873,140 @@
           <t>aten::addmm</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>788</v>
-      </c>
-      <c r="C3" t="n">
-        <v>3072</v>
-      </c>
-      <c r="D3" t="n">
-        <v>768</v>
-      </c>
-      <c r="E3" t="b">
-        <v>1</v>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>GEMM</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>((3072,), (788, 768), (768, 3072), (), ())</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>('c10::BFloat16', 'c10::BFloat16', 'c10::BFloat16', 'Scalar', 'Scalar')</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>((1,), (768, 1), (1, 768), (), ())</t>
+        </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>(768, 1)</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>(1, 768)</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>('c10::BFloat16', 'c10::BFloat16')</t>
-        </is>
+          <t>('', '', '', '1', '1')</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>104</v>
+      </c>
+      <c r="H3" t="n">
+        <v>12</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>469.666</v>
       </c>
       <c r="J3" t="n">
+        <v>39.13883333333333</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1.635353997448167</v>
+      </c>
+      <c r="L3" t="n">
         <v>3.720671232</v>
       </c>
-      <c r="K3" t="n">
+      <c r="M3" t="n">
         <v>10.27734375</v>
       </c>
-      <c r="L3" t="n">
+      <c r="N3" t="n">
         <v>345.2554161915621</v>
       </c>
-      <c r="M3" t="n">
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>matrix_bf16</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
         <v>0.7763136653796865</v>
       </c>
-      <c r="N3" t="n">
-        <v>0.775993800442447</v>
-      </c>
-      <c r="O3" t="n">
+      <c r="Q3" t="n">
         <v>0.00587259665798289</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0.7601972840093</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0.783180839516687</v>
       </c>
       <c r="R3" t="n">
         <v>268.0264976358607</v>
       </c>
       <c r="S3" t="n">
+        <v>2.027545803277043</v>
+      </c>
+      <c r="T3" t="n">
+        <v>13.88246663411458</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.1063651301764554</v>
+      </c>
+      <c r="V3" t="n">
+        <v>166.589599609375</v>
+      </c>
+      <c r="W3" t="n">
+        <v>38.6155</v>
+      </c>
+      <c r="X3" t="n">
+        <v>37.56</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>43.91</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0.775993800442447</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.7601972840093</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.783180839516687</v>
+      </c>
+      <c r="AC3" t="n">
         <v>267.9160625338291</v>
       </c>
-      <c r="T3" t="n">
-        <v>2.027545803277043</v>
-      </c>
-      <c r="U3" t="n">
+      <c r="AD3" t="n">
         <v>262.462229678326</v>
       </c>
-      <c r="V3" t="n">
+      <c r="AE3" t="n">
         <v>270.3974267005908</v>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="AF3" t="n">
+        <v>13.887451171875</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>13.760009765625</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>14.176025390625</v>
+      </c>
+      <c r="AI3" t="inlineStr">
         <is>
           <t>[{'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'count': 12, 'total_duration_us': np.float64(166.59), 'mean_duration_us': np.float64(13.8825), 'median_duration_us': np.float64(13.8875), 'std_dev_duration_us': np.float64(0.10183278777813505), 'min_duration_us': np.float64(13.76), 'max_duration_us': np.float64(14.176)}]</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="AJ3" t="inlineStr">
         <is>
           <t>[{'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warp...', 'stream': 7, 'mean_duration_us': np.float64(13.88)}]</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>[[3072], [788, 768], [768, 3072], [], []]</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>['c10::BFloat16', 'c10::BFloat16', 'c10::BFloat16', 'Scalar', 'Scalar']</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>[[1], [768, 1], [1, 768], [], []]</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>['', '', '', '1', '1']</t>
-        </is>
-      </c>
-      <c r="AC3" t="n">
-        <v>13.88246663411458</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>13.887451171875</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0.1063651301764554</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>13.760009765625</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>14.176025390625</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>166.589599609375</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>12</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>104</v>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>{'M': 788, 'N': 3072, 'K': 768, 'bias': True, 'stride_A': (768, 1), 'stride_B': (1, 768), 'dtype_A_B': ('c10::BFloat16', 'c10::BFloat16'), 'B': 1}</t>
+        </is>
+      </c>
+      <c r="AL3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>13.59572333585382</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>46.1701002119005</v>
       </c>
     </row>
     <row r="4">
@@ -2339,252 +3015,1280 @@
           <t>aten::addmm</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>788</v>
-      </c>
-      <c r="C4" t="n">
-        <v>768</v>
-      </c>
-      <c r="D4" t="n">
-        <v>3072</v>
-      </c>
-      <c r="E4" t="b">
-        <v>1</v>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>GEMM</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>((768,), (788, 3072), (3072, 768), (), ())</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>('c10::BFloat16', 'c10::BFloat16', 'c10::BFloat16', 'Scalar', 'Scalar')</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>((1,), (3072, 1), (1, 3072), (), ())</t>
+        </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>(3072, 1)</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>(1, 3072)</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>('c10::BFloat16', 'c10::BFloat16')</t>
-        </is>
+          <t>('', '', '', '1', '1')</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>114</v>
+      </c>
+      <c r="H4" t="n">
+        <v>12</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>430.237</v>
       </c>
       <c r="J4" t="n">
+        <v>35.85308333333334</v>
+      </c>
+      <c r="K4" t="n">
+        <v>3.536968564857183</v>
+      </c>
+      <c r="L4" t="n">
         <v>3.71885568</v>
       </c>
-      <c r="K4" t="n">
+      <c r="M4" t="n">
         <v>10.27294921875</v>
       </c>
-      <c r="L4" t="n">
+      <c r="N4" t="n">
         <v>345.2345643804363</v>
       </c>
-      <c r="M4" t="n">
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>matrix_bf16</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
         <v>0.7959277904370671</v>
       </c>
-      <c r="N4" t="n">
-        <v>0.7986396051796765</v>
-      </c>
-      <c r="O4" t="n">
+      <c r="Q4" t="n">
         <v>0.01027516892316802</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0.7720786905349362</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0.8072521530270598</v>
       </c>
       <c r="R4" t="n">
         <v>274.781784009824</v>
       </c>
       <c r="S4" t="n">
+        <v>3.547343467125292</v>
+      </c>
+      <c r="T4" t="n">
+        <v>13.53594970703125</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.1773776572326171</v>
+      </c>
+      <c r="V4" t="n">
+        <v>162.431396484375</v>
+      </c>
+      <c r="W4" t="n">
+        <v>34.531</v>
+      </c>
+      <c r="X4" t="n">
+        <v>33.86</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>45.29</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0.7986396051796765</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.7720786905349362</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8072521530270598</v>
+      </c>
+      <c r="AC4" t="n">
         <v>275.7179961911693</v>
       </c>
-      <c r="T4" t="n">
-        <v>3.547343467125292</v>
-      </c>
-      <c r="U4" t="n">
+      <c r="AD4" t="n">
         <v>266.5482503942464</v>
       </c>
-      <c r="V4" t="n">
+      <c r="AE4" t="n">
         <v>278.6913453954663</v>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="AF4" t="n">
+        <v>13.4879150390625</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>13.343994140625</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>13.951904296875</v>
+      </c>
+      <c r="AI4" t="inlineStr">
         <is>
           <t>[{'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x64x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'count': 12, 'total_duration_us': np.float64(162.43200000000002), 'mean_duration_us': np.float64(13.536000000000001), 'median_duration_us': np.float64(13.488), 'std_dev_duration_us': np.float64(0.16983128883296716), 'min_duration_us': np.float64(13.344), 'max_duration_us': np.float64(13.952)}]</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="AJ4" t="inlineStr">
         <is>
           <t>[{'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x64x64_warpg...', 'stream': 7, 'mean_duration_us': np.float64(13.54)}]</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>[[768], [788, 3072], [3072, 768], [], []]</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>['c10::BFloat16', 'c10::BFloat16', 'c10::BFloat16', 'Scalar', 'Scalar']</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>[[1], [3072, 1], [1, 3072], [], []]</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>['', '', '', '1', '1']</t>
-        </is>
-      </c>
-      <c r="AC4" t="n">
-        <v>13.53594970703125</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>13.4879150390625</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0.1773776572326171</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>13.343994140625</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>13.951904296875</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>162.431396484375</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>12</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>114</v>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>{'M': 788, 'N': 768, 'K': 3072, 'bias': True, 'stride_A': (3072, 1), 'stride_B': (1, 3072), 'dtype_A_B': ('c10::BFloat16', 'c10::BFloat16'), 'B': 1}</t>
+        </is>
+      </c>
+      <c r="AL4" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>13.25636373961045</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>59.42646395151095</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>aten::convolution</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>CONV_fwd</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>((4, 3, 224, 224), (768, 3, 16, 16), (768,), (), (), (), (), (), ())</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>('c10::BFloat16', 'c10::BFloat16', 'c10::BFloat16', 'ScalarList', 'ScalarList', 'ScalarList', 'Scalar', 'ScalarList', 'Scalar')</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>((150528, 50176, 224, 1), (768, 256, 16, 1), (1,), (), (), (), (), (), ())</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>('', '', '', '[16, 16]', '[0, 0]', '[1, 1]', 'False', '[0, 0]', '1')</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>101.661</v>
+      </c>
+      <c r="J5" t="n">
+        <v>101.661</v>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="n">
+        <v>0.924844032</v>
+      </c>
+      <c r="M5" t="n">
+        <v>3.421875</v>
+      </c>
+      <c r="N5" t="n">
+        <v>257.7534246575343</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>matrix_bf16</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>0.02768590506403035</v>
+      </c>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="n">
+        <v>7.136136844997193</v>
+      </c>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="n">
+        <v>129.60009765625</v>
+      </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="n">
+        <v>129.60009765625</v>
+      </c>
+      <c r="W5" t="n">
+        <v>101.661</v>
+      </c>
+      <c r="X5" t="n">
+        <v>101.661</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>101.661</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0.02768590506403035</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.02768590506403035</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.02768590506403035</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>7.136136844997193</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>7.136136844997193</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>7.136136844997193</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>129.60009765625</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>129.60009765625</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>129.60009765625</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>[{'name': 'Memset (Device)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(2.272), 'mean_duration_us': np.float64(2.272), 'median_duration_us': np.float64(2.272), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(2.272), 'max_duration_us': np.float64(2.272)}, {'name': 'void cudnn::engines_precompiled::nchwToNhwcKernel&lt;__nv_bfloat16, __nv_bfloat16, float, false, true, (cudnnKernelDataType_t)0&gt;(cudnn::engines_precompiled::nchw2nhwc_params_t&lt;float&gt;, __nv_bfloat16 const*, __nv_bfloat16*)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(10.464), 'mean_duration_us': np.float64(10.464), 'median_duration_us': np.float64(10.464), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(10.464), 'max_duration_us': np.float64(10.464)}, {'name': 'Memset (Device)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(2.112), 'mean_duration_us': np.float64(2.112), 'median_duration_us': np.float64(2.112), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(2.112), 'max_duration_us': np.float64(2.112)}, {'name': 'void cudnn::engines_precompiled::nchwToNhwcKernel&lt;__nv_bfloat16, __nv_bfloat16, float, false, true, (cudnnKernelDataType_t)0&gt;(cudnn::engines_precompiled::nchw2nhwc_params_t&lt;float&gt;, __nv_bfloat16 const*, __nv_bfloat16*)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(10.4), 'mean_duration_us': np.float64(10.4), 'median_duration_us': np.float64(10.4), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(10.4), 'max_duration_us': np.float64(10.4)}, {'name': 'void cutlass__5x_cudnn::Kernel&lt;cutlass_tensorop_bf16_s16816fprop_optimized_bf16_256x64_32x4_nhwc_align8&gt;(cutlass_tensorop_bf16_s16816fprop_optimized_bf16_256x64_32x4_nhwc_align8::Params)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(98.176), 'mean_duration_us': np.float64(98.176), 'median_duration_us': np.float64(98.176), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(98.176), 'max_duration_us': np.float64(98.176)}, {'name': 'void cudnn::engines_precompiled::nhwcToNchwKernel&lt;__nv_bfloat16, __nv_bfloat16, float, true, false, (cudnnKernelDataType_t)0&gt;(cudnn::engines_precompiled::nhwc2nchw_params_t&lt;float&gt;, __nv_bfloat16 const*, __nv_bfloat16*)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(2.208), 'mean_duration_us': np.float64(2.208), 'median_duration_us': np.float64(2.208), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(2.208), 'max_duration_us': np.float64(2.208)}, {'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(3.968), 'mean_duration_us': np.float64(3.968), 'median_duration_us': np.float64(3.968), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(3.968), 'max_duration_us': np.float64(3.968)}]</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>[{'name': 'Memset (Device)', 'stream': 7, 'mean_duration_us': np.float64(2.27)}, {'name': 'void cudnn::engines_precompiled::nchwToNhwcKernel&lt;__nv_bfloat16,...', 'stream': 7, 'mean_duration_us': np.float64(10.46)}, {'name': 'Memset (Device)', 'stream': 7, 'mean_duration_us': np.float64(2.11)}, {'name': 'void cudnn::engines_precompiled::nchwToNhwcKernel&lt;__nv_bfloat16,...', 'stream': 7, 'mean_duration_us': np.float64(10.4)}, {'name': 'void cutlass__5x_cudnn::Kernel&lt;cutlass_tensorop_bf16_s16816fprop...', 'stream': 7, 'mean_duration_us': np.float64(98.18)}, {'name': 'void cudnn::engines_precompiled::nhwcToNchwKernel&lt;__nv_bfloat16,...', 'stream': 7, 'mean_duration_us': np.float64(2.21)}, {'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(3.97)}]</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>{'convNd': 'conv2d', 'input_shape': (4, 3, 224, 224), 'filter_shape': (768, 3, 16, 16), 'dtype_input_weight': ('c10::BFloat16', 'c10::BFloat16'), 'input_stride': (150528, 50176, 224, 1), 'weight_stride': (768, 256, 16, 1), 'bias': False, 'stride': (16, 16), 'padding': (0, 0), 'dilation': (1, 1), 'transposed_conv': False, 'output_padding': (0, 0), 'groups': 1}</t>
+        </is>
+      </c>
+      <c r="AL5" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>10.57693323091974</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>70.00339718243069</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>aten::_scaled_dot_product_flash_attention</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>SDPA_fwd</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>((4, 12, 197, 64), (4, 12, 197, 64), (4, 12, 197, 64), (), (), (), ())</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>('c10::BFloat16', 'c10::BFloat16', 'c10::BFloat16', 'Scalar', 'Scalar', 'Scalar', 'Scalar')</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>((151296, 64, 768, 1), (151296, 64, 768, 1), (151296, 64, 768, 1), (), (), (), ())</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>('', '', '', '0.', 'False', 'False', '0.125')</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>61</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="n">
+        <v>491.448</v>
+      </c>
+      <c r="J6" t="n">
+        <v>40.954</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2.08990247706355</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.476884992</v>
+      </c>
+      <c r="M6" t="n">
+        <v>4.6171875</v>
+      </c>
+      <c r="N6" t="n">
+        <v>98.5</v>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="n">
+        <v>0.4731315968327939</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.01022134818763448</v>
+      </c>
+      <c r="R6" t="n">
+        <v>46.60346228803019</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.006802796481996</v>
+      </c>
+      <c r="T6" t="n">
+        <v>10.23734537760417</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.228442528412397</v>
+      </c>
+      <c r="V6" t="n">
+        <v>122.84814453125</v>
+      </c>
+      <c r="W6" t="n">
+        <v>40.6005</v>
+      </c>
+      <c r="X6" t="n">
+        <v>39.25</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>47.251</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0.4735411097882475</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.4463049830531362</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.4833683350070687</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>46.64379931414237</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>43.96104083073391</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>47.61178099819627</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>10.2239990234375</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>10.01611328125</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>10.847900390625</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>[{'name': 'void pytorch_flash::flash_fwd_kernel&lt;pytorch_flash::Flash_fwd_kernel_traits&lt;64, 128, 128, 4, false, false, cutlass::bfloat16_t, pytorch_flash::Flash_kernel_traits&lt;64, 128, 128, 4, cutlass::bfloat16_t&gt; &gt;, false, false, false, false, false, true, false&gt;(pytorch_flash::Flash_fwd_params)', 'stream': 7, 'count': 12, 'total_duration_us': np.float64(122.848), 'mean_duration_us': np.float64(10.237333333333334), 'median_duration_us': np.float64(10.224), 'std_dev_duration_us': np.float64(0.21878045819699932), 'min_duration_us': np.float64(10.016), 'max_duration_us': np.float64(10.848)}]</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>[{'name': 'void pytorch_flash::flash_fwd_kernel&lt;pytorch_flash::Flash_fwd_ke...', 'stream': 7, 'mean_duration_us': np.float64(10.24)}]</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>{'B': 4, 'N_Q': 197, 'H_Q': 12, 'N_KV': 197, 'H_KV': 12, 'd_h_qk': 64, 'd_h_v': 64, 'dropout': 0.0, 'causal': False, 'flash_impl': True}</t>
+        </is>
+      </c>
+      <c r="AL6" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>10.02589230832071</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>80.0292894907514</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>aten::layer_norm</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>NORM_fwd</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>((4, 197, 768), (), (768,), (768,), (), ())</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>('c10::BFloat16', 'ScalarList', 'c10::BFloat16', 'c10::BFloat16', 'Scalar', 'Scalar')</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>((151296, 768, 1), (), (1,), (1,), (), ())</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>('', '[768]', '', '', '9.9999999999999998e-13', 'True')</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>17</v>
+      </c>
+      <c r="H7" t="n">
+        <v>25</v>
+      </c>
+      <c r="I7" t="n">
+        <v>616.799</v>
+      </c>
+      <c r="J7" t="n">
+        <v>24.67196</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2.70387186086915</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.003030528</v>
+      </c>
+      <c r="M7" t="n">
+        <v>2.3173828125</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1.247155499367889</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>vector_bf16</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>0.5466261436434106</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.0136524750083966</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.6817278011431411</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.01702675928670446</v>
+      </c>
+      <c r="T7" t="n">
+        <v>4.448037109375</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.1115342775722907</v>
+      </c>
+      <c r="V7" t="n">
+        <v>111.200927734375</v>
+      </c>
+      <c r="W7" t="n">
+        <v>23.71</v>
+      </c>
+      <c r="X7" t="n">
+        <v>22.44</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>33.221</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0.5463023981557714</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0.5237086762430939</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.5709334820168646</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.6813240401778364</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.6531461556432518</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0.7120428318705904</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>4.447998046875</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>4.256103515625</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>4.639892578125</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 7, 'count': 25, 'total_duration_us': np.float64(111.20100000000001), 'mean_duration_us': np.float64(4.448040000000001), 'median_duration_us': np.float64(4.448), 'std_dev_duration_us': np.float64(0.10934037863479323), 'min_duration_us': np.float64(4.256), 'max_duration_us': np.float64(4.64)}]</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_ke...', 'stream': 7, 'mean_duration_us': np.float64(4.45)}]</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>{'op_shape': (4, 197, 768), 'dtype_in_out': ('c10::BFloat16', None), 'stride_input': (151296, 768, 1), 'stride_output': None, 'num_channels': 768, 'has_bias': True, 'is_affine': True, 'is_training': True}</t>
+        </is>
+      </c>
+      <c r="AL7" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>9.075338746907917</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>89.10462823765931</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>aten::gelu</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>((4, 197, 3072), ())</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>('c10::BFloat16', '')</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>((605184, 3072, 1), ())</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>('', '')</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>107</v>
+      </c>
+      <c r="H8" t="n">
+        <v>12</v>
+      </c>
+      <c r="I8" t="n">
+        <v>153.193</v>
+      </c>
+      <c r="J8" t="n">
+        <v>12.76608333333333</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2.932567892985548</v>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="n">
+        <v>5.04510498046875</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.03943788318148379</v>
+      </c>
+      <c r="V8" t="n">
+        <v>60.541259765625</v>
+      </c>
+      <c r="W8" t="n">
+        <v>11.9605</v>
+      </c>
+      <c r="X8" t="n">
+        <v>11.42</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>22.04</v>
+      </c>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="n">
+        <v>5.055419921875</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>4.990966796875</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>5.1201171875</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::GeluCUDAKernelImpl(at::TensorIteratorBase&amp;, at::native::GeluType)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::GeluCUDAKernelImpl(at::TensorIteratorBase&amp;, at::native::GeluType)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 12, 'total_duration_us': np.float64(60.541999999999994), 'mean_duration_us': np.float64(5.045166666666666), 'median_duration_us': np.float64(5.0555), 'std_dev_duration_us': np.float64(0.037739972914080884), 'min_duration_us': np.float64(4.991), 'max_duration_us': np.float64(5.12)}]</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::Ge...', 'stream': 7, 'mean_duration_us': np.float64(5.05)}]</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr"/>
+      <c r="AL8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>4.940897991876649</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>94.04552622953597</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>aten::add</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>((4, 197, 768), (4, 197, 768), ())</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>('c10::BFloat16', 'c10::BFloat16', 'Scalar')</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>((151296, 768, 1), (151296, 768, 1), ())</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>('', '', '1')</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>90</v>
+      </c>
+      <c r="H9" t="n">
+        <v>24</v>
+      </c>
+      <c r="I9" t="n">
+        <v>298.853</v>
+      </c>
+      <c r="J9" t="n">
+        <v>12.45220833333333</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.4364494073142128</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.000605184</v>
+      </c>
+      <c r="M9" t="n">
+        <v>3.462890625</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>vector_bf16</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>1.628184728894159</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.02497608869878607</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.2713641214823599</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.00416268144979767</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.230662027994792</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.03450867810431143</v>
+      </c>
+      <c r="V9" t="n">
+        <v>53.535888671875</v>
+      </c>
+      <c r="W9" t="n">
+        <v>12.405</v>
+      </c>
+      <c r="X9" t="n">
+        <v>11.76</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>13.47</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1.632412270219935</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.576030728409452</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.668686411309323</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0.2720687117033225</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.262671788068242</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0.2781144018848872</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>2.2244873046875</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>2.176025390625</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>2.303955078125</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 7, 'count': 24, 'total_duration_us': np.float64(53.536), 'mean_duration_us': np.float64(2.2306666666666666), 'median_duration_us': np.float64(2.2245), 'std_dev_duration_us': np.float64(0.033798011118341686), 'min_duration_us': np.float64(2.176), 'max_duration_us': np.float64(2.304)}]</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CU...', 'stream': 7, 'mean_duration_us': np.float64(2.23)}]</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>{'shape_in1': (4, 197, 768), 'shape_in2': (4, 197, 768), 'dtype_in1_in2_out': ('c10::BFloat16', 'c10::BFloat16', None), 'stride_input1': (151296, 768, 1), 'stride_input2': (151296, 768, 1), 'stride_output': None}</t>
+        </is>
+      </c>
+      <c r="AL9" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>4.369175102338875</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>98.41470133187484</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>aten::cat</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>(((4, 1, 768), (4, 196, 768)), ())</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>('TensorList', 'Scalar')</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>(((0, 768, 1), (150528, 1, 196)), ())</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>('', '1')</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>14</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="n">
+        <v>16.66</v>
+      </c>
+      <c r="J10" t="n">
+        <v>16.66</v>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="n">
+        <v>7.263916015625</v>
+      </c>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="n">
+        <v>7.263916015625</v>
+      </c>
+      <c r="W10" t="n">
+        <v>16.66</v>
+      </c>
+      <c r="X10" t="n">
+        <v>16.66</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>16.66</v>
+      </c>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="n">
+        <v>7.263916015625</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>7.263916015625</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>7.263916015625</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>[{'name': 'void at::native::(anonymous namespace)::CatArrayBatchedCopy&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 3, 64, 64&gt;(at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;*, at::native::(anonymous namespace)::CatArrInputTensorMetadata&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 64, 64&gt;, at::native::(anonymous namespace)::TensorSizeStride&lt;unsigned int, 4u&gt;, int, unsigned int)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(7.264), 'mean_duration_us': np.float64(7.264), 'median_duration_us': np.float64(7.264), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(7.264), 'max_duration_us': np.float64(7.264)}]</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>[{'name': 'void at::native::(anonymous namespace)::CatArrayBatchedCopy&lt;at::...', 'stream': 7, 'mean_duration_us': np.float64(7.26)}]</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr"/>
+      <c r="AL10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0.5928232777729626</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>99.0075246096478</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>aten::addmm</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>4</v>
-      </c>
-      <c r="C5" t="n">
-        <v>768</v>
-      </c>
-      <c r="D5" t="n">
-        <v>768</v>
-      </c>
-      <c r="E5" t="b">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>GEMM</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>((768,), (4, 768), (768, 768), (), ())</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>('c10::BFloat16', 'c10::BFloat16', 'c10::BFloat16', 'Scalar', 'Scalar')</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>((1,), (151296, 1), (1, 768), (), ())</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>('', '', '', '1', '1')</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>1256</v>
+      </c>
+      <c r="H11" t="n">
         <v>1</v>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>(151296, 1)</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>(1, 768)</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>('c10::BFloat16', 'c10::BFloat16')</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
+      <c r="I11" t="n">
+        <v>31.331</v>
+      </c>
+      <c r="J11" t="n">
+        <v>31.331</v>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="n">
+        <v>0.004721664</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.13818359375</v>
+      </c>
+      <c r="N11" t="n">
+        <v>3.956241956241956</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>matrix_bf16</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>0.1734973492333901</v>
+      </c>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="n">
+        <v>0.6863974923339013</v>
+      </c>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="n">
+        <v>6.87890625</v>
+      </c>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="n">
+        <v>6.87890625</v>
+      </c>
+      <c r="W11" t="n">
+        <v>31.331</v>
+      </c>
+      <c r="X11" t="n">
+        <v>31.331</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>31.331</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0.1734973492333901</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0.1734973492333901</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.1734973492333901</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0.6863974923339013</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0.6863974923339013</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0.6863974923339013</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>6.87890625</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>6.87890625</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>6.87890625</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_64x64_64x6_tn_align8&gt;(cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_64x64_64x6_tn_align8::Params)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(6.879), 'mean_duration_us': np.float64(6.879), 'median_duration_us': np.float64(6.879), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(6.879), 'max_duration_us': np.float64(6.879)}]</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_80_tensorop_bf16_s16816gemm_relu_b...', 'stream': 7, 'mean_duration_us': np.float64(6.88)}]</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>{'M': 4, 'N': 768, 'K': 768, 'bias': True, 'stride_A': (151296, 1), 'stride_B': (1, 768), 'dtype_A_B': ('c10::BFloat16', 'c10::BFloat16'), 'B': 1}</t>
+        </is>
+      </c>
+      <c r="AL11" t="b">
         <v>1</v>
       </c>
-      <c r="J5" t="n">
-        <v>0.004721664</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1.13818359375</v>
-      </c>
-      <c r="L5" t="n">
-        <v>3.956241956241956</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0.1734973492333901</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0.1734973492333901</v>
-      </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="n">
-        <v>0.1734973492333901</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0.1734973492333901</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0.6863974923339013</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0.6863974923339013</v>
-      </c>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="n">
-        <v>0.6863974923339013</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0.6863974923339013</v>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_64x64_64x6_tn_align8&gt;(cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_64x64_64x6_tn_align8::Params)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(6.879), 'mean_duration_us': np.float64(6.879), 'median_duration_us': np.float64(6.879), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(6.879), 'max_duration_us': np.float64(6.879)}]</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_80_tensorop_bf16_s16816gemm_relu_b...', 'stream': 7, 'mean_duration_us': np.float64(6.88)}]</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>[[768], [4, 768], [768, 768], [], []]</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>['c10::BFloat16', 'c10::BFloat16', 'c10::BFloat16', 'Scalar', 'Scalar']</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>[[1], [151296, 1], [1, 768], [], []]</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>['', '', '', '1', '1']</t>
-        </is>
-      </c>
-      <c r="AC5" t="n">
-        <v>6.87890625</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>6.87890625</v>
-      </c>
-      <c r="AE5" t="inlineStr"/>
-      <c r="AF5" t="n">
-        <v>6.87890625</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>6.87890625</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>6.87890625</v>
-      </c>
-      <c r="AI5" t="n">
+      <c r="AM11" t="n">
+        <v>0.5614018308920443</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>99.56892644053984</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>aten::add</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>((4, 197, 768), (1, 197, 768), ())</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>('c10::BFloat16', 'c10::BFloat16', 'Scalar')</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>((151296, 768, 1), (151296, 768, 1), ())</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>('', '', '1')</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>15</v>
+      </c>
+      <c r="H12" t="n">
         <v>1</v>
       </c>
-      <c r="AJ5" t="n">
-        <v>1256</v>
+      <c r="I12" t="n">
+        <v>10.421</v>
+      </c>
+      <c r="J12" t="n">
+        <v>10.421</v>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="n">
+        <v>0.000605184</v>
+      </c>
+      <c r="M12" t="n">
+        <v>2.59716796875</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>vector_bf16</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>0.7210103734729494</v>
+      </c>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="n">
+        <v>0.1602245274384332</v>
+      </c>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="n">
+        <v>3.777099609375</v>
+      </c>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="n">
+        <v>3.777099609375</v>
+      </c>
+      <c r="W12" t="n">
+        <v>10.421</v>
+      </c>
+      <c r="X12" t="n">
+        <v>10.421</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>10.421</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0.7210103734729494</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0.7210103734729494</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.7210103734729494</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0.1602245274384332</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.1602245274384332</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0.1602245274384332</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>3.777099609375</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>3.777099609375</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>3.777099609375</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(3.777), 'mean_duration_us': np.float64(3.777), 'median_duration_us': np.float64(3.777), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(3.777), 'max_duration_us': np.float64(3.777)}]</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(3.78)}]</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>{'shape_in1': (4, 197, 768), 'shape_in2': (1, 197, 768), 'dtype_in1_in2_out': ('c10::BFloat16', 'c10::BFloat16', None), 'stride_input1': (151296, 768, 1), 'stride_input2': (151296, 768, 1), 'stride_output': None}</t>
+        </is>
+      </c>
+      <c r="AL12" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0.3082569465407019</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>99.87718338708055</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>aten::tanh</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>((4, 768),)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>('c10::BFloat16',)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>((768, 1),)</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>('',)</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>1258</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>12.47</v>
+      </c>
+      <c r="J13" t="n">
+        <v>12.47</v>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="n">
+        <v>1.5048828125</v>
+      </c>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="n">
+        <v>1.5048828125</v>
+      </c>
+      <c r="W13" t="n">
+        <v>12.47</v>
+      </c>
+      <c r="X13" t="n">
+        <v>12.47</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>12.47</v>
+      </c>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr"/>
+      <c r="AE13" t="inlineStr"/>
+      <c r="AF13" t="n">
+        <v>1.5048828125</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.5048828125</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.5048828125</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::tanh_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::tanh_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(1.505), 'mean_duration_us': np.float64(1.505), 'median_duration_us': np.float64(1.505), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(1.505), 'max_duration_us': np.float64(1.505)}]</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::ta...', 'stream': 7, 'mean_duration_us': np.float64(1.5)}]</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr"/>
+      <c r="AL13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0.1228166129194549</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -2598,7 +4302,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL2"/>
+  <dimension ref="A1:AK5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2609,185 +4313,180 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>param: M</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>param: N</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>param: K</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>param: bias</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>param: stride_A</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>param: stride_B</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>param: dtype_A_B</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>param: B</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>param: N_Q</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>param: H_Q</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>param: N_KV</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>param: H_KV</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>param: d_h_qk</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>param: d_h_v</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>param: dropout</t>
-        </is>
-      </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>param: causal</t>
+          <t>GFLOPS_first</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>param: flash_impl</t>
+          <t>Data Moved (MB)_first</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>GFLOPS_first</t>
+          <t>FLOPS/Byte_first</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Data Moved (MB)_first</t>
+          <t>TB/s_mean</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>FLOPS/Byte_first</t>
+          <t>TB/s_median</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>TB/s_mean</t>
+          <t>TB/s_std</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>TB/s_median</t>
+          <t>TB/s_min</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>TB/s_std</t>
+          <t>TB/s_max</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>TB/s_min</t>
+          <t>TFLOPS/s_mean</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>TB/s_max</t>
+          <t>TFLOPS/s_median</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>TFLOPS/s_mean</t>
+          <t>TFLOPS/s_std</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>TFLOPS/s_median</t>
+          <t>TFLOPS/s_min</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>TFLOPS/s_std</t>
+          <t>TFLOPS/s_max</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>TFLOPS/s_min</t>
+          <t>Compute Spec</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>TFLOPS/s_max</t>
+          <t>kernel_details__summarize_kernel_stats</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>kernel_details__summarize_kernel_stats</t>
+          <t>trunc_kernel_details</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>trunc_kernel_details</t>
+          <t>Input Dims_first</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>Input Dims_first</t>
+          <t>Input type_first</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>Input type_first</t>
+          <t>Input Strides_first</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>Input Strides_first</t>
+          <t>Concrete Inputs_first</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>Concrete Inputs_first</t>
+          <t>Kernel Time (µs)_mean</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>Kernel Time (µs)_mean</t>
+          <t>Kernel Time (µs)_median</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>Kernel Time (µs)_median</t>
+          <t>Kernel Time (µs)_std</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>Kernel Time (µs)_std</t>
+          <t>Kernel Time (µs)_min</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>Kernel Time (µs)_min</t>
+          <t>Kernel Time (µs)_max</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>Kernel Time (µs)_max</t>
+          <t>Kernel Time (µs)_sum</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>Kernel Time (µs)_sum</t>
+          <t>name_count</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>name_count</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>UID_first</t>
         </is>
@@ -2796,131 +4495,575 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>aten::_scaled_dot_product_flash_attention</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>4</v>
-      </c>
-      <c r="C2" t="n">
-        <v>197</v>
-      </c>
-      <c r="D2" t="n">
+          <t>aten::addmm</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>788</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>768</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>768</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>(768, 1)</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>(1, 768)</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>('c10::BFloat16', 'c10::BFloat16')</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>0.930167808</v>
+      </c>
+      <c r="K2" t="n">
+        <v>3.43505859375</v>
+      </c>
+      <c r="L2" t="n">
+        <v>258.2422174840085</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.4332748290550287</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.4362735996688056</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.006921872667601486</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.4168940721693182</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.4431534398654331</v>
+      </c>
+      <c r="R2" t="n">
+        <v>111.8898526351753</v>
+      </c>
+      <c r="S2" t="n">
+        <v>112.664261808203</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.78751974682336</v>
+      </c>
+      <c r="U2" t="n">
+        <v>107.659649652943</v>
+      </c>
+      <c r="V2" t="n">
+        <v>114.4409269965157</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>matrix_bf16</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_128x64_64x6_tn_align8&gt;(cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_128x64_64x6_tn_align8::Params)', 'stream': 7, 'count': 48, 'total_duration_us': np.float64(399.136), 'mean_duration_us': np.float64(8.315333333333333), 'median_duration_us': np.float64(8.256), 'std_dev_duration_us': np.float64(0.13305517861231703), 'min_duration_us': np.float64(8.128), 'max_duration_us': np.float64(8.64)}]</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_80_tensorop_bf16_s16816gemm_relu_b...', 'stream': 7, 'mean_duration_us': np.float64(8.32)}]</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>[[768], [788, 768], [768, 768], [], []]</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>['c10::BFloat16', 'c10::BFloat16', 'c10::BFloat16', 'Scalar', 'Scalar']</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>[[1], [768, 1], [1, 768], [], []]</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>['', '', '', '1', '1']</t>
+        </is>
+      </c>
+      <c r="AD2" t="n">
+        <v>8.315348307291666</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>8.256103515625</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0.1344482499064346</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>8.1279296875</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>8.639892578125</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>399.13671875</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>48</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>aten::addmm</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>788</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>3072</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>768</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>(768, 1)</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>(1, 768)</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>('c10::BFloat16', 'c10::BFloat16')</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>3.720671232</v>
+      </c>
+      <c r="K3" t="n">
+        <v>10.27734375</v>
+      </c>
+      <c r="L3" t="n">
+        <v>345.2554161915621</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.7763136653796865</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.775993800442447</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.00587259665798289</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.7601972840093</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.783180839516687</v>
+      </c>
+      <c r="R3" t="n">
+        <v>268.0264976358607</v>
+      </c>
+      <c r="S3" t="n">
+        <v>267.9160625338291</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.027545803277043</v>
+      </c>
+      <c r="U3" t="n">
+        <v>262.462229678326</v>
+      </c>
+      <c r="V3" t="n">
+        <v>270.3974267005908</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>matrix_bf16</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>[{'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'count': 12, 'total_duration_us': np.float64(166.59), 'mean_duration_us': np.float64(13.8825), 'median_duration_us': np.float64(13.8875), 'std_dev_duration_us': np.float64(0.10183278777813505), 'min_duration_us': np.float64(13.76), 'max_duration_us': np.float64(14.176)}]</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>[{'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warp...', 'stream': 7, 'mean_duration_us': np.float64(13.88)}]</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>[[3072], [788, 768], [768, 3072], [], []]</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>['c10::BFloat16', 'c10::BFloat16', 'c10::BFloat16', 'Scalar', 'Scalar']</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>[[1], [768, 1], [1, 768], [], []]</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>['', '', '', '1', '1']</t>
+        </is>
+      </c>
+      <c r="AD3" t="n">
+        <v>13.88246663411458</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>13.887451171875</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0.1063651301764554</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>13.760009765625</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>14.176025390625</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>166.589599609375</v>
+      </c>
+      <c r="AJ3" t="n">
         <v>12</v>
       </c>
-      <c r="E2" t="n">
-        <v>197</v>
-      </c>
-      <c r="F2" t="n">
+      <c r="AK3" t="n">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>aten::addmm</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>788</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>768</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>3072</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>(3072, 1)</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>(1, 3072)</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>('c10::BFloat16', 'c10::BFloat16')</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>3.71885568</v>
+      </c>
+      <c r="K4" t="n">
+        <v>10.27294921875</v>
+      </c>
+      <c r="L4" t="n">
+        <v>345.2345643804363</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.7959277904370671</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.7986396051796765</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.01027516892316802</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.7720786905349362</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.8072521530270598</v>
+      </c>
+      <c r="R4" t="n">
+        <v>274.781784009824</v>
+      </c>
+      <c r="S4" t="n">
+        <v>275.7179961911693</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3.547343467125292</v>
+      </c>
+      <c r="U4" t="n">
+        <v>266.5482503942464</v>
+      </c>
+      <c r="V4" t="n">
+        <v>278.6913453954663</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>matrix_bf16</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>[{'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x64x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'count': 12, 'total_duration_us': np.float64(162.43200000000002), 'mean_duration_us': np.float64(13.536000000000001), 'median_duration_us': np.float64(13.488), 'std_dev_duration_us': np.float64(0.16983128883296716), 'min_duration_us': np.float64(13.344), 'max_duration_us': np.float64(13.952)}]</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>[{'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x64x64_warpg...', 'stream': 7, 'mean_duration_us': np.float64(13.54)}]</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>[[768], [788, 3072], [3072, 768], [], []]</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>['c10::BFloat16', 'c10::BFloat16', 'c10::BFloat16', 'Scalar', 'Scalar']</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>[[1], [3072, 1], [1, 3072], [], []]</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>['', '', '', '1', '1']</t>
+        </is>
+      </c>
+      <c r="AD4" t="n">
+        <v>13.53594970703125</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>13.4879150390625</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.1773776572326171</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>13.343994140625</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>13.951904296875</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>162.431396484375</v>
+      </c>
+      <c r="AJ4" t="n">
         <v>12</v>
       </c>
-      <c r="G2" t="n">
-        <v>64</v>
-      </c>
-      <c r="H2" t="n">
-        <v>64</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="b">
-        <v>0</v>
-      </c>
-      <c r="K2" t="b">
+      <c r="AK4" t="n">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>aten::addmm</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>768</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>768</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>(151296, 1)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>(1, 768)</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>('c10::BFloat16', 'c10::BFloat16')</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>0.004721664</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1.13818359375</v>
+      </c>
+      <c r="L5" t="n">
+        <v>3.956241956241956</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.1734973492333901</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.1734973492333901</v>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="n">
+        <v>0.1734973492333901</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.1734973492333901</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.6863974923339013</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.6863974923339013</v>
+      </c>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="n">
+        <v>0.6863974923339013</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.6863974923339013</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>matrix_bf16</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_64x64_64x6_tn_align8&gt;(cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_64x64_64x6_tn_align8::Params)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(6.879), 'mean_duration_us': np.float64(6.879), 'median_duration_us': np.float64(6.879), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(6.879), 'max_duration_us': np.float64(6.879)}]</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_80_tensorop_bf16_s16816gemm_relu_b...', 'stream': 7, 'mean_duration_us': np.float64(6.88)}]</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>[[768], [4, 768], [768, 768], [], []]</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>['c10::BFloat16', 'c10::BFloat16', 'c10::BFloat16', 'Scalar', 'Scalar']</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>[[1], [151296, 1], [1, 768], [], []]</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>['', '', '', '1', '1']</t>
+        </is>
+      </c>
+      <c r="AD5" t="n">
+        <v>6.87890625</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>6.87890625</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="n">
+        <v>6.87890625</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>6.87890625</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>6.87890625</v>
+      </c>
+      <c r="AJ5" t="n">
         <v>1</v>
       </c>
-      <c r="L2" t="n">
-        <v>0.476884992</v>
-      </c>
-      <c r="M2" t="n">
-        <v>4.6171875</v>
-      </c>
-      <c r="N2" t="n">
-        <v>98.5</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0.4731315968327939</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0.4735411097882475</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0.01022134818763448</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0.4463049830531362</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0.4833683350070687</v>
-      </c>
-      <c r="T2" t="n">
-        <v>46.60346228803019</v>
-      </c>
-      <c r="U2" t="n">
-        <v>46.64379931414237</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.006802796481996</v>
-      </c>
-      <c r="W2" t="n">
-        <v>43.96104083073391</v>
-      </c>
-      <c r="X2" t="n">
-        <v>47.61178099819627</v>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>[{'name': 'void pytorch_flash::flash_fwd_kernel&lt;pytorch_flash::Flash_fwd_kernel_traits&lt;64, 128, 128, 4, false, false, cutlass::bfloat16_t, pytorch_flash::Flash_kernel_traits&lt;64, 128, 128, 4, cutlass::bfloat16_t&gt; &gt;, false, false, false, false, false, true, false&gt;(pytorch_flash::Flash_fwd_params)', 'stream': 7, 'count': 12, 'total_duration_us': np.float64(122.848), 'mean_duration_us': np.float64(10.237333333333334), 'median_duration_us': np.float64(10.224), 'std_dev_duration_us': np.float64(0.21878045819699932), 'min_duration_us': np.float64(10.016), 'max_duration_us': np.float64(10.848)}]</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>[{'name': 'void pytorch_flash::flash_fwd_kernel&lt;pytorch_flash::Flash_fwd_ke...', 'stream': 7, 'mean_duration_us': np.float64(10.24)}]</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>[[4, 12, 197, 64], [4, 12, 197, 64], [4, 12, 197, 64], [], [], [], []]</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>['c10::BFloat16', 'c10::BFloat16', 'c10::BFloat16', 'Scalar', 'Scalar', 'Scalar', 'Scalar']</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>[[151296, 64, 768, 1], [151296, 64, 768, 1], [151296, 64, 768, 1], [], [], [], []]</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>['', '', '', '0.', 'False', 'False', '0.125']</t>
-        </is>
-      </c>
-      <c r="AE2" t="n">
-        <v>10.23734537760417</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>10.2239990234375</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>0.228442528412397</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>10.01611328125</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>10.847900390625</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>122.84814453125</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>12</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>61</v>
+      <c r="AK5" t="n">
+        <v>1256</v>
       </c>
     </row>
   </sheetData>
@@ -2934,7 +5077,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO2"/>
+  <dimension ref="A1:AM2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2945,200 +5088,190 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>param: convNd</t>
+          <t>param: B</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>param: input_shape</t>
+          <t>param: N_Q</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>param: filter_shape</t>
+          <t>param: H_Q</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>param: dtype_input_weight</t>
+          <t>param: N_KV</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>param: input_stride</t>
+          <t>param: H_KV</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>param: weight_stride</t>
+          <t>param: d_h_qk</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>param: bias</t>
+          <t>param: d_h_v</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>param: stride</t>
+          <t>param: dropout</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>param: padding</t>
+          <t>param: causal</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>param: dilation</t>
+          <t>param: flash_impl</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>param: transposed_conv</t>
+          <t>GFLOPS_first</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>param: output_padding</t>
+          <t>Data Moved (MB)_first</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>param: groups</t>
+          <t>FLOPS/Byte_first</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>GFLOPS_first</t>
+          <t>TB/s_mean</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Data Moved (MB)_first</t>
+          <t>TB/s_median</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>FLOPS/Byte_first</t>
+          <t>TB/s_std</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>TB/s_mean</t>
+          <t>TB/s_min</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>TB/s_median</t>
+          <t>TB/s_max</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>TB/s_std</t>
+          <t>TFLOPS/s_mean</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>TB/s_min</t>
+          <t>TFLOPS/s_median</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>TB/s_max</t>
+          <t>TFLOPS/s_std</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>TFLOPS/s_mean</t>
+          <t>TFLOPS/s_min</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>TFLOPS/s_median</t>
+          <t>TFLOPS/s_max</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>TFLOPS/s_std</t>
+          <t>Compute Spec</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>TFLOPS/s_min</t>
+          <t>kernel_details__summarize_kernel_stats</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>TFLOPS/s_max</t>
+          <t>trunc_kernel_details</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>kernel_details__summarize_kernel_stats</t>
+          <t>Input Dims_first</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>trunc_kernel_details</t>
+          <t>Input type_first</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>Input Dims_first</t>
+          <t>Input Strides_first</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>Input type_first</t>
+          <t>Concrete Inputs_first</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>Input Strides_first</t>
+          <t>Kernel Time (µs)_mean</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>Concrete Inputs_first</t>
+          <t>Kernel Time (µs)_median</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>Kernel Time (µs)_mean</t>
+          <t>Kernel Time (µs)_std</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>Kernel Time (µs)_median</t>
+          <t>Kernel Time (µs)_min</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>Kernel Time (µs)_std</t>
+          <t>Kernel Time (µs)_max</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>Kernel Time (µs)_min</t>
+          <t>Kernel Time (µs)_sum</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>Kernel Time (µs)_max</t>
+          <t>name_count</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>Kernel Time (µs)_sum</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>name_count</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>UID_first</t>
         </is>
@@ -3147,154 +5280,152 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>aten::convolution</t>
+          <t>aten::_scaled_dot_product_flash_attention</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>conv2d</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>(4, 3, 224, 224)</t>
+          <t>197</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>(768, 3, 16, 16)</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>('c10::BFloat16', 'c10::BFloat16')</t>
+          <t>197</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>(150528, 50176, 224, 1)</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>(768, 256, 16, 1)</t>
-        </is>
-      </c>
-      <c r="H2" t="b">
-        <v>0</v>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>(16, 16)</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>(0, 0)</t>
+          <t>False</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>(1, 1)</t>
-        </is>
-      </c>
-      <c r="L2" t="b">
-        <v>0</v>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>(0, 0)</t>
-        </is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>0.476884992</v>
+      </c>
+      <c r="M2" t="n">
+        <v>4.6171875</v>
       </c>
       <c r="N2" t="n">
-        <v>1</v>
+        <v>98.5</v>
       </c>
       <c r="O2" t="n">
-        <v>0.924844032</v>
+        <v>0.4731315968327939</v>
       </c>
       <c r="P2" t="n">
-        <v>3.421875</v>
+        <v>0.4735411097882475</v>
       </c>
       <c r="Q2" t="n">
-        <v>257.7534246575343</v>
+        <v>0.01022134818763448</v>
       </c>
       <c r="R2" t="n">
-        <v>0.02768590506403035</v>
+        <v>0.4463049830531362</v>
       </c>
       <c r="S2" t="n">
-        <v>0.02768590506403035</v>
-      </c>
-      <c r="T2" t="inlineStr"/>
+        <v>0.4833683350070687</v>
+      </c>
+      <c r="T2" t="n">
+        <v>46.60346228803019</v>
+      </c>
       <c r="U2" t="n">
-        <v>0.02768590506403035</v>
+        <v>46.64379931414237</v>
       </c>
       <c r="V2" t="n">
-        <v>0.02768590506403035</v>
+        <v>1.006802796481996</v>
       </c>
       <c r="W2" t="n">
-        <v>7.136136844997193</v>
+        <v>43.96104083073391</v>
       </c>
       <c r="X2" t="n">
-        <v>7.136136844997193</v>
+        <v>47.61178099819627</v>
       </c>
       <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="n">
-        <v>7.136136844997193</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>7.136136844997193</v>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>[{'name': 'void pytorch_flash::flash_fwd_kernel&lt;pytorch_flash::Flash_fwd_kernel_traits&lt;64, 128, 128, 4, false, false, cutlass::bfloat16_t, pytorch_flash::Flash_kernel_traits&lt;64, 128, 128, 4, cutlass::bfloat16_t&gt; &gt;, false, false, false, false, false, true, false&gt;(pytorch_flash::Flash_fwd_params)', 'stream': 7, 'count': 12, 'total_duration_us': np.float64(122.848), 'mean_duration_us': np.float64(10.237333333333334), 'median_duration_us': np.float64(10.224), 'std_dev_duration_us': np.float64(0.21878045819699932), 'min_duration_us': np.float64(10.016), 'max_duration_us': np.float64(10.848)}]</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>[{'name': 'void pytorch_flash::flash_fwd_kernel&lt;pytorch_flash::Flash_fwd_ke...', 'stream': 7, 'mean_duration_us': np.float64(10.24)}]</t>
+        </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>[{'name': 'Memset (Device)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(2.272), 'mean_duration_us': np.float64(2.272), 'median_duration_us': np.float64(2.272), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(2.272), 'max_duration_us': np.float64(2.272)}, {'name': 'void cudnn::engines_precompiled::nchwToNhwcKernel&lt;__nv_bfloat16, __nv_bfloat16, float, false, true, (cudnnKernelDataType_t)0&gt;(cudnn::engines_precompiled::nchw2nhwc_params_t&lt;float&gt;, __nv_bfloat16 const*, __nv_bfloat16*)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(10.464), 'mean_duration_us': np.float64(10.464), 'median_duration_us': np.float64(10.464), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(10.464), 'max_duration_us': np.float64(10.464)}, {'name': 'Memset (Device)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(2.112), 'mean_duration_us': np.float64(2.112), 'median_duration_us': np.float64(2.112), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(2.112), 'max_duration_us': np.float64(2.112)}, {'name': 'void cudnn::engines_precompiled::nchwToNhwcKernel&lt;__nv_bfloat16, __nv_bfloat16, float, false, true, (cudnnKernelDataType_t)0&gt;(cudnn::engines_precompiled::nchw2nhwc_params_t&lt;float&gt;, __nv_bfloat16 const*, __nv_bfloat16*)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(10.4), 'mean_duration_us': np.float64(10.4), 'median_duration_us': np.float64(10.4), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(10.4), 'max_duration_us': np.float64(10.4)}, {'name': 'void cutlass__5x_cudnn::Kernel&lt;cutlass_tensorop_bf16_s16816fprop_optimized_bf16_256x64_32x4_nhwc_align8&gt;(cutlass_tensorop_bf16_s16816fprop_optimized_bf16_256x64_32x4_nhwc_align8::Params)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(98.176), 'mean_duration_us': np.float64(98.176), 'median_duration_us': np.float64(98.176), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(98.176), 'max_duration_us': np.float64(98.176)}, {'name': 'void cudnn::engines_precompiled::nhwcToNchwKernel&lt;__nv_bfloat16, __nv_bfloat16, float, true, false, (cudnnKernelDataType_t)0&gt;(cudnn::engines_precompiled::nhwc2nchw_params_t&lt;float&gt;, __nv_bfloat16 const*, __nv_bfloat16*)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(2.208), 'mean_duration_us': np.float64(2.208), 'median_duration_us': np.float64(2.208), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(2.208), 'max_duration_us': np.float64(2.208)}, {'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(3.968), 'mean_duration_us': np.float64(3.968), 'median_duration_us': np.float64(3.968), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(3.968), 'max_duration_us': np.float64(3.968)}]</t>
+          <t>[[4, 12, 197, 64], [4, 12, 197, 64], [4, 12, 197, 64], [], [], [], []]</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>[{'name': 'Memset (Device)', 'stream': 7, 'mean_duration_us': np.float64(2.27)}, {'name': 'void cudnn::engines_precompiled::nchwToNhwcKernel&lt;__nv_bfloat16,...', 'stream': 7, 'mean_duration_us': np.float64(10.46)}, {'name': 'Memset (Device)', 'stream': 7, 'mean_duration_us': np.float64(2.11)}, {'name': 'void cudnn::engines_precompiled::nchwToNhwcKernel&lt;__nv_bfloat16,...', 'stream': 7, 'mean_duration_us': np.float64(10.4)}, {'name': 'void cutlass__5x_cudnn::Kernel&lt;cutlass_tensorop_bf16_s16816fprop...', 'stream': 7, 'mean_duration_us': np.float64(98.18)}, {'name': 'void cudnn::engines_precompiled::nhwcToNchwKernel&lt;__nv_bfloat16,...', 'stream': 7, 'mean_duration_us': np.float64(2.21)}, {'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(3.97)}]</t>
+          <t>['c10::BFloat16', 'c10::BFloat16', 'c10::BFloat16', 'Scalar', 'Scalar', 'Scalar', 'Scalar']</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>[[4, 3, 224, 224], [768, 3, 16, 16], [768], [], [], [], [], [], []]</t>
+          <t>[[151296, 64, 768, 1], [151296, 64, 768, 1], [151296, 64, 768, 1], [], [], [], []]</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>['c10::BFloat16', 'c10::BFloat16', 'c10::BFloat16', 'ScalarList', 'ScalarList', 'ScalarList', 'Scalar', 'ScalarList', 'Scalar']</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>[[150528, 50176, 224, 1], [768, 256, 16, 1], [1], [], [], [], [], [], []]</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>['', '', '', '[16, 16]', '[0, 0]', '[1, 1]', 'False', '[0, 0]', '1']</t>
-        </is>
+          <t>['', '', '', '0.', 'False', 'False', '0.125']</t>
+        </is>
+      </c>
+      <c r="AF2" t="n">
+        <v>10.23734537760417</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>10.2239990234375</v>
       </c>
       <c r="AH2" t="n">
-        <v>129.60009765625</v>
+        <v>0.228442528412397</v>
       </c>
       <c r="AI2" t="n">
-        <v>129.60009765625</v>
-      </c>
-      <c r="AJ2" t="inlineStr"/>
+        <v>10.01611328125</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>10.847900390625</v>
+      </c>
       <c r="AK2" t="n">
-        <v>129.60009765625</v>
+        <v>122.84814453125</v>
       </c>
       <c r="AL2" t="n">
-        <v>129.60009765625</v>
+        <v>12</v>
       </c>
       <c r="AM2" t="n">
-        <v>129.60009765625</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>2</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -3308,7 +5439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH4"/>
+  <dimension ref="A1:AP2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3319,165 +5450,205 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>param: shape_in1</t>
+          <t>param: convNd</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>param: shape_in2</t>
+          <t>param: input_shape</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>param: dtype_in1_in2_out</t>
+          <t>param: filter_shape</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>param: stride_input1</t>
+          <t>param: dtype_input_weight</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>param: stride_input2</t>
+          <t>param: input_stride</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>param: stride_output</t>
+          <t>param: weight_stride</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>param: bias</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>param: stride</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>param: padding</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>param: dilation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>param: transposed_conv</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>param: output_padding</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>param: groups</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>GFLOPS_first</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Data Moved (MB)_first</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>FLOPS/Byte_first</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>TB/s_mean</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>TB/s_median</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>TB/s_std</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>TB/s_min</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>TB/s_max</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>TFLOPS/s_mean</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>TFLOPS/s_median</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>TFLOPS/s_std</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>TFLOPS/s_min</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>TFLOPS/s_max</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Compute Spec</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>kernel_details__summarize_kernel_stats</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>trunc_kernel_details</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Input Dims_first</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>Input type_first</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>Input Strides_first</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>Concrete Inputs_first</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_mean</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_median</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_std</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_min</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_max</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_sum</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>name_count</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>UID_first</t>
         </is>
@@ -3486,6 +5657,361 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>aten::convolution</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>conv2d</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>(4, 3, 224, 224)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>(768, 3, 16, 16)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>('c10::BFloat16', 'c10::BFloat16')</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>(150528, 50176, 224, 1)</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>(768, 256, 16, 1)</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>(16, 16)</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>(0, 0)</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>(1, 1)</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>(0, 0)</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
+        <v>0.924844032</v>
+      </c>
+      <c r="P2" t="n">
+        <v>3.421875</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>257.7534246575343</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.02768590506403035</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.02768590506403035</v>
+      </c>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="n">
+        <v>0.02768590506403035</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.02768590506403035</v>
+      </c>
+      <c r="W2" t="n">
+        <v>7.136136844997193</v>
+      </c>
+      <c r="X2" t="n">
+        <v>7.136136844997193</v>
+      </c>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="n">
+        <v>7.136136844997193</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>7.136136844997193</v>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>matrix_bf16</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>[{'name': 'Memset (Device)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(2.272), 'mean_duration_us': np.float64(2.272), 'median_duration_us': np.float64(2.272), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(2.272), 'max_duration_us': np.float64(2.272)}, {'name': 'void cudnn::engines_precompiled::nchwToNhwcKernel&lt;__nv_bfloat16, __nv_bfloat16, float, false, true, (cudnnKernelDataType_t)0&gt;(cudnn::engines_precompiled::nchw2nhwc_params_t&lt;float&gt;, __nv_bfloat16 const*, __nv_bfloat16*)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(10.464), 'mean_duration_us': np.float64(10.464), 'median_duration_us': np.float64(10.464), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(10.464), 'max_duration_us': np.float64(10.464)}, {'name': 'Memset (Device)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(2.112), 'mean_duration_us': np.float64(2.112), 'median_duration_us': np.float64(2.112), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(2.112), 'max_duration_us': np.float64(2.112)}, {'name': 'void cudnn::engines_precompiled::nchwToNhwcKernel&lt;__nv_bfloat16, __nv_bfloat16, float, false, true, (cudnnKernelDataType_t)0&gt;(cudnn::engines_precompiled::nchw2nhwc_params_t&lt;float&gt;, __nv_bfloat16 const*, __nv_bfloat16*)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(10.4), 'mean_duration_us': np.float64(10.4), 'median_duration_us': np.float64(10.4), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(10.4), 'max_duration_us': np.float64(10.4)}, {'name': 'void cutlass__5x_cudnn::Kernel&lt;cutlass_tensorop_bf16_s16816fprop_optimized_bf16_256x64_32x4_nhwc_align8&gt;(cutlass_tensorop_bf16_s16816fprop_optimized_bf16_256x64_32x4_nhwc_align8::Params)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(98.176), 'mean_duration_us': np.float64(98.176), 'median_duration_us': np.float64(98.176), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(98.176), 'max_duration_us': np.float64(98.176)}, {'name': 'void cudnn::engines_precompiled::nhwcToNchwKernel&lt;__nv_bfloat16, __nv_bfloat16, float, true, false, (cudnnKernelDataType_t)0&gt;(cudnn::engines_precompiled::nhwc2nchw_params_t&lt;float&gt;, __nv_bfloat16 const*, __nv_bfloat16*)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(2.208), 'mean_duration_us': np.float64(2.208), 'median_duration_us': np.float64(2.208), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(2.208), 'max_duration_us': np.float64(2.208)}, {'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(3.968), 'mean_duration_us': np.float64(3.968), 'median_duration_us': np.float64(3.968), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(3.968), 'max_duration_us': np.float64(3.968)}]</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>[{'name': 'Memset (Device)', 'stream': 7, 'mean_duration_us': np.float64(2.27)}, {'name': 'void cudnn::engines_precompiled::nchwToNhwcKernel&lt;__nv_bfloat16,...', 'stream': 7, 'mean_duration_us': np.float64(10.46)}, {'name': 'Memset (Device)', 'stream': 7, 'mean_duration_us': np.float64(2.11)}, {'name': 'void cudnn::engines_precompiled::nchwToNhwcKernel&lt;__nv_bfloat16,...', 'stream': 7, 'mean_duration_us': np.float64(10.4)}, {'name': 'void cutlass__5x_cudnn::Kernel&lt;cutlass_tensorop_bf16_s16816fprop...', 'stream': 7, 'mean_duration_us': np.float64(98.18)}, {'name': 'void cudnn::engines_precompiled::nhwcToNchwKernel&lt;__nv_bfloat16,...', 'stream': 7, 'mean_duration_us': np.float64(2.21)}, {'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(3.97)}]</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>[[4, 3, 224, 224], [768, 3, 16, 16], [768], [], [], [], [], [], []]</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>['c10::BFloat16', 'c10::BFloat16', 'c10::BFloat16', 'ScalarList', 'ScalarList', 'ScalarList', 'Scalar', 'ScalarList', 'Scalar']</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>[[150528, 50176, 224, 1], [768, 256, 16, 1], [1], [], [], [], [], [], []]</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>['', '', '', '[16, 16]', '[0, 0]', '[1, 1]', 'False', '[0, 0]', '1']</t>
+        </is>
+      </c>
+      <c r="AI2" t="n">
+        <v>129.60009765625</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>129.60009765625</v>
+      </c>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="n">
+        <v>129.60009765625</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>129.60009765625</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>129.60009765625</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AI4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>param: shape_in1</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>param: shape_in2</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>param: dtype_in1_in2_out</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>param: stride_input1</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>param: stride_input2</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>param: stride_output</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>GFLOPS_first</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Data Moved (MB)_first</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>FLOPS/Byte_first</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>TB/s_mean</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>TB/s_median</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>TB/s_std</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>TB/s_min</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>TB/s_max</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>TFLOPS/s_mean</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>TFLOPS/s_median</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>TFLOPS/s_std</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>TFLOPS/s_min</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>TFLOPS/s_max</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Compute Spec</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>kernel_details__summarize_kernel_stats</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>trunc_kernel_details</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Input Dims_first</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Input type_first</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Input Strides_first</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Concrete Inputs_first</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel Time (µs)_mean</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel Time (µs)_median</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel Time (µs)_std</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel Time (µs)_min</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel Time (µs)_max</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel Time (µs)_sum</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>name_count</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>UID_first</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
           <t>aten::add</t>
         </is>
       </c>
@@ -3514,7 +6040,11 @@
           <t>(151296, 768, 1)</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="H2" t="n">
         <v>0.000605184</v>
       </c>
@@ -3556,56 +6086,61 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
+          <t>vector_bf16</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 7, 'count': 24, 'total_duration_us': np.float64(53.536), 'mean_duration_us': np.float64(2.2306666666666666), 'median_duration_us': np.float64(2.2245), 'std_dev_duration_us': np.float64(0.033798011118341686), 'min_duration_us': np.float64(2.176), 'max_duration_us': np.float64(2.304)}]</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CU...', 'stream': 7, 'mean_duration_us': np.float64(2.23)}]</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>[[4, 197, 768], [4, 197, 768], []]</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>['c10::BFloat16', 'c10::BFloat16', 'Scalar']</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>[[151296, 768, 1], [151296, 768, 1], []]</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>['', '', '1']</t>
         </is>
       </c>
-      <c r="AA2" t="n">
+      <c r="AB2" t="n">
         <v>2.230662027994792</v>
       </c>
-      <c r="AB2" t="n">
+      <c r="AC2" t="n">
         <v>2.2244873046875</v>
       </c>
-      <c r="AC2" t="n">
+      <c r="AD2" t="n">
         <v>0.03450867810431143</v>
       </c>
-      <c r="AD2" t="n">
+      <c r="AE2" t="n">
         <v>2.176025390625</v>
       </c>
-      <c r="AE2" t="n">
+      <c r="AF2" t="n">
         <v>2.303955078125</v>
       </c>
-      <c r="AF2" t="n">
+      <c r="AG2" t="n">
         <v>53.535888671875</v>
       </c>
-      <c r="AG2" t="n">
+      <c r="AH2" t="n">
         <v>24</v>
       </c>
-      <c r="AH2" t="n">
+      <c r="AI2" t="n">
         <v>90</v>
       </c>
     </row>
@@ -3640,7 +6175,11 @@
           <t>(768, 1, 1, 1)</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="H3" t="n">
         <v>0.000602112</v>
       </c>
@@ -3678,44 +6217,46 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
+          <t>vector_bf16</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
           <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(3.968), 'mean_duration_us': np.float64(3.968), 'median_duration_us': np.float64(3.968), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(3.968), 'max_duration_us': np.float64(3.968)}]</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(3.97)}]</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>[[4, 768, 14, 14], [1, 768, 1, 1], []]</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>['c10::BFloat16', 'c10::BFloat16', 'Scalar']</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>[[150528, 196, 14, 1], [768, 1, 1, 1], []]</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>['', '', '1']</t>
         </is>
-      </c>
-      <c r="AA3" t="n">
-        <v>3.968017578125</v>
       </c>
       <c r="AB3" t="n">
         <v>3.968017578125</v>
       </c>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="n">
+      <c r="AC3" t="n">
         <v>3.968017578125</v>
       </c>
+      <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="n">
         <v>3.968017578125</v>
       </c>
@@ -3723,9 +6264,12 @@
         <v>3.968017578125</v>
       </c>
       <c r="AG3" t="n">
+        <v>3.968017578125</v>
+      </c>
+      <c r="AH3" t="n">
         <v>1</v>
       </c>
-      <c r="AH3" t="n">
+      <c r="AI3" t="n">
         <v>7</v>
       </c>
     </row>
@@ -3760,7 +6304,11 @@
           <t>(151296, 768, 1)</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="H4" t="n">
         <v>0.000605184</v>
       </c>
@@ -3798,44 +6346,46 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
+          <t>vector_bf16</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
           <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(3.777), 'mean_duration_us': np.float64(3.777), 'median_duration_us': np.float64(3.777), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(3.777), 'max_duration_us': np.float64(3.777)}]</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(3.78)}]</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>[[4, 197, 768], [1, 197, 768], []]</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>['c10::BFloat16', 'c10::BFloat16', 'Scalar']</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>[[151296, 768, 1], [151296, 768, 1], []]</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>['', '', '1']</t>
         </is>
-      </c>
-      <c r="AA4" t="n">
-        <v>3.777099609375</v>
       </c>
       <c r="AB4" t="n">
         <v>3.777099609375</v>
       </c>
-      <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="n">
+      <c r="AC4" t="n">
         <v>3.777099609375</v>
       </c>
+      <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="n">
         <v>3.777099609375</v>
       </c>
@@ -3843,9 +6393,12 @@
         <v>3.777099609375</v>
       </c>
       <c r="AG4" t="n">
+        <v>3.777099609375</v>
+      </c>
+      <c r="AH4" t="n">
         <v>1</v>
       </c>
-      <c r="AH4" t="n">
+      <c r="AI4" t="n">
         <v>15</v>
       </c>
     </row>

--- a/tests/traces/h100/Falconsai_nsfw_image_detection__1016002_perf_report.xlsx
+++ b/tests/traces/h100/Falconsai_nsfw_image_detection__1016002_perf_report.xlsx
@@ -1,22 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="gpu_timeline" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="ops_summary_by_category" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="ops_summary" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="ops_unique_args" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="unified_perf_summary" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="GEMM" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="SDPA_fwd" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="CONV_fwd" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="BinaryElementwise" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Normalization" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="gpu_timeline" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ops_summary_by_category" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ops_summary" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ops_unique_args" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="unified_perf_summary" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GEMM" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SDPA_fwd" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CONV_fwd" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BinaryElementwise" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Normalization" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="kernel_summary" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="short_kernel_histogram" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="short_kernels_summary" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -569,7 +572,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK3"/>
+  <dimension ref="A1:AN3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -685,75 +688,90 @@
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
+          <t>process_name_first</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>process_label_first</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>thread_name_first</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
           <t>Compute Spec</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>kernel_details__summarize_kernel_stats</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>trunc_kernel_details</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Input Dims_first</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Input type_first</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Input Strides_first</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>Concrete Inputs_first</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_mean</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_median</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_std</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_min</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_max</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_sum</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>name_count</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>UID_first</t>
         </is>
@@ -846,61 +864,76 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>thread 5617 (python3)</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>vector_bf16</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 7, 'count': 25, 'total_duration_us': np.float64(111.20100000000001), 'mean_duration_us': np.float64(4.448040000000001), 'median_duration_us': np.float64(4.448), 'std_dev_duration_us': np.float64(0.10934037863479323), 'min_duration_us': np.float64(4.256), 'max_duration_us': np.float64(4.64)}]</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_ke...', 'stream': 7, 'mean_duration_us': np.float64(4.45)}]</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>[[4, 197, 768], [], [768], [768], [], []]</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>['c10::BFloat16', 'ScalarList', 'c10::BFloat16', 'c10::BFloat16', 'Scalar', 'Scalar']</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>[[151296, 768, 1], [], [1], [1], [], []]</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>['', '[768]', '', '', '9.9999999999999998e-13', 'True']</t>
         </is>
       </c>
-      <c r="AD2" t="n">
+      <c r="AG2" t="n">
         <v>4.448037109375</v>
       </c>
-      <c r="AE2" t="n">
+      <c r="AH2" t="n">
         <v>4.447998046875</v>
       </c>
-      <c r="AF2" t="n">
+      <c r="AI2" t="n">
         <v>0.1115342775722907</v>
       </c>
-      <c r="AG2" t="n">
+      <c r="AJ2" t="n">
         <v>4.256103515625</v>
       </c>
-      <c r="AH2" t="n">
+      <c r="AK2" t="n">
         <v>4.639892578125</v>
       </c>
-      <c r="AI2" t="n">
+      <c r="AL2" t="n">
         <v>111.200927734375</v>
       </c>
-      <c r="AJ2" t="n">
+      <c r="AM2" t="n">
         <v>25</v>
       </c>
-      <c r="AK2" t="n">
+      <c r="AN2" t="n">
         <v>17</v>
       </c>
     </row>
@@ -991,62 +1024,2345 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>thread 5617 (python3)</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>vector_bf16</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 7, 'count': 25, 'total_duration_us': np.float64(111.20100000000001), 'mean_duration_us': np.float64(4.448040000000001), 'median_duration_us': np.float64(4.448), 'std_dev_duration_us': np.float64(0.10934037863479323), 'min_duration_us': np.float64(4.256), 'max_duration_us': np.float64(4.64)}]</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_ke...', 'stream': 7, 'mean_duration_us': np.float64(4.45)}]</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>[[4, 197, 768], [], [768], [768], []]</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>['c10::BFloat16', 'ScalarList', 'c10::BFloat16', 'c10::BFloat16', 'Scalar']</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>[[151296, 768, 1], [], [1], [1], []]</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
         <is>
           <t>['', '[768]', '', '', '9.9999999999999998e-13']</t>
         </is>
       </c>
-      <c r="AD3" t="n">
+      <c r="AG3" t="n">
         <v>4.448037109375</v>
       </c>
-      <c r="AE3" t="n">
+      <c r="AH3" t="n">
         <v>4.447998046875</v>
       </c>
-      <c r="AF3" t="n">
+      <c r="AI3" t="n">
         <v>0.1115342775722907</v>
       </c>
-      <c r="AG3" t="n">
+      <c r="AJ3" t="n">
         <v>4.256103515625</v>
       </c>
-      <c r="AH3" t="n">
+      <c r="AK3" t="n">
         <v>4.639892578125</v>
       </c>
-      <c r="AI3" t="n">
+      <c r="AL3" t="n">
         <v>111.200927734375</v>
       </c>
-      <c r="AJ3" t="n">
+      <c r="AM3" t="n">
         <v>25</v>
       </c>
-      <c r="AK3" t="n">
+      <c r="AN3" t="n">
         <v>18</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Parent op category</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Parent cpu_op</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel name</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel stream</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel duration (µs)_sum</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel duration (µs)_count</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel duration (µs)_mean</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel duration (µs)_min</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel duration (µs)_max</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Percent of kernels time (%)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Percent of total time (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>GEMM</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>aten::addmm</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>void cutlass::Kernel2&lt;cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_128x64_64x6_tn_align8&gt;(cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_128x64_64x6_tn_align8::Params)</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E2" t="n">
+        <v>399.136</v>
+      </c>
+      <c r="F2" t="n">
+        <v>48</v>
+      </c>
+      <c r="G2" t="n">
+        <v>8.315333333333333</v>
+      </c>
+      <c r="H2" t="n">
+        <v>8.128</v>
+      </c>
+      <c r="I2" t="n">
+        <v>8.640000000000001</v>
+      </c>
+      <c r="J2" t="n">
+        <v>32.69125237729396</v>
+      </c>
+      <c r="K2" t="n">
+        <v>5.279685669563507</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>GEMM</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>aten::addmm</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>7</v>
+      </c>
+      <c r="E3" t="n">
+        <v>166.59</v>
+      </c>
+      <c r="F3" t="n">
+        <v>12</v>
+      </c>
+      <c r="G3" t="n">
+        <v>13.8825</v>
+      </c>
+      <c r="H3" t="n">
+        <v>13.76</v>
+      </c>
+      <c r="I3" t="n">
+        <v>14.176</v>
+      </c>
+      <c r="J3" t="n">
+        <v>13.64456158686112</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2.203616901739218</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>GEMM</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>aten::addmm</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x64x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>7</v>
+      </c>
+      <c r="E4" t="n">
+        <v>162.432</v>
+      </c>
+      <c r="F4" t="n">
+        <v>12</v>
+      </c>
+      <c r="G4" t="n">
+        <v>13.536</v>
+      </c>
+      <c r="H4" t="n">
+        <v>13.344</v>
+      </c>
+      <c r="I4" t="n">
+        <v>13.952</v>
+      </c>
+      <c r="J4" t="n">
+        <v>13.30400040624903</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2.148615766752534</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>aten::_flash_attention_forward</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>void pytorch_flash::flash_fwd_kernel&lt;pytorch_flash::Flash_fwd_kernel_traits&lt;64, 128, 128, 4, false, false, cutlass::bfloat16_t, pytorch_flash::Flash_kernel_traits&lt;64, 128, 128, 4, cutlass::bfloat16_t&gt; &gt;, false, false, false, false, false, true, false&gt;(pytorch_flash::Flash_fwd_params)</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E5" t="n">
+        <v>122.848</v>
+      </c>
+      <c r="F5" t="n">
+        <v>12</v>
+      </c>
+      <c r="G5" t="n">
+        <v>10.23733333333333</v>
+      </c>
+      <c r="H5" t="n">
+        <v>10.016</v>
+      </c>
+      <c r="I5" t="n">
+        <v>10.848</v>
+      </c>
+      <c r="J5" t="n">
+        <v>10.06187107162924</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1.625007078125094</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>NORM_fwd</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>aten::native_layer_norm</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>7</v>
+      </c>
+      <c r="E6" t="n">
+        <v>111.201</v>
+      </c>
+      <c r="F6" t="n">
+        <v>25</v>
+      </c>
+      <c r="G6" t="n">
+        <v>4.448040000000001</v>
+      </c>
+      <c r="H6" t="n">
+        <v>4.256</v>
+      </c>
+      <c r="I6" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="J6" t="n">
+        <v>9.107923002704506</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1.470943052345896</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CONV_fwd</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>aten::cudnn_convolution</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>void cutlass__5x_cudnn::Kernel&lt;cutlass_tensorop_bf16_s16816fprop_optimized_bf16_256x64_32x4_nhwc_align8&gt;(cutlass_tensorop_bf16_s16816fprop_optimized_bf16_256x64_32x4_nhwc_align8::Params)</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>7</v>
+      </c>
+      <c r="E7" t="n">
+        <v>98.176</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>98.176</v>
+      </c>
+      <c r="H7" t="n">
+        <v>98.176</v>
+      </c>
+      <c r="I7" t="n">
+        <v>98.176</v>
+      </c>
+      <c r="J7" t="n">
+        <v>8.041109780609144</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1.298651137194006</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>aten::gelu</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::GeluCUDAKernelImpl(at::TensorIteratorBase&amp;, at::native::GeluType)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::GeluCUDAKernelImpl(at::TensorIteratorBase&amp;, at::native::GeluType)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>7</v>
+      </c>
+      <c r="E8" t="n">
+        <v>60.542</v>
+      </c>
+      <c r="F8" t="n">
+        <v>12</v>
+      </c>
+      <c r="G8" t="n">
+        <v>5.045166666666667</v>
+      </c>
+      <c r="H8" t="n">
+        <v>4.991</v>
+      </c>
+      <c r="I8" t="n">
+        <v>5.12</v>
+      </c>
+      <c r="J8" t="n">
+        <v>4.958695285381752</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.8008366316411294</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>aten::add</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>7</v>
+      </c>
+      <c r="E9" t="n">
+        <v>53.536</v>
+      </c>
+      <c r="F9" t="n">
+        <v>24</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2.230666666666667</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.176</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.304</v>
+      </c>
+      <c r="J9" t="n">
+        <v>4.384868534210919</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.7081627615793913</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>CONV_fwd</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>aten::cudnn_convolution</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>void cudnn::engines_precompiled::nchwToNhwcKernel&lt;__nv_bfloat16, __nv_bfloat16, float, false, true, (cudnnKernelDataType_t)0&gt;(cudnn::engines_precompiled::nchw2nhwc_params_t&lt;float&gt;, __nv_bfloat16 const*, __nv_bfloat16*)</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>7</v>
+      </c>
+      <c r="E10" t="n">
+        <v>20.864</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2</v>
+      </c>
+      <c r="G10" t="n">
+        <v>10.432</v>
+      </c>
+      <c r="H10" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="I10" t="n">
+        <v>10.464</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.708866876452791</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.2759845311116337</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>aten::cat</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>void at::native::(anonymous namespace)::CatArrayBatchedCopy&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 3, 64, 64&gt;(at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;*, at::native::(anonymous namespace)::CatArrInputTensorMetadata&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 64, 64&gt;, at::native::(anonymous namespace)::TensorSizeStride&lt;unsigned int, 4u&gt;, int, unsigned int)</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>7</v>
+      </c>
+      <c r="E11" t="n">
+        <v>7.264</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>7.264</v>
+      </c>
+      <c r="H11" t="n">
+        <v>7.264</v>
+      </c>
+      <c r="I11" t="n">
+        <v>7.264</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.5949582529981343</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.09608663889929576</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>GEMM</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>aten::addmm</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>void cutlass::Kernel2&lt;cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_64x64_64x6_tn_align8&gt;(cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_64x64_64x6_tn_align8::Params)</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>7</v>
+      </c>
+      <c r="E12" t="n">
+        <v>6.879</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>6.879</v>
+      </c>
+      <c r="H12" t="n">
+        <v>6.879</v>
+      </c>
+      <c r="I12" t="n">
+        <v>6.879</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.5634248103488664</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.09099394121534354</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>aten::add_</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1})</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>7</v>
+      </c>
+      <c r="E13" t="n">
+        <v>3.968</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>3.968</v>
+      </c>
+      <c r="H13" t="n">
+        <v>3.968</v>
+      </c>
+      <c r="I13" t="n">
+        <v>3.968</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.3249992219020645</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.05248785561018799</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>aten::add</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1})</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>7</v>
+      </c>
+      <c r="E14" t="n">
+        <v>3.777</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>3.777</v>
+      </c>
+      <c r="H14" t="n">
+        <v>3.777</v>
+      </c>
+      <c r="I14" t="n">
+        <v>3.777</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.309355358146194</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.04996134844750001</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>CONV_fwd</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>aten::cudnn_convolution</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>void cudnn::engines_precompiled::nhwcToNchwKernel&lt;__nv_bfloat16, __nv_bfloat16, float, true, false, (cudnnKernelDataType_t)0&gt;(cudnn::engines_precompiled::nhwc2nchw_params_t&lt;float&gt;, __nv_bfloat16 const*, __nv_bfloat16*)</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>7</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2.208</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2.208</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2.208</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.208</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.1808463412196972</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.02920695191212074</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>aten::tanh</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::tanh_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::tanh_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>7</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1.505</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.505</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.505</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.505</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.1232670939925925</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.01990781821908592</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C101"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>bin_start</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>bin_end</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.505</v>
+      </c>
+      <c r="B2" t="n">
+        <v>1.57635</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1.57635</v>
+      </c>
+      <c r="B3" t="n">
+        <v>1.6477</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1.6477</v>
+      </c>
+      <c r="B4" t="n">
+        <v>1.71905</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1.71905</v>
+      </c>
+      <c r="B5" t="n">
+        <v>1.7904</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1.7904</v>
+      </c>
+      <c r="B6" t="n">
+        <v>1.86175</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1.86175</v>
+      </c>
+      <c r="B7" t="n">
+        <v>1.9331</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1.9331</v>
+      </c>
+      <c r="B8" t="n">
+        <v>2.00445</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>2.00445</v>
+      </c>
+      <c r="B9" t="n">
+        <v>2.0758</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>2.0758</v>
+      </c>
+      <c r="B10" t="n">
+        <v>2.14715</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>2.14715</v>
+      </c>
+      <c r="B11" t="n">
+        <v>2.2185</v>
+      </c>
+      <c r="C11" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>2.2185</v>
+      </c>
+      <c r="B12" t="n">
+        <v>2.28985</v>
+      </c>
+      <c r="C12" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>2.28985</v>
+      </c>
+      <c r="B13" t="n">
+        <v>2.3612</v>
+      </c>
+      <c r="C13" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>2.3612</v>
+      </c>
+      <c r="B14" t="n">
+        <v>2.43255</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>2.43255</v>
+      </c>
+      <c r="B15" t="n">
+        <v>2.5039</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>2.5039</v>
+      </c>
+      <c r="B16" t="n">
+        <v>2.57525</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>2.57525</v>
+      </c>
+      <c r="B17" t="n">
+        <v>2.6466</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>2.6466</v>
+      </c>
+      <c r="B18" t="n">
+        <v>2.71795</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>2.71795</v>
+      </c>
+      <c r="B19" t="n">
+        <v>2.7893</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>2.7893</v>
+      </c>
+      <c r="B20" t="n">
+        <v>2.86065</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>2.86065</v>
+      </c>
+      <c r="B21" t="n">
+        <v>2.932</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>2.932</v>
+      </c>
+      <c r="B22" t="n">
+        <v>3.00335</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>3.00335</v>
+      </c>
+      <c r="B23" t="n">
+        <v>3.0747</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>3.0747</v>
+      </c>
+      <c r="B24" t="n">
+        <v>3.14605</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>3.14605</v>
+      </c>
+      <c r="B25" t="n">
+        <v>3.2174</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>3.2174</v>
+      </c>
+      <c r="B26" t="n">
+        <v>3.28875</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>3.28875</v>
+      </c>
+      <c r="B27" t="n">
+        <v>3.3601</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>3.3601</v>
+      </c>
+      <c r="B28" t="n">
+        <v>3.43145</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>3.43145</v>
+      </c>
+      <c r="B29" t="n">
+        <v>3.5028</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>3.5028</v>
+      </c>
+      <c r="B30" t="n">
+        <v>3.57415</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>3.57415</v>
+      </c>
+      <c r="B31" t="n">
+        <v>3.6455</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>3.6455</v>
+      </c>
+      <c r="B32" t="n">
+        <v>3.71685</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>3.71685</v>
+      </c>
+      <c r="B33" t="n">
+        <v>3.7882</v>
+      </c>
+      <c r="C33" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>3.7882</v>
+      </c>
+      <c r="B34" t="n">
+        <v>3.85955</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>3.85955</v>
+      </c>
+      <c r="B35" t="n">
+        <v>3.9309</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>3.9309</v>
+      </c>
+      <c r="B36" t="n">
+        <v>4.00225</v>
+      </c>
+      <c r="C36" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>4.00225</v>
+      </c>
+      <c r="B37" t="n">
+        <v>4.073600000000001</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>4.073600000000001</v>
+      </c>
+      <c r="B38" t="n">
+        <v>4.14495</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>4.14495</v>
+      </c>
+      <c r="B39" t="n">
+        <v>4.2163</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>4.2163</v>
+      </c>
+      <c r="B40" t="n">
+        <v>4.28765</v>
+      </c>
+      <c r="C40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>4.28765</v>
+      </c>
+      <c r="B41" t="n">
+        <v>4.359</v>
+      </c>
+      <c r="C41" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>4.359</v>
+      </c>
+      <c r="B42" t="n">
+        <v>4.430350000000001</v>
+      </c>
+      <c r="C42" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>4.430350000000001</v>
+      </c>
+      <c r="B43" t="n">
+        <v>4.5017</v>
+      </c>
+      <c r="C43" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>4.5017</v>
+      </c>
+      <c r="B44" t="n">
+        <v>4.57305</v>
+      </c>
+      <c r="C44" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>4.57305</v>
+      </c>
+      <c r="B45" t="n">
+        <v>4.644400000000001</v>
+      </c>
+      <c r="C45" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>4.644400000000001</v>
+      </c>
+      <c r="B46" t="n">
+        <v>4.71575</v>
+      </c>
+      <c r="C46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>4.71575</v>
+      </c>
+      <c r="B47" t="n">
+        <v>4.787100000000001</v>
+      </c>
+      <c r="C47" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>4.787100000000001</v>
+      </c>
+      <c r="B48" t="n">
+        <v>4.85845</v>
+      </c>
+      <c r="C48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>4.85845</v>
+      </c>
+      <c r="B49" t="n">
+        <v>4.9298</v>
+      </c>
+      <c r="C49" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>4.9298</v>
+      </c>
+      <c r="B50" t="n">
+        <v>5.001150000000001</v>
+      </c>
+      <c r="C50" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>5.001150000000001</v>
+      </c>
+      <c r="B51" t="n">
+        <v>5.0725</v>
+      </c>
+      <c r="C51" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>5.0725</v>
+      </c>
+      <c r="B52" t="n">
+        <v>5.14385</v>
+      </c>
+      <c r="C52" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>5.14385</v>
+      </c>
+      <c r="B53" t="n">
+        <v>5.2152</v>
+      </c>
+      <c r="C53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>5.2152</v>
+      </c>
+      <c r="B54" t="n">
+        <v>5.28655</v>
+      </c>
+      <c r="C54" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>5.28655</v>
+      </c>
+      <c r="B55" t="n">
+        <v>5.357900000000001</v>
+      </c>
+      <c r="C55" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>5.357900000000001</v>
+      </c>
+      <c r="B56" t="n">
+        <v>5.429250000000001</v>
+      </c>
+      <c r="C56" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>5.429250000000001</v>
+      </c>
+      <c r="B57" t="n">
+        <v>5.5006</v>
+      </c>
+      <c r="C57" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>5.5006</v>
+      </c>
+      <c r="B58" t="n">
+        <v>5.57195</v>
+      </c>
+      <c r="C58" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>5.57195</v>
+      </c>
+      <c r="B59" t="n">
+        <v>5.643300000000001</v>
+      </c>
+      <c r="C59" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>5.643300000000001</v>
+      </c>
+      <c r="B60" t="n">
+        <v>5.714650000000001</v>
+      </c>
+      <c r="C60" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>5.714650000000001</v>
+      </c>
+      <c r="B61" t="n">
+        <v>5.786</v>
+      </c>
+      <c r="C61" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>5.786</v>
+      </c>
+      <c r="B62" t="n">
+        <v>5.85735</v>
+      </c>
+      <c r="C62" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>5.85735</v>
+      </c>
+      <c r="B63" t="n">
+        <v>5.928700000000001</v>
+      </c>
+      <c r="C63" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>5.928700000000001</v>
+      </c>
+      <c r="B64" t="n">
+        <v>6.000050000000001</v>
+      </c>
+      <c r="C64" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>6.000050000000001</v>
+      </c>
+      <c r="B65" t="n">
+        <v>6.071400000000001</v>
+      </c>
+      <c r="C65" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>6.071400000000001</v>
+      </c>
+      <c r="B66" t="n">
+        <v>6.14275</v>
+      </c>
+      <c r="C66" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>6.14275</v>
+      </c>
+      <c r="B67" t="n">
+        <v>6.2141</v>
+      </c>
+      <c r="C67" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>6.2141</v>
+      </c>
+      <c r="B68" t="n">
+        <v>6.285450000000001</v>
+      </c>
+      <c r="C68" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>6.285450000000001</v>
+      </c>
+      <c r="B69" t="n">
+        <v>6.356800000000001</v>
+      </c>
+      <c r="C69" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>6.356800000000001</v>
+      </c>
+      <c r="B70" t="n">
+        <v>6.42815</v>
+      </c>
+      <c r="C70" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>6.42815</v>
+      </c>
+      <c r="B71" t="n">
+        <v>6.4995</v>
+      </c>
+      <c r="C71" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>6.4995</v>
+      </c>
+      <c r="B72" t="n">
+        <v>6.570850000000001</v>
+      </c>
+      <c r="C72" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>6.570850000000001</v>
+      </c>
+      <c r="B73" t="n">
+        <v>6.642200000000001</v>
+      </c>
+      <c r="C73" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>6.642200000000001</v>
+      </c>
+      <c r="B74" t="n">
+        <v>6.713550000000001</v>
+      </c>
+      <c r="C74" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>6.713550000000001</v>
+      </c>
+      <c r="B75" t="n">
+        <v>6.7849</v>
+      </c>
+      <c r="C75" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>6.7849</v>
+      </c>
+      <c r="B76" t="n">
+        <v>6.856250000000001</v>
+      </c>
+      <c r="C76" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>6.856250000000001</v>
+      </c>
+      <c r="B77" t="n">
+        <v>6.927600000000001</v>
+      </c>
+      <c r="C77" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>6.927600000000001</v>
+      </c>
+      <c r="B78" t="n">
+        <v>6.998950000000001</v>
+      </c>
+      <c r="C78" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>6.998950000000001</v>
+      </c>
+      <c r="B79" t="n">
+        <v>7.0703</v>
+      </c>
+      <c r="C79" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>7.0703</v>
+      </c>
+      <c r="B80" t="n">
+        <v>7.141650000000001</v>
+      </c>
+      <c r="C80" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>7.141650000000001</v>
+      </c>
+      <c r="B81" t="n">
+        <v>7.213000000000001</v>
+      </c>
+      <c r="C81" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>7.213000000000001</v>
+      </c>
+      <c r="B82" t="n">
+        <v>7.284350000000001</v>
+      </c>
+      <c r="C82" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>7.284350000000001</v>
+      </c>
+      <c r="B83" t="n">
+        <v>7.355700000000001</v>
+      </c>
+      <c r="C83" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>7.355700000000001</v>
+      </c>
+      <c r="B84" t="n">
+        <v>7.42705</v>
+      </c>
+      <c r="C84" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>7.42705</v>
+      </c>
+      <c r="B85" t="n">
+        <v>7.498400000000001</v>
+      </c>
+      <c r="C85" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>7.498400000000001</v>
+      </c>
+      <c r="B86" t="n">
+        <v>7.569750000000001</v>
+      </c>
+      <c r="C86" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>7.569750000000001</v>
+      </c>
+      <c r="B87" t="n">
+        <v>7.641100000000001</v>
+      </c>
+      <c r="C87" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>7.641100000000001</v>
+      </c>
+      <c r="B88" t="n">
+        <v>7.71245</v>
+      </c>
+      <c r="C88" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>7.71245</v>
+      </c>
+      <c r="B89" t="n">
+        <v>7.783800000000001</v>
+      </c>
+      <c r="C89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>7.783800000000001</v>
+      </c>
+      <c r="B90" t="n">
+        <v>7.855150000000001</v>
+      </c>
+      <c r="C90" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>7.855150000000001</v>
+      </c>
+      <c r="B91" t="n">
+        <v>7.926500000000001</v>
+      </c>
+      <c r="C91" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>7.926500000000001</v>
+      </c>
+      <c r="B92" t="n">
+        <v>7.997850000000001</v>
+      </c>
+      <c r="C92" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>7.997850000000001</v>
+      </c>
+      <c r="B93" t="n">
+        <v>8.069200000000002</v>
+      </c>
+      <c r="C93" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>8.069200000000002</v>
+      </c>
+      <c r="B94" t="n">
+        <v>8.140550000000001</v>
+      </c>
+      <c r="C94" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>8.140550000000001</v>
+      </c>
+      <c r="B95" t="n">
+        <v>8.2119</v>
+      </c>
+      <c r="C95" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>8.2119</v>
+      </c>
+      <c r="B96" t="n">
+        <v>8.283250000000001</v>
+      </c>
+      <c r="C96" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>8.283250000000001</v>
+      </c>
+      <c r="B97" t="n">
+        <v>8.354600000000001</v>
+      </c>
+      <c r="C97" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>8.354600000000001</v>
+      </c>
+      <c r="B98" t="n">
+        <v>8.42595</v>
+      </c>
+      <c r="C98" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>8.42595</v>
+      </c>
+      <c r="B99" t="n">
+        <v>8.497300000000001</v>
+      </c>
+      <c r="C99" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>8.497300000000001</v>
+      </c>
+      <c r="B100" t="n">
+        <v>8.568650000000002</v>
+      </c>
+      <c r="C100" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>8.568650000000002</v>
+      </c>
+      <c r="B101" t="n">
+        <v>8.640000000000001</v>
+      </c>
+      <c r="C101" t="n">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Parent cpu_op</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Input dims</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Input strides</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Concrete Inputs</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel name</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Short Kernel duration (µs) sum</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Short Kernel count</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Short Kernel duration (µs) mean</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Short Kernel duration (µs) percent of total time</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>aten::addmm</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>((768,), (788, 768), (768, 768), (), ())</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>((1,), (768, 1), (1, 768), (), ())</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>('', '', '', '1', '1')</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>void cutlass::Kernel2&lt;cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_128x64_64x6_tn_align8&gt;(cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_128x64_64x6_tn_align8::Params)</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>399.136</v>
+      </c>
+      <c r="G2" t="n">
+        <v>48</v>
+      </c>
+      <c r="H2" t="n">
+        <v>8.315333333333333</v>
+      </c>
+      <c r="I2" t="n">
+        <v>5.279685669563507</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>aten::native_layer_norm</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>((4, 197, 768), (), (768,), (768,), ())</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>((151296, 768, 1), (), (1,), (1,), ())</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>('', '[768]', '', '', '9.9999999999999998e-13')</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>111.201</v>
+      </c>
+      <c r="G3" t="n">
+        <v>25</v>
+      </c>
+      <c r="H3" t="n">
+        <v>4.448040000000001</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.470943052345896</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>aten::gelu</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>((4, 197, 3072), ())</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>((605184, 3072, 1), ())</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>('', '')</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::GeluCUDAKernelImpl(at::TensorIteratorBase&amp;, at::native::GeluType)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::GeluCUDAKernelImpl(at::TensorIteratorBase&amp;, at::native::GeluType)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>60.542</v>
+      </c>
+      <c r="G4" t="n">
+        <v>12</v>
+      </c>
+      <c r="H4" t="n">
+        <v>5.045166666666667</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.8008366316411294</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>aten::add</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>((4, 197, 768), (4, 197, 768), ())</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>((151296, 768, 1), (151296, 768, 1), ())</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>('', '', '1')</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>53.536</v>
+      </c>
+      <c r="G5" t="n">
+        <v>24</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.230666666666667</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.7081627615793913</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>aten::cat</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>(((4, 1, 768), (4, 196, 768)), ())</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>(((0, 768, 1), (150528, 1, 196)), ())</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>('', '1')</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>void at::native::(anonymous namespace)::CatArrayBatchedCopy&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 3, 64, 64&gt;(at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;*, at::native::(anonymous namespace)::CatArrInputTensorMetadata&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 64, 64&gt;, at::native::(anonymous namespace)::TensorSizeStride&lt;unsigned int, 4u&gt;, int, unsigned int)</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>7.264</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>7.264</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.09608663889929576</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>aten::addmm</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>((768,), (4, 768), (768, 768), (), ())</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>((1,), (151296, 1), (1, 768), (), ())</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>('', '', '', '1', '1')</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>void cutlass::Kernel2&lt;cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_64x64_64x6_tn_align8&gt;(cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_64x64_64x6_tn_align8::Params)</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>6.879</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>6.879</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.09099394121534354</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>aten::add_</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>((4, 768, 14, 14), (1, 768, 1, 1), ())</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>((150528, 196, 14, 1), (768, 1, 1, 1), ())</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>('', '', '1')</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1})</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>3.968</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>3.968</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.05248785561018799</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>aten::add</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>((4, 197, 768), (1, 197, 768), ())</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>((151296, 768, 1), (151296, 768, 1), ())</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>('', '', '1')</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1})</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>3.777</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3.777</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.04996134844750001</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>aten::cudnn_convolution</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>((4, 3, 224, 224), (768, 3, 16, 16), (), (), (), (), (), (), ())</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>((150528, 50176, 224, 1), (768, 256, 16, 1), (), (), (), (), (), (), ())</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>('', '', '[0, 0]', '[16, 16]', '[1, 1]', '1', 'False', 'False', 'True')</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>void cudnn::engines_precompiled::nhwcToNchwKernel&lt;__nv_bfloat16, __nv_bfloat16, float, true, false, (cudnnKernelDataType_t)0&gt;(cudnn::engines_precompiled::nhwc2nchw_params_t&lt;float&gt;, __nv_bfloat16 const*, __nv_bfloat16*)</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>2.208</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.208</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.02920695191212074</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>aten::tanh</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>((4, 768),)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>((768, 1),)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>('',)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::tanh_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::tanh_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>1.505</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.505</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.01990781821908592</v>
       </c>
     </row>
   </sheetData>
@@ -1196,7 +3512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1212,25 +3528,35 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>total_subtree_kernel_time_sum</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>total_direct_kernel_time_ms</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>total_subtree_kernel_time_ms</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Count</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Categories</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>total_direct_kernel_time_ms</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Percentage (%)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Cumulative Percentage (%)</t>
         </is>
@@ -1246,20 +3572,26 @@
         <v>735.03662109375</v>
       </c>
       <c r="C2" t="n">
-        <v>73</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>{'GEMM'}</t>
-        </is>
+        <v>735.03662109375</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.73503662109375</v>
       </c>
       <c r="E2" t="n">
         <v>0.73503662109375</v>
       </c>
       <c r="F2" t="n">
+        <v>73</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>{'GEMM'}</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
         <v>59.98786578240299</v>
       </c>
-      <c r="G2" t="n">
+      <c r="I2" t="n">
         <v>59.98786578240299</v>
       </c>
     </row>
@@ -1273,20 +3605,26 @@
         <v>125.632080078125</v>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>{'CONV_fwd'}</t>
-        </is>
+        <v>125.632080078125</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.125632080078125</v>
       </c>
       <c r="E3" t="n">
         <v>0.125632080078125</v>
       </c>
       <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>{'CONV_fwd'}</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
         <v>10.25309507229224</v>
       </c>
-      <c r="G3" t="n">
+      <c r="I3" t="n">
         <v>70.24096085469523</v>
       </c>
     </row>
@@ -1300,20 +3638,26 @@
         <v>122.84814453125</v>
       </c>
       <c r="C4" t="n">
-        <v>12</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>{'other'}</t>
-        </is>
+        <v>122.84814453125</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.12284814453125</v>
       </c>
       <c r="E4" t="n">
         <v>0.12284814453125</v>
       </c>
       <c r="F4" t="n">
+        <v>12</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>{'other'}</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
         <v>10.02589230832071</v>
       </c>
-      <c r="G4" t="n">
+      <c r="I4" t="n">
         <v>80.26685316301594</v>
       </c>
     </row>
@@ -1327,20 +3671,26 @@
         <v>111.200927734375</v>
       </c>
       <c r="C5" t="n">
-        <v>25</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>{'NORM_fwd'}</t>
-        </is>
+        <v>111.200927734375</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.111200927734375</v>
       </c>
       <c r="E5" t="n">
         <v>0.111200927734375</v>
       </c>
       <c r="F5" t="n">
+        <v>25</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>{'NORM_fwd'}</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
         <v>9.075338746907917</v>
       </c>
-      <c r="G5" t="n">
+      <c r="I5" t="n">
         <v>89.34219190992386</v>
       </c>
     </row>
@@ -1354,20 +3704,26 @@
         <v>60.541259765625</v>
       </c>
       <c r="C6" t="n">
-        <v>12</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>{'elementwise'}</t>
-        </is>
+        <v>60.541259765625</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.060541259765625</v>
       </c>
       <c r="E6" t="n">
         <v>0.060541259765625</v>
       </c>
       <c r="F6" t="n">
+        <v>12</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>{'elementwise'}</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
         <v>4.94089799187665</v>
       </c>
-      <c r="G6" t="n">
+      <c r="I6" t="n">
         <v>94.28308990180051</v>
       </c>
     </row>
@@ -1381,20 +3737,26 @@
         <v>57.31298828125</v>
       </c>
       <c r="C7" t="n">
-        <v>25</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>{'elementwise'}</t>
-        </is>
+        <v>57.31298828125</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.05731298828125</v>
       </c>
       <c r="E7" t="n">
         <v>0.05731298828125</v>
       </c>
       <c r="F7" t="n">
+        <v>25</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>{'elementwise'}</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
         <v>4.677432048879577</v>
       </c>
-      <c r="G7" t="n">
+      <c r="I7" t="n">
         <v>98.96052195068009</v>
       </c>
     </row>
@@ -1408,20 +3770,26 @@
         <v>7.263916015625</v>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>{'other'}</t>
-        </is>
+        <v>7.263916015625</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.007263916015625</v>
       </c>
       <c r="E8" t="n">
         <v>0.007263916015625</v>
       </c>
       <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>{'other'}</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
         <v>0.5928232777729626</v>
       </c>
-      <c r="G8" t="n">
+      <c r="I8" t="n">
         <v>99.55334522845305</v>
       </c>
     </row>
@@ -1435,20 +3803,26 @@
         <v>3.968017578125</v>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>{'elementwise'}</t>
-        </is>
+        <v>3.968017578125</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.003968017578125</v>
       </c>
       <c r="E9" t="n">
         <v>0.003968017578125</v>
       </c>
       <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>{'elementwise'}</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
         <v>0.3238381586274984</v>
       </c>
-      <c r="G9" t="n">
+      <c r="I9" t="n">
         <v>99.87718338708055</v>
       </c>
     </row>
@@ -1462,20 +3836,26 @@
         <v>1.5048828125</v>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>{'elementwise'}</t>
-        </is>
+        <v>1.5048828125</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.0015048828125</v>
       </c>
       <c r="E10" t="n">
         <v>0.0015048828125</v>
       </c>
       <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>{'elementwise'}</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
         <v>0.1228166129194549</v>
       </c>
-      <c r="G10" t="n">
+      <c r="I10" t="n">
         <v>100</v>
       </c>
     </row>
@@ -1490,7 +3870,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R14"/>
+  <dimension ref="A1:AA14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1506,80 +3886,125 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>process_name</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>process_label</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>thread_name</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Input Dims</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Input type</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Input Strides</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Concrete Inputs</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>operation_count</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>total_direct_kernel_time_mean</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>total_subtree_kernel_time_mean</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>total_direct_kernel_time_median</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>total_subtree_kernel_time_median</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>total_direct_kernel_time_std</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>total_subtree_kernel_time_std</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>total_direct_kernel_time_min</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>total_subtree_kernel_time_min</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>total_direct_kernel_time_max</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>total_subtree_kernel_time_max</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>total_direct_kernel_time_sum</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>total_subtree_kernel_time_sum</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>ex_UID</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>kernel_details_summary</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>trunc_kernel_details</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Percentage (%)</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Cumulative Percentage (%)</t>
         </is>
@@ -1598,62 +4023,95 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>thread 5617 (python3)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>((768,), (788, 768), (768, 768), (), ())</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>('c10::BFloat16', 'c10::BFloat16', 'c10::BFloat16', 'Scalar', 'Scalar')</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>((1,), (768, 1), (1, 768), (), ())</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>('', '', '', '1', '1')</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="J2" t="n">
         <v>48</v>
       </c>
-      <c r="H2" t="n">
+      <c r="K2" t="n">
         <v>8.315348307291666</v>
       </c>
-      <c r="I2" t="n">
+      <c r="L2" t="n">
+        <v>8.315348307291666</v>
+      </c>
+      <c r="M2" t="n">
         <v>8.256103515625</v>
       </c>
-      <c r="J2" t="n">
+      <c r="N2" t="n">
+        <v>8.256103515625</v>
+      </c>
+      <c r="O2" t="n">
         <v>0.1344482499064346</v>
       </c>
-      <c r="K2" t="n">
+      <c r="P2" t="n">
+        <v>0.1344482499064346</v>
+      </c>
+      <c r="Q2" t="n">
         <v>8.1279296875</v>
       </c>
-      <c r="L2" t="n">
+      <c r="R2" t="n">
+        <v>8.1279296875</v>
+      </c>
+      <c r="S2" t="n">
         <v>8.639892578125</v>
       </c>
-      <c r="M2" t="n">
+      <c r="T2" t="n">
+        <v>8.639892578125</v>
+      </c>
+      <c r="U2" t="n">
         <v>399.13671875</v>
       </c>
-      <c r="N2" t="n">
+      <c r="V2" t="n">
+        <v>399.13671875</v>
+      </c>
+      <c r="W2" t="n">
         <v>30</v>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_128x64_64x6_tn_align8&gt;(cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_128x64_64x6_tn_align8::Params)', 'stream': 7, 'count': 48, 'total_duration_us': np.float64(399.136), 'mean_duration_us': np.float64(8.315333333333333), 'median_duration_us': np.float64(8.256), 'std_dev_duration_us': np.float64(0.13305517861231703), 'min_duration_us': np.float64(8.128), 'max_duration_us': np.float64(8.64)}]</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_80_tensorop_bf16_s16816gemm_relu_b...', 'stream': 7, 'mean_duration_us': np.float64(8.32)}]</t>
         </is>
       </c>
-      <c r="Q2" t="n">
+      <c r="Z2" t="n">
         <v>32.57437687604667</v>
       </c>
-      <c r="R2" t="n">
+      <c r="AA2" t="n">
         <v>32.57437687604667</v>
       </c>
     </row>
@@ -1670,62 +4128,95 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>thread 5617 (python3)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>((3072,), (788, 768), (768, 3072), (), ())</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>('c10::BFloat16', 'c10::BFloat16', 'c10::BFloat16', 'Scalar', 'Scalar')</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>((1,), (768, 1), (1, 768), (), ())</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>('', '', '', '1', '1')</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="J3" t="n">
         <v>12</v>
       </c>
-      <c r="H3" t="n">
+      <c r="K3" t="n">
         <v>13.88246663411458</v>
       </c>
-      <c r="I3" t="n">
+      <c r="L3" t="n">
+        <v>13.88246663411458</v>
+      </c>
+      <c r="M3" t="n">
         <v>13.887451171875</v>
       </c>
-      <c r="J3" t="n">
+      <c r="N3" t="n">
+        <v>13.887451171875</v>
+      </c>
+      <c r="O3" t="n">
         <v>0.1063651301764554</v>
       </c>
-      <c r="K3" t="n">
+      <c r="P3" t="n">
+        <v>0.1063651301764554</v>
+      </c>
+      <c r="Q3" t="n">
         <v>13.760009765625</v>
       </c>
-      <c r="L3" t="n">
+      <c r="R3" t="n">
+        <v>13.760009765625</v>
+      </c>
+      <c r="S3" t="n">
         <v>14.176025390625</v>
       </c>
-      <c r="M3" t="n">
+      <c r="T3" t="n">
+        <v>14.176025390625</v>
+      </c>
+      <c r="U3" t="n">
         <v>166.589599609375</v>
       </c>
-      <c r="N3" t="n">
+      <c r="V3" t="n">
+        <v>166.589599609375</v>
+      </c>
+      <c r="W3" t="n">
         <v>104</v>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>[{'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'count': 12, 'total_duration_us': np.float64(166.59), 'mean_duration_us': np.float64(13.8825), 'median_duration_us': np.float64(13.8875), 'std_dev_duration_us': np.float64(0.10183278777813505), 'min_duration_us': np.float64(13.76), 'max_duration_us': np.float64(14.176)}]</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>[{'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warp...', 'stream': 7, 'mean_duration_us': np.float64(13.88)}]</t>
         </is>
       </c>
-      <c r="Q3" t="n">
+      <c r="Z3" t="n">
         <v>13.59572333585382</v>
       </c>
-      <c r="R3" t="n">
+      <c r="AA3" t="n">
         <v>46.1701002119005</v>
       </c>
     </row>
@@ -1742,62 +4233,95 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>thread 5617 (python3)</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>((768,), (788, 3072), (3072, 768), (), ())</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>('c10::BFloat16', 'c10::BFloat16', 'c10::BFloat16', 'Scalar', 'Scalar')</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>((1,), (3072, 1), (1, 3072), (), ())</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>('', '', '', '1', '1')</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="J4" t="n">
         <v>12</v>
       </c>
-      <c r="H4" t="n">
+      <c r="K4" t="n">
         <v>13.53594970703125</v>
       </c>
-      <c r="I4" t="n">
+      <c r="L4" t="n">
+        <v>13.53594970703125</v>
+      </c>
+      <c r="M4" t="n">
         <v>13.4879150390625</v>
       </c>
-      <c r="J4" t="n">
+      <c r="N4" t="n">
+        <v>13.4879150390625</v>
+      </c>
+      <c r="O4" t="n">
         <v>0.1773776572326171</v>
       </c>
-      <c r="K4" t="n">
+      <c r="P4" t="n">
+        <v>0.1773776572326171</v>
+      </c>
+      <c r="Q4" t="n">
         <v>13.343994140625</v>
       </c>
-      <c r="L4" t="n">
+      <c r="R4" t="n">
+        <v>13.343994140625</v>
+      </c>
+      <c r="S4" t="n">
         <v>13.951904296875</v>
       </c>
-      <c r="M4" t="n">
+      <c r="T4" t="n">
+        <v>13.951904296875</v>
+      </c>
+      <c r="U4" t="n">
         <v>162.431396484375</v>
       </c>
-      <c r="N4" t="n">
+      <c r="V4" t="n">
+        <v>162.431396484375</v>
+      </c>
+      <c r="W4" t="n">
         <v>114</v>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>[{'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x64x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'count': 12, 'total_duration_us': np.float64(162.43200000000002), 'mean_duration_us': np.float64(13.536000000000001), 'median_duration_us': np.float64(13.488), 'std_dev_duration_us': np.float64(0.16983128883296716), 'min_duration_us': np.float64(13.344), 'max_duration_us': np.float64(13.952)}]</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>[{'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x64x64_warpg...', 'stream': 7, 'mean_duration_us': np.float64(13.54)}]</t>
         </is>
       </c>
-      <c r="Q4" t="n">
+      <c r="Z4" t="n">
         <v>13.25636373961045</v>
       </c>
-      <c r="R4" t="n">
+      <c r="AA4" t="n">
         <v>59.42646395151095</v>
       </c>
     </row>
@@ -1814,34 +4338,42 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>thread 5617 (python3)</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>((4, 3, 224, 224), (768, 3, 16, 16), (), (), (), (), (), (), ())</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>('c10::BFloat16', 'c10::BFloat16', 'ScalarList', 'ScalarList', 'ScalarList', 'Scalar', 'Scalar', 'Scalar', 'Scalar')</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>((150528, 50176, 224, 1), (768, 256, 16, 1), (), (), (), (), (), (), ())</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>('', '', '[0, 0]', '[16, 16]', '[1, 1]', '1', 'False', 'False', 'True')</t>
         </is>
       </c>
-      <c r="G5" t="n">
+      <c r="J5" t="n">
         <v>1</v>
       </c>
-      <c r="H5" t="n">
-        <v>125.632080078125</v>
-      </c>
-      <c r="I5" t="n">
-        <v>125.632080078125</v>
-      </c>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
         <v>125.632080078125</v>
       </c>
@@ -1852,22 +4384,45 @@
         <v>125.632080078125</v>
       </c>
       <c r="N5" t="n">
+        <v>125.632080078125</v>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="n">
+        <v>125.632080078125</v>
+      </c>
+      <c r="R5" t="n">
+        <v>125.632080078125</v>
+      </c>
+      <c r="S5" t="n">
+        <v>125.632080078125</v>
+      </c>
+      <c r="T5" t="n">
+        <v>125.632080078125</v>
+      </c>
+      <c r="U5" t="n">
+        <v>125.632080078125</v>
+      </c>
+      <c r="V5" t="n">
+        <v>125.632080078125</v>
+      </c>
+      <c r="W5" t="n">
         <v>4</v>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>[{'name': 'Memset (Device)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(2.272), 'mean_duration_us': np.float64(2.272), 'median_duration_us': np.float64(2.272), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(2.272), 'max_duration_us': np.float64(2.272)}, {'name': 'void cudnn::engines_precompiled::nchwToNhwcKernel&lt;__nv_bfloat16, __nv_bfloat16, float, false, true, (cudnnKernelDataType_t)0&gt;(cudnn::engines_precompiled::nchw2nhwc_params_t&lt;float&gt;, __nv_bfloat16 const*, __nv_bfloat16*)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(10.464), 'mean_duration_us': np.float64(10.464), 'median_duration_us': np.float64(10.464), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(10.464), 'max_duration_us': np.float64(10.464)}, {'name': 'Memset (Device)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(2.112), 'mean_duration_us': np.float64(2.112), 'median_duration_us': np.float64(2.112), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(2.112), 'max_duration_us': np.float64(2.112)}, {'name': 'void cudnn::engines_precompiled::nchwToNhwcKernel&lt;__nv_bfloat16, __nv_bfloat16, float, false, true, (cudnnKernelDataType_t)0&gt;(cudnn::engines_precompiled::nchw2nhwc_params_t&lt;float&gt;, __nv_bfloat16 const*, __nv_bfloat16*)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(10.4), 'mean_duration_us': np.float64(10.4), 'median_duration_us': np.float64(10.4), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(10.4), 'max_duration_us': np.float64(10.4)}, {'name': 'void cutlass__5x_cudnn::Kernel&lt;cutlass_tensorop_bf16_s16816fprop_optimized_bf16_256x64_32x4_nhwc_align8&gt;(cutlass_tensorop_bf16_s16816fprop_optimized_bf16_256x64_32x4_nhwc_align8::Params)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(98.176), 'mean_duration_us': np.float64(98.176), 'median_duration_us': np.float64(98.176), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(98.176), 'max_duration_us': np.float64(98.176)}, {'name': 'void cudnn::engines_precompiled::nhwcToNchwKernel&lt;__nv_bfloat16, __nv_bfloat16, float, true, false, (cudnnKernelDataType_t)0&gt;(cudnn::engines_precompiled::nhwc2nchw_params_t&lt;float&gt;, __nv_bfloat16 const*, __nv_bfloat16*)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(2.208), 'mean_duration_us': np.float64(2.208), 'median_duration_us': np.float64(2.208), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(2.208), 'max_duration_us': np.float64(2.208)}]</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>[{'name': 'Memset (Device)', 'stream': 7, 'mean_duration_us': np.float64(2.27)}, {'name': 'void cudnn::engines_precompiled::nchwToNhwcKernel&lt;__nv_bfloat16,...', 'stream': 7, 'mean_duration_us': np.float64(10.46)}, {'name': 'Memset (Device)', 'stream': 7, 'mean_duration_us': np.float64(2.11)}, {'name': 'void cudnn::engines_precompiled::nchwToNhwcKernel&lt;__nv_bfloat16,...', 'stream': 7, 'mean_duration_us': np.float64(10.4)}, {'name': 'void cutlass__5x_cudnn::Kernel&lt;cutlass_tensorop_bf16_s16816fprop...', 'stream': 7, 'mean_duration_us': np.float64(98.18)}, {'name': 'void cudnn::engines_precompiled::nhwcToNchwKernel&lt;__nv_bfloat16,...', 'stream': 7, 'mean_duration_us': np.float64(2.21)}]</t>
         </is>
       </c>
-      <c r="Q5" t="n">
+      <c r="Z5" t="n">
         <v>10.25309507229224</v>
       </c>
-      <c r="R5" t="n">
+      <c r="AA5" t="n">
         <v>69.67955902380319</v>
       </c>
     </row>
@@ -1884,62 +4439,95 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>thread 5617 (python3)</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>((4, 197, 12, 64), (4, 197, 12, 64), (4, 197, 12, 64), (), (), (), (), (), (), (), (), (), (), (), ())</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>('c10::BFloat16', 'c10::BFloat16', 'c10::BFloat16', '', '', 'Scalar', 'Scalar', 'Scalar', 'Scalar', 'Scalar', 'Scalar', '', '', '', '')</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>((151296, 768, 64, 1), (151296, 768, 64, 1), (151296, 768, 64, 1), (), (), (), (), (), (), (), (), (), (), (), ())</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>('', '', '', '', '', '197', '197', '0.', 'False', 'False', '0.125', '', '', '', '')</t>
         </is>
       </c>
-      <c r="G6" t="n">
+      <c r="J6" t="n">
         <v>12</v>
       </c>
-      <c r="H6" t="n">
+      <c r="K6" t="n">
         <v>10.23734537760417</v>
       </c>
-      <c r="I6" t="n">
+      <c r="L6" t="n">
+        <v>10.23734537760417</v>
+      </c>
+      <c r="M6" t="n">
         <v>10.2239990234375</v>
       </c>
-      <c r="J6" t="n">
+      <c r="N6" t="n">
+        <v>10.2239990234375</v>
+      </c>
+      <c r="O6" t="n">
         <v>0.228442528412397</v>
       </c>
-      <c r="K6" t="n">
+      <c r="P6" t="n">
+        <v>0.228442528412397</v>
+      </c>
+      <c r="Q6" t="n">
         <v>10.01611328125</v>
       </c>
-      <c r="L6" t="n">
+      <c r="R6" t="n">
+        <v>10.01611328125</v>
+      </c>
+      <c r="S6" t="n">
         <v>10.847900390625</v>
       </c>
-      <c r="M6" t="n">
+      <c r="T6" t="n">
+        <v>10.847900390625</v>
+      </c>
+      <c r="U6" t="n">
         <v>122.84814453125</v>
       </c>
-      <c r="N6" t="n">
+      <c r="V6" t="n">
+        <v>122.84814453125</v>
+      </c>
+      <c r="W6" t="n">
         <v>68</v>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>[{'name': 'void pytorch_flash::flash_fwd_kernel&lt;pytorch_flash::Flash_fwd_kernel_traits&lt;64, 128, 128, 4, false, false, cutlass::bfloat16_t, pytorch_flash::Flash_kernel_traits&lt;64, 128, 128, 4, cutlass::bfloat16_t&gt; &gt;, false, false, false, false, false, true, false&gt;(pytorch_flash::Flash_fwd_params)', 'stream': 7, 'count': 12, 'total_duration_us': np.float64(122.848), 'mean_duration_us': np.float64(10.237333333333334), 'median_duration_us': np.float64(10.224), 'std_dev_duration_us': np.float64(0.21878045819699932), 'min_duration_us': np.float64(10.016), 'max_duration_us': np.float64(10.848)}]</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>[{'name': 'void pytorch_flash::flash_fwd_kernel&lt;pytorch_flash::Flash_fwd_ke...', 'stream': 7, 'mean_duration_us': np.float64(10.24)}]</t>
         </is>
       </c>
-      <c r="Q6" t="n">
+      <c r="Z6" t="n">
         <v>10.02589230832071</v>
       </c>
-      <c r="R6" t="n">
+      <c r="AA6" t="n">
         <v>79.7054513321239</v>
       </c>
     </row>
@@ -1956,62 +4544,95 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>thread 5617 (python3)</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>((4, 197, 768), (), (768,), (768,), ())</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>('c10::BFloat16', 'ScalarList', 'c10::BFloat16', 'c10::BFloat16', 'Scalar')</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>((151296, 768, 1), (), (1,), (1,), ())</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>('', '[768]', '', '', '9.9999999999999998e-13')</t>
         </is>
       </c>
-      <c r="G7" t="n">
+      <c r="J7" t="n">
         <v>25</v>
       </c>
-      <c r="H7" t="n">
+      <c r="K7" t="n">
         <v>4.448037109375</v>
       </c>
-      <c r="I7" t="n">
+      <c r="L7" t="n">
+        <v>4.448037109375</v>
+      </c>
+      <c r="M7" t="n">
         <v>4.447998046875</v>
       </c>
-      <c r="J7" t="n">
+      <c r="N7" t="n">
+        <v>4.447998046875</v>
+      </c>
+      <c r="O7" t="n">
         <v>0.1115342775722907</v>
       </c>
-      <c r="K7" t="n">
+      <c r="P7" t="n">
+        <v>0.1115342775722907</v>
+      </c>
+      <c r="Q7" t="n">
         <v>4.256103515625</v>
       </c>
-      <c r="L7" t="n">
+      <c r="R7" t="n">
+        <v>4.256103515625</v>
+      </c>
+      <c r="S7" t="n">
         <v>4.639892578125</v>
       </c>
-      <c r="M7" t="n">
+      <c r="T7" t="n">
+        <v>4.639892578125</v>
+      </c>
+      <c r="U7" t="n">
         <v>111.200927734375</v>
       </c>
-      <c r="N7" t="n">
+      <c r="V7" t="n">
+        <v>111.200927734375</v>
+      </c>
+      <c r="W7" t="n">
         <v>18</v>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 7, 'count': 25, 'total_duration_us': np.float64(111.20100000000001), 'mean_duration_us': np.float64(4.448040000000001), 'median_duration_us': np.float64(4.448), 'std_dev_duration_us': np.float64(0.10934037863479323), 'min_duration_us': np.float64(4.256), 'max_duration_us': np.float64(4.64)}]</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_ke...', 'stream': 7, 'mean_duration_us': np.float64(4.45)}]</t>
         </is>
       </c>
-      <c r="Q7" t="n">
+      <c r="Z7" t="n">
         <v>9.075338746907917</v>
       </c>
-      <c r="R7" t="n">
+      <c r="AA7" t="n">
         <v>88.78079007903182</v>
       </c>
     </row>
@@ -2028,62 +4649,95 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>thread 5617 (python3)</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>((4, 197, 3072), ())</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>('c10::BFloat16', '')</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>((605184, 3072, 1), ())</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>('', '')</t>
         </is>
       </c>
-      <c r="G8" t="n">
+      <c r="J8" t="n">
         <v>12</v>
       </c>
-      <c r="H8" t="n">
+      <c r="K8" t="n">
         <v>5.04510498046875</v>
       </c>
-      <c r="I8" t="n">
+      <c r="L8" t="n">
+        <v>5.04510498046875</v>
+      </c>
+      <c r="M8" t="n">
         <v>5.055419921875</v>
       </c>
-      <c r="J8" t="n">
+      <c r="N8" t="n">
+        <v>5.055419921875</v>
+      </c>
+      <c r="O8" t="n">
         <v>0.03943788318148379</v>
       </c>
-      <c r="K8" t="n">
+      <c r="P8" t="n">
+        <v>0.03943788318148379</v>
+      </c>
+      <c r="Q8" t="n">
         <v>4.990966796875</v>
       </c>
-      <c r="L8" t="n">
+      <c r="R8" t="n">
+        <v>4.990966796875</v>
+      </c>
+      <c r="S8" t="n">
         <v>5.1201171875</v>
       </c>
-      <c r="M8" t="n">
+      <c r="T8" t="n">
+        <v>5.1201171875</v>
+      </c>
+      <c r="U8" t="n">
         <v>60.541259765625</v>
       </c>
-      <c r="N8" t="n">
+      <c r="V8" t="n">
+        <v>60.541259765625</v>
+      </c>
+      <c r="W8" t="n">
         <v>107</v>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::GeluCUDAKernelImpl(at::TensorIteratorBase&amp;, at::native::GeluType)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::GeluCUDAKernelImpl(at::TensorIteratorBase&amp;, at::native::GeluType)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 12, 'total_duration_us': np.float64(60.541999999999994), 'mean_duration_us': np.float64(5.045166666666666), 'median_duration_us': np.float64(5.0555), 'std_dev_duration_us': np.float64(0.037739972914080884), 'min_duration_us': np.float64(4.991), 'max_duration_us': np.float64(5.12)}]</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::Ge...', 'stream': 7, 'mean_duration_us': np.float64(5.05)}]</t>
         </is>
       </c>
-      <c r="Q8" t="n">
+      <c r="Z8" t="n">
         <v>4.940897991876649</v>
       </c>
-      <c r="R8" t="n">
+      <c r="AA8" t="n">
         <v>93.72168807090847</v>
       </c>
     </row>
@@ -2100,62 +4754,95 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>thread 5617 (python3)</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t>((4, 197, 768), (4, 197, 768), ())</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>('c10::BFloat16', 'c10::BFloat16', 'Scalar')</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>((151296, 768, 1), (151296, 768, 1), ())</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>('', '', '1')</t>
         </is>
       </c>
-      <c r="G9" t="n">
+      <c r="J9" t="n">
         <v>24</v>
       </c>
-      <c r="H9" t="n">
+      <c r="K9" t="n">
         <v>2.230662027994792</v>
       </c>
-      <c r="I9" t="n">
+      <c r="L9" t="n">
+        <v>2.230662027994792</v>
+      </c>
+      <c r="M9" t="n">
         <v>2.2244873046875</v>
       </c>
-      <c r="J9" t="n">
+      <c r="N9" t="n">
+        <v>2.2244873046875</v>
+      </c>
+      <c r="O9" t="n">
         <v>0.03450867810431143</v>
       </c>
-      <c r="K9" t="n">
+      <c r="P9" t="n">
+        <v>0.03450867810431143</v>
+      </c>
+      <c r="Q9" t="n">
         <v>2.176025390625</v>
       </c>
-      <c r="L9" t="n">
+      <c r="R9" t="n">
+        <v>2.176025390625</v>
+      </c>
+      <c r="S9" t="n">
         <v>2.303955078125</v>
       </c>
-      <c r="M9" t="n">
+      <c r="T9" t="n">
+        <v>2.303955078125</v>
+      </c>
+      <c r="U9" t="n">
         <v>53.535888671875</v>
       </c>
-      <c r="N9" t="n">
+      <c r="V9" t="n">
+        <v>53.535888671875</v>
+      </c>
+      <c r="W9" t="n">
         <v>90</v>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 7, 'count': 24, 'total_duration_us': np.float64(53.536), 'mean_duration_us': np.float64(2.2306666666666666), 'median_duration_us': np.float64(2.2245), 'std_dev_duration_us': np.float64(0.033798011118341686), 'min_duration_us': np.float64(2.176), 'max_duration_us': np.float64(2.304)}]</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CU...', 'stream': 7, 'mean_duration_us': np.float64(2.23)}]</t>
         </is>
       </c>
-      <c r="Q9" t="n">
+      <c r="Z9" t="n">
         <v>4.369175102338875</v>
       </c>
-      <c r="R9" t="n">
+      <c r="AA9" t="n">
         <v>98.09086317324734</v>
       </c>
     </row>
@@ -2172,34 +4859,42 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>thread 5617 (python3)</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t>(((4, 1, 768), (4, 196, 768)), ())</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>('TensorList', 'Scalar')</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>(((0, 768, 1), (150528, 1, 196)), ())</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>('', '1')</t>
         </is>
       </c>
-      <c r="G10" t="n">
+      <c r="J10" t="n">
         <v>1</v>
       </c>
-      <c r="H10" t="n">
-        <v>7.263916015625</v>
-      </c>
-      <c r="I10" t="n">
-        <v>7.263916015625</v>
-      </c>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="n">
         <v>7.263916015625</v>
       </c>
@@ -2210,22 +4905,45 @@
         <v>7.263916015625</v>
       </c>
       <c r="N10" t="n">
+        <v>7.263916015625</v>
+      </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="n">
+        <v>7.263916015625</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7.263916015625</v>
+      </c>
+      <c r="S10" t="n">
+        <v>7.263916015625</v>
+      </c>
+      <c r="T10" t="n">
+        <v>7.263916015625</v>
+      </c>
+      <c r="U10" t="n">
+        <v>7.263916015625</v>
+      </c>
+      <c r="V10" t="n">
+        <v>7.263916015625</v>
+      </c>
+      <c r="W10" t="n">
         <v>14</v>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::(anonymous namespace)::CatArrayBatchedCopy&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 3, 64, 64&gt;(at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;*, at::native::(anonymous namespace)::CatArrInputTensorMetadata&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 64, 64&gt;, at::native::(anonymous namespace)::TensorSizeStride&lt;unsigned int, 4u&gt;, int, unsigned int)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(7.264), 'mean_duration_us': np.float64(7.264), 'median_duration_us': np.float64(7.264), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(7.264), 'max_duration_us': np.float64(7.264)}]</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::(anonymous namespace)::CatArrayBatchedCopy&lt;at::...', 'stream': 7, 'mean_duration_us': np.float64(7.26)}]</t>
         </is>
       </c>
-      <c r="Q10" t="n">
+      <c r="Z10" t="n">
         <v>0.5928232777729626</v>
       </c>
-      <c r="R10" t="n">
+      <c r="AA10" t="n">
         <v>98.68368645102031</v>
       </c>
     </row>
@@ -2242,34 +4960,42 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>thread 5617 (python3)</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t>((768,), (4, 768), (768, 768), (), ())</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>('c10::BFloat16', 'c10::BFloat16', 'c10::BFloat16', 'Scalar', 'Scalar')</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>((1,), (151296, 1), (1, 768), (), ())</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>('', '', '', '1', '1')</t>
         </is>
       </c>
-      <c r="G11" t="n">
+      <c r="J11" t="n">
         <v>1</v>
       </c>
-      <c r="H11" t="n">
-        <v>6.87890625</v>
-      </c>
-      <c r="I11" t="n">
-        <v>6.87890625</v>
-      </c>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="n">
         <v>6.87890625</v>
       </c>
@@ -2280,22 +5006,45 @@
         <v>6.87890625</v>
       </c>
       <c r="N11" t="n">
+        <v>6.87890625</v>
+      </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="n">
+        <v>6.87890625</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6.87890625</v>
+      </c>
+      <c r="S11" t="n">
+        <v>6.87890625</v>
+      </c>
+      <c r="T11" t="n">
+        <v>6.87890625</v>
+      </c>
+      <c r="U11" t="n">
+        <v>6.87890625</v>
+      </c>
+      <c r="V11" t="n">
+        <v>6.87890625</v>
+      </c>
+      <c r="W11" t="n">
         <v>1256</v>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_64x64_64x6_tn_align8&gt;(cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_64x64_64x6_tn_align8::Params)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(6.879), 'mean_duration_us': np.float64(6.879), 'median_duration_us': np.float64(6.879), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(6.879), 'max_duration_us': np.float64(6.879)}]</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_80_tensorop_bf16_s16816gemm_relu_b...', 'stream': 7, 'mean_duration_us': np.float64(6.88)}]</t>
         </is>
       </c>
-      <c r="Q11" t="n">
+      <c r="Z11" t="n">
         <v>0.5614018308920443</v>
       </c>
-      <c r="R11" t="n">
+      <c r="AA11" t="n">
         <v>99.24508828191234</v>
       </c>
     </row>
@@ -2312,34 +5061,42 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>thread 5617 (python3)</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t>((4, 768, 14, 14), (1, 768, 1, 1), ())</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>('c10::BFloat16', 'c10::BFloat16', 'Scalar')</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>((150528, 196, 14, 1), (768, 1, 1, 1), ())</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>('', '', '1')</t>
         </is>
       </c>
-      <c r="G12" t="n">
+      <c r="J12" t="n">
         <v>1</v>
       </c>
-      <c r="H12" t="n">
-        <v>3.968017578125</v>
-      </c>
-      <c r="I12" t="n">
-        <v>3.968017578125</v>
-      </c>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="n">
         <v>3.968017578125</v>
       </c>
@@ -2350,22 +5107,45 @@
         <v>3.968017578125</v>
       </c>
       <c r="N12" t="n">
+        <v>3.968017578125</v>
+      </c>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="n">
+        <v>3.968017578125</v>
+      </c>
+      <c r="R12" t="n">
+        <v>3.968017578125</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.968017578125</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3.968017578125</v>
+      </c>
+      <c r="U12" t="n">
+        <v>3.968017578125</v>
+      </c>
+      <c r="V12" t="n">
+        <v>3.968017578125</v>
+      </c>
+      <c r="W12" t="n">
         <v>7</v>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(3.968), 'mean_duration_us': np.float64(3.968), 'median_duration_us': np.float64(3.968), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(3.968), 'max_duration_us': np.float64(3.968)}]</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(3.97)}]</t>
         </is>
       </c>
-      <c r="Q12" t="n">
+      <c r="Z12" t="n">
         <v>0.3238381586274984</v>
       </c>
-      <c r="R12" t="n">
+      <c r="AA12" t="n">
         <v>99.56892644053984</v>
       </c>
     </row>
@@ -2382,34 +5162,42 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>thread 5617 (python3)</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t>((4, 197, 768), (1, 197, 768), ())</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>('c10::BFloat16', 'c10::BFloat16', 'Scalar')</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>((151296, 768, 1), (151296, 768, 1), ())</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>('', '', '1')</t>
         </is>
       </c>
-      <c r="G13" t="n">
+      <c r="J13" t="n">
         <v>1</v>
       </c>
-      <c r="H13" t="n">
-        <v>3.777099609375</v>
-      </c>
-      <c r="I13" t="n">
-        <v>3.777099609375</v>
-      </c>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="n">
         <v>3.777099609375</v>
       </c>
@@ -2420,22 +5208,45 @@
         <v>3.777099609375</v>
       </c>
       <c r="N13" t="n">
+        <v>3.777099609375</v>
+      </c>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="n">
+        <v>3.777099609375</v>
+      </c>
+      <c r="R13" t="n">
+        <v>3.777099609375</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.777099609375</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3.777099609375</v>
+      </c>
+      <c r="U13" t="n">
+        <v>3.777099609375</v>
+      </c>
+      <c r="V13" t="n">
+        <v>3.777099609375</v>
+      </c>
+      <c r="W13" t="n">
         <v>15</v>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(3.777), 'mean_duration_us': np.float64(3.777), 'median_duration_us': np.float64(3.777), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(3.777), 'max_duration_us': np.float64(3.777)}]</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="Y13" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(3.78)}]</t>
         </is>
       </c>
-      <c r="Q13" t="n">
+      <c r="Z13" t="n">
         <v>0.3082569465407019</v>
       </c>
-      <c r="R13" t="n">
+      <c r="AA13" t="n">
         <v>99.87718338708055</v>
       </c>
     </row>
@@ -2452,34 +5263,42 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>thread 5617 (python3)</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t>((4, 768),)</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>('c10::BFloat16',)</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>((768, 1),)</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>('',)</t>
         </is>
       </c>
-      <c r="G14" t="n">
+      <c r="J14" t="n">
         <v>1</v>
       </c>
-      <c r="H14" t="n">
-        <v>1.5048828125</v>
-      </c>
-      <c r="I14" t="n">
-        <v>1.5048828125</v>
-      </c>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="n">
         <v>1.5048828125</v>
       </c>
@@ -2490,22 +5309,45 @@
         <v>1.5048828125</v>
       </c>
       <c r="N14" t="n">
+        <v>1.5048828125</v>
+      </c>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="n">
+        <v>1.5048828125</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.5048828125</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1.5048828125</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.5048828125</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.5048828125</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.5048828125</v>
+      </c>
+      <c r="W14" t="n">
         <v>1258</v>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::tanh_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::tanh_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(1.505), 'mean_duration_us': np.float64(1.505), 'median_duration_us': np.float64(1.505), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(1.505), 'max_duration_us': np.float64(1.505)}]</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="Y14" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::ta...', 'stream': 7, 'mean_duration_us': np.float64(1.5)}]</t>
         </is>
       </c>
-      <c r="Q14" t="n">
+      <c r="Z14" t="n">
         <v>0.1228166129194549</v>
       </c>
-      <c r="R14" t="n">
+      <c r="AA14" t="n">
         <v>100</v>
       </c>
     </row>
@@ -2520,7 +5362,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN13"/>
+  <dimension ref="A1:AQ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2536,190 +5378,205 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>process_name</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>process_label</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>thread_name</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Input Dims</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Input type</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Input Strides</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Concrete Inputs</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>ex_UID</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>operation_count</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>total_duration_us</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>mean_duration_us</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>std_duration_us</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>GFLOPS</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Data Moved (MB)</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>FLOPS/Byte</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Compute Spec</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>TB/s_mean</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>TB/s_std</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>TFLOPS/s_mean</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>TFLOPS/s_std</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_mean</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_std</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_sum</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>duration_us_median</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>duration_us_min</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>duration_us_max</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>TB/s_median</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>TB/s_min</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>TB/s_max</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>TFLOPS/s_median</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>TFLOPS/s_min</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>TFLOPS/s_max</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_median</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_min</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_max</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>kernel_details_summary</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>trunc_kernel_details</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>perf_params</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>has_perf_model</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>Percentage (%)</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>Cumulative Percentage (%)</t>
         </is>
@@ -2738,132 +5595,147 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>thread 5617 (python3)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>((768,), (788, 768), (768, 768), (), ())</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>('c10::BFloat16', 'c10::BFloat16', 'c10::BFloat16', 'Scalar', 'Scalar')</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>((1,), (768, 1), (1, 768), (), ())</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>('', '', '', '1', '1')</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="J2" t="n">
         <v>30</v>
       </c>
-      <c r="H2" t="n">
+      <c r="K2" t="n">
         <v>48</v>
       </c>
-      <c r="I2" t="n">
+      <c r="L2" t="n">
         <v>1154.879</v>
       </c>
-      <c r="J2" t="n">
+      <c r="M2" t="n">
         <v>24.05997916666666</v>
       </c>
-      <c r="K2" t="n">
+      <c r="N2" t="n">
         <v>3.557746534509176</v>
       </c>
-      <c r="L2" t="n">
+      <c r="O2" t="n">
         <v>0.930167808</v>
       </c>
-      <c r="M2" t="n">
+      <c r="P2" t="n">
         <v>3.43505859375</v>
       </c>
-      <c r="N2" t="n">
+      <c r="Q2" t="n">
         <v>258.2422174840085</v>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>matrix_bf16</t>
         </is>
       </c>
-      <c r="P2" t="n">
+      <c r="S2" t="n">
         <v>0.4332748290550287</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="T2" t="n">
         <v>0.006921872667601486</v>
       </c>
-      <c r="R2" t="n">
+      <c r="U2" t="n">
         <v>111.8898526351753</v>
       </c>
-      <c r="S2" t="n">
+      <c r="V2" t="n">
         <v>1.78751974682336</v>
       </c>
-      <c r="T2" t="n">
+      <c r="W2" t="n">
         <v>8.315348307291666</v>
       </c>
-      <c r="U2" t="n">
+      <c r="X2" t="n">
         <v>0.1344482499064346</v>
       </c>
-      <c r="V2" t="n">
+      <c r="Y2" t="n">
         <v>399.13671875</v>
       </c>
-      <c r="W2" t="n">
+      <c r="Z2" t="n">
         <v>25.2705</v>
       </c>
-      <c r="X2" t="n">
+      <c r="AA2" t="n">
         <v>19.16</v>
       </c>
-      <c r="Y2" t="n">
+      <c r="AB2" t="n">
         <v>34.53</v>
       </c>
-      <c r="Z2" t="n">
+      <c r="AC2" t="n">
         <v>0.4362735996688056</v>
       </c>
-      <c r="AA2" t="n">
+      <c r="AD2" t="n">
         <v>0.4168940721693182</v>
       </c>
-      <c r="AB2" t="n">
+      <c r="AE2" t="n">
         <v>0.4431534398654331</v>
       </c>
-      <c r="AC2" t="n">
+      <c r="AF2" t="n">
         <v>112.664261808203</v>
       </c>
-      <c r="AD2" t="n">
+      <c r="AG2" t="n">
         <v>107.659649652943</v>
       </c>
-      <c r="AE2" t="n">
+      <c r="AH2" t="n">
         <v>114.4409269965157</v>
       </c>
-      <c r="AF2" t="n">
+      <c r="AI2" t="n">
         <v>8.256103515625</v>
       </c>
-      <c r="AG2" t="n">
+      <c r="AJ2" t="n">
         <v>8.1279296875</v>
       </c>
-      <c r="AH2" t="n">
+      <c r="AK2" t="n">
         <v>8.639892578125</v>
       </c>
-      <c r="AI2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
         <is>
           <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_128x64_64x6_tn_align8&gt;(cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_128x64_64x6_tn_align8::Params)', 'stream': 7, 'count': 48, 'total_duration_us': np.float64(399.136), 'mean_duration_us': np.float64(8.315333333333333), 'median_duration_us': np.float64(8.256), 'std_dev_duration_us': np.float64(0.13305517861231703), 'min_duration_us': np.float64(8.128), 'max_duration_us': np.float64(8.64)}]</t>
         </is>
       </c>
-      <c r="AJ2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_80_tensorop_bf16_s16816gemm_relu_b...', 'stream': 7, 'mean_duration_us': np.float64(8.32)}]</t>
         </is>
       </c>
-      <c r="AK2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>{'M': 788, 'N': 768, 'K': 768, 'bias': True, 'stride_A': (768, 1), 'stride_B': (1, 768), 'dtype_A_B': ('c10::BFloat16', 'c10::BFloat16'), 'B': 1}</t>
         </is>
       </c>
-      <c r="AL2" t="b">
+      <c r="AO2" t="b">
         <v>1</v>
       </c>
-      <c r="AM2" t="n">
+      <c r="AP2" t="n">
         <v>32.57437687604667</v>
       </c>
-      <c r="AN2" t="n">
+      <c r="AQ2" t="n">
         <v>32.57437687604667</v>
       </c>
     </row>
@@ -2880,132 +5752,147 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>thread 5617 (python3)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>((3072,), (788, 768), (768, 3072), (), ())</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>('c10::BFloat16', 'c10::BFloat16', 'c10::BFloat16', 'Scalar', 'Scalar')</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>((1,), (768, 1), (1, 768), (), ())</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>('', '', '', '1', '1')</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="J3" t="n">
         <v>104</v>
       </c>
-      <c r="H3" t="n">
+      <c r="K3" t="n">
         <v>12</v>
       </c>
-      <c r="I3" t="n">
+      <c r="L3" t="n">
         <v>469.666</v>
       </c>
-      <c r="J3" t="n">
+      <c r="M3" t="n">
         <v>39.13883333333333</v>
       </c>
-      <c r="K3" t="n">
+      <c r="N3" t="n">
         <v>1.635353997448167</v>
       </c>
-      <c r="L3" t="n">
+      <c r="O3" t="n">
         <v>3.720671232</v>
       </c>
-      <c r="M3" t="n">
+      <c r="P3" t="n">
         <v>10.27734375</v>
       </c>
-      <c r="N3" t="n">
+      <c r="Q3" t="n">
         <v>345.2554161915621</v>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>matrix_bf16</t>
         </is>
       </c>
-      <c r="P3" t="n">
+      <c r="S3" t="n">
         <v>0.7763136653796865</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="T3" t="n">
         <v>0.00587259665798289</v>
       </c>
-      <c r="R3" t="n">
+      <c r="U3" t="n">
         <v>268.0264976358607</v>
       </c>
-      <c r="S3" t="n">
+      <c r="V3" t="n">
         <v>2.027545803277043</v>
       </c>
-      <c r="T3" t="n">
+      <c r="W3" t="n">
         <v>13.88246663411458</v>
       </c>
-      <c r="U3" t="n">
+      <c r="X3" t="n">
         <v>0.1063651301764554</v>
       </c>
-      <c r="V3" t="n">
+      <c r="Y3" t="n">
         <v>166.589599609375</v>
       </c>
-      <c r="W3" t="n">
+      <c r="Z3" t="n">
         <v>38.6155</v>
       </c>
-      <c r="X3" t="n">
+      <c r="AA3" t="n">
         <v>37.56</v>
       </c>
-      <c r="Y3" t="n">
+      <c r="AB3" t="n">
         <v>43.91</v>
       </c>
-      <c r="Z3" t="n">
+      <c r="AC3" t="n">
         <v>0.775993800442447</v>
       </c>
-      <c r="AA3" t="n">
+      <c r="AD3" t="n">
         <v>0.7601972840093</v>
       </c>
-      <c r="AB3" t="n">
+      <c r="AE3" t="n">
         <v>0.783180839516687</v>
       </c>
-      <c r="AC3" t="n">
+      <c r="AF3" t="n">
         <v>267.9160625338291</v>
       </c>
-      <c r="AD3" t="n">
+      <c r="AG3" t="n">
         <v>262.462229678326</v>
       </c>
-      <c r="AE3" t="n">
+      <c r="AH3" t="n">
         <v>270.3974267005908</v>
       </c>
-      <c r="AF3" t="n">
+      <c r="AI3" t="n">
         <v>13.887451171875</v>
       </c>
-      <c r="AG3" t="n">
+      <c r="AJ3" t="n">
         <v>13.760009765625</v>
       </c>
-      <c r="AH3" t="n">
+      <c r="AK3" t="n">
         <v>14.176025390625</v>
       </c>
-      <c r="AI3" t="inlineStr">
+      <c r="AL3" t="inlineStr">
         <is>
           <t>[{'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'count': 12, 'total_duration_us': np.float64(166.59), 'mean_duration_us': np.float64(13.8825), 'median_duration_us': np.float64(13.8875), 'std_dev_duration_us': np.float64(0.10183278777813505), 'min_duration_us': np.float64(13.76), 'max_duration_us': np.float64(14.176)}]</t>
         </is>
       </c>
-      <c r="AJ3" t="inlineStr">
+      <c r="AM3" t="inlineStr">
         <is>
           <t>[{'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warp...', 'stream': 7, 'mean_duration_us': np.float64(13.88)}]</t>
         </is>
       </c>
-      <c r="AK3" t="inlineStr">
+      <c r="AN3" t="inlineStr">
         <is>
           <t>{'M': 788, 'N': 3072, 'K': 768, 'bias': True, 'stride_A': (768, 1), 'stride_B': (1, 768), 'dtype_A_B': ('c10::BFloat16', 'c10::BFloat16'), 'B': 1}</t>
         </is>
       </c>
-      <c r="AL3" t="b">
+      <c r="AO3" t="b">
         <v>1</v>
       </c>
-      <c r="AM3" t="n">
+      <c r="AP3" t="n">
         <v>13.59572333585382</v>
       </c>
-      <c r="AN3" t="n">
+      <c r="AQ3" t="n">
         <v>46.1701002119005</v>
       </c>
     </row>
@@ -3022,132 +5909,147 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>thread 5617 (python3)</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>((768,), (788, 3072), (3072, 768), (), ())</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>('c10::BFloat16', 'c10::BFloat16', 'c10::BFloat16', 'Scalar', 'Scalar')</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>((1,), (3072, 1), (1, 3072), (), ())</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>('', '', '', '1', '1')</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="J4" t="n">
         <v>114</v>
       </c>
-      <c r="H4" t="n">
+      <c r="K4" t="n">
         <v>12</v>
       </c>
-      <c r="I4" t="n">
+      <c r="L4" t="n">
         <v>430.237</v>
       </c>
-      <c r="J4" t="n">
+      <c r="M4" t="n">
         <v>35.85308333333334</v>
       </c>
-      <c r="K4" t="n">
+      <c r="N4" t="n">
         <v>3.536968564857183</v>
       </c>
-      <c r="L4" t="n">
+      <c r="O4" t="n">
         <v>3.71885568</v>
       </c>
-      <c r="M4" t="n">
+      <c r="P4" t="n">
         <v>10.27294921875</v>
       </c>
-      <c r="N4" t="n">
+      <c r="Q4" t="n">
         <v>345.2345643804363</v>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>matrix_bf16</t>
         </is>
       </c>
-      <c r="P4" t="n">
+      <c r="S4" t="n">
         <v>0.7959277904370671</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="T4" t="n">
         <v>0.01027516892316802</v>
       </c>
-      <c r="R4" t="n">
+      <c r="U4" t="n">
         <v>274.781784009824</v>
       </c>
-      <c r="S4" t="n">
+      <c r="V4" t="n">
         <v>3.547343467125292</v>
       </c>
-      <c r="T4" t="n">
+      <c r="W4" t="n">
         <v>13.53594970703125</v>
       </c>
-      <c r="U4" t="n">
+      <c r="X4" t="n">
         <v>0.1773776572326171</v>
       </c>
-      <c r="V4" t="n">
+      <c r="Y4" t="n">
         <v>162.431396484375</v>
       </c>
-      <c r="W4" t="n">
+      <c r="Z4" t="n">
         <v>34.531</v>
       </c>
-      <c r="X4" t="n">
+      <c r="AA4" t="n">
         <v>33.86</v>
       </c>
-      <c r="Y4" t="n">
+      <c r="AB4" t="n">
         <v>45.29</v>
       </c>
-      <c r="Z4" t="n">
+      <c r="AC4" t="n">
         <v>0.7986396051796765</v>
       </c>
-      <c r="AA4" t="n">
+      <c r="AD4" t="n">
         <v>0.7720786905349362</v>
       </c>
-      <c r="AB4" t="n">
+      <c r="AE4" t="n">
         <v>0.8072521530270598</v>
       </c>
-      <c r="AC4" t="n">
+      <c r="AF4" t="n">
         <v>275.7179961911693</v>
       </c>
-      <c r="AD4" t="n">
+      <c r="AG4" t="n">
         <v>266.5482503942464</v>
       </c>
-      <c r="AE4" t="n">
+      <c r="AH4" t="n">
         <v>278.6913453954663</v>
       </c>
-      <c r="AF4" t="n">
+      <c r="AI4" t="n">
         <v>13.4879150390625</v>
       </c>
-      <c r="AG4" t="n">
+      <c r="AJ4" t="n">
         <v>13.343994140625</v>
       </c>
-      <c r="AH4" t="n">
+      <c r="AK4" t="n">
         <v>13.951904296875</v>
       </c>
-      <c r="AI4" t="inlineStr">
+      <c r="AL4" t="inlineStr">
         <is>
           <t>[{'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x64x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'count': 12, 'total_duration_us': np.float64(162.43200000000002), 'mean_duration_us': np.float64(13.536000000000001), 'median_duration_us': np.float64(13.488), 'std_dev_duration_us': np.float64(0.16983128883296716), 'min_duration_us': np.float64(13.344), 'max_duration_us': np.float64(13.952)}]</t>
         </is>
       </c>
-      <c r="AJ4" t="inlineStr">
+      <c r="AM4" t="inlineStr">
         <is>
           <t>[{'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x64x64_warpg...', 'stream': 7, 'mean_duration_us': np.float64(13.54)}]</t>
         </is>
       </c>
-      <c r="AK4" t="inlineStr">
+      <c r="AN4" t="inlineStr">
         <is>
           <t>{'M': 788, 'N': 768, 'K': 3072, 'bias': True, 'stride_A': (3072, 1), 'stride_B': (1, 3072), 'dtype_A_B': ('c10::BFloat16', 'c10::BFloat16'), 'B': 1}</t>
         </is>
       </c>
-      <c r="AL4" t="b">
+      <c r="AO4" t="b">
         <v>1</v>
       </c>
-      <c r="AM4" t="n">
+      <c r="AP4" t="n">
         <v>13.25636373961045</v>
       </c>
-      <c r="AN4" t="n">
+      <c r="AQ4" t="n">
         <v>59.42646395151095</v>
       </c>
     </row>
@@ -3164,124 +6066,139 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>thread 5617 (python3)</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>((4, 3, 224, 224), (768, 3, 16, 16), (768,), (), (), (), (), (), ())</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>('c10::BFloat16', 'c10::BFloat16', 'c10::BFloat16', 'ScalarList', 'ScalarList', 'ScalarList', 'Scalar', 'ScalarList', 'Scalar')</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>((150528, 50176, 224, 1), (768, 256, 16, 1), (1,), (), (), (), (), (), ())</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>('', '', '', '[16, 16]', '[0, 0]', '[1, 1]', 'False', '[0, 0]', '1')</t>
         </is>
       </c>
-      <c r="G5" t="n">
+      <c r="J5" t="n">
         <v>2</v>
       </c>
-      <c r="H5" t="n">
+      <c r="K5" t="n">
         <v>1</v>
       </c>
-      <c r="I5" t="n">
+      <c r="L5" t="n">
         <v>101.661</v>
       </c>
-      <c r="J5" t="n">
+      <c r="M5" t="n">
         <v>101.661</v>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="n">
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="n">
         <v>0.924844032</v>
       </c>
-      <c r="M5" t="n">
+      <c r="P5" t="n">
         <v>3.421875</v>
       </c>
-      <c r="N5" t="n">
+      <c r="Q5" t="n">
         <v>257.7534246575343</v>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>matrix_bf16</t>
         </is>
       </c>
-      <c r="P5" t="n">
+      <c r="S5" t="n">
         <v>0.02768590506403035</v>
       </c>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="n">
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="n">
         <v>7.136136844997193</v>
       </c>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="n">
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="n">
         <v>129.60009765625</v>
       </c>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="n">
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="n">
         <v>129.60009765625</v>
       </c>
-      <c r="W5" t="n">
+      <c r="Z5" t="n">
         <v>101.661</v>
       </c>
-      <c r="X5" t="n">
+      <c r="AA5" t="n">
         <v>101.661</v>
       </c>
-      <c r="Y5" t="n">
+      <c r="AB5" t="n">
         <v>101.661</v>
       </c>
-      <c r="Z5" t="n">
+      <c r="AC5" t="n">
         <v>0.02768590506403035</v>
       </c>
-      <c r="AA5" t="n">
+      <c r="AD5" t="n">
         <v>0.02768590506403035</v>
       </c>
-      <c r="AB5" t="n">
+      <c r="AE5" t="n">
         <v>0.02768590506403035</v>
       </c>
-      <c r="AC5" t="n">
+      <c r="AF5" t="n">
         <v>7.136136844997193</v>
       </c>
-      <c r="AD5" t="n">
+      <c r="AG5" t="n">
         <v>7.136136844997193</v>
       </c>
-      <c r="AE5" t="n">
+      <c r="AH5" t="n">
         <v>7.136136844997193</v>
       </c>
-      <c r="AF5" t="n">
+      <c r="AI5" t="n">
         <v>129.60009765625</v>
       </c>
-      <c r="AG5" t="n">
+      <c r="AJ5" t="n">
         <v>129.60009765625</v>
       </c>
-      <c r="AH5" t="n">
+      <c r="AK5" t="n">
         <v>129.60009765625</v>
       </c>
-      <c r="AI5" t="inlineStr">
+      <c r="AL5" t="inlineStr">
         <is>
           <t>[{'name': 'Memset (Device)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(2.272), 'mean_duration_us': np.float64(2.272), 'median_duration_us': np.float64(2.272), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(2.272), 'max_duration_us': np.float64(2.272)}, {'name': 'void cudnn::engines_precompiled::nchwToNhwcKernel&lt;__nv_bfloat16, __nv_bfloat16, float, false, true, (cudnnKernelDataType_t)0&gt;(cudnn::engines_precompiled::nchw2nhwc_params_t&lt;float&gt;, __nv_bfloat16 const*, __nv_bfloat16*)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(10.464), 'mean_duration_us': np.float64(10.464), 'median_duration_us': np.float64(10.464), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(10.464), 'max_duration_us': np.float64(10.464)}, {'name': 'Memset (Device)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(2.112), 'mean_duration_us': np.float64(2.112), 'median_duration_us': np.float64(2.112), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(2.112), 'max_duration_us': np.float64(2.112)}, {'name': 'void cudnn::engines_precompiled::nchwToNhwcKernel&lt;__nv_bfloat16, __nv_bfloat16, float, false, true, (cudnnKernelDataType_t)0&gt;(cudnn::engines_precompiled::nchw2nhwc_params_t&lt;float&gt;, __nv_bfloat16 const*, __nv_bfloat16*)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(10.4), 'mean_duration_us': np.float64(10.4), 'median_duration_us': np.float64(10.4), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(10.4), 'max_duration_us': np.float64(10.4)}, {'name': 'void cutlass__5x_cudnn::Kernel&lt;cutlass_tensorop_bf16_s16816fprop_optimized_bf16_256x64_32x4_nhwc_align8&gt;(cutlass_tensorop_bf16_s16816fprop_optimized_bf16_256x64_32x4_nhwc_align8::Params)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(98.176), 'mean_duration_us': np.float64(98.176), 'median_duration_us': np.float64(98.176), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(98.176), 'max_duration_us': np.float64(98.176)}, {'name': 'void cudnn::engines_precompiled::nhwcToNchwKernel&lt;__nv_bfloat16, __nv_bfloat16, float, true, false, (cudnnKernelDataType_t)0&gt;(cudnn::engines_precompiled::nhwc2nchw_params_t&lt;float&gt;, __nv_bfloat16 const*, __nv_bfloat16*)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(2.208), 'mean_duration_us': np.float64(2.208), 'median_duration_us': np.float64(2.208), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(2.208), 'max_duration_us': np.float64(2.208)}, {'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(3.968), 'mean_duration_us': np.float64(3.968), 'median_duration_us': np.float64(3.968), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(3.968), 'max_duration_us': np.float64(3.968)}]</t>
         </is>
       </c>
-      <c r="AJ5" t="inlineStr">
+      <c r="AM5" t="inlineStr">
         <is>
           <t>[{'name': 'Memset (Device)', 'stream': 7, 'mean_duration_us': np.float64(2.27)}, {'name': 'void cudnn::engines_precompiled::nchwToNhwcKernel&lt;__nv_bfloat16,...', 'stream': 7, 'mean_duration_us': np.float64(10.46)}, {'name': 'Memset (Device)', 'stream': 7, 'mean_duration_us': np.float64(2.11)}, {'name': 'void cudnn::engines_precompiled::nchwToNhwcKernel&lt;__nv_bfloat16,...', 'stream': 7, 'mean_duration_us': np.float64(10.4)}, {'name': 'void cutlass__5x_cudnn::Kernel&lt;cutlass_tensorop_bf16_s16816fprop...', 'stream': 7, 'mean_duration_us': np.float64(98.18)}, {'name': 'void cudnn::engines_precompiled::nhwcToNchwKernel&lt;__nv_bfloat16,...', 'stream': 7, 'mean_duration_us': np.float64(2.21)}, {'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(3.97)}]</t>
         </is>
       </c>
-      <c r="AK5" t="inlineStr">
+      <c r="AN5" t="inlineStr">
         <is>
           <t>{'convNd': 'conv2d', 'input_shape': (4, 3, 224, 224), 'filter_shape': (768, 3, 16, 16), 'dtype_input_weight': ('c10::BFloat16', 'c10::BFloat16'), 'input_stride': (150528, 50176, 224, 1), 'weight_stride': (768, 256, 16, 1), 'bias': False, 'stride': (16, 16), 'padding': (0, 0), 'dilation': (1, 1), 'transposed_conv': False, 'output_padding': (0, 0), 'groups': 1}</t>
         </is>
       </c>
-      <c r="AL5" t="b">
+      <c r="AO5" t="b">
         <v>1</v>
       </c>
-      <c r="AM5" t="n">
+      <c r="AP5" t="n">
         <v>10.57693323091974</v>
       </c>
-      <c r="AN5" t="n">
+      <c r="AQ5" t="n">
         <v>70.00339718243069</v>
       </c>
     </row>
@@ -3298,128 +6215,143 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>thread 5617 (python3)</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>((4, 12, 197, 64), (4, 12, 197, 64), (4, 12, 197, 64), (), (), (), ())</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>('c10::BFloat16', 'c10::BFloat16', 'c10::BFloat16', 'Scalar', 'Scalar', 'Scalar', 'Scalar')</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>((151296, 64, 768, 1), (151296, 64, 768, 1), (151296, 64, 768, 1), (), (), (), ())</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>('', '', '', '0.', 'False', 'False', '0.125')</t>
         </is>
       </c>
-      <c r="G6" t="n">
+      <c r="J6" t="n">
         <v>61</v>
       </c>
-      <c r="H6" t="n">
+      <c r="K6" t="n">
         <v>12</v>
       </c>
-      <c r="I6" t="n">
+      <c r="L6" t="n">
         <v>491.448</v>
       </c>
-      <c r="J6" t="n">
+      <c r="M6" t="n">
         <v>40.954</v>
       </c>
-      <c r="K6" t="n">
+      <c r="N6" t="n">
         <v>2.08990247706355</v>
       </c>
-      <c r="L6" t="n">
+      <c r="O6" t="n">
         <v>0.476884992</v>
       </c>
-      <c r="M6" t="n">
+      <c r="P6" t="n">
         <v>4.6171875</v>
       </c>
-      <c r="N6" t="n">
+      <c r="Q6" t="n">
         <v>98.5</v>
       </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="n">
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="n">
         <v>0.4731315968327939</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="T6" t="n">
         <v>0.01022134818763448</v>
       </c>
-      <c r="R6" t="n">
+      <c r="U6" t="n">
         <v>46.60346228803019</v>
       </c>
-      <c r="S6" t="n">
+      <c r="V6" t="n">
         <v>1.006802796481996</v>
       </c>
-      <c r="T6" t="n">
+      <c r="W6" t="n">
         <v>10.23734537760417</v>
       </c>
-      <c r="U6" t="n">
+      <c r="X6" t="n">
         <v>0.228442528412397</v>
       </c>
-      <c r="V6" t="n">
+      <c r="Y6" t="n">
         <v>122.84814453125</v>
       </c>
-      <c r="W6" t="n">
+      <c r="Z6" t="n">
         <v>40.6005</v>
       </c>
-      <c r="X6" t="n">
+      <c r="AA6" t="n">
         <v>39.25</v>
       </c>
-      <c r="Y6" t="n">
+      <c r="AB6" t="n">
         <v>47.251</v>
       </c>
-      <c r="Z6" t="n">
+      <c r="AC6" t="n">
         <v>0.4735411097882475</v>
       </c>
-      <c r="AA6" t="n">
+      <c r="AD6" t="n">
         <v>0.4463049830531362</v>
       </c>
-      <c r="AB6" t="n">
+      <c r="AE6" t="n">
         <v>0.4833683350070687</v>
       </c>
-      <c r="AC6" t="n">
+      <c r="AF6" t="n">
         <v>46.64379931414237</v>
       </c>
-      <c r="AD6" t="n">
+      <c r="AG6" t="n">
         <v>43.96104083073391</v>
       </c>
-      <c r="AE6" t="n">
+      <c r="AH6" t="n">
         <v>47.61178099819627</v>
       </c>
-      <c r="AF6" t="n">
+      <c r="AI6" t="n">
         <v>10.2239990234375</v>
       </c>
-      <c r="AG6" t="n">
+      <c r="AJ6" t="n">
         <v>10.01611328125</v>
       </c>
-      <c r="AH6" t="n">
+      <c r="AK6" t="n">
         <v>10.847900390625</v>
       </c>
-      <c r="AI6" t="inlineStr">
+      <c r="AL6" t="inlineStr">
         <is>
           <t>[{'name': 'void pytorch_flash::flash_fwd_kernel&lt;pytorch_flash::Flash_fwd_kernel_traits&lt;64, 128, 128, 4, false, false, cutlass::bfloat16_t, pytorch_flash::Flash_kernel_traits&lt;64, 128, 128, 4, cutlass::bfloat16_t&gt; &gt;, false, false, false, false, false, true, false&gt;(pytorch_flash::Flash_fwd_params)', 'stream': 7, 'count': 12, 'total_duration_us': np.float64(122.848), 'mean_duration_us': np.float64(10.237333333333334), 'median_duration_us': np.float64(10.224), 'std_dev_duration_us': np.float64(0.21878045819699932), 'min_duration_us': np.float64(10.016), 'max_duration_us': np.float64(10.848)}]</t>
         </is>
       </c>
-      <c r="AJ6" t="inlineStr">
+      <c r="AM6" t="inlineStr">
         <is>
           <t>[{'name': 'void pytorch_flash::flash_fwd_kernel&lt;pytorch_flash::Flash_fwd_ke...', 'stream': 7, 'mean_duration_us': np.float64(10.24)}]</t>
         </is>
       </c>
-      <c r="AK6" t="inlineStr">
+      <c r="AN6" t="inlineStr">
         <is>
           <t>{'B': 4, 'N_Q': 197, 'H_Q': 12, 'N_KV': 197, 'H_KV': 12, 'd_h_qk': 64, 'd_h_v': 64, 'dropout': 0.0, 'causal': False, 'flash_impl': True}</t>
         </is>
       </c>
-      <c r="AL6" t="b">
+      <c r="AO6" t="b">
         <v>1</v>
       </c>
-      <c r="AM6" t="n">
+      <c r="AP6" t="n">
         <v>10.02589230832071</v>
       </c>
-      <c r="AN6" t="n">
+      <c r="AQ6" t="n">
         <v>80.0292894907514</v>
       </c>
     </row>
@@ -3436,132 +6368,147 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>thread 5617 (python3)</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>((4, 197, 768), (), (768,), (768,), (), ())</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>('c10::BFloat16', 'ScalarList', 'c10::BFloat16', 'c10::BFloat16', 'Scalar', 'Scalar')</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>((151296, 768, 1), (), (1,), (1,), (), ())</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>('', '[768]', '', '', '9.9999999999999998e-13', 'True')</t>
         </is>
       </c>
-      <c r="G7" t="n">
+      <c r="J7" t="n">
         <v>17</v>
       </c>
-      <c r="H7" t="n">
+      <c r="K7" t="n">
         <v>25</v>
       </c>
-      <c r="I7" t="n">
+      <c r="L7" t="n">
         <v>616.799</v>
       </c>
-      <c r="J7" t="n">
+      <c r="M7" t="n">
         <v>24.67196</v>
       </c>
-      <c r="K7" t="n">
+      <c r="N7" t="n">
         <v>2.70387186086915</v>
       </c>
-      <c r="L7" t="n">
+      <c r="O7" t="n">
         <v>0.003030528</v>
       </c>
-      <c r="M7" t="n">
+      <c r="P7" t="n">
         <v>2.3173828125</v>
       </c>
-      <c r="N7" t="n">
+      <c r="Q7" t="n">
         <v>1.247155499367889</v>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>vector_bf16</t>
         </is>
       </c>
-      <c r="P7" t="n">
+      <c r="S7" t="n">
         <v>0.5466261436434106</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="T7" t="n">
         <v>0.0136524750083966</v>
       </c>
-      <c r="R7" t="n">
+      <c r="U7" t="n">
         <v>0.6817278011431411</v>
       </c>
-      <c r="S7" t="n">
+      <c r="V7" t="n">
         <v>0.01702675928670446</v>
       </c>
-      <c r="T7" t="n">
+      <c r="W7" t="n">
         <v>4.448037109375</v>
       </c>
-      <c r="U7" t="n">
+      <c r="X7" t="n">
         <v>0.1115342775722907</v>
       </c>
-      <c r="V7" t="n">
+      <c r="Y7" t="n">
         <v>111.200927734375</v>
       </c>
-      <c r="W7" t="n">
+      <c r="Z7" t="n">
         <v>23.71</v>
       </c>
-      <c r="X7" t="n">
+      <c r="AA7" t="n">
         <v>22.44</v>
       </c>
-      <c r="Y7" t="n">
+      <c r="AB7" t="n">
         <v>33.221</v>
       </c>
-      <c r="Z7" t="n">
+      <c r="AC7" t="n">
         <v>0.5463023981557714</v>
       </c>
-      <c r="AA7" t="n">
+      <c r="AD7" t="n">
         <v>0.5237086762430939</v>
       </c>
-      <c r="AB7" t="n">
+      <c r="AE7" t="n">
         <v>0.5709334820168646</v>
       </c>
-      <c r="AC7" t="n">
+      <c r="AF7" t="n">
         <v>0.6813240401778364</v>
       </c>
-      <c r="AD7" t="n">
+      <c r="AG7" t="n">
         <v>0.6531461556432518</v>
       </c>
-      <c r="AE7" t="n">
+      <c r="AH7" t="n">
         <v>0.7120428318705904</v>
       </c>
-      <c r="AF7" t="n">
+      <c r="AI7" t="n">
         <v>4.447998046875</v>
       </c>
-      <c r="AG7" t="n">
+      <c r="AJ7" t="n">
         <v>4.256103515625</v>
       </c>
-      <c r="AH7" t="n">
+      <c r="AK7" t="n">
         <v>4.639892578125</v>
       </c>
-      <c r="AI7" t="inlineStr">
+      <c r="AL7" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 7, 'count': 25, 'total_duration_us': np.float64(111.20100000000001), 'mean_duration_us': np.float64(4.448040000000001), 'median_duration_us': np.float64(4.448), 'std_dev_duration_us': np.float64(0.10934037863479323), 'min_duration_us': np.float64(4.256), 'max_duration_us': np.float64(4.64)}]</t>
         </is>
       </c>
-      <c r="AJ7" t="inlineStr">
+      <c r="AM7" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_ke...', 'stream': 7, 'mean_duration_us': np.float64(4.45)}]</t>
         </is>
       </c>
-      <c r="AK7" t="inlineStr">
+      <c r="AN7" t="inlineStr">
         <is>
           <t>{'op_shape': (4, 197, 768), 'dtype_in_out': ('c10::BFloat16', None), 'stride_input': (151296, 768, 1), 'stride_output': None, 'num_channels': 768, 'has_bias': True, 'is_affine': True, 'is_training': True}</t>
         </is>
       </c>
-      <c r="AL7" t="b">
+      <c r="AO7" t="b">
         <v>1</v>
       </c>
-      <c r="AM7" t="n">
+      <c r="AP7" t="n">
         <v>9.075338746907917</v>
       </c>
-      <c r="AN7" t="n">
+      <c r="AQ7" t="n">
         <v>89.10462823765931</v>
       </c>
     </row>
@@ -3578,98 +6525,113 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>thread 5617 (python3)</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>((4, 197, 3072), ())</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>('c10::BFloat16', '')</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>((605184, 3072, 1), ())</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>('', '')</t>
         </is>
       </c>
-      <c r="G8" t="n">
+      <c r="J8" t="n">
         <v>107</v>
       </c>
-      <c r="H8" t="n">
+      <c r="K8" t="n">
         <v>12</v>
       </c>
-      <c r="I8" t="n">
+      <c r="L8" t="n">
         <v>153.193</v>
       </c>
-      <c r="J8" t="n">
+      <c r="M8" t="n">
         <v>12.76608333333333</v>
       </c>
-      <c r="K8" t="n">
+      <c r="N8" t="n">
         <v>2.932567892985548</v>
       </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr"/>
-      <c r="T8" t="n">
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="n">
         <v>5.04510498046875</v>
       </c>
-      <c r="U8" t="n">
+      <c r="X8" t="n">
         <v>0.03943788318148379</v>
       </c>
-      <c r="V8" t="n">
+      <c r="Y8" t="n">
         <v>60.541259765625</v>
       </c>
-      <c r="W8" t="n">
+      <c r="Z8" t="n">
         <v>11.9605</v>
       </c>
-      <c r="X8" t="n">
+      <c r="AA8" t="n">
         <v>11.42</v>
       </c>
-      <c r="Y8" t="n">
+      <c r="AB8" t="n">
         <v>22.04</v>
       </c>
-      <c r="Z8" t="inlineStr"/>
-      <c r="AA8" t="inlineStr"/>
-      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="inlineStr"/>
-      <c r="AF8" t="n">
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr"/>
+      <c r="AI8" t="n">
         <v>5.055419921875</v>
       </c>
-      <c r="AG8" t="n">
+      <c r="AJ8" t="n">
         <v>4.990966796875</v>
       </c>
-      <c r="AH8" t="n">
+      <c r="AK8" t="n">
         <v>5.1201171875</v>
       </c>
-      <c r="AI8" t="inlineStr">
+      <c r="AL8" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::GeluCUDAKernelImpl(at::TensorIteratorBase&amp;, at::native::GeluType)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::GeluCUDAKernelImpl(at::TensorIteratorBase&amp;, at::native::GeluType)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 12, 'total_duration_us': np.float64(60.541999999999994), 'mean_duration_us': np.float64(5.045166666666666), 'median_duration_us': np.float64(5.0555), 'std_dev_duration_us': np.float64(0.037739972914080884), 'min_duration_us': np.float64(4.991), 'max_duration_us': np.float64(5.12)}]</t>
         </is>
       </c>
-      <c r="AJ8" t="inlineStr">
+      <c r="AM8" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::Ge...', 'stream': 7, 'mean_duration_us': np.float64(5.05)}]</t>
         </is>
       </c>
-      <c r="AK8" t="inlineStr"/>
-      <c r="AL8" t="b">
+      <c r="AN8" t="inlineStr"/>
+      <c r="AO8" t="b">
         <v>0</v>
       </c>
-      <c r="AM8" t="n">
+      <c r="AP8" t="n">
         <v>4.940897991876649</v>
       </c>
-      <c r="AN8" t="n">
+      <c r="AQ8" t="n">
         <v>94.04552622953597</v>
       </c>
     </row>
@@ -3686,132 +6648,147 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>thread 5617 (python3)</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t>((4, 197, 768), (4, 197, 768), ())</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>('c10::BFloat16', 'c10::BFloat16', 'Scalar')</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>((151296, 768, 1), (151296, 768, 1), ())</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>('', '', '1')</t>
         </is>
       </c>
-      <c r="G9" t="n">
+      <c r="J9" t="n">
         <v>90</v>
       </c>
-      <c r="H9" t="n">
+      <c r="K9" t="n">
         <v>24</v>
       </c>
-      <c r="I9" t="n">
+      <c r="L9" t="n">
         <v>298.853</v>
       </c>
-      <c r="J9" t="n">
+      <c r="M9" t="n">
         <v>12.45220833333333</v>
       </c>
-      <c r="K9" t="n">
+      <c r="N9" t="n">
         <v>0.4364494073142128</v>
       </c>
-      <c r="L9" t="n">
+      <c r="O9" t="n">
         <v>0.000605184</v>
       </c>
-      <c r="M9" t="n">
+      <c r="P9" t="n">
         <v>3.462890625</v>
       </c>
-      <c r="N9" t="n">
+      <c r="Q9" t="n">
         <v>0.1666666666666667</v>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>vector_bf16</t>
         </is>
       </c>
-      <c r="P9" t="n">
+      <c r="S9" t="n">
         <v>1.628184728894159</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="T9" t="n">
         <v>0.02497608869878607</v>
       </c>
-      <c r="R9" t="n">
+      <c r="U9" t="n">
         <v>0.2713641214823599</v>
       </c>
-      <c r="S9" t="n">
+      <c r="V9" t="n">
         <v>0.00416268144979767</v>
       </c>
-      <c r="T9" t="n">
+      <c r="W9" t="n">
         <v>2.230662027994792</v>
       </c>
-      <c r="U9" t="n">
+      <c r="X9" t="n">
         <v>0.03450867810431143</v>
       </c>
-      <c r="V9" t="n">
+      <c r="Y9" t="n">
         <v>53.535888671875</v>
       </c>
-      <c r="W9" t="n">
+      <c r="Z9" t="n">
         <v>12.405</v>
       </c>
-      <c r="X9" t="n">
+      <c r="AA9" t="n">
         <v>11.76</v>
       </c>
-      <c r="Y9" t="n">
+      <c r="AB9" t="n">
         <v>13.47</v>
       </c>
-      <c r="Z9" t="n">
+      <c r="AC9" t="n">
         <v>1.632412270219935</v>
       </c>
-      <c r="AA9" t="n">
+      <c r="AD9" t="n">
         <v>1.576030728409452</v>
       </c>
-      <c r="AB9" t="n">
+      <c r="AE9" t="n">
         <v>1.668686411309323</v>
       </c>
-      <c r="AC9" t="n">
+      <c r="AF9" t="n">
         <v>0.2720687117033225</v>
       </c>
-      <c r="AD9" t="n">
+      <c r="AG9" t="n">
         <v>0.262671788068242</v>
       </c>
-      <c r="AE9" t="n">
+      <c r="AH9" t="n">
         <v>0.2781144018848872</v>
       </c>
-      <c r="AF9" t="n">
+      <c r="AI9" t="n">
         <v>2.2244873046875</v>
       </c>
-      <c r="AG9" t="n">
+      <c r="AJ9" t="n">
         <v>2.176025390625</v>
       </c>
-      <c r="AH9" t="n">
+      <c r="AK9" t="n">
         <v>2.303955078125</v>
       </c>
-      <c r="AI9" t="inlineStr">
+      <c r="AL9" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 7, 'count': 24, 'total_duration_us': np.float64(53.536), 'mean_duration_us': np.float64(2.2306666666666666), 'median_duration_us': np.float64(2.2245), 'std_dev_duration_us': np.float64(0.033798011118341686), 'min_duration_us': np.float64(2.176), 'max_duration_us': np.float64(2.304)}]</t>
         </is>
       </c>
-      <c r="AJ9" t="inlineStr">
+      <c r="AM9" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CU...', 'stream': 7, 'mean_duration_us': np.float64(2.23)}]</t>
         </is>
       </c>
-      <c r="AK9" t="inlineStr">
+      <c r="AN9" t="inlineStr">
         <is>
           <t>{'shape_in1': (4, 197, 768), 'shape_in2': (4, 197, 768), 'dtype_in1_in2_out': ('c10::BFloat16', 'c10::BFloat16', None), 'stride_input1': (151296, 768, 1), 'stride_input2': (151296, 768, 1), 'stride_output': None}</t>
         </is>
       </c>
-      <c r="AL9" t="b">
+      <c r="AO9" t="b">
         <v>1</v>
       </c>
-      <c r="AM9" t="n">
+      <c r="AP9" t="n">
         <v>4.369175102338875</v>
       </c>
-      <c r="AN9" t="n">
+      <c r="AQ9" t="n">
         <v>98.41470133187484</v>
       </c>
     </row>
@@ -3828,94 +6805,109 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>thread 5617 (python3)</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t>(((4, 1, 768), (4, 196, 768)), ())</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>('TensorList', 'Scalar')</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>(((0, 768, 1), (150528, 1, 196)), ())</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>('', '1')</t>
         </is>
       </c>
-      <c r="G10" t="n">
+      <c r="J10" t="n">
         <v>14</v>
       </c>
-      <c r="H10" t="n">
+      <c r="K10" t="n">
         <v>1</v>
       </c>
-      <c r="I10" t="n">
+      <c r="L10" t="n">
         <v>16.66</v>
       </c>
-      <c r="J10" t="n">
+      <c r="M10" t="n">
         <v>16.66</v>
       </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr"/>
-      <c r="T10" t="n">
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="n">
         <v>7.263916015625</v>
       </c>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="n">
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="n">
         <v>7.263916015625</v>
       </c>
-      <c r="W10" t="n">
+      <c r="Z10" t="n">
         <v>16.66</v>
       </c>
-      <c r="X10" t="n">
+      <c r="AA10" t="n">
         <v>16.66</v>
       </c>
-      <c r="Y10" t="n">
+      <c r="AB10" t="n">
         <v>16.66</v>
       </c>
-      <c r="Z10" t="inlineStr"/>
-      <c r="AA10" t="inlineStr"/>
-      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="inlineStr"/>
-      <c r="AF10" t="n">
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr"/>
+      <c r="AI10" t="n">
         <v>7.263916015625</v>
       </c>
-      <c r="AG10" t="n">
+      <c r="AJ10" t="n">
         <v>7.263916015625</v>
       </c>
-      <c r="AH10" t="n">
+      <c r="AK10" t="n">
         <v>7.263916015625</v>
       </c>
-      <c r="AI10" t="inlineStr">
+      <c r="AL10" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::(anonymous namespace)::CatArrayBatchedCopy&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 3, 64, 64&gt;(at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;*, at::native::(anonymous namespace)::CatArrInputTensorMetadata&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 64, 64&gt;, at::native::(anonymous namespace)::TensorSizeStride&lt;unsigned int, 4u&gt;, int, unsigned int)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(7.264), 'mean_duration_us': np.float64(7.264), 'median_duration_us': np.float64(7.264), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(7.264), 'max_duration_us': np.float64(7.264)}]</t>
         </is>
       </c>
-      <c r="AJ10" t="inlineStr">
+      <c r="AM10" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::(anonymous namespace)::CatArrayBatchedCopy&lt;at::...', 'stream': 7, 'mean_duration_us': np.float64(7.26)}]</t>
         </is>
       </c>
-      <c r="AK10" t="inlineStr"/>
-      <c r="AL10" t="b">
+      <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="b">
         <v>0</v>
       </c>
-      <c r="AM10" t="n">
+      <c r="AP10" t="n">
         <v>0.5928232777729626</v>
       </c>
-      <c r="AN10" t="n">
+      <c r="AQ10" t="n">
         <v>99.0075246096478</v>
       </c>
     </row>
@@ -3932,124 +6924,139 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>thread 5617 (python3)</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t>((768,), (4, 768), (768, 768), (), ())</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>('c10::BFloat16', 'c10::BFloat16', 'c10::BFloat16', 'Scalar', 'Scalar')</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>((1,), (151296, 1), (1, 768), (), ())</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>('', '', '', '1', '1')</t>
         </is>
       </c>
-      <c r="G11" t="n">
+      <c r="J11" t="n">
         <v>1256</v>
       </c>
-      <c r="H11" t="n">
+      <c r="K11" t="n">
         <v>1</v>
       </c>
-      <c r="I11" t="n">
+      <c r="L11" t="n">
         <v>31.331</v>
       </c>
-      <c r="J11" t="n">
+      <c r="M11" t="n">
         <v>31.331</v>
       </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="n">
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="n">
         <v>0.004721664</v>
       </c>
-      <c r="M11" t="n">
+      <c r="P11" t="n">
         <v>1.13818359375</v>
       </c>
-      <c r="N11" t="n">
+      <c r="Q11" t="n">
         <v>3.956241956241956</v>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>matrix_bf16</t>
         </is>
       </c>
-      <c r="P11" t="n">
+      <c r="S11" t="n">
         <v>0.1734973492333901</v>
       </c>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="n">
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="n">
         <v>0.6863974923339013</v>
       </c>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="n">
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="n">
         <v>6.87890625</v>
       </c>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="n">
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="n">
         <v>6.87890625</v>
       </c>
-      <c r="W11" t="n">
+      <c r="Z11" t="n">
         <v>31.331</v>
       </c>
-      <c r="X11" t="n">
+      <c r="AA11" t="n">
         <v>31.331</v>
       </c>
-      <c r="Y11" t="n">
+      <c r="AB11" t="n">
         <v>31.331</v>
       </c>
-      <c r="Z11" t="n">
+      <c r="AC11" t="n">
         <v>0.1734973492333901</v>
       </c>
-      <c r="AA11" t="n">
+      <c r="AD11" t="n">
         <v>0.1734973492333901</v>
       </c>
-      <c r="AB11" t="n">
+      <c r="AE11" t="n">
         <v>0.1734973492333901</v>
       </c>
-      <c r="AC11" t="n">
+      <c r="AF11" t="n">
         <v>0.6863974923339013</v>
       </c>
-      <c r="AD11" t="n">
+      <c r="AG11" t="n">
         <v>0.6863974923339013</v>
       </c>
-      <c r="AE11" t="n">
+      <c r="AH11" t="n">
         <v>0.6863974923339013</v>
       </c>
-      <c r="AF11" t="n">
+      <c r="AI11" t="n">
         <v>6.87890625</v>
       </c>
-      <c r="AG11" t="n">
+      <c r="AJ11" t="n">
         <v>6.87890625</v>
       </c>
-      <c r="AH11" t="n">
+      <c r="AK11" t="n">
         <v>6.87890625</v>
       </c>
-      <c r="AI11" t="inlineStr">
+      <c r="AL11" t="inlineStr">
         <is>
           <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_64x64_64x6_tn_align8&gt;(cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_64x64_64x6_tn_align8::Params)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(6.879), 'mean_duration_us': np.float64(6.879), 'median_duration_us': np.float64(6.879), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(6.879), 'max_duration_us': np.float64(6.879)}]</t>
         </is>
       </c>
-      <c r="AJ11" t="inlineStr">
+      <c r="AM11" t="inlineStr">
         <is>
           <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_80_tensorop_bf16_s16816gemm_relu_b...', 'stream': 7, 'mean_duration_us': np.float64(6.88)}]</t>
         </is>
       </c>
-      <c r="AK11" t="inlineStr">
+      <c r="AN11" t="inlineStr">
         <is>
           <t>{'M': 4, 'N': 768, 'K': 768, 'bias': True, 'stride_A': (151296, 1), 'stride_B': (1, 768), 'dtype_A_B': ('c10::BFloat16', 'c10::BFloat16'), 'B': 1}</t>
         </is>
       </c>
-      <c r="AL11" t="b">
+      <c r="AO11" t="b">
         <v>1</v>
       </c>
-      <c r="AM11" t="n">
+      <c r="AP11" t="n">
         <v>0.5614018308920443</v>
       </c>
-      <c r="AN11" t="n">
+      <c r="AQ11" t="n">
         <v>99.56892644053984</v>
       </c>
     </row>
@@ -4066,124 +7073,139 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>thread 5617 (python3)</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t>((4, 197, 768), (1, 197, 768), ())</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>('c10::BFloat16', 'c10::BFloat16', 'Scalar')</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>((151296, 768, 1), (151296, 768, 1), ())</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>('', '', '1')</t>
         </is>
       </c>
-      <c r="G12" t="n">
+      <c r="J12" t="n">
         <v>15</v>
       </c>
-      <c r="H12" t="n">
+      <c r="K12" t="n">
         <v>1</v>
       </c>
-      <c r="I12" t="n">
+      <c r="L12" t="n">
         <v>10.421</v>
       </c>
-      <c r="J12" t="n">
+      <c r="M12" t="n">
         <v>10.421</v>
       </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="n">
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="n">
         <v>0.000605184</v>
       </c>
-      <c r="M12" t="n">
+      <c r="P12" t="n">
         <v>2.59716796875</v>
       </c>
-      <c r="N12" t="n">
+      <c r="Q12" t="n">
         <v>0.2222222222222222</v>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>vector_bf16</t>
         </is>
       </c>
-      <c r="P12" t="n">
+      <c r="S12" t="n">
         <v>0.7210103734729494</v>
       </c>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="n">
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="n">
         <v>0.1602245274384332</v>
       </c>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="n">
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="n">
         <v>3.777099609375</v>
       </c>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="n">
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="n">
         <v>3.777099609375</v>
       </c>
-      <c r="W12" t="n">
+      <c r="Z12" t="n">
         <v>10.421</v>
       </c>
-      <c r="X12" t="n">
+      <c r="AA12" t="n">
         <v>10.421</v>
       </c>
-      <c r="Y12" t="n">
+      <c r="AB12" t="n">
         <v>10.421</v>
       </c>
-      <c r="Z12" t="n">
+      <c r="AC12" t="n">
         <v>0.7210103734729494</v>
       </c>
-      <c r="AA12" t="n">
+      <c r="AD12" t="n">
         <v>0.7210103734729494</v>
       </c>
-      <c r="AB12" t="n">
+      <c r="AE12" t="n">
         <v>0.7210103734729494</v>
       </c>
-      <c r="AC12" t="n">
+      <c r="AF12" t="n">
         <v>0.1602245274384332</v>
       </c>
-      <c r="AD12" t="n">
+      <c r="AG12" t="n">
         <v>0.1602245274384332</v>
       </c>
-      <c r="AE12" t="n">
+      <c r="AH12" t="n">
         <v>0.1602245274384332</v>
       </c>
-      <c r="AF12" t="n">
+      <c r="AI12" t="n">
         <v>3.777099609375</v>
       </c>
-      <c r="AG12" t="n">
+      <c r="AJ12" t="n">
         <v>3.777099609375</v>
       </c>
-      <c r="AH12" t="n">
+      <c r="AK12" t="n">
         <v>3.777099609375</v>
       </c>
-      <c r="AI12" t="inlineStr">
+      <c r="AL12" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(3.777), 'mean_duration_us': np.float64(3.777), 'median_duration_us': np.float64(3.777), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(3.777), 'max_duration_us': np.float64(3.777)}]</t>
         </is>
       </c>
-      <c r="AJ12" t="inlineStr">
+      <c r="AM12" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(3.78)}]</t>
         </is>
       </c>
-      <c r="AK12" t="inlineStr">
+      <c r="AN12" t="inlineStr">
         <is>
           <t>{'shape_in1': (4, 197, 768), 'shape_in2': (1, 197, 768), 'dtype_in1_in2_out': ('c10::BFloat16', 'c10::BFloat16', None), 'stride_input1': (151296, 768, 1), 'stride_input2': (151296, 768, 1), 'stride_output': None}</t>
         </is>
       </c>
-      <c r="AL12" t="b">
+      <c r="AO12" t="b">
         <v>1</v>
       </c>
-      <c r="AM12" t="n">
+      <c r="AP12" t="n">
         <v>0.3082569465407019</v>
       </c>
-      <c r="AN12" t="n">
+      <c r="AQ12" t="n">
         <v>99.87718338708055</v>
       </c>
     </row>
@@ -4200,94 +7222,109 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>thread 5617 (python3)</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t>((4, 768),)</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>('c10::BFloat16',)</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>((768, 1),)</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>('',)</t>
         </is>
       </c>
-      <c r="G13" t="n">
+      <c r="J13" t="n">
         <v>1258</v>
       </c>
-      <c r="H13" t="n">
+      <c r="K13" t="n">
         <v>1</v>
       </c>
-      <c r="I13" t="n">
+      <c r="L13" t="n">
         <v>12.47</v>
       </c>
-      <c r="J13" t="n">
+      <c r="M13" t="n">
         <v>12.47</v>
       </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr"/>
-      <c r="T13" t="n">
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="n">
         <v>1.5048828125</v>
       </c>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="n">
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="n">
         <v>1.5048828125</v>
       </c>
-      <c r="W13" t="n">
+      <c r="Z13" t="n">
         <v>12.47</v>
       </c>
-      <c r="X13" t="n">
+      <c r="AA13" t="n">
         <v>12.47</v>
       </c>
-      <c r="Y13" t="n">
+      <c r="AB13" t="n">
         <v>12.47</v>
       </c>
-      <c r="Z13" t="inlineStr"/>
-      <c r="AA13" t="inlineStr"/>
-      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="inlineStr"/>
-      <c r="AF13" t="n">
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="inlineStr"/>
+      <c r="AH13" t="inlineStr"/>
+      <c r="AI13" t="n">
         <v>1.5048828125</v>
       </c>
-      <c r="AG13" t="n">
+      <c r="AJ13" t="n">
         <v>1.5048828125</v>
       </c>
-      <c r="AH13" t="n">
+      <c r="AK13" t="n">
         <v>1.5048828125</v>
       </c>
-      <c r="AI13" t="inlineStr">
+      <c r="AL13" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::tanh_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::tanh_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(1.505), 'mean_duration_us': np.float64(1.505), 'median_duration_us': np.float64(1.505), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(1.505), 'max_duration_us': np.float64(1.505)}]</t>
         </is>
       </c>
-      <c r="AJ13" t="inlineStr">
+      <c r="AM13" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::ta...', 'stream': 7, 'mean_duration_us': np.float64(1.5)}]</t>
         </is>
       </c>
-      <c r="AK13" t="inlineStr"/>
-      <c r="AL13" t="b">
+      <c r="AN13" t="inlineStr"/>
+      <c r="AO13" t="b">
         <v>0</v>
       </c>
-      <c r="AM13" t="n">
+      <c r="AP13" t="n">
         <v>0.1228166129194549</v>
       </c>
-      <c r="AN13" t="n">
+      <c r="AQ13" t="n">
         <v>100</v>
       </c>
     </row>
@@ -4302,7 +7339,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK5"/>
+  <dimension ref="A1:AN5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4418,75 +7455,90 @@
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
+          <t>process_name_first</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>process_label_first</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>thread_name_first</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
           <t>Compute Spec</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>kernel_details__summarize_kernel_stats</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>trunc_kernel_details</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Input Dims_first</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Input type_first</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Input Strides_first</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>Concrete Inputs_first</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_mean</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_median</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_std</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_min</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_max</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_sum</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>name_count</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>UID_first</t>
         </is>
@@ -4579,61 +7631,76 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>thread 5617 (python3)</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>matrix_bf16</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_128x64_64x6_tn_align8&gt;(cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_128x64_64x6_tn_align8::Params)', 'stream': 7, 'count': 48, 'total_duration_us': np.float64(399.136), 'mean_duration_us': np.float64(8.315333333333333), 'median_duration_us': np.float64(8.256), 'std_dev_duration_us': np.float64(0.13305517861231703), 'min_duration_us': np.float64(8.128), 'max_duration_us': np.float64(8.64)}]</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_80_tensorop_bf16_s16816gemm_relu_b...', 'stream': 7, 'mean_duration_us': np.float64(8.32)}]</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>[[768], [788, 768], [768, 768], [], []]</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>['c10::BFloat16', 'c10::BFloat16', 'c10::BFloat16', 'Scalar', 'Scalar']</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>[[1], [768, 1], [1, 768], [], []]</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>['', '', '', '1', '1']</t>
         </is>
       </c>
-      <c r="AD2" t="n">
+      <c r="AG2" t="n">
         <v>8.315348307291666</v>
       </c>
-      <c r="AE2" t="n">
+      <c r="AH2" t="n">
         <v>8.256103515625</v>
       </c>
-      <c r="AF2" t="n">
+      <c r="AI2" t="n">
         <v>0.1344482499064346</v>
       </c>
-      <c r="AG2" t="n">
+      <c r="AJ2" t="n">
         <v>8.1279296875</v>
       </c>
-      <c r="AH2" t="n">
+      <c r="AK2" t="n">
         <v>8.639892578125</v>
       </c>
-      <c r="AI2" t="n">
+      <c r="AL2" t="n">
         <v>399.13671875</v>
       </c>
-      <c r="AJ2" t="n">
+      <c r="AM2" t="n">
         <v>48</v>
       </c>
-      <c r="AK2" t="n">
+      <c r="AN2" t="n">
         <v>30</v>
       </c>
     </row>
@@ -4724,61 +7791,76 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>thread 5617 (python3)</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>matrix_bf16</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>[{'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'count': 12, 'total_duration_us': np.float64(166.59), 'mean_duration_us': np.float64(13.8825), 'median_duration_us': np.float64(13.8875), 'std_dev_duration_us': np.float64(0.10183278777813505), 'min_duration_us': np.float64(13.76), 'max_duration_us': np.float64(14.176)}]</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>[{'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warp...', 'stream': 7, 'mean_duration_us': np.float64(13.88)}]</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>[[3072], [788, 768], [768, 3072], [], []]</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>['c10::BFloat16', 'c10::BFloat16', 'c10::BFloat16', 'Scalar', 'Scalar']</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>[[1], [768, 1], [1, 768], [], []]</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
         <is>
           <t>['', '', '', '1', '1']</t>
         </is>
       </c>
-      <c r="AD3" t="n">
+      <c r="AG3" t="n">
         <v>13.88246663411458</v>
       </c>
-      <c r="AE3" t="n">
+      <c r="AH3" t="n">
         <v>13.887451171875</v>
       </c>
-      <c r="AF3" t="n">
+      <c r="AI3" t="n">
         <v>0.1063651301764554</v>
       </c>
-      <c r="AG3" t="n">
+      <c r="AJ3" t="n">
         <v>13.760009765625</v>
       </c>
-      <c r="AH3" t="n">
+      <c r="AK3" t="n">
         <v>14.176025390625</v>
       </c>
-      <c r="AI3" t="n">
+      <c r="AL3" t="n">
         <v>166.589599609375</v>
       </c>
-      <c r="AJ3" t="n">
+      <c r="AM3" t="n">
         <v>12</v>
       </c>
-      <c r="AK3" t="n">
+      <c r="AN3" t="n">
         <v>104</v>
       </c>
     </row>
@@ -4869,61 +7951,76 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>thread 5617 (python3)</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>matrix_bf16</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>[{'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x64x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'count': 12, 'total_duration_us': np.float64(162.43200000000002), 'mean_duration_us': np.float64(13.536000000000001), 'median_duration_us': np.float64(13.488), 'std_dev_duration_us': np.float64(0.16983128883296716), 'min_duration_us': np.float64(13.344), 'max_duration_us': np.float64(13.952)}]</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>[{'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x64x64_warpg...', 'stream': 7, 'mean_duration_us': np.float64(13.54)}]</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>[[768], [788, 3072], [3072, 768], [], []]</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>['c10::BFloat16', 'c10::BFloat16', 'c10::BFloat16', 'Scalar', 'Scalar']</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>[[1], [3072, 1], [1, 3072], [], []]</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
         <is>
           <t>['', '', '', '1', '1']</t>
         </is>
       </c>
-      <c r="AD4" t="n">
+      <c r="AG4" t="n">
         <v>13.53594970703125</v>
       </c>
-      <c r="AE4" t="n">
+      <c r="AH4" t="n">
         <v>13.4879150390625</v>
       </c>
-      <c r="AF4" t="n">
+      <c r="AI4" t="n">
         <v>0.1773776572326171</v>
       </c>
-      <c r="AG4" t="n">
+      <c r="AJ4" t="n">
         <v>13.343994140625</v>
       </c>
-      <c r="AH4" t="n">
+      <c r="AK4" t="n">
         <v>13.951904296875</v>
       </c>
-      <c r="AI4" t="n">
+      <c r="AL4" t="n">
         <v>162.431396484375</v>
       </c>
-      <c r="AJ4" t="n">
+      <c r="AM4" t="n">
         <v>12</v>
       </c>
-      <c r="AK4" t="n">
+      <c r="AN4" t="n">
         <v>114</v>
       </c>
     </row>
@@ -5010,59 +8107,74 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>thread 5617 (python3)</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>matrix_bf16</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_64x64_64x6_tn_align8&gt;(cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_64x64_64x6_tn_align8::Params)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(6.879), 'mean_duration_us': np.float64(6.879), 'median_duration_us': np.float64(6.879), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(6.879), 'max_duration_us': np.float64(6.879)}]</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_80_tensorop_bf16_s16816gemm_relu_b...', 'stream': 7, 'mean_duration_us': np.float64(6.88)}]</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>[[768], [4, 768], [768, 768], [], []]</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>['c10::BFloat16', 'c10::BFloat16', 'c10::BFloat16', 'Scalar', 'Scalar']</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>[[1], [151296, 1], [1, 768], [], []]</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
         <is>
           <t>['', '', '', '1', '1']</t>
         </is>
       </c>
-      <c r="AD5" t="n">
-        <v>6.87890625</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>6.87890625</v>
-      </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="n">
         <v>6.87890625</v>
       </c>
       <c r="AH5" t="n">
         <v>6.87890625</v>
       </c>
-      <c r="AI5" t="n">
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="n">
         <v>6.87890625</v>
       </c>
-      <c r="AJ5" t="n">
+      <c r="AK5" t="n">
+        <v>6.87890625</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>6.87890625</v>
+      </c>
+      <c r="AM5" t="n">
         <v>1</v>
       </c>
-      <c r="AK5" t="n">
+      <c r="AN5" t="n">
         <v>1256</v>
       </c>
     </row>
@@ -5077,7 +8189,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM2"/>
+  <dimension ref="A1:AP2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5203,75 +8315,90 @@
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
+          <t>process_name_first</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>process_label_first</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>thread_name_first</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
           <t>Compute Spec</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>kernel_details__summarize_kernel_stats</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>trunc_kernel_details</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Input Dims_first</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>Input type_first</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>Input Strides_first</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>Concrete Inputs_first</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_mean</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_median</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_std</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_min</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_max</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_sum</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>name_count</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>UID_first</t>
         </is>
@@ -5372,59 +8499,74 @@
       <c r="X2" t="n">
         <v>47.61178099819627</v>
       </c>
-      <c r="Y2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>python3</t>
+        </is>
+      </c>
       <c r="Z2" t="inlineStr">
         <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>thread 5617 (python3)</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr">
+        <is>
           <t>[{'name': 'void pytorch_flash::flash_fwd_kernel&lt;pytorch_flash::Flash_fwd_kernel_traits&lt;64, 128, 128, 4, false, false, cutlass::bfloat16_t, pytorch_flash::Flash_kernel_traits&lt;64, 128, 128, 4, cutlass::bfloat16_t&gt; &gt;, false, false, false, false, false, true, false&gt;(pytorch_flash::Flash_fwd_params)', 'stream': 7, 'count': 12, 'total_duration_us': np.float64(122.848), 'mean_duration_us': np.float64(10.237333333333334), 'median_duration_us': np.float64(10.224), 'std_dev_duration_us': np.float64(0.21878045819699932), 'min_duration_us': np.float64(10.016), 'max_duration_us': np.float64(10.848)}]</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>[{'name': 'void pytorch_flash::flash_fwd_kernel&lt;pytorch_flash::Flash_fwd_ke...', 'stream': 7, 'mean_duration_us': np.float64(10.24)}]</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>[[4, 12, 197, 64], [4, 12, 197, 64], [4, 12, 197, 64], [], [], [], []]</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>['c10::BFloat16', 'c10::BFloat16', 'c10::BFloat16', 'Scalar', 'Scalar', 'Scalar', 'Scalar']</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>[[151296, 64, 768, 1], [151296, 64, 768, 1], [151296, 64, 768, 1], [], [], [], []]</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
         <is>
           <t>['', '', '', '0.', 'False', 'False', '0.125']</t>
         </is>
       </c>
-      <c r="AF2" t="n">
+      <c r="AI2" t="n">
         <v>10.23734537760417</v>
       </c>
-      <c r="AG2" t="n">
+      <c r="AJ2" t="n">
         <v>10.2239990234375</v>
       </c>
-      <c r="AH2" t="n">
+      <c r="AK2" t="n">
         <v>0.228442528412397</v>
       </c>
-      <c r="AI2" t="n">
+      <c r="AL2" t="n">
         <v>10.01611328125</v>
       </c>
-      <c r="AJ2" t="n">
+      <c r="AM2" t="n">
         <v>10.847900390625</v>
       </c>
-      <c r="AK2" t="n">
+      <c r="AN2" t="n">
         <v>122.84814453125</v>
       </c>
-      <c r="AL2" t="n">
+      <c r="AO2" t="n">
         <v>12</v>
       </c>
-      <c r="AM2" t="n">
+      <c r="AP2" t="n">
         <v>61</v>
       </c>
     </row>
@@ -5439,7 +8581,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP2"/>
+  <dimension ref="A1:AS2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5580,75 +8722,90 @@
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
+          <t>process_name_first</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>process_label_first</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>thread_name_first</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
           <t>Compute Spec</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>kernel_details__summarize_kernel_stats</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>trunc_kernel_details</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>Input Dims_first</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>Input type_first</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>Input Strides_first</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>Concrete Inputs_first</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_mean</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_median</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_std</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_min</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_max</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_sum</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>name_count</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>UID_first</t>
         </is>
@@ -5762,59 +8919,74 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>thread 5617 (python3)</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
           <t>matrix_bf16</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>[{'name': 'Memset (Device)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(2.272), 'mean_duration_us': np.float64(2.272), 'median_duration_us': np.float64(2.272), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(2.272), 'max_duration_us': np.float64(2.272)}, {'name': 'void cudnn::engines_precompiled::nchwToNhwcKernel&lt;__nv_bfloat16, __nv_bfloat16, float, false, true, (cudnnKernelDataType_t)0&gt;(cudnn::engines_precompiled::nchw2nhwc_params_t&lt;float&gt;, __nv_bfloat16 const*, __nv_bfloat16*)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(10.464), 'mean_duration_us': np.float64(10.464), 'median_duration_us': np.float64(10.464), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(10.464), 'max_duration_us': np.float64(10.464)}, {'name': 'Memset (Device)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(2.112), 'mean_duration_us': np.float64(2.112), 'median_duration_us': np.float64(2.112), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(2.112), 'max_duration_us': np.float64(2.112)}, {'name': 'void cudnn::engines_precompiled::nchwToNhwcKernel&lt;__nv_bfloat16, __nv_bfloat16, float, false, true, (cudnnKernelDataType_t)0&gt;(cudnn::engines_precompiled::nchw2nhwc_params_t&lt;float&gt;, __nv_bfloat16 const*, __nv_bfloat16*)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(10.4), 'mean_duration_us': np.float64(10.4), 'median_duration_us': np.float64(10.4), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(10.4), 'max_duration_us': np.float64(10.4)}, {'name': 'void cutlass__5x_cudnn::Kernel&lt;cutlass_tensorop_bf16_s16816fprop_optimized_bf16_256x64_32x4_nhwc_align8&gt;(cutlass_tensorop_bf16_s16816fprop_optimized_bf16_256x64_32x4_nhwc_align8::Params)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(98.176), 'mean_duration_us': np.float64(98.176), 'median_duration_us': np.float64(98.176), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(98.176), 'max_duration_us': np.float64(98.176)}, {'name': 'void cudnn::engines_precompiled::nhwcToNchwKernel&lt;__nv_bfloat16, __nv_bfloat16, float, true, false, (cudnnKernelDataType_t)0&gt;(cudnn::engines_precompiled::nhwc2nchw_params_t&lt;float&gt;, __nv_bfloat16 const*, __nv_bfloat16*)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(2.208), 'mean_duration_us': np.float64(2.208), 'median_duration_us': np.float64(2.208), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(2.208), 'max_duration_us': np.float64(2.208)}, {'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(3.968), 'mean_duration_us': np.float64(3.968), 'median_duration_us': np.float64(3.968), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(3.968), 'max_duration_us': np.float64(3.968)}]</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>[{'name': 'Memset (Device)', 'stream': 7, 'mean_duration_us': np.float64(2.27)}, {'name': 'void cudnn::engines_precompiled::nchwToNhwcKernel&lt;__nv_bfloat16,...', 'stream': 7, 'mean_duration_us': np.float64(10.46)}, {'name': 'Memset (Device)', 'stream': 7, 'mean_duration_us': np.float64(2.11)}, {'name': 'void cudnn::engines_precompiled::nchwToNhwcKernel&lt;__nv_bfloat16,...', 'stream': 7, 'mean_duration_us': np.float64(10.4)}, {'name': 'void cutlass__5x_cudnn::Kernel&lt;cutlass_tensorop_bf16_s16816fprop...', 'stream': 7, 'mean_duration_us': np.float64(98.18)}, {'name': 'void cudnn::engines_precompiled::nhwcToNchwKernel&lt;__nv_bfloat16,...', 'stream': 7, 'mean_duration_us': np.float64(2.21)}, {'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(3.97)}]</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
         <is>
           <t>[[4, 3, 224, 224], [768, 3, 16, 16], [768], [], [], [], [], [], []]</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
         <is>
           <t>['c10::BFloat16', 'c10::BFloat16', 'c10::BFloat16', 'ScalarList', 'ScalarList', 'ScalarList', 'Scalar', 'ScalarList', 'Scalar']</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AJ2" t="inlineStr">
         <is>
           <t>[[150528, 50176, 224, 1], [768, 256, 16, 1], [1], [], [], [], [], [], []]</t>
         </is>
       </c>
-      <c r="AH2" t="inlineStr">
+      <c r="AK2" t="inlineStr">
         <is>
           <t>['', '', '', '[16, 16]', '[0, 0]', '[1, 1]', 'False', '[0, 0]', '1']</t>
         </is>
       </c>
-      <c r="AI2" t="n">
-        <v>129.60009765625</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>129.60009765625</v>
-      </c>
-      <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="n">
         <v>129.60009765625</v>
       </c>
       <c r="AM2" t="n">
         <v>129.60009765625</v>
       </c>
-      <c r="AN2" t="n">
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="n">
         <v>129.60009765625</v>
       </c>
-      <c r="AO2" t="n">
+      <c r="AP2" t="n">
+        <v>129.60009765625</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>129.60009765625</v>
+      </c>
+      <c r="AR2" t="n">
         <v>1</v>
       </c>
-      <c r="AP2" t="n">
+      <c r="AS2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -5829,7 +9001,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI4"/>
+  <dimension ref="A1:AL4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5935,75 +9107,90 @@
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
+          <t>process_name_first</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>process_label_first</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>thread_name_first</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
           <t>Compute Spec</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>kernel_details__summarize_kernel_stats</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>trunc_kernel_details</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Input Dims_first</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Input type_first</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Input Strides_first</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Concrete Inputs_first</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_mean</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_median</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_std</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_min</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_max</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_sum</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>name_count</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>UID_first</t>
         </is>
@@ -6086,61 +9273,76 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>thread 5617 (python3)</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
           <t>vector_bf16</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 7, 'count': 24, 'total_duration_us': np.float64(53.536), 'mean_duration_us': np.float64(2.2306666666666666), 'median_duration_us': np.float64(2.2245), 'std_dev_duration_us': np.float64(0.033798011118341686), 'min_duration_us': np.float64(2.176), 'max_duration_us': np.float64(2.304)}]</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CU...', 'stream': 7, 'mean_duration_us': np.float64(2.23)}]</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>[[4, 197, 768], [4, 197, 768], []]</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>['c10::BFloat16', 'c10::BFloat16', 'Scalar']</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>[[151296, 768, 1], [151296, 768, 1], []]</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>['', '', '1']</t>
         </is>
       </c>
-      <c r="AB2" t="n">
+      <c r="AE2" t="n">
         <v>2.230662027994792</v>
       </c>
-      <c r="AC2" t="n">
+      <c r="AF2" t="n">
         <v>2.2244873046875</v>
       </c>
-      <c r="AD2" t="n">
+      <c r="AG2" t="n">
         <v>0.03450867810431143</v>
       </c>
-      <c r="AE2" t="n">
+      <c r="AH2" t="n">
         <v>2.176025390625</v>
       </c>
-      <c r="AF2" t="n">
+      <c r="AI2" t="n">
         <v>2.303955078125</v>
       </c>
-      <c r="AG2" t="n">
+      <c r="AJ2" t="n">
         <v>53.535888671875</v>
       </c>
-      <c r="AH2" t="n">
+      <c r="AK2" t="n">
         <v>24</v>
       </c>
-      <c r="AI2" t="n">
+      <c r="AL2" t="n">
         <v>90</v>
       </c>
     </row>
@@ -6217,59 +9419,74 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>thread 5617 (python3)</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
           <t>vector_bf16</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(3.968), 'mean_duration_us': np.float64(3.968), 'median_duration_us': np.float64(3.968), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(3.968), 'max_duration_us': np.float64(3.968)}]</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(3.97)}]</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>[[4, 768, 14, 14], [1, 768, 1, 1], []]</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>['c10::BFloat16', 'c10::BFloat16', 'Scalar']</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>[[150528, 196, 14, 1], [768, 1, 1, 1], []]</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>['', '', '1']</t>
         </is>
       </c>
-      <c r="AB3" t="n">
-        <v>3.968017578125</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>3.968017578125</v>
-      </c>
-      <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="n">
         <v>3.968017578125</v>
       </c>
       <c r="AF3" t="n">
         <v>3.968017578125</v>
       </c>
-      <c r="AG3" t="n">
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="n">
         <v>3.968017578125</v>
       </c>
-      <c r="AH3" t="n">
+      <c r="AI3" t="n">
+        <v>3.968017578125</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>3.968017578125</v>
+      </c>
+      <c r="AK3" t="n">
         <v>1</v>
       </c>
-      <c r="AI3" t="n">
+      <c r="AL3" t="n">
         <v>7</v>
       </c>
     </row>
@@ -6346,59 +9563,74 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>thread 5617 (python3)</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
           <t>vector_bf16</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(3.777), 'mean_duration_us': np.float64(3.777), 'median_duration_us': np.float64(3.777), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(3.777), 'max_duration_us': np.float64(3.777)}]</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(3.78)}]</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>[[4, 197, 768], [1, 197, 768], []]</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>['c10::BFloat16', 'c10::BFloat16', 'Scalar']</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>[[151296, 768, 1], [151296, 768, 1], []]</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>['', '', '1']</t>
         </is>
       </c>
-      <c r="AB4" t="n">
-        <v>3.777099609375</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>3.777099609375</v>
-      </c>
-      <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="n">
         <v>3.777099609375</v>
       </c>
       <c r="AF4" t="n">
         <v>3.777099609375</v>
       </c>
-      <c r="AG4" t="n">
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="n">
         <v>3.777099609375</v>
       </c>
-      <c r="AH4" t="n">
+      <c r="AI4" t="n">
+        <v>3.777099609375</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>3.777099609375</v>
+      </c>
+      <c r="AK4" t="n">
         <v>1</v>
       </c>
-      <c r="AI4" t="n">
+      <c r="AL4" t="n">
         <v>15</v>
       </c>
     </row>

--- a/tests/traces/h100/Falconsai_nsfw_image_detection__1016002_perf_report.xlsx
+++ b/tests/traces/h100/Falconsai_nsfw_image_detection__1016002_perf_report.xlsx
@@ -17,6 +17,9 @@
     <sheet name="CONV_fwd" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="BinaryElementwise" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="Normalization" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="kernel_summary" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="short_kernel_histogram" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="short_kernels_summary" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -26,16 +29,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -46,7 +46,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -54,21 +54,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -438,17 +429,17 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>time ms</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>percent</t>
         </is>
@@ -569,191 +560,206 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK3"/>
+  <dimension ref="A1:AN3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>param: op_shape</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>param: dtype_in_out</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>param: stride_input</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>param: stride_output</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>param: num_channels</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>param: has_bias</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>param: is_affine</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>param: is_training</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>GFLOPS_first</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Data Moved (MB)_first</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>FLOPS/Byte_first</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>TB/s_mean</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>TB/s_median</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>TB/s_std</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>TB/s_min</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>TB/s_max</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>TFLOPS/s_mean</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>TFLOPS/s_median</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>TFLOPS/s_std</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>TFLOPS/s_min</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>TFLOPS/s_max</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>process_name_first</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>process_label_first</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>thread_name_first</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Compute Spec</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>kernel_details__summarize_kernel_stats</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>trunc_kernel_details</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Input Dims_first</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Input type_first</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Input Strides_first</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Concrete Inputs_first</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_mean</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_median</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_std</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_min</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_max</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_sum</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>name_count</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>UID_first</t>
         </is>
@@ -780,11 +786,7 @@
           <t>(151296, 768, 1)</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>768</t>
@@ -846,61 +848,76 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>thread 5617 (python3)</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>vector_bf16</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 7, 'count': 25, 'total_duration_us': np.float64(111.20100000000001), 'mean_duration_us': np.float64(4.448040000000001), 'median_duration_us': np.float64(4.448), 'std_dev_duration_us': np.float64(0.10934037863479323), 'min_duration_us': np.float64(4.256), 'max_duration_us': np.float64(4.64)}]</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_ke...', 'stream': 7, 'mean_duration_us': np.float64(4.45)}]</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>[[4, 197, 768], [], [768], [768], [], []]</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>['c10::BFloat16', 'ScalarList', 'c10::BFloat16', 'c10::BFloat16', 'Scalar', 'Scalar']</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>[[151296, 768, 1], [], [1], [1], [], []]</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>['', '[768]', '', '', '9.9999999999999998e-13', 'True']</t>
         </is>
       </c>
-      <c r="AD2" t="n">
+      <c r="AG2" t="n">
         <v>4.448037109375</v>
       </c>
-      <c r="AE2" t="n">
+      <c r="AH2" t="n">
         <v>4.447998046875</v>
       </c>
-      <c r="AF2" t="n">
+      <c r="AI2" t="n">
         <v>0.1115342775722907</v>
       </c>
-      <c r="AG2" t="n">
+      <c r="AJ2" t="n">
         <v>4.256103515625</v>
       </c>
-      <c r="AH2" t="n">
+      <c r="AK2" t="n">
         <v>4.639892578125</v>
       </c>
-      <c r="AI2" t="n">
+      <c r="AL2" t="n">
         <v>111.200927734375</v>
       </c>
-      <c r="AJ2" t="n">
+      <c r="AM2" t="n">
         <v>25</v>
       </c>
-      <c r="AK2" t="n">
+      <c r="AN2" t="n">
         <v>17</v>
       </c>
     </row>
@@ -925,11 +942,7 @@
           <t>(151296, 768, 1)</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>768</t>
@@ -991,62 +1004,2345 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>thread 5617 (python3)</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>vector_bf16</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 7, 'count': 25, 'total_duration_us': np.float64(111.20100000000001), 'mean_duration_us': np.float64(4.448040000000001), 'median_duration_us': np.float64(4.448), 'std_dev_duration_us': np.float64(0.10934037863479323), 'min_duration_us': np.float64(4.256), 'max_duration_us': np.float64(4.64)}]</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_ke...', 'stream': 7, 'mean_duration_us': np.float64(4.45)}]</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>[[4, 197, 768], [], [768], [768], []]</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>['c10::BFloat16', 'ScalarList', 'c10::BFloat16', 'c10::BFloat16', 'Scalar']</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>[[151296, 768, 1], [], [1], [1], []]</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
         <is>
           <t>['', '[768]', '', '', '9.9999999999999998e-13']</t>
         </is>
       </c>
-      <c r="AD3" t="n">
+      <c r="AG3" t="n">
         <v>4.448037109375</v>
       </c>
-      <c r="AE3" t="n">
+      <c r="AH3" t="n">
         <v>4.447998046875</v>
       </c>
-      <c r="AF3" t="n">
+      <c r="AI3" t="n">
         <v>0.1115342775722907</v>
       </c>
-      <c r="AG3" t="n">
+      <c r="AJ3" t="n">
         <v>4.256103515625</v>
       </c>
-      <c r="AH3" t="n">
+      <c r="AK3" t="n">
         <v>4.639892578125</v>
       </c>
-      <c r="AI3" t="n">
+      <c r="AL3" t="n">
         <v>111.200927734375</v>
       </c>
-      <c r="AJ3" t="n">
+      <c r="AM3" t="n">
         <v>25</v>
       </c>
-      <c r="AK3" t="n">
+      <c r="AN3" t="n">
         <v>18</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Parent op category</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Parent cpu_op</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Kernel name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Kernel stream</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Kernel duration (µs)_sum</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Kernel duration (µs)_count</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Kernel duration (µs)_mean</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Kernel duration (µs)_min</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Kernel duration (µs)_max</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Percent of kernels time (%)</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Percent of total time (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>GEMM</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>aten::addmm</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>void cutlass::Kernel2&lt;cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_128x64_64x6_tn_align8&gt;(cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_128x64_64x6_tn_align8::Params)</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E2" t="n">
+        <v>399.136</v>
+      </c>
+      <c r="F2" t="n">
+        <v>48</v>
+      </c>
+      <c r="G2" t="n">
+        <v>8.315333333333333</v>
+      </c>
+      <c r="H2" t="n">
+        <v>8.128</v>
+      </c>
+      <c r="I2" t="n">
+        <v>8.640000000000001</v>
+      </c>
+      <c r="J2" t="n">
+        <v>32.69125237729396</v>
+      </c>
+      <c r="K2" t="n">
+        <v>5.279685669563507</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>GEMM</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>aten::addmm</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>7</v>
+      </c>
+      <c r="E3" t="n">
+        <v>166.59</v>
+      </c>
+      <c r="F3" t="n">
+        <v>12</v>
+      </c>
+      <c r="G3" t="n">
+        <v>13.8825</v>
+      </c>
+      <c r="H3" t="n">
+        <v>13.76</v>
+      </c>
+      <c r="I3" t="n">
+        <v>14.176</v>
+      </c>
+      <c r="J3" t="n">
+        <v>13.64456158686112</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2.203616901739218</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>GEMM</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>aten::addmm</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x64x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>7</v>
+      </c>
+      <c r="E4" t="n">
+        <v>162.432</v>
+      </c>
+      <c r="F4" t="n">
+        <v>12</v>
+      </c>
+      <c r="G4" t="n">
+        <v>13.536</v>
+      </c>
+      <c r="H4" t="n">
+        <v>13.344</v>
+      </c>
+      <c r="I4" t="n">
+        <v>13.952</v>
+      </c>
+      <c r="J4" t="n">
+        <v>13.30400040624903</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2.148615766752534</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>aten::_flash_attention_forward</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>void pytorch_flash::flash_fwd_kernel&lt;pytorch_flash::Flash_fwd_kernel_traits&lt;64, 128, 128, 4, false, false, cutlass::bfloat16_t, pytorch_flash::Flash_kernel_traits&lt;64, 128, 128, 4, cutlass::bfloat16_t&gt; &gt;, false, false, false, false, false, true, false&gt;(pytorch_flash::Flash_fwd_params)</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E5" t="n">
+        <v>122.848</v>
+      </c>
+      <c r="F5" t="n">
+        <v>12</v>
+      </c>
+      <c r="G5" t="n">
+        <v>10.23733333333333</v>
+      </c>
+      <c r="H5" t="n">
+        <v>10.016</v>
+      </c>
+      <c r="I5" t="n">
+        <v>10.848</v>
+      </c>
+      <c r="J5" t="n">
+        <v>10.06187107162924</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1.625007078125094</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>NORM_fwd</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>aten::native_layer_norm</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>7</v>
+      </c>
+      <c r="E6" t="n">
+        <v>111.201</v>
+      </c>
+      <c r="F6" t="n">
+        <v>25</v>
+      </c>
+      <c r="G6" t="n">
+        <v>4.448040000000001</v>
+      </c>
+      <c r="H6" t="n">
+        <v>4.256</v>
+      </c>
+      <c r="I6" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="J6" t="n">
+        <v>9.107923002704506</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1.470943052345896</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CONV_fwd</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>aten::cudnn_convolution</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>void cutlass__5x_cudnn::Kernel&lt;cutlass_tensorop_bf16_s16816fprop_optimized_bf16_256x64_32x4_nhwc_align8&gt;(cutlass_tensorop_bf16_s16816fprop_optimized_bf16_256x64_32x4_nhwc_align8::Params)</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>7</v>
+      </c>
+      <c r="E7" t="n">
+        <v>98.176</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>98.176</v>
+      </c>
+      <c r="H7" t="n">
+        <v>98.176</v>
+      </c>
+      <c r="I7" t="n">
+        <v>98.176</v>
+      </c>
+      <c r="J7" t="n">
+        <v>8.041109780609144</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1.298651137194006</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>aten::gelu</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::GeluCUDAKernelImpl(at::TensorIteratorBase&amp;, at::native::GeluType)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::GeluCUDAKernelImpl(at::TensorIteratorBase&amp;, at::native::GeluType)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>7</v>
+      </c>
+      <c r="E8" t="n">
+        <v>60.542</v>
+      </c>
+      <c r="F8" t="n">
+        <v>12</v>
+      </c>
+      <c r="G8" t="n">
+        <v>5.045166666666667</v>
+      </c>
+      <c r="H8" t="n">
+        <v>4.991</v>
+      </c>
+      <c r="I8" t="n">
+        <v>5.12</v>
+      </c>
+      <c r="J8" t="n">
+        <v>4.958695285381752</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.8008366316411294</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>aten::add</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>7</v>
+      </c>
+      <c r="E9" t="n">
+        <v>53.536</v>
+      </c>
+      <c r="F9" t="n">
+        <v>24</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2.230666666666667</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.176</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.304</v>
+      </c>
+      <c r="J9" t="n">
+        <v>4.384868534210919</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.7081627615793913</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>CONV_fwd</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>aten::cudnn_convolution</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>void cudnn::engines_precompiled::nchwToNhwcKernel&lt;__nv_bfloat16, __nv_bfloat16, float, false, true, (cudnnKernelDataType_t)0&gt;(cudnn::engines_precompiled::nchw2nhwc_params_t&lt;float&gt;, __nv_bfloat16 const*, __nv_bfloat16*)</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>7</v>
+      </c>
+      <c r="E10" t="n">
+        <v>20.864</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2</v>
+      </c>
+      <c r="G10" t="n">
+        <v>10.432</v>
+      </c>
+      <c r="H10" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="I10" t="n">
+        <v>10.464</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.708866876452791</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.2759845311116337</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>aten::cat</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>void at::native::(anonymous namespace)::CatArrayBatchedCopy&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 3, 64, 64&gt;(at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;*, at::native::(anonymous namespace)::CatArrInputTensorMetadata&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 64, 64&gt;, at::native::(anonymous namespace)::TensorSizeStride&lt;unsigned int, 4u&gt;, int, unsigned int)</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>7</v>
+      </c>
+      <c r="E11" t="n">
+        <v>7.264</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>7.264</v>
+      </c>
+      <c r="H11" t="n">
+        <v>7.264</v>
+      </c>
+      <c r="I11" t="n">
+        <v>7.264</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.5949582529981343</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.09608663889929576</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>GEMM</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>aten::addmm</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>void cutlass::Kernel2&lt;cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_64x64_64x6_tn_align8&gt;(cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_64x64_64x6_tn_align8::Params)</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>7</v>
+      </c>
+      <c r="E12" t="n">
+        <v>6.879</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>6.879</v>
+      </c>
+      <c r="H12" t="n">
+        <v>6.879</v>
+      </c>
+      <c r="I12" t="n">
+        <v>6.879</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.5634248103488664</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.09099394121534354</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>aten::add_</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1})</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>7</v>
+      </c>
+      <c r="E13" t="n">
+        <v>3.968</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>3.968</v>
+      </c>
+      <c r="H13" t="n">
+        <v>3.968</v>
+      </c>
+      <c r="I13" t="n">
+        <v>3.968</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.3249992219020645</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.05248785561018799</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>aten::add</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1})</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>7</v>
+      </c>
+      <c r="E14" t="n">
+        <v>3.777</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>3.777</v>
+      </c>
+      <c r="H14" t="n">
+        <v>3.777</v>
+      </c>
+      <c r="I14" t="n">
+        <v>3.777</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.309355358146194</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.04996134844750001</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>CONV_fwd</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>aten::cudnn_convolution</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>void cudnn::engines_precompiled::nhwcToNchwKernel&lt;__nv_bfloat16, __nv_bfloat16, float, true, false, (cudnnKernelDataType_t)0&gt;(cudnn::engines_precompiled::nhwc2nchw_params_t&lt;float&gt;, __nv_bfloat16 const*, __nv_bfloat16*)</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>7</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2.208</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2.208</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2.208</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.208</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.1808463412196972</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.02920695191212074</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>aten::tanh</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::tanh_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::tanh_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>7</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1.505</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.505</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.505</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.505</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.1232670939925925</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.01990781821908592</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C101"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>bin_start</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>bin_end</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.505</v>
+      </c>
+      <c r="B2" t="n">
+        <v>1.57635</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1.57635</v>
+      </c>
+      <c r="B3" t="n">
+        <v>1.6477</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1.6477</v>
+      </c>
+      <c r="B4" t="n">
+        <v>1.71905</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1.71905</v>
+      </c>
+      <c r="B5" t="n">
+        <v>1.7904</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1.7904</v>
+      </c>
+      <c r="B6" t="n">
+        <v>1.86175</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1.86175</v>
+      </c>
+      <c r="B7" t="n">
+        <v>1.9331</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1.9331</v>
+      </c>
+      <c r="B8" t="n">
+        <v>2.00445</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>2.00445</v>
+      </c>
+      <c r="B9" t="n">
+        <v>2.0758</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>2.0758</v>
+      </c>
+      <c r="B10" t="n">
+        <v>2.14715</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>2.14715</v>
+      </c>
+      <c r="B11" t="n">
+        <v>2.2185</v>
+      </c>
+      <c r="C11" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>2.2185</v>
+      </c>
+      <c r="B12" t="n">
+        <v>2.28985</v>
+      </c>
+      <c r="C12" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>2.28985</v>
+      </c>
+      <c r="B13" t="n">
+        <v>2.3612</v>
+      </c>
+      <c r="C13" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>2.3612</v>
+      </c>
+      <c r="B14" t="n">
+        <v>2.43255</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>2.43255</v>
+      </c>
+      <c r="B15" t="n">
+        <v>2.5039</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>2.5039</v>
+      </c>
+      <c r="B16" t="n">
+        <v>2.57525</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>2.57525</v>
+      </c>
+      <c r="B17" t="n">
+        <v>2.6466</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>2.6466</v>
+      </c>
+      <c r="B18" t="n">
+        <v>2.71795</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>2.71795</v>
+      </c>
+      <c r="B19" t="n">
+        <v>2.7893</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>2.7893</v>
+      </c>
+      <c r="B20" t="n">
+        <v>2.86065</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>2.86065</v>
+      </c>
+      <c r="B21" t="n">
+        <v>2.932</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>2.932</v>
+      </c>
+      <c r="B22" t="n">
+        <v>3.00335</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>3.00335</v>
+      </c>
+      <c r="B23" t="n">
+        <v>3.0747</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>3.0747</v>
+      </c>
+      <c r="B24" t="n">
+        <v>3.14605</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>3.14605</v>
+      </c>
+      <c r="B25" t="n">
+        <v>3.2174</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>3.2174</v>
+      </c>
+      <c r="B26" t="n">
+        <v>3.28875</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>3.28875</v>
+      </c>
+      <c r="B27" t="n">
+        <v>3.3601</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>3.3601</v>
+      </c>
+      <c r="B28" t="n">
+        <v>3.43145</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>3.43145</v>
+      </c>
+      <c r="B29" t="n">
+        <v>3.5028</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>3.5028</v>
+      </c>
+      <c r="B30" t="n">
+        <v>3.57415</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>3.57415</v>
+      </c>
+      <c r="B31" t="n">
+        <v>3.6455</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>3.6455</v>
+      </c>
+      <c r="B32" t="n">
+        <v>3.71685</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>3.71685</v>
+      </c>
+      <c r="B33" t="n">
+        <v>3.7882</v>
+      </c>
+      <c r="C33" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>3.7882</v>
+      </c>
+      <c r="B34" t="n">
+        <v>3.85955</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>3.85955</v>
+      </c>
+      <c r="B35" t="n">
+        <v>3.9309</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>3.9309</v>
+      </c>
+      <c r="B36" t="n">
+        <v>4.00225</v>
+      </c>
+      <c r="C36" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>4.00225</v>
+      </c>
+      <c r="B37" t="n">
+        <v>4.073600000000001</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>4.073600000000001</v>
+      </c>
+      <c r="B38" t="n">
+        <v>4.14495</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>4.14495</v>
+      </c>
+      <c r="B39" t="n">
+        <v>4.2163</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>4.2163</v>
+      </c>
+      <c r="B40" t="n">
+        <v>4.28765</v>
+      </c>
+      <c r="C40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>4.28765</v>
+      </c>
+      <c r="B41" t="n">
+        <v>4.359</v>
+      </c>
+      <c r="C41" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>4.359</v>
+      </c>
+      <c r="B42" t="n">
+        <v>4.430350000000001</v>
+      </c>
+      <c r="C42" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>4.430350000000001</v>
+      </c>
+      <c r="B43" t="n">
+        <v>4.5017</v>
+      </c>
+      <c r="C43" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>4.5017</v>
+      </c>
+      <c r="B44" t="n">
+        <v>4.57305</v>
+      </c>
+      <c r="C44" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>4.57305</v>
+      </c>
+      <c r="B45" t="n">
+        <v>4.644400000000001</v>
+      </c>
+      <c r="C45" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>4.644400000000001</v>
+      </c>
+      <c r="B46" t="n">
+        <v>4.71575</v>
+      </c>
+      <c r="C46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>4.71575</v>
+      </c>
+      <c r="B47" t="n">
+        <v>4.787100000000001</v>
+      </c>
+      <c r="C47" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>4.787100000000001</v>
+      </c>
+      <c r="B48" t="n">
+        <v>4.85845</v>
+      </c>
+      <c r="C48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>4.85845</v>
+      </c>
+      <c r="B49" t="n">
+        <v>4.9298</v>
+      </c>
+      <c r="C49" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>4.9298</v>
+      </c>
+      <c r="B50" t="n">
+        <v>5.001150000000001</v>
+      </c>
+      <c r="C50" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>5.001150000000001</v>
+      </c>
+      <c r="B51" t="n">
+        <v>5.0725</v>
+      </c>
+      <c r="C51" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>5.0725</v>
+      </c>
+      <c r="B52" t="n">
+        <v>5.14385</v>
+      </c>
+      <c r="C52" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>5.14385</v>
+      </c>
+      <c r="B53" t="n">
+        <v>5.2152</v>
+      </c>
+      <c r="C53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>5.2152</v>
+      </c>
+      <c r="B54" t="n">
+        <v>5.28655</v>
+      </c>
+      <c r="C54" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>5.28655</v>
+      </c>
+      <c r="B55" t="n">
+        <v>5.357900000000001</v>
+      </c>
+      <c r="C55" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>5.357900000000001</v>
+      </c>
+      <c r="B56" t="n">
+        <v>5.429250000000001</v>
+      </c>
+      <c r="C56" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>5.429250000000001</v>
+      </c>
+      <c r="B57" t="n">
+        <v>5.5006</v>
+      </c>
+      <c r="C57" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>5.5006</v>
+      </c>
+      <c r="B58" t="n">
+        <v>5.57195</v>
+      </c>
+      <c r="C58" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>5.57195</v>
+      </c>
+      <c r="B59" t="n">
+        <v>5.643300000000001</v>
+      </c>
+      <c r="C59" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>5.643300000000001</v>
+      </c>
+      <c r="B60" t="n">
+        <v>5.714650000000001</v>
+      </c>
+      <c r="C60" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>5.714650000000001</v>
+      </c>
+      <c r="B61" t="n">
+        <v>5.786</v>
+      </c>
+      <c r="C61" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>5.786</v>
+      </c>
+      <c r="B62" t="n">
+        <v>5.85735</v>
+      </c>
+      <c r="C62" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>5.85735</v>
+      </c>
+      <c r="B63" t="n">
+        <v>5.928700000000001</v>
+      </c>
+      <c r="C63" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>5.928700000000001</v>
+      </c>
+      <c r="B64" t="n">
+        <v>6.000050000000001</v>
+      </c>
+      <c r="C64" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>6.000050000000001</v>
+      </c>
+      <c r="B65" t="n">
+        <v>6.071400000000001</v>
+      </c>
+      <c r="C65" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>6.071400000000001</v>
+      </c>
+      <c r="B66" t="n">
+        <v>6.14275</v>
+      </c>
+      <c r="C66" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>6.14275</v>
+      </c>
+      <c r="B67" t="n">
+        <v>6.2141</v>
+      </c>
+      <c r="C67" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>6.2141</v>
+      </c>
+      <c r="B68" t="n">
+        <v>6.285450000000001</v>
+      </c>
+      <c r="C68" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>6.285450000000001</v>
+      </c>
+      <c r="B69" t="n">
+        <v>6.356800000000001</v>
+      </c>
+      <c r="C69" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>6.356800000000001</v>
+      </c>
+      <c r="B70" t="n">
+        <v>6.42815</v>
+      </c>
+      <c r="C70" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>6.42815</v>
+      </c>
+      <c r="B71" t="n">
+        <v>6.4995</v>
+      </c>
+      <c r="C71" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>6.4995</v>
+      </c>
+      <c r="B72" t="n">
+        <v>6.570850000000001</v>
+      </c>
+      <c r="C72" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>6.570850000000001</v>
+      </c>
+      <c r="B73" t="n">
+        <v>6.642200000000001</v>
+      </c>
+      <c r="C73" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>6.642200000000001</v>
+      </c>
+      <c r="B74" t="n">
+        <v>6.713550000000001</v>
+      </c>
+      <c r="C74" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>6.713550000000001</v>
+      </c>
+      <c r="B75" t="n">
+        <v>6.7849</v>
+      </c>
+      <c r="C75" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>6.7849</v>
+      </c>
+      <c r="B76" t="n">
+        <v>6.856250000000001</v>
+      </c>
+      <c r="C76" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>6.856250000000001</v>
+      </c>
+      <c r="B77" t="n">
+        <v>6.927600000000001</v>
+      </c>
+      <c r="C77" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>6.927600000000001</v>
+      </c>
+      <c r="B78" t="n">
+        <v>6.998950000000001</v>
+      </c>
+      <c r="C78" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>6.998950000000001</v>
+      </c>
+      <c r="B79" t="n">
+        <v>7.0703</v>
+      </c>
+      <c r="C79" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>7.0703</v>
+      </c>
+      <c r="B80" t="n">
+        <v>7.141650000000001</v>
+      </c>
+      <c r="C80" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>7.141650000000001</v>
+      </c>
+      <c r="B81" t="n">
+        <v>7.213000000000001</v>
+      </c>
+      <c r="C81" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>7.213000000000001</v>
+      </c>
+      <c r="B82" t="n">
+        <v>7.284350000000001</v>
+      </c>
+      <c r="C82" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>7.284350000000001</v>
+      </c>
+      <c r="B83" t="n">
+        <v>7.355700000000001</v>
+      </c>
+      <c r="C83" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>7.355700000000001</v>
+      </c>
+      <c r="B84" t="n">
+        <v>7.42705</v>
+      </c>
+      <c r="C84" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>7.42705</v>
+      </c>
+      <c r="B85" t="n">
+        <v>7.498400000000001</v>
+      </c>
+      <c r="C85" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>7.498400000000001</v>
+      </c>
+      <c r="B86" t="n">
+        <v>7.569750000000001</v>
+      </c>
+      <c r="C86" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>7.569750000000001</v>
+      </c>
+      <c r="B87" t="n">
+        <v>7.641100000000001</v>
+      </c>
+      <c r="C87" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>7.641100000000001</v>
+      </c>
+      <c r="B88" t="n">
+        <v>7.71245</v>
+      </c>
+      <c r="C88" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>7.71245</v>
+      </c>
+      <c r="B89" t="n">
+        <v>7.783800000000001</v>
+      </c>
+      <c r="C89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>7.783800000000001</v>
+      </c>
+      <c r="B90" t="n">
+        <v>7.855150000000001</v>
+      </c>
+      <c r="C90" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>7.855150000000001</v>
+      </c>
+      <c r="B91" t="n">
+        <v>7.926500000000001</v>
+      </c>
+      <c r="C91" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>7.926500000000001</v>
+      </c>
+      <c r="B92" t="n">
+        <v>7.997850000000001</v>
+      </c>
+      <c r="C92" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>7.997850000000001</v>
+      </c>
+      <c r="B93" t="n">
+        <v>8.069200000000002</v>
+      </c>
+      <c r="C93" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>8.069200000000002</v>
+      </c>
+      <c r="B94" t="n">
+        <v>8.140550000000001</v>
+      </c>
+      <c r="C94" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>8.140550000000001</v>
+      </c>
+      <c r="B95" t="n">
+        <v>8.2119</v>
+      </c>
+      <c r="C95" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>8.2119</v>
+      </c>
+      <c r="B96" t="n">
+        <v>8.283250000000001</v>
+      </c>
+      <c r="C96" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>8.283250000000001</v>
+      </c>
+      <c r="B97" t="n">
+        <v>8.354600000000001</v>
+      </c>
+      <c r="C97" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>8.354600000000001</v>
+      </c>
+      <c r="B98" t="n">
+        <v>8.42595</v>
+      </c>
+      <c r="C98" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>8.42595</v>
+      </c>
+      <c r="B99" t="n">
+        <v>8.497300000000001</v>
+      </c>
+      <c r="C99" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>8.497300000000001</v>
+      </c>
+      <c r="B100" t="n">
+        <v>8.568650000000002</v>
+      </c>
+      <c r="C100" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>8.568650000000002</v>
+      </c>
+      <c r="B101" t="n">
+        <v>8.640000000000001</v>
+      </c>
+      <c r="C101" t="n">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Parent cpu_op</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Input dims</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Input strides</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Concrete Inputs</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Kernel name</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Short Kernel duration (µs) sum</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Short Kernel count</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Short Kernel duration (µs) mean</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Short Kernel duration (µs) percent of total time</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>aten::addmm</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>((768,), (788, 768), (768, 768), (), ())</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>((1,), (768, 1), (1, 768), (), ())</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>('', '', '', '1', '1')</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>void cutlass::Kernel2&lt;cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_128x64_64x6_tn_align8&gt;(cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_128x64_64x6_tn_align8::Params)</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>399.136</v>
+      </c>
+      <c r="G2" t="n">
+        <v>48</v>
+      </c>
+      <c r="H2" t="n">
+        <v>8.315333333333333</v>
+      </c>
+      <c r="I2" t="n">
+        <v>5.279685669563507</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>aten::native_layer_norm</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>((4, 197, 768), (), (768,), (768,), ())</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>((151296, 768, 1), (), (1,), (1,), ())</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>('', '[768]', '', '', '9.9999999999999998e-13')</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>111.201</v>
+      </c>
+      <c r="G3" t="n">
+        <v>25</v>
+      </c>
+      <c r="H3" t="n">
+        <v>4.448040000000001</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.470943052345896</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>aten::gelu</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>((4, 197, 3072), ())</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>((605184, 3072, 1), ())</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>('', '')</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::GeluCUDAKernelImpl(at::TensorIteratorBase&amp;, at::native::GeluType)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::GeluCUDAKernelImpl(at::TensorIteratorBase&amp;, at::native::GeluType)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>60.542</v>
+      </c>
+      <c r="G4" t="n">
+        <v>12</v>
+      </c>
+      <c r="H4" t="n">
+        <v>5.045166666666667</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.8008366316411294</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>aten::add</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>((4, 197, 768), (4, 197, 768), ())</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>((151296, 768, 1), (151296, 768, 1), ())</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>('', '', '1')</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>53.536</v>
+      </c>
+      <c r="G5" t="n">
+        <v>24</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.230666666666667</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.7081627615793913</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>aten::cat</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>(((4, 1, 768), (4, 196, 768)), ())</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>(((0, 768, 1), (150528, 1, 196)), ())</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>('', '1')</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>void at::native::(anonymous namespace)::CatArrayBatchedCopy&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 3, 64, 64&gt;(at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;*, at::native::(anonymous namespace)::CatArrInputTensorMetadata&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 64, 64&gt;, at::native::(anonymous namespace)::TensorSizeStride&lt;unsigned int, 4u&gt;, int, unsigned int)</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>7.264</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>7.264</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.09608663889929576</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>aten::addmm</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>((768,), (4, 768), (768, 768), (), ())</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>((1,), (151296, 1), (1, 768), (), ())</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>('', '', '', '1', '1')</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>void cutlass::Kernel2&lt;cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_64x64_64x6_tn_align8&gt;(cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_64x64_64x6_tn_align8::Params)</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>6.879</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>6.879</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.09099394121534354</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>aten::add_</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>((4, 768, 14, 14), (1, 768, 1, 1), ())</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>((150528, 196, 14, 1), (768, 1, 1, 1), ())</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>('', '', '1')</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1})</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>3.968</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>3.968</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.05248785561018799</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>aten::add</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>((4, 197, 768), (1, 197, 768), ())</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>((151296, 768, 1), (151296, 768, 1), ())</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>('', '', '1')</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1})</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>3.777</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3.777</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.04996134844750001</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>aten::cudnn_convolution</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>((4, 3, 224, 224), (768, 3, 16, 16), (), (), (), (), (), (), ())</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>((150528, 50176, 224, 1), (768, 256, 16, 1), (), (), (), (), (), (), ())</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>('', '', '[0, 0]', '[16, 16]', '[1, 1]', '1', 'False', 'False', 'True')</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>void cudnn::engines_precompiled::nhwcToNchwKernel&lt;__nv_bfloat16, __nv_bfloat16, float, true, false, (cudnnKernelDataType_t)0&gt;(cudnn::engines_precompiled::nhwc2nchw_params_t&lt;float&gt;, __nv_bfloat16 const*, __nv_bfloat16*)</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>2.208</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.208</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.02920695191212074</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>aten::tanh</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>((4, 768),)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>((768, 1),)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>('',)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::tanh_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::tanh_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>1.505</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.505</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.01990781821908592</v>
       </c>
     </row>
   </sheetData>
@@ -1064,27 +3360,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>op category</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>total_direct_kernel_time_ms</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Percentage (%)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Cumulative Percentage (%)</t>
         </is>
@@ -1200,37 +3496,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>total_direct_kernel_time_sum</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Categories</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>total_direct_kernel_time_ms</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Percentage (%)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Cumulative Percentage (%)</t>
         </is>
@@ -1490,96 +3786,111 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R14"/>
+  <dimension ref="A1:U14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>op category</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>process_name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>process_label</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>thread_name</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
         <is>
           <t>Input Dims</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Input type</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Input Strides</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Concrete Inputs</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>operation_count</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>total_direct_kernel_time_mean</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>total_direct_kernel_time_median</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>total_direct_kernel_time_std</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>total_direct_kernel_time_min</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>total_direct_kernel_time_max</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>total_direct_kernel_time_sum</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>ex_UID</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>kernel_details_summary</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>trunc_kernel_details</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Percentage (%)</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Cumulative Percentage (%)</t>
         </is>
@@ -1598,62 +3909,77 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>thread 5617 (python3)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>((768,), (788, 768), (768, 768), (), ())</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>('c10::BFloat16', 'c10::BFloat16', 'c10::BFloat16', 'Scalar', 'Scalar')</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>((1,), (768, 1), (1, 768), (), ())</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>('', '', '', '1', '1')</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="J2" t="n">
         <v>48</v>
       </c>
-      <c r="H2" t="n">
+      <c r="K2" t="n">
         <v>8.315348307291666</v>
       </c>
-      <c r="I2" t="n">
+      <c r="L2" t="n">
         <v>8.256103515625</v>
       </c>
-      <c r="J2" t="n">
+      <c r="M2" t="n">
         <v>0.1344482499064346</v>
       </c>
-      <c r="K2" t="n">
+      <c r="N2" t="n">
         <v>8.1279296875</v>
       </c>
-      <c r="L2" t="n">
+      <c r="O2" t="n">
         <v>8.639892578125</v>
       </c>
-      <c r="M2" t="n">
+      <c r="P2" t="n">
         <v>399.13671875</v>
       </c>
-      <c r="N2" t="n">
+      <c r="Q2" t="n">
         <v>30</v>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_128x64_64x6_tn_align8&gt;(cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_128x64_64x6_tn_align8::Params)', 'stream': 7, 'count': 48, 'total_duration_us': np.float64(399.136), 'mean_duration_us': np.float64(8.315333333333333), 'median_duration_us': np.float64(8.256), 'std_dev_duration_us': np.float64(0.13305517861231703), 'min_duration_us': np.float64(8.128), 'max_duration_us': np.float64(8.64)}]</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_80_tensorop_bf16_s16816gemm_relu_b...', 'stream': 7, 'mean_duration_us': np.float64(8.32)}]</t>
         </is>
       </c>
-      <c r="Q2" t="n">
+      <c r="T2" t="n">
         <v>32.57437687604667</v>
       </c>
-      <c r="R2" t="n">
+      <c r="U2" t="n">
         <v>32.57437687604667</v>
       </c>
     </row>
@@ -1670,62 +3996,77 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>thread 5617 (python3)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>((3072,), (788, 768), (768, 3072), (), ())</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>('c10::BFloat16', 'c10::BFloat16', 'c10::BFloat16', 'Scalar', 'Scalar')</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>((1,), (768, 1), (1, 768), (), ())</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>('', '', '', '1', '1')</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="J3" t="n">
         <v>12</v>
       </c>
-      <c r="H3" t="n">
+      <c r="K3" t="n">
         <v>13.88246663411458</v>
       </c>
-      <c r="I3" t="n">
+      <c r="L3" t="n">
         <v>13.887451171875</v>
       </c>
-      <c r="J3" t="n">
+      <c r="M3" t="n">
         <v>0.1063651301764554</v>
       </c>
-      <c r="K3" t="n">
+      <c r="N3" t="n">
         <v>13.760009765625</v>
       </c>
-      <c r="L3" t="n">
+      <c r="O3" t="n">
         <v>14.176025390625</v>
       </c>
-      <c r="M3" t="n">
+      <c r="P3" t="n">
         <v>166.589599609375</v>
       </c>
-      <c r="N3" t="n">
+      <c r="Q3" t="n">
         <v>104</v>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>[{'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'count': 12, 'total_duration_us': np.float64(166.59), 'mean_duration_us': np.float64(13.8825), 'median_duration_us': np.float64(13.8875), 'std_dev_duration_us': np.float64(0.10183278777813505), 'min_duration_us': np.float64(13.76), 'max_duration_us': np.float64(14.176)}]</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>[{'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warp...', 'stream': 7, 'mean_duration_us': np.float64(13.88)}]</t>
         </is>
       </c>
-      <c r="Q3" t="n">
+      <c r="T3" t="n">
         <v>13.59572333585382</v>
       </c>
-      <c r="R3" t="n">
+      <c r="U3" t="n">
         <v>46.1701002119005</v>
       </c>
     </row>
@@ -1742,62 +4083,77 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>thread 5617 (python3)</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>((768,), (788, 3072), (3072, 768), (), ())</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>('c10::BFloat16', 'c10::BFloat16', 'c10::BFloat16', 'Scalar', 'Scalar')</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>((1,), (3072, 1), (1, 3072), (), ())</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>('', '', '', '1', '1')</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="J4" t="n">
         <v>12</v>
       </c>
-      <c r="H4" t="n">
+      <c r="K4" t="n">
         <v>13.53594970703125</v>
       </c>
-      <c r="I4" t="n">
+      <c r="L4" t="n">
         <v>13.4879150390625</v>
       </c>
-      <c r="J4" t="n">
+      <c r="M4" t="n">
         <v>0.1773776572326171</v>
       </c>
-      <c r="K4" t="n">
+      <c r="N4" t="n">
         <v>13.343994140625</v>
       </c>
-      <c r="L4" t="n">
+      <c r="O4" t="n">
         <v>13.951904296875</v>
       </c>
-      <c r="M4" t="n">
+      <c r="P4" t="n">
         <v>162.431396484375</v>
       </c>
-      <c r="N4" t="n">
+      <c r="Q4" t="n">
         <v>114</v>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>[{'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x64x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'count': 12, 'total_duration_us': np.float64(162.43200000000002), 'mean_duration_us': np.float64(13.536000000000001), 'median_duration_us': np.float64(13.488), 'std_dev_duration_us': np.float64(0.16983128883296716), 'min_duration_us': np.float64(13.344), 'max_duration_us': np.float64(13.952)}]</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>[{'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x64x64_warpg...', 'stream': 7, 'mean_duration_us': np.float64(13.54)}]</t>
         </is>
       </c>
-      <c r="Q4" t="n">
+      <c r="T4" t="n">
         <v>13.25636373961045</v>
       </c>
-      <c r="R4" t="n">
+      <c r="U4" t="n">
         <v>59.42646395151095</v>
       </c>
     </row>
@@ -1814,60 +4170,75 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>thread 5617 (python3)</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>((4, 3, 224, 224), (768, 3, 16, 16), (), (), (), (), (), (), ())</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>('c10::BFloat16', 'c10::BFloat16', 'ScalarList', 'ScalarList', 'ScalarList', 'Scalar', 'Scalar', 'Scalar', 'Scalar')</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>((150528, 50176, 224, 1), (768, 256, 16, 1), (), (), (), (), (), (), ())</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>('', '', '[0, 0]', '[16, 16]', '[1, 1]', '1', 'False', 'False', 'True')</t>
         </is>
       </c>
-      <c r="G5" t="n">
+      <c r="J5" t="n">
         <v>1</v>
       </c>
-      <c r="H5" t="n">
-        <v>125.632080078125</v>
-      </c>
-      <c r="I5" t="n">
-        <v>125.632080078125</v>
-      </c>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
         <v>125.632080078125</v>
       </c>
       <c r="L5" t="n">
         <v>125.632080078125</v>
       </c>
-      <c r="M5" t="n">
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="n">
         <v>125.632080078125</v>
       </c>
-      <c r="N5" t="n">
+      <c r="O5" t="n">
+        <v>125.632080078125</v>
+      </c>
+      <c r="P5" t="n">
+        <v>125.632080078125</v>
+      </c>
+      <c r="Q5" t="n">
         <v>4</v>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>[{'name': 'Memset (Device)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(2.272), 'mean_duration_us': np.float64(2.272), 'median_duration_us': np.float64(2.272), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(2.272), 'max_duration_us': np.float64(2.272)}, {'name': 'void cudnn::engines_precompiled::nchwToNhwcKernel&lt;__nv_bfloat16, __nv_bfloat16, float, false, true, (cudnnKernelDataType_t)0&gt;(cudnn::engines_precompiled::nchw2nhwc_params_t&lt;float&gt;, __nv_bfloat16 const*, __nv_bfloat16*)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(10.464), 'mean_duration_us': np.float64(10.464), 'median_duration_us': np.float64(10.464), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(10.464), 'max_duration_us': np.float64(10.464)}, {'name': 'Memset (Device)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(2.112), 'mean_duration_us': np.float64(2.112), 'median_duration_us': np.float64(2.112), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(2.112), 'max_duration_us': np.float64(2.112)}, {'name': 'void cudnn::engines_precompiled::nchwToNhwcKernel&lt;__nv_bfloat16, __nv_bfloat16, float, false, true, (cudnnKernelDataType_t)0&gt;(cudnn::engines_precompiled::nchw2nhwc_params_t&lt;float&gt;, __nv_bfloat16 const*, __nv_bfloat16*)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(10.4), 'mean_duration_us': np.float64(10.4), 'median_duration_us': np.float64(10.4), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(10.4), 'max_duration_us': np.float64(10.4)}, {'name': 'void cutlass__5x_cudnn::Kernel&lt;cutlass_tensorop_bf16_s16816fprop_optimized_bf16_256x64_32x4_nhwc_align8&gt;(cutlass_tensorop_bf16_s16816fprop_optimized_bf16_256x64_32x4_nhwc_align8::Params)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(98.176), 'mean_duration_us': np.float64(98.176), 'median_duration_us': np.float64(98.176), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(98.176), 'max_duration_us': np.float64(98.176)}, {'name': 'void cudnn::engines_precompiled::nhwcToNchwKernel&lt;__nv_bfloat16, __nv_bfloat16, float, true, false, (cudnnKernelDataType_t)0&gt;(cudnn::engines_precompiled::nhwc2nchw_params_t&lt;float&gt;, __nv_bfloat16 const*, __nv_bfloat16*)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(2.208), 'mean_duration_us': np.float64(2.208), 'median_duration_us': np.float64(2.208), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(2.208), 'max_duration_us': np.float64(2.208)}]</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>[{'name': 'Memset (Device)', 'stream': 7, 'mean_duration_us': np.float64(2.27)}, {'name': 'void cudnn::engines_precompiled::nchwToNhwcKernel&lt;__nv_bfloat16,...', 'stream': 7, 'mean_duration_us': np.float64(10.46)}, {'name': 'Memset (Device)', 'stream': 7, 'mean_duration_us': np.float64(2.11)}, {'name': 'void cudnn::engines_precompiled::nchwToNhwcKernel&lt;__nv_bfloat16,...', 'stream': 7, 'mean_duration_us': np.float64(10.4)}, {'name': 'void cutlass__5x_cudnn::Kernel&lt;cutlass_tensorop_bf16_s16816fprop...', 'stream': 7, 'mean_duration_us': np.float64(98.18)}, {'name': 'void cudnn::engines_precompiled::nhwcToNchwKernel&lt;__nv_bfloat16,...', 'stream': 7, 'mean_duration_us': np.float64(2.21)}]</t>
         </is>
       </c>
-      <c r="Q5" t="n">
+      <c r="T5" t="n">
         <v>10.25309507229224</v>
       </c>
-      <c r="R5" t="n">
+      <c r="U5" t="n">
         <v>69.67955902380319</v>
       </c>
     </row>
@@ -1884,62 +4255,77 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>thread 5617 (python3)</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>((4, 197, 12, 64), (4, 197, 12, 64), (4, 197, 12, 64), (), (), (), (), (), (), (), (), (), (), (), ())</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>('c10::BFloat16', 'c10::BFloat16', 'c10::BFloat16', '', '', 'Scalar', 'Scalar', 'Scalar', 'Scalar', 'Scalar', 'Scalar', '', '', '', '')</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>((151296, 768, 64, 1), (151296, 768, 64, 1), (151296, 768, 64, 1), (), (), (), (), (), (), (), (), (), (), (), ())</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>('', '', '', '', '', '197', '197', '0.', 'False', 'False', '0.125', '', '', '', '')</t>
         </is>
       </c>
-      <c r="G6" t="n">
+      <c r="J6" t="n">
         <v>12</v>
       </c>
-      <c r="H6" t="n">
+      <c r="K6" t="n">
         <v>10.23734537760417</v>
       </c>
-      <c r="I6" t="n">
+      <c r="L6" t="n">
         <v>10.2239990234375</v>
       </c>
-      <c r="J6" t="n">
+      <c r="M6" t="n">
         <v>0.228442528412397</v>
       </c>
-      <c r="K6" t="n">
+      <c r="N6" t="n">
         <v>10.01611328125</v>
       </c>
-      <c r="L6" t="n">
+      <c r="O6" t="n">
         <v>10.847900390625</v>
       </c>
-      <c r="M6" t="n">
+      <c r="P6" t="n">
         <v>122.84814453125</v>
       </c>
-      <c r="N6" t="n">
+      <c r="Q6" t="n">
         <v>68</v>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>[{'name': 'void pytorch_flash::flash_fwd_kernel&lt;pytorch_flash::Flash_fwd_kernel_traits&lt;64, 128, 128, 4, false, false, cutlass::bfloat16_t, pytorch_flash::Flash_kernel_traits&lt;64, 128, 128, 4, cutlass::bfloat16_t&gt; &gt;, false, false, false, false, false, true, false&gt;(pytorch_flash::Flash_fwd_params)', 'stream': 7, 'count': 12, 'total_duration_us': np.float64(122.848), 'mean_duration_us': np.float64(10.237333333333334), 'median_duration_us': np.float64(10.224), 'std_dev_duration_us': np.float64(0.21878045819699932), 'min_duration_us': np.float64(10.016), 'max_duration_us': np.float64(10.848)}]</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>[{'name': 'void pytorch_flash::flash_fwd_kernel&lt;pytorch_flash::Flash_fwd_ke...', 'stream': 7, 'mean_duration_us': np.float64(10.24)}]</t>
         </is>
       </c>
-      <c r="Q6" t="n">
+      <c r="T6" t="n">
         <v>10.02589230832071</v>
       </c>
-      <c r="R6" t="n">
+      <c r="U6" t="n">
         <v>79.7054513321239</v>
       </c>
     </row>
@@ -1956,62 +4342,77 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>thread 5617 (python3)</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>((4, 197, 768), (), (768,), (768,), ())</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>('c10::BFloat16', 'ScalarList', 'c10::BFloat16', 'c10::BFloat16', 'Scalar')</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>((151296, 768, 1), (), (1,), (1,), ())</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>('', '[768]', '', '', '9.9999999999999998e-13')</t>
         </is>
       </c>
-      <c r="G7" t="n">
+      <c r="J7" t="n">
         <v>25</v>
       </c>
-      <c r="H7" t="n">
+      <c r="K7" t="n">
         <v>4.448037109375</v>
       </c>
-      <c r="I7" t="n">
+      <c r="L7" t="n">
         <v>4.447998046875</v>
       </c>
-      <c r="J7" t="n">
+      <c r="M7" t="n">
         <v>0.1115342775722907</v>
       </c>
-      <c r="K7" t="n">
+      <c r="N7" t="n">
         <v>4.256103515625</v>
       </c>
-      <c r="L7" t="n">
+      <c r="O7" t="n">
         <v>4.639892578125</v>
       </c>
-      <c r="M7" t="n">
+      <c r="P7" t="n">
         <v>111.200927734375</v>
       </c>
-      <c r="N7" t="n">
+      <c r="Q7" t="n">
         <v>18</v>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 7, 'count': 25, 'total_duration_us': np.float64(111.20100000000001), 'mean_duration_us': np.float64(4.448040000000001), 'median_duration_us': np.float64(4.448), 'std_dev_duration_us': np.float64(0.10934037863479323), 'min_duration_us': np.float64(4.256), 'max_duration_us': np.float64(4.64)}]</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_ke...', 'stream': 7, 'mean_duration_us': np.float64(4.45)}]</t>
         </is>
       </c>
-      <c r="Q7" t="n">
+      <c r="T7" t="n">
         <v>9.075338746907917</v>
       </c>
-      <c r="R7" t="n">
+      <c r="U7" t="n">
         <v>88.78079007903182</v>
       </c>
     </row>
@@ -2028,62 +4429,77 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>thread 5617 (python3)</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>((4, 197, 3072), ())</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>('c10::BFloat16', '')</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>((605184, 3072, 1), ())</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>('', '')</t>
         </is>
       </c>
-      <c r="G8" t="n">
+      <c r="J8" t="n">
         <v>12</v>
       </c>
-      <c r="H8" t="n">
+      <c r="K8" t="n">
         <v>5.04510498046875</v>
       </c>
-      <c r="I8" t="n">
+      <c r="L8" t="n">
         <v>5.055419921875</v>
       </c>
-      <c r="J8" t="n">
+      <c r="M8" t="n">
         <v>0.03943788318148379</v>
       </c>
-      <c r="K8" t="n">
+      <c r="N8" t="n">
         <v>4.990966796875</v>
       </c>
-      <c r="L8" t="n">
+      <c r="O8" t="n">
         <v>5.1201171875</v>
       </c>
-      <c r="M8" t="n">
+      <c r="P8" t="n">
         <v>60.541259765625</v>
       </c>
-      <c r="N8" t="n">
+      <c r="Q8" t="n">
         <v>107</v>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::GeluCUDAKernelImpl(at::TensorIteratorBase&amp;, at::native::GeluType)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::GeluCUDAKernelImpl(at::TensorIteratorBase&amp;, at::native::GeluType)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 12, 'total_duration_us': np.float64(60.541999999999994), 'mean_duration_us': np.float64(5.045166666666666), 'median_duration_us': np.float64(5.0555), 'std_dev_duration_us': np.float64(0.037739972914080884), 'min_duration_us': np.float64(4.991), 'max_duration_us': np.float64(5.12)}]</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::Ge...', 'stream': 7, 'mean_duration_us': np.float64(5.05)}]</t>
         </is>
       </c>
-      <c r="Q8" t="n">
+      <c r="T8" t="n">
         <v>4.940897991876649</v>
       </c>
-      <c r="R8" t="n">
+      <c r="U8" t="n">
         <v>93.72168807090847</v>
       </c>
     </row>
@@ -2100,62 +4516,77 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>thread 5617 (python3)</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t>((4, 197, 768), (4, 197, 768), ())</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>('c10::BFloat16', 'c10::BFloat16', 'Scalar')</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>((151296, 768, 1), (151296, 768, 1), ())</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>('', '', '1')</t>
         </is>
       </c>
-      <c r="G9" t="n">
+      <c r="J9" t="n">
         <v>24</v>
       </c>
-      <c r="H9" t="n">
+      <c r="K9" t="n">
         <v>2.230662027994792</v>
       </c>
-      <c r="I9" t="n">
+      <c r="L9" t="n">
         <v>2.2244873046875</v>
       </c>
-      <c r="J9" t="n">
+      <c r="M9" t="n">
         <v>0.03450867810431143</v>
       </c>
-      <c r="K9" t="n">
+      <c r="N9" t="n">
         <v>2.176025390625</v>
       </c>
-      <c r="L9" t="n">
+      <c r="O9" t="n">
         <v>2.303955078125</v>
       </c>
-      <c r="M9" t="n">
+      <c r="P9" t="n">
         <v>53.535888671875</v>
       </c>
-      <c r="N9" t="n">
+      <c r="Q9" t="n">
         <v>90</v>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 7, 'count': 24, 'total_duration_us': np.float64(53.536), 'mean_duration_us': np.float64(2.2306666666666666), 'median_duration_us': np.float64(2.2245), 'std_dev_duration_us': np.float64(0.033798011118341686), 'min_duration_us': np.float64(2.176), 'max_duration_us': np.float64(2.304)}]</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CU...', 'stream': 7, 'mean_duration_us': np.float64(2.23)}]</t>
         </is>
       </c>
-      <c r="Q9" t="n">
+      <c r="T9" t="n">
         <v>4.369175102338875</v>
       </c>
-      <c r="R9" t="n">
+      <c r="U9" t="n">
         <v>98.09086317324734</v>
       </c>
     </row>
@@ -2172,60 +4603,75 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>thread 5617 (python3)</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t>(((4, 1, 768), (4, 196, 768)), ())</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>('TensorList', 'Scalar')</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>(((0, 768, 1), (150528, 1, 196)), ())</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>('', '1')</t>
         </is>
       </c>
-      <c r="G10" t="n">
+      <c r="J10" t="n">
         <v>1</v>
       </c>
-      <c r="H10" t="n">
-        <v>7.263916015625</v>
-      </c>
-      <c r="I10" t="n">
-        <v>7.263916015625</v>
-      </c>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="n">
         <v>7.263916015625</v>
       </c>
       <c r="L10" t="n">
         <v>7.263916015625</v>
       </c>
-      <c r="M10" t="n">
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="n">
         <v>7.263916015625</v>
       </c>
-      <c r="N10" t="n">
+      <c r="O10" t="n">
+        <v>7.263916015625</v>
+      </c>
+      <c r="P10" t="n">
+        <v>7.263916015625</v>
+      </c>
+      <c r="Q10" t="n">
         <v>14</v>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::(anonymous namespace)::CatArrayBatchedCopy&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 3, 64, 64&gt;(at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;*, at::native::(anonymous namespace)::CatArrInputTensorMetadata&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 64, 64&gt;, at::native::(anonymous namespace)::TensorSizeStride&lt;unsigned int, 4u&gt;, int, unsigned int)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(7.264), 'mean_duration_us': np.float64(7.264), 'median_duration_us': np.float64(7.264), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(7.264), 'max_duration_us': np.float64(7.264)}]</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::(anonymous namespace)::CatArrayBatchedCopy&lt;at::...', 'stream': 7, 'mean_duration_us': np.float64(7.26)}]</t>
         </is>
       </c>
-      <c r="Q10" t="n">
+      <c r="T10" t="n">
         <v>0.5928232777729626</v>
       </c>
-      <c r="R10" t="n">
+      <c r="U10" t="n">
         <v>98.68368645102031</v>
       </c>
     </row>
@@ -2242,60 +4688,75 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>thread 5617 (python3)</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t>((768,), (4, 768), (768, 768), (), ())</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>('c10::BFloat16', 'c10::BFloat16', 'c10::BFloat16', 'Scalar', 'Scalar')</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>((1,), (151296, 1), (1, 768), (), ())</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>('', '', '', '1', '1')</t>
         </is>
       </c>
-      <c r="G11" t="n">
+      <c r="J11" t="n">
         <v>1</v>
       </c>
-      <c r="H11" t="n">
-        <v>6.87890625</v>
-      </c>
-      <c r="I11" t="n">
-        <v>6.87890625</v>
-      </c>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="n">
         <v>6.87890625</v>
       </c>
       <c r="L11" t="n">
         <v>6.87890625</v>
       </c>
-      <c r="M11" t="n">
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="n">
         <v>6.87890625</v>
       </c>
-      <c r="N11" t="n">
+      <c r="O11" t="n">
+        <v>6.87890625</v>
+      </c>
+      <c r="P11" t="n">
+        <v>6.87890625</v>
+      </c>
+      <c r="Q11" t="n">
         <v>1256</v>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_64x64_64x6_tn_align8&gt;(cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_64x64_64x6_tn_align8::Params)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(6.879), 'mean_duration_us': np.float64(6.879), 'median_duration_us': np.float64(6.879), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(6.879), 'max_duration_us': np.float64(6.879)}]</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_80_tensorop_bf16_s16816gemm_relu_b...', 'stream': 7, 'mean_duration_us': np.float64(6.88)}]</t>
         </is>
       </c>
-      <c r="Q11" t="n">
+      <c r="T11" t="n">
         <v>0.5614018308920443</v>
       </c>
-      <c r="R11" t="n">
+      <c r="U11" t="n">
         <v>99.24508828191234</v>
       </c>
     </row>
@@ -2312,60 +4773,75 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>thread 5617 (python3)</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t>((4, 768, 14, 14), (1, 768, 1, 1), ())</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>('c10::BFloat16', 'c10::BFloat16', 'Scalar')</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>((150528, 196, 14, 1), (768, 1, 1, 1), ())</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>('', '', '1')</t>
         </is>
       </c>
-      <c r="G12" t="n">
+      <c r="J12" t="n">
         <v>1</v>
       </c>
-      <c r="H12" t="n">
-        <v>3.968017578125</v>
-      </c>
-      <c r="I12" t="n">
-        <v>3.968017578125</v>
-      </c>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="n">
         <v>3.968017578125</v>
       </c>
       <c r="L12" t="n">
         <v>3.968017578125</v>
       </c>
-      <c r="M12" t="n">
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="n">
         <v>3.968017578125</v>
       </c>
-      <c r="N12" t="n">
+      <c r="O12" t="n">
+        <v>3.968017578125</v>
+      </c>
+      <c r="P12" t="n">
+        <v>3.968017578125</v>
+      </c>
+      <c r="Q12" t="n">
         <v>7</v>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(3.968), 'mean_duration_us': np.float64(3.968), 'median_duration_us': np.float64(3.968), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(3.968), 'max_duration_us': np.float64(3.968)}]</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(3.97)}]</t>
         </is>
       </c>
-      <c r="Q12" t="n">
+      <c r="T12" t="n">
         <v>0.3238381586274984</v>
       </c>
-      <c r="R12" t="n">
+      <c r="U12" t="n">
         <v>99.56892644053984</v>
       </c>
     </row>
@@ -2382,60 +4858,75 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>thread 5617 (python3)</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t>((4, 197, 768), (1, 197, 768), ())</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>('c10::BFloat16', 'c10::BFloat16', 'Scalar')</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>((151296, 768, 1), (151296, 768, 1), ())</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>('', '', '1')</t>
         </is>
       </c>
-      <c r="G13" t="n">
+      <c r="J13" t="n">
         <v>1</v>
       </c>
-      <c r="H13" t="n">
-        <v>3.777099609375</v>
-      </c>
-      <c r="I13" t="n">
-        <v>3.777099609375</v>
-      </c>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="n">
         <v>3.777099609375</v>
       </c>
       <c r="L13" t="n">
         <v>3.777099609375</v>
       </c>
-      <c r="M13" t="n">
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="n">
         <v>3.777099609375</v>
       </c>
-      <c r="N13" t="n">
+      <c r="O13" t="n">
+        <v>3.777099609375</v>
+      </c>
+      <c r="P13" t="n">
+        <v>3.777099609375</v>
+      </c>
+      <c r="Q13" t="n">
         <v>15</v>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(3.777), 'mean_duration_us': np.float64(3.777), 'median_duration_us': np.float64(3.777), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(3.777), 'max_duration_us': np.float64(3.777)}]</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(3.78)}]</t>
         </is>
       </c>
-      <c r="Q13" t="n">
+      <c r="T13" t="n">
         <v>0.3082569465407019</v>
       </c>
-      <c r="R13" t="n">
+      <c r="U13" t="n">
         <v>99.87718338708055</v>
       </c>
     </row>
@@ -2452,60 +4943,75 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>thread 5617 (python3)</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t>((4, 768),)</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>('c10::BFloat16',)</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>((768, 1),)</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>('',)</t>
         </is>
       </c>
-      <c r="G14" t="n">
+      <c r="J14" t="n">
         <v>1</v>
       </c>
-      <c r="H14" t="n">
-        <v>1.5048828125</v>
-      </c>
-      <c r="I14" t="n">
-        <v>1.5048828125</v>
-      </c>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="n">
         <v>1.5048828125</v>
       </c>
       <c r="L14" t="n">
         <v>1.5048828125</v>
       </c>
-      <c r="M14" t="n">
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="n">
         <v>1.5048828125</v>
       </c>
-      <c r="N14" t="n">
+      <c r="O14" t="n">
+        <v>1.5048828125</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.5048828125</v>
+      </c>
+      <c r="Q14" t="n">
         <v>1258</v>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="R14" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::tanh_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::tanh_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(1.505), 'mean_duration_us': np.float64(1.505), 'median_duration_us': np.float64(1.505), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(1.505), 'max_duration_us': np.float64(1.505)}]</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::ta...', 'stream': 7, 'mean_duration_us': np.float64(1.5)}]</t>
         </is>
       </c>
-      <c r="Q14" t="n">
+      <c r="T14" t="n">
         <v>0.1228166129194549</v>
       </c>
-      <c r="R14" t="n">
+      <c r="U14" t="n">
         <v>100</v>
       </c>
     </row>
@@ -2520,206 +5026,221 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN13"/>
+  <dimension ref="A1:AQ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>op category</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>process_name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>process_label</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>thread_name</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
         <is>
           <t>Input Dims</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Input type</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Input Strides</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Concrete Inputs</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>ex_UID</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>operation_count</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>total_duration_us</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>mean_duration_us</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>std_duration_us</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>GFLOPS</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Data Moved (MB)</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>FLOPS/Byte</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Compute Spec</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>TB/s_mean</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>TB/s_std</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>TFLOPS/s_mean</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>TFLOPS/s_std</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_mean</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_std</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_sum</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>duration_us_median</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>duration_us_min</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>duration_us_max</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>TB/s_median</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>TB/s_min</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>TB/s_max</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>TFLOPS/s_median</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>TFLOPS/s_min</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>TFLOPS/s_max</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_median</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_min</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_max</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>kernel_details_summary</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>trunc_kernel_details</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>perf_params</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>has_perf_model</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>Percentage (%)</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>Cumulative Percentage (%)</t>
         </is>
@@ -2738,132 +5259,147 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>thread 5617 (python3)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>((768,), (788, 768), (768, 768), (), ())</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>('c10::BFloat16', 'c10::BFloat16', 'c10::BFloat16', 'Scalar', 'Scalar')</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>((1,), (768, 1), (1, 768), (), ())</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>('', '', '', '1', '1')</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="J2" t="n">
         <v>30</v>
       </c>
-      <c r="H2" t="n">
+      <c r="K2" t="n">
         <v>48</v>
       </c>
-      <c r="I2" t="n">
+      <c r="L2" t="n">
         <v>1154.879</v>
       </c>
-      <c r="J2" t="n">
+      <c r="M2" t="n">
         <v>24.05997916666666</v>
       </c>
-      <c r="K2" t="n">
+      <c r="N2" t="n">
         <v>3.557746534509176</v>
       </c>
-      <c r="L2" t="n">
+      <c r="O2" t="n">
         <v>0.930167808</v>
       </c>
-      <c r="M2" t="n">
+      <c r="P2" t="n">
         <v>3.43505859375</v>
       </c>
-      <c r="N2" t="n">
+      <c r="Q2" t="n">
         <v>258.2422174840085</v>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>matrix_bf16</t>
         </is>
       </c>
-      <c r="P2" t="n">
+      <c r="S2" t="n">
         <v>0.4332748290550287</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="T2" t="n">
         <v>0.006921872667601486</v>
       </c>
-      <c r="R2" t="n">
+      <c r="U2" t="n">
         <v>111.8898526351753</v>
       </c>
-      <c r="S2" t="n">
+      <c r="V2" t="n">
         <v>1.78751974682336</v>
       </c>
-      <c r="T2" t="n">
+      <c r="W2" t="n">
         <v>8.315348307291666</v>
       </c>
-      <c r="U2" t="n">
+      <c r="X2" t="n">
         <v>0.1344482499064346</v>
       </c>
-      <c r="V2" t="n">
+      <c r="Y2" t="n">
         <v>399.13671875</v>
       </c>
-      <c r="W2" t="n">
+      <c r="Z2" t="n">
         <v>25.2705</v>
       </c>
-      <c r="X2" t="n">
+      <c r="AA2" t="n">
         <v>19.16</v>
       </c>
-      <c r="Y2" t="n">
+      <c r="AB2" t="n">
         <v>34.53</v>
       </c>
-      <c r="Z2" t="n">
+      <c r="AC2" t="n">
         <v>0.4362735996688056</v>
       </c>
-      <c r="AA2" t="n">
+      <c r="AD2" t="n">
         <v>0.4168940721693182</v>
       </c>
-      <c r="AB2" t="n">
+      <c r="AE2" t="n">
         <v>0.4431534398654331</v>
       </c>
-      <c r="AC2" t="n">
+      <c r="AF2" t="n">
         <v>112.664261808203</v>
       </c>
-      <c r="AD2" t="n">
+      <c r="AG2" t="n">
         <v>107.659649652943</v>
       </c>
-      <c r="AE2" t="n">
+      <c r="AH2" t="n">
         <v>114.4409269965157</v>
       </c>
-      <c r="AF2" t="n">
+      <c r="AI2" t="n">
         <v>8.256103515625</v>
       </c>
-      <c r="AG2" t="n">
+      <c r="AJ2" t="n">
         <v>8.1279296875</v>
       </c>
-      <c r="AH2" t="n">
+      <c r="AK2" t="n">
         <v>8.639892578125</v>
       </c>
-      <c r="AI2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
         <is>
           <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_128x64_64x6_tn_align8&gt;(cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_128x64_64x6_tn_align8::Params)', 'stream': 7, 'count': 48, 'total_duration_us': np.float64(399.136), 'mean_duration_us': np.float64(8.315333333333333), 'median_duration_us': np.float64(8.256), 'std_dev_duration_us': np.float64(0.13305517861231703), 'min_duration_us': np.float64(8.128), 'max_duration_us': np.float64(8.64)}]</t>
         </is>
       </c>
-      <c r="AJ2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_80_tensorop_bf16_s16816gemm_relu_b...', 'stream': 7, 'mean_duration_us': np.float64(8.32)}]</t>
         </is>
       </c>
-      <c r="AK2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>{'M': 788, 'N': 768, 'K': 768, 'bias': True, 'stride_A': (768, 1), 'stride_B': (1, 768), 'dtype_A_B': ('c10::BFloat16', 'c10::BFloat16'), 'B': 1}</t>
         </is>
       </c>
-      <c r="AL2" t="b">
+      <c r="AO2" t="b">
         <v>1</v>
       </c>
-      <c r="AM2" t="n">
+      <c r="AP2" t="n">
         <v>32.57437687604667</v>
       </c>
-      <c r="AN2" t="n">
+      <c r="AQ2" t="n">
         <v>32.57437687604667</v>
       </c>
     </row>
@@ -2880,132 +5416,147 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>thread 5617 (python3)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>((3072,), (788, 768), (768, 3072), (), ())</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>('c10::BFloat16', 'c10::BFloat16', 'c10::BFloat16', 'Scalar', 'Scalar')</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>((1,), (768, 1), (1, 768), (), ())</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>('', '', '', '1', '1')</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="J3" t="n">
         <v>104</v>
       </c>
-      <c r="H3" t="n">
+      <c r="K3" t="n">
         <v>12</v>
       </c>
-      <c r="I3" t="n">
+      <c r="L3" t="n">
         <v>469.666</v>
       </c>
-      <c r="J3" t="n">
+      <c r="M3" t="n">
         <v>39.13883333333333</v>
       </c>
-      <c r="K3" t="n">
+      <c r="N3" t="n">
         <v>1.635353997448167</v>
       </c>
-      <c r="L3" t="n">
+      <c r="O3" t="n">
         <v>3.720671232</v>
       </c>
-      <c r="M3" t="n">
+      <c r="P3" t="n">
         <v>10.27734375</v>
       </c>
-      <c r="N3" t="n">
+      <c r="Q3" t="n">
         <v>345.2554161915621</v>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>matrix_bf16</t>
         </is>
       </c>
-      <c r="P3" t="n">
+      <c r="S3" t="n">
         <v>0.7763136653796865</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="T3" t="n">
         <v>0.00587259665798289</v>
       </c>
-      <c r="R3" t="n">
+      <c r="U3" t="n">
         <v>268.0264976358607</v>
       </c>
-      <c r="S3" t="n">
+      <c r="V3" t="n">
         <v>2.027545803277043</v>
       </c>
-      <c r="T3" t="n">
+      <c r="W3" t="n">
         <v>13.88246663411458</v>
       </c>
-      <c r="U3" t="n">
+      <c r="X3" t="n">
         <v>0.1063651301764554</v>
       </c>
-      <c r="V3" t="n">
+      <c r="Y3" t="n">
         <v>166.589599609375</v>
       </c>
-      <c r="W3" t="n">
+      <c r="Z3" t="n">
         <v>38.6155</v>
       </c>
-      <c r="X3" t="n">
+      <c r="AA3" t="n">
         <v>37.56</v>
       </c>
-      <c r="Y3" t="n">
+      <c r="AB3" t="n">
         <v>43.91</v>
       </c>
-      <c r="Z3" t="n">
+      <c r="AC3" t="n">
         <v>0.775993800442447</v>
       </c>
-      <c r="AA3" t="n">
+      <c r="AD3" t="n">
         <v>0.7601972840093</v>
       </c>
-      <c r="AB3" t="n">
+      <c r="AE3" t="n">
         <v>0.783180839516687</v>
       </c>
-      <c r="AC3" t="n">
+      <c r="AF3" t="n">
         <v>267.9160625338291</v>
       </c>
-      <c r="AD3" t="n">
+      <c r="AG3" t="n">
         <v>262.462229678326</v>
       </c>
-      <c r="AE3" t="n">
+      <c r="AH3" t="n">
         <v>270.3974267005908</v>
       </c>
-      <c r="AF3" t="n">
+      <c r="AI3" t="n">
         <v>13.887451171875</v>
       </c>
-      <c r="AG3" t="n">
+      <c r="AJ3" t="n">
         <v>13.760009765625</v>
       </c>
-      <c r="AH3" t="n">
+      <c r="AK3" t="n">
         <v>14.176025390625</v>
       </c>
-      <c r="AI3" t="inlineStr">
+      <c r="AL3" t="inlineStr">
         <is>
           <t>[{'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'count': 12, 'total_duration_us': np.float64(166.59), 'mean_duration_us': np.float64(13.8825), 'median_duration_us': np.float64(13.8875), 'std_dev_duration_us': np.float64(0.10183278777813505), 'min_duration_us': np.float64(13.76), 'max_duration_us': np.float64(14.176)}]</t>
         </is>
       </c>
-      <c r="AJ3" t="inlineStr">
+      <c r="AM3" t="inlineStr">
         <is>
           <t>[{'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warp...', 'stream': 7, 'mean_duration_us': np.float64(13.88)}]</t>
         </is>
       </c>
-      <c r="AK3" t="inlineStr">
+      <c r="AN3" t="inlineStr">
         <is>
           <t>{'M': 788, 'N': 3072, 'K': 768, 'bias': True, 'stride_A': (768, 1), 'stride_B': (1, 768), 'dtype_A_B': ('c10::BFloat16', 'c10::BFloat16'), 'B': 1}</t>
         </is>
       </c>
-      <c r="AL3" t="b">
+      <c r="AO3" t="b">
         <v>1</v>
       </c>
-      <c r="AM3" t="n">
+      <c r="AP3" t="n">
         <v>13.59572333585382</v>
       </c>
-      <c r="AN3" t="n">
+      <c r="AQ3" t="n">
         <v>46.1701002119005</v>
       </c>
     </row>
@@ -3022,132 +5573,147 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>thread 5617 (python3)</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>((768,), (788, 3072), (3072, 768), (), ())</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>('c10::BFloat16', 'c10::BFloat16', 'c10::BFloat16', 'Scalar', 'Scalar')</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>((1,), (3072, 1), (1, 3072), (), ())</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>('', '', '', '1', '1')</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="J4" t="n">
         <v>114</v>
       </c>
-      <c r="H4" t="n">
+      <c r="K4" t="n">
         <v>12</v>
       </c>
-      <c r="I4" t="n">
+      <c r="L4" t="n">
         <v>430.237</v>
       </c>
-      <c r="J4" t="n">
+      <c r="M4" t="n">
         <v>35.85308333333334</v>
       </c>
-      <c r="K4" t="n">
+      <c r="N4" t="n">
         <v>3.536968564857183</v>
       </c>
-      <c r="L4" t="n">
+      <c r="O4" t="n">
         <v>3.71885568</v>
       </c>
-      <c r="M4" t="n">
+      <c r="P4" t="n">
         <v>10.27294921875</v>
       </c>
-      <c r="N4" t="n">
+      <c r="Q4" t="n">
         <v>345.2345643804363</v>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>matrix_bf16</t>
         </is>
       </c>
-      <c r="P4" t="n">
+      <c r="S4" t="n">
         <v>0.7959277904370671</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="T4" t="n">
         <v>0.01027516892316802</v>
       </c>
-      <c r="R4" t="n">
+      <c r="U4" t="n">
         <v>274.781784009824</v>
       </c>
-      <c r="S4" t="n">
+      <c r="V4" t="n">
         <v>3.547343467125292</v>
       </c>
-      <c r="T4" t="n">
+      <c r="W4" t="n">
         <v>13.53594970703125</v>
       </c>
-      <c r="U4" t="n">
+      <c r="X4" t="n">
         <v>0.1773776572326171</v>
       </c>
-      <c r="V4" t="n">
+      <c r="Y4" t="n">
         <v>162.431396484375</v>
       </c>
-      <c r="W4" t="n">
+      <c r="Z4" t="n">
         <v>34.531</v>
       </c>
-      <c r="X4" t="n">
+      <c r="AA4" t="n">
         <v>33.86</v>
       </c>
-      <c r="Y4" t="n">
+      <c r="AB4" t="n">
         <v>45.29</v>
       </c>
-      <c r="Z4" t="n">
+      <c r="AC4" t="n">
         <v>0.7986396051796765</v>
       </c>
-      <c r="AA4" t="n">
+      <c r="AD4" t="n">
         <v>0.7720786905349362</v>
       </c>
-      <c r="AB4" t="n">
+      <c r="AE4" t="n">
         <v>0.8072521530270598</v>
       </c>
-      <c r="AC4" t="n">
+      <c r="AF4" t="n">
         <v>275.7179961911693</v>
       </c>
-      <c r="AD4" t="n">
+      <c r="AG4" t="n">
         <v>266.5482503942464</v>
       </c>
-      <c r="AE4" t="n">
+      <c r="AH4" t="n">
         <v>278.6913453954663</v>
       </c>
-      <c r="AF4" t="n">
+      <c r="AI4" t="n">
         <v>13.4879150390625</v>
       </c>
-      <c r="AG4" t="n">
+      <c r="AJ4" t="n">
         <v>13.343994140625</v>
       </c>
-      <c r="AH4" t="n">
+      <c r="AK4" t="n">
         <v>13.951904296875</v>
       </c>
-      <c r="AI4" t="inlineStr">
+      <c r="AL4" t="inlineStr">
         <is>
           <t>[{'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x64x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'count': 12, 'total_duration_us': np.float64(162.43200000000002), 'mean_duration_us': np.float64(13.536000000000001), 'median_duration_us': np.float64(13.488), 'std_dev_duration_us': np.float64(0.16983128883296716), 'min_duration_us': np.float64(13.344), 'max_duration_us': np.float64(13.952)}]</t>
         </is>
       </c>
-      <c r="AJ4" t="inlineStr">
+      <c r="AM4" t="inlineStr">
         <is>
           <t>[{'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x64x64_warpg...', 'stream': 7, 'mean_duration_us': np.float64(13.54)}]</t>
         </is>
       </c>
-      <c r="AK4" t="inlineStr">
+      <c r="AN4" t="inlineStr">
         <is>
           <t>{'M': 788, 'N': 768, 'K': 3072, 'bias': True, 'stride_A': (3072, 1), 'stride_B': (1, 3072), 'dtype_A_B': ('c10::BFloat16', 'c10::BFloat16'), 'B': 1}</t>
         </is>
       </c>
-      <c r="AL4" t="b">
+      <c r="AO4" t="b">
         <v>1</v>
       </c>
-      <c r="AM4" t="n">
+      <c r="AP4" t="n">
         <v>13.25636373961045</v>
       </c>
-      <c r="AN4" t="n">
+      <c r="AQ4" t="n">
         <v>59.42646395151095</v>
       </c>
     </row>
@@ -3164,124 +5730,139 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>thread 5617 (python3)</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>((4, 3, 224, 224), (768, 3, 16, 16), (768,), (), (), (), (), (), ())</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>('c10::BFloat16', 'c10::BFloat16', 'c10::BFloat16', 'ScalarList', 'ScalarList', 'ScalarList', 'Scalar', 'ScalarList', 'Scalar')</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>((150528, 50176, 224, 1), (768, 256, 16, 1), (1,), (), (), (), (), (), ())</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>('', '', '', '[16, 16]', '[0, 0]', '[1, 1]', 'False', '[0, 0]', '1')</t>
         </is>
       </c>
-      <c r="G5" t="n">
+      <c r="J5" t="n">
         <v>2</v>
       </c>
-      <c r="H5" t="n">
+      <c r="K5" t="n">
         <v>1</v>
       </c>
-      <c r="I5" t="n">
+      <c r="L5" t="n">
         <v>101.661</v>
       </c>
-      <c r="J5" t="n">
+      <c r="M5" t="n">
         <v>101.661</v>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="n">
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="n">
         <v>0.924844032</v>
       </c>
-      <c r="M5" t="n">
+      <c r="P5" t="n">
         <v>3.421875</v>
       </c>
-      <c r="N5" t="n">
+      <c r="Q5" t="n">
         <v>257.7534246575343</v>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>matrix_bf16</t>
         </is>
       </c>
-      <c r="P5" t="n">
+      <c r="S5" t="n">
         <v>0.02768590506403035</v>
       </c>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="n">
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="n">
         <v>7.136136844997193</v>
       </c>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="n">
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="n">
         <v>129.60009765625</v>
       </c>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="n">
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="n">
         <v>129.60009765625</v>
       </c>
-      <c r="W5" t="n">
+      <c r="Z5" t="n">
         <v>101.661</v>
       </c>
-      <c r="X5" t="n">
+      <c r="AA5" t="n">
         <v>101.661</v>
       </c>
-      <c r="Y5" t="n">
+      <c r="AB5" t="n">
         <v>101.661</v>
       </c>
-      <c r="Z5" t="n">
+      <c r="AC5" t="n">
         <v>0.02768590506403035</v>
       </c>
-      <c r="AA5" t="n">
+      <c r="AD5" t="n">
         <v>0.02768590506403035</v>
       </c>
-      <c r="AB5" t="n">
+      <c r="AE5" t="n">
         <v>0.02768590506403035</v>
       </c>
-      <c r="AC5" t="n">
+      <c r="AF5" t="n">
         <v>7.136136844997193</v>
       </c>
-      <c r="AD5" t="n">
+      <c r="AG5" t="n">
         <v>7.136136844997193</v>
       </c>
-      <c r="AE5" t="n">
+      <c r="AH5" t="n">
         <v>7.136136844997193</v>
       </c>
-      <c r="AF5" t="n">
+      <c r="AI5" t="n">
         <v>129.60009765625</v>
       </c>
-      <c r="AG5" t="n">
+      <c r="AJ5" t="n">
         <v>129.60009765625</v>
       </c>
-      <c r="AH5" t="n">
+      <c r="AK5" t="n">
         <v>129.60009765625</v>
       </c>
-      <c r="AI5" t="inlineStr">
+      <c r="AL5" t="inlineStr">
         <is>
           <t>[{'name': 'Memset (Device)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(2.272), 'mean_duration_us': np.float64(2.272), 'median_duration_us': np.float64(2.272), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(2.272), 'max_duration_us': np.float64(2.272)}, {'name': 'void cudnn::engines_precompiled::nchwToNhwcKernel&lt;__nv_bfloat16, __nv_bfloat16, float, false, true, (cudnnKernelDataType_t)0&gt;(cudnn::engines_precompiled::nchw2nhwc_params_t&lt;float&gt;, __nv_bfloat16 const*, __nv_bfloat16*)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(10.464), 'mean_duration_us': np.float64(10.464), 'median_duration_us': np.float64(10.464), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(10.464), 'max_duration_us': np.float64(10.464)}, {'name': 'Memset (Device)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(2.112), 'mean_duration_us': np.float64(2.112), 'median_duration_us': np.float64(2.112), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(2.112), 'max_duration_us': np.float64(2.112)}, {'name': 'void cudnn::engines_precompiled::nchwToNhwcKernel&lt;__nv_bfloat16, __nv_bfloat16, float, false, true, (cudnnKernelDataType_t)0&gt;(cudnn::engines_precompiled::nchw2nhwc_params_t&lt;float&gt;, __nv_bfloat16 const*, __nv_bfloat16*)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(10.4), 'mean_duration_us': np.float64(10.4), 'median_duration_us': np.float64(10.4), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(10.4), 'max_duration_us': np.float64(10.4)}, {'name': 'void cutlass__5x_cudnn::Kernel&lt;cutlass_tensorop_bf16_s16816fprop_optimized_bf16_256x64_32x4_nhwc_align8&gt;(cutlass_tensorop_bf16_s16816fprop_optimized_bf16_256x64_32x4_nhwc_align8::Params)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(98.176), 'mean_duration_us': np.float64(98.176), 'median_duration_us': np.float64(98.176), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(98.176), 'max_duration_us': np.float64(98.176)}, {'name': 'void cudnn::engines_precompiled::nhwcToNchwKernel&lt;__nv_bfloat16, __nv_bfloat16, float, true, false, (cudnnKernelDataType_t)0&gt;(cudnn::engines_precompiled::nhwc2nchw_params_t&lt;float&gt;, __nv_bfloat16 const*, __nv_bfloat16*)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(2.208), 'mean_duration_us': np.float64(2.208), 'median_duration_us': np.float64(2.208), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(2.208), 'max_duration_us': np.float64(2.208)}, {'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(3.968), 'mean_duration_us': np.float64(3.968), 'median_duration_us': np.float64(3.968), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(3.968), 'max_duration_us': np.float64(3.968)}]</t>
         </is>
       </c>
-      <c r="AJ5" t="inlineStr">
+      <c r="AM5" t="inlineStr">
         <is>
           <t>[{'name': 'Memset (Device)', 'stream': 7, 'mean_duration_us': np.float64(2.27)}, {'name': 'void cudnn::engines_precompiled::nchwToNhwcKernel&lt;__nv_bfloat16,...', 'stream': 7, 'mean_duration_us': np.float64(10.46)}, {'name': 'Memset (Device)', 'stream': 7, 'mean_duration_us': np.float64(2.11)}, {'name': 'void cudnn::engines_precompiled::nchwToNhwcKernel&lt;__nv_bfloat16,...', 'stream': 7, 'mean_duration_us': np.float64(10.4)}, {'name': 'void cutlass__5x_cudnn::Kernel&lt;cutlass_tensorop_bf16_s16816fprop...', 'stream': 7, 'mean_duration_us': np.float64(98.18)}, {'name': 'void cudnn::engines_precompiled::nhwcToNchwKernel&lt;__nv_bfloat16,...', 'stream': 7, 'mean_duration_us': np.float64(2.21)}, {'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(3.97)}]</t>
         </is>
       </c>
-      <c r="AK5" t="inlineStr">
+      <c r="AN5" t="inlineStr">
         <is>
           <t>{'convNd': 'conv2d', 'input_shape': (4, 3, 224, 224), 'filter_shape': (768, 3, 16, 16), 'dtype_input_weight': ('c10::BFloat16', 'c10::BFloat16'), 'input_stride': (150528, 50176, 224, 1), 'weight_stride': (768, 256, 16, 1), 'bias': False, 'stride': (16, 16), 'padding': (0, 0), 'dilation': (1, 1), 'transposed_conv': False, 'output_padding': (0, 0), 'groups': 1}</t>
         </is>
       </c>
-      <c r="AL5" t="b">
+      <c r="AO5" t="b">
         <v>1</v>
       </c>
-      <c r="AM5" t="n">
+      <c r="AP5" t="n">
         <v>10.57693323091974</v>
       </c>
-      <c r="AN5" t="n">
+      <c r="AQ5" t="n">
         <v>70.00339718243069</v>
       </c>
     </row>
@@ -3298,128 +5879,143 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>thread 5617 (python3)</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>((4, 12, 197, 64), (4, 12, 197, 64), (4, 12, 197, 64), (), (), (), ())</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>('c10::BFloat16', 'c10::BFloat16', 'c10::BFloat16', 'Scalar', 'Scalar', 'Scalar', 'Scalar')</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>((151296, 64, 768, 1), (151296, 64, 768, 1), (151296, 64, 768, 1), (), (), (), ())</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>('', '', '', '0.', 'False', 'False', '0.125')</t>
         </is>
       </c>
-      <c r="G6" t="n">
+      <c r="J6" t="n">
         <v>61</v>
       </c>
-      <c r="H6" t="n">
+      <c r="K6" t="n">
         <v>12</v>
       </c>
-      <c r="I6" t="n">
+      <c r="L6" t="n">
         <v>491.448</v>
       </c>
-      <c r="J6" t="n">
+      <c r="M6" t="n">
         <v>40.954</v>
       </c>
-      <c r="K6" t="n">
+      <c r="N6" t="n">
         <v>2.08990247706355</v>
       </c>
-      <c r="L6" t="n">
+      <c r="O6" t="n">
         <v>0.476884992</v>
       </c>
-      <c r="M6" t="n">
+      <c r="P6" t="n">
         <v>4.6171875</v>
       </c>
-      <c r="N6" t="n">
+      <c r="Q6" t="n">
         <v>98.5</v>
       </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="n">
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="n">
         <v>0.4731315968327939</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="T6" t="n">
         <v>0.01022134818763448</v>
       </c>
-      <c r="R6" t="n">
+      <c r="U6" t="n">
         <v>46.60346228803019</v>
       </c>
-      <c r="S6" t="n">
+      <c r="V6" t="n">
         <v>1.006802796481996</v>
       </c>
-      <c r="T6" t="n">
+      <c r="W6" t="n">
         <v>10.23734537760417</v>
       </c>
-      <c r="U6" t="n">
+      <c r="X6" t="n">
         <v>0.228442528412397</v>
       </c>
-      <c r="V6" t="n">
+      <c r="Y6" t="n">
         <v>122.84814453125</v>
       </c>
-      <c r="W6" t="n">
+      <c r="Z6" t="n">
         <v>40.6005</v>
       </c>
-      <c r="X6" t="n">
+      <c r="AA6" t="n">
         <v>39.25</v>
       </c>
-      <c r="Y6" t="n">
+      <c r="AB6" t="n">
         <v>47.251</v>
       </c>
-      <c r="Z6" t="n">
+      <c r="AC6" t="n">
         <v>0.4735411097882475</v>
       </c>
-      <c r="AA6" t="n">
+      <c r="AD6" t="n">
         <v>0.4463049830531362</v>
       </c>
-      <c r="AB6" t="n">
+      <c r="AE6" t="n">
         <v>0.4833683350070687</v>
       </c>
-      <c r="AC6" t="n">
+      <c r="AF6" t="n">
         <v>46.64379931414237</v>
       </c>
-      <c r="AD6" t="n">
+      <c r="AG6" t="n">
         <v>43.96104083073391</v>
       </c>
-      <c r="AE6" t="n">
+      <c r="AH6" t="n">
         <v>47.61178099819627</v>
       </c>
-      <c r="AF6" t="n">
+      <c r="AI6" t="n">
         <v>10.2239990234375</v>
       </c>
-      <c r="AG6" t="n">
+      <c r="AJ6" t="n">
         <v>10.01611328125</v>
       </c>
-      <c r="AH6" t="n">
+      <c r="AK6" t="n">
         <v>10.847900390625</v>
       </c>
-      <c r="AI6" t="inlineStr">
+      <c r="AL6" t="inlineStr">
         <is>
           <t>[{'name': 'void pytorch_flash::flash_fwd_kernel&lt;pytorch_flash::Flash_fwd_kernel_traits&lt;64, 128, 128, 4, false, false, cutlass::bfloat16_t, pytorch_flash::Flash_kernel_traits&lt;64, 128, 128, 4, cutlass::bfloat16_t&gt; &gt;, false, false, false, false, false, true, false&gt;(pytorch_flash::Flash_fwd_params)', 'stream': 7, 'count': 12, 'total_duration_us': np.float64(122.848), 'mean_duration_us': np.float64(10.237333333333334), 'median_duration_us': np.float64(10.224), 'std_dev_duration_us': np.float64(0.21878045819699932), 'min_duration_us': np.float64(10.016), 'max_duration_us': np.float64(10.848)}]</t>
         </is>
       </c>
-      <c r="AJ6" t="inlineStr">
+      <c r="AM6" t="inlineStr">
         <is>
           <t>[{'name': 'void pytorch_flash::flash_fwd_kernel&lt;pytorch_flash::Flash_fwd_ke...', 'stream': 7, 'mean_duration_us': np.float64(10.24)}]</t>
         </is>
       </c>
-      <c r="AK6" t="inlineStr">
+      <c r="AN6" t="inlineStr">
         <is>
           <t>{'B': 4, 'N_Q': 197, 'H_Q': 12, 'N_KV': 197, 'H_KV': 12, 'd_h_qk': 64, 'd_h_v': 64, 'dropout': 0.0, 'causal': False, 'flash_impl': True}</t>
         </is>
       </c>
-      <c r="AL6" t="b">
+      <c r="AO6" t="b">
         <v>1</v>
       </c>
-      <c r="AM6" t="n">
+      <c r="AP6" t="n">
         <v>10.02589230832071</v>
       </c>
-      <c r="AN6" t="n">
+      <c r="AQ6" t="n">
         <v>80.0292894907514</v>
       </c>
     </row>
@@ -3436,132 +6032,147 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>thread 5617 (python3)</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>((4, 197, 768), (), (768,), (768,), (), ())</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>('c10::BFloat16', 'ScalarList', 'c10::BFloat16', 'c10::BFloat16', 'Scalar', 'Scalar')</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>((151296, 768, 1), (), (1,), (1,), (), ())</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>('', '[768]', '', '', '9.9999999999999998e-13', 'True')</t>
         </is>
       </c>
-      <c r="G7" t="n">
+      <c r="J7" t="n">
         <v>17</v>
       </c>
-      <c r="H7" t="n">
+      <c r="K7" t="n">
         <v>25</v>
       </c>
-      <c r="I7" t="n">
+      <c r="L7" t="n">
         <v>616.799</v>
       </c>
-      <c r="J7" t="n">
+      <c r="M7" t="n">
         <v>24.67196</v>
       </c>
-      <c r="K7" t="n">
+      <c r="N7" t="n">
         <v>2.70387186086915</v>
       </c>
-      <c r="L7" t="n">
+      <c r="O7" t="n">
         <v>0.003030528</v>
       </c>
-      <c r="M7" t="n">
+      <c r="P7" t="n">
         <v>2.3173828125</v>
       </c>
-      <c r="N7" t="n">
+      <c r="Q7" t="n">
         <v>1.247155499367889</v>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>vector_bf16</t>
         </is>
       </c>
-      <c r="P7" t="n">
+      <c r="S7" t="n">
         <v>0.5466261436434106</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="T7" t="n">
         <v>0.0136524750083966</v>
       </c>
-      <c r="R7" t="n">
+      <c r="U7" t="n">
         <v>0.6817278011431411</v>
       </c>
-      <c r="S7" t="n">
+      <c r="V7" t="n">
         <v>0.01702675928670446</v>
       </c>
-      <c r="T7" t="n">
+      <c r="W7" t="n">
         <v>4.448037109375</v>
       </c>
-      <c r="U7" t="n">
+      <c r="X7" t="n">
         <v>0.1115342775722907</v>
       </c>
-      <c r="V7" t="n">
+      <c r="Y7" t="n">
         <v>111.200927734375</v>
       </c>
-      <c r="W7" t="n">
+      <c r="Z7" t="n">
         <v>23.71</v>
       </c>
-      <c r="X7" t="n">
+      <c r="AA7" t="n">
         <v>22.44</v>
       </c>
-      <c r="Y7" t="n">
+      <c r="AB7" t="n">
         <v>33.221</v>
       </c>
-      <c r="Z7" t="n">
+      <c r="AC7" t="n">
         <v>0.5463023981557714</v>
       </c>
-      <c r="AA7" t="n">
+      <c r="AD7" t="n">
         <v>0.5237086762430939</v>
       </c>
-      <c r="AB7" t="n">
+      <c r="AE7" t="n">
         <v>0.5709334820168646</v>
       </c>
-      <c r="AC7" t="n">
+      <c r="AF7" t="n">
         <v>0.6813240401778364</v>
       </c>
-      <c r="AD7" t="n">
+      <c r="AG7" t="n">
         <v>0.6531461556432518</v>
       </c>
-      <c r="AE7" t="n">
+      <c r="AH7" t="n">
         <v>0.7120428318705904</v>
       </c>
-      <c r="AF7" t="n">
+      <c r="AI7" t="n">
         <v>4.447998046875</v>
       </c>
-      <c r="AG7" t="n">
+      <c r="AJ7" t="n">
         <v>4.256103515625</v>
       </c>
-      <c r="AH7" t="n">
+      <c r="AK7" t="n">
         <v>4.639892578125</v>
       </c>
-      <c r="AI7" t="inlineStr">
+      <c r="AL7" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 7, 'count': 25, 'total_duration_us': np.float64(111.20100000000001), 'mean_duration_us': np.float64(4.448040000000001), 'median_duration_us': np.float64(4.448), 'std_dev_duration_us': np.float64(0.10934037863479323), 'min_duration_us': np.float64(4.256), 'max_duration_us': np.float64(4.64)}]</t>
         </is>
       </c>
-      <c r="AJ7" t="inlineStr">
+      <c r="AM7" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_ke...', 'stream': 7, 'mean_duration_us': np.float64(4.45)}]</t>
         </is>
       </c>
-      <c r="AK7" t="inlineStr">
+      <c r="AN7" t="inlineStr">
         <is>
           <t>{'op_shape': (4, 197, 768), 'dtype_in_out': ('c10::BFloat16', None), 'stride_input': (151296, 768, 1), 'stride_output': None, 'num_channels': 768, 'has_bias': True, 'is_affine': True, 'is_training': True}</t>
         </is>
       </c>
-      <c r="AL7" t="b">
+      <c r="AO7" t="b">
         <v>1</v>
       </c>
-      <c r="AM7" t="n">
+      <c r="AP7" t="n">
         <v>9.075338746907917</v>
       </c>
-      <c r="AN7" t="n">
+      <c r="AQ7" t="n">
         <v>89.10462823765931</v>
       </c>
     </row>
@@ -3578,98 +6189,113 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>thread 5617 (python3)</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>((4, 197, 3072), ())</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>('c10::BFloat16', '')</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>((605184, 3072, 1), ())</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>('', '')</t>
         </is>
       </c>
-      <c r="G8" t="n">
+      <c r="J8" t="n">
         <v>107</v>
       </c>
-      <c r="H8" t="n">
+      <c r="K8" t="n">
         <v>12</v>
       </c>
-      <c r="I8" t="n">
+      <c r="L8" t="n">
         <v>153.193</v>
       </c>
-      <c r="J8" t="n">
+      <c r="M8" t="n">
         <v>12.76608333333333</v>
       </c>
-      <c r="K8" t="n">
+      <c r="N8" t="n">
         <v>2.932567892985548</v>
       </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr"/>
-      <c r="T8" t="n">
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="n">
         <v>5.04510498046875</v>
       </c>
-      <c r="U8" t="n">
+      <c r="X8" t="n">
         <v>0.03943788318148379</v>
       </c>
-      <c r="V8" t="n">
+      <c r="Y8" t="n">
         <v>60.541259765625</v>
       </c>
-      <c r="W8" t="n">
+      <c r="Z8" t="n">
         <v>11.9605</v>
       </c>
-      <c r="X8" t="n">
+      <c r="AA8" t="n">
         <v>11.42</v>
       </c>
-      <c r="Y8" t="n">
+      <c r="AB8" t="n">
         <v>22.04</v>
       </c>
-      <c r="Z8" t="inlineStr"/>
-      <c r="AA8" t="inlineStr"/>
-      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="inlineStr"/>
-      <c r="AF8" t="n">
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr"/>
+      <c r="AI8" t="n">
         <v>5.055419921875</v>
       </c>
-      <c r="AG8" t="n">
+      <c r="AJ8" t="n">
         <v>4.990966796875</v>
       </c>
-      <c r="AH8" t="n">
+      <c r="AK8" t="n">
         <v>5.1201171875</v>
       </c>
-      <c r="AI8" t="inlineStr">
+      <c r="AL8" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::GeluCUDAKernelImpl(at::TensorIteratorBase&amp;, at::native::GeluType)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::GeluCUDAKernelImpl(at::TensorIteratorBase&amp;, at::native::GeluType)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 12, 'total_duration_us': np.float64(60.541999999999994), 'mean_duration_us': np.float64(5.045166666666666), 'median_duration_us': np.float64(5.0555), 'std_dev_duration_us': np.float64(0.037739972914080884), 'min_duration_us': np.float64(4.991), 'max_duration_us': np.float64(5.12)}]</t>
         </is>
       </c>
-      <c r="AJ8" t="inlineStr">
+      <c r="AM8" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::Ge...', 'stream': 7, 'mean_duration_us': np.float64(5.05)}]</t>
         </is>
       </c>
-      <c r="AK8" t="inlineStr"/>
-      <c r="AL8" t="b">
+      <c r="AN8" t="inlineStr"/>
+      <c r="AO8" t="b">
         <v>0</v>
       </c>
-      <c r="AM8" t="n">
+      <c r="AP8" t="n">
         <v>4.940897991876649</v>
       </c>
-      <c r="AN8" t="n">
+      <c r="AQ8" t="n">
         <v>94.04552622953597</v>
       </c>
     </row>
@@ -3686,132 +6312,147 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>thread 5617 (python3)</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t>((4, 197, 768), (4, 197, 768), ())</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>('c10::BFloat16', 'c10::BFloat16', 'Scalar')</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>((151296, 768, 1), (151296, 768, 1), ())</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>('', '', '1')</t>
         </is>
       </c>
-      <c r="G9" t="n">
+      <c r="J9" t="n">
         <v>90</v>
       </c>
-      <c r="H9" t="n">
+      <c r="K9" t="n">
         <v>24</v>
       </c>
-      <c r="I9" t="n">
+      <c r="L9" t="n">
         <v>298.853</v>
       </c>
-      <c r="J9" t="n">
+      <c r="M9" t="n">
         <v>12.45220833333333</v>
       </c>
-      <c r="K9" t="n">
+      <c r="N9" t="n">
         <v>0.4364494073142128</v>
       </c>
-      <c r="L9" t="n">
+      <c r="O9" t="n">
         <v>0.000605184</v>
       </c>
-      <c r="M9" t="n">
+      <c r="P9" t="n">
         <v>3.462890625</v>
       </c>
-      <c r="N9" t="n">
+      <c r="Q9" t="n">
         <v>0.1666666666666667</v>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>vector_bf16</t>
         </is>
       </c>
-      <c r="P9" t="n">
+      <c r="S9" t="n">
         <v>1.628184728894159</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="T9" t="n">
         <v>0.02497608869878607</v>
       </c>
-      <c r="R9" t="n">
+      <c r="U9" t="n">
         <v>0.2713641214823599</v>
       </c>
-      <c r="S9" t="n">
+      <c r="V9" t="n">
         <v>0.00416268144979767</v>
       </c>
-      <c r="T9" t="n">
+      <c r="W9" t="n">
         <v>2.230662027994792</v>
       </c>
-      <c r="U9" t="n">
+      <c r="X9" t="n">
         <v>0.03450867810431143</v>
       </c>
-      <c r="V9" t="n">
+      <c r="Y9" t="n">
         <v>53.535888671875</v>
       </c>
-      <c r="W9" t="n">
+      <c r="Z9" t="n">
         <v>12.405</v>
       </c>
-      <c r="X9" t="n">
+      <c r="AA9" t="n">
         <v>11.76</v>
       </c>
-      <c r="Y9" t="n">
+      <c r="AB9" t="n">
         <v>13.47</v>
       </c>
-      <c r="Z9" t="n">
+      <c r="AC9" t="n">
         <v>1.632412270219935</v>
       </c>
-      <c r="AA9" t="n">
+      <c r="AD9" t="n">
         <v>1.576030728409452</v>
       </c>
-      <c r="AB9" t="n">
+      <c r="AE9" t="n">
         <v>1.668686411309323</v>
       </c>
-      <c r="AC9" t="n">
+      <c r="AF9" t="n">
         <v>0.2720687117033225</v>
       </c>
-      <c r="AD9" t="n">
+      <c r="AG9" t="n">
         <v>0.262671788068242</v>
       </c>
-      <c r="AE9" t="n">
+      <c r="AH9" t="n">
         <v>0.2781144018848872</v>
       </c>
-      <c r="AF9" t="n">
+      <c r="AI9" t="n">
         <v>2.2244873046875</v>
       </c>
-      <c r="AG9" t="n">
+      <c r="AJ9" t="n">
         <v>2.176025390625</v>
       </c>
-      <c r="AH9" t="n">
+      <c r="AK9" t="n">
         <v>2.303955078125</v>
       </c>
-      <c r="AI9" t="inlineStr">
+      <c r="AL9" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 7, 'count': 24, 'total_duration_us': np.float64(53.536), 'mean_duration_us': np.float64(2.2306666666666666), 'median_duration_us': np.float64(2.2245), 'std_dev_duration_us': np.float64(0.033798011118341686), 'min_duration_us': np.float64(2.176), 'max_duration_us': np.float64(2.304)}]</t>
         </is>
       </c>
-      <c r="AJ9" t="inlineStr">
+      <c r="AM9" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CU...', 'stream': 7, 'mean_duration_us': np.float64(2.23)}]</t>
         </is>
       </c>
-      <c r="AK9" t="inlineStr">
+      <c r="AN9" t="inlineStr">
         <is>
           <t>{'shape_in1': (4, 197, 768), 'shape_in2': (4, 197, 768), 'dtype_in1_in2_out': ('c10::BFloat16', 'c10::BFloat16', None), 'stride_input1': (151296, 768, 1), 'stride_input2': (151296, 768, 1), 'stride_output': None}</t>
         </is>
       </c>
-      <c r="AL9" t="b">
+      <c r="AO9" t="b">
         <v>1</v>
       </c>
-      <c r="AM9" t="n">
+      <c r="AP9" t="n">
         <v>4.369175102338875</v>
       </c>
-      <c r="AN9" t="n">
+      <c r="AQ9" t="n">
         <v>98.41470133187484</v>
       </c>
     </row>
@@ -3828,94 +6469,109 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>thread 5617 (python3)</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t>(((4, 1, 768), (4, 196, 768)), ())</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>('TensorList', 'Scalar')</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>(((0, 768, 1), (150528, 1, 196)), ())</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>('', '1')</t>
         </is>
       </c>
-      <c r="G10" t="n">
+      <c r="J10" t="n">
         <v>14</v>
       </c>
-      <c r="H10" t="n">
+      <c r="K10" t="n">
         <v>1</v>
       </c>
-      <c r="I10" t="n">
+      <c r="L10" t="n">
         <v>16.66</v>
       </c>
-      <c r="J10" t="n">
+      <c r="M10" t="n">
         <v>16.66</v>
       </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr"/>
-      <c r="T10" t="n">
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="n">
         <v>7.263916015625</v>
       </c>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="n">
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="n">
         <v>7.263916015625</v>
       </c>
-      <c r="W10" t="n">
+      <c r="Z10" t="n">
         <v>16.66</v>
       </c>
-      <c r="X10" t="n">
+      <c r="AA10" t="n">
         <v>16.66</v>
       </c>
-      <c r="Y10" t="n">
+      <c r="AB10" t="n">
         <v>16.66</v>
       </c>
-      <c r="Z10" t="inlineStr"/>
-      <c r="AA10" t="inlineStr"/>
-      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="inlineStr"/>
-      <c r="AF10" t="n">
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr"/>
+      <c r="AI10" t="n">
         <v>7.263916015625</v>
       </c>
-      <c r="AG10" t="n">
+      <c r="AJ10" t="n">
         <v>7.263916015625</v>
       </c>
-      <c r="AH10" t="n">
+      <c r="AK10" t="n">
         <v>7.263916015625</v>
       </c>
-      <c r="AI10" t="inlineStr">
+      <c r="AL10" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::(anonymous namespace)::CatArrayBatchedCopy&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 3, 64, 64&gt;(at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;*, at::native::(anonymous namespace)::CatArrInputTensorMetadata&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 64, 64&gt;, at::native::(anonymous namespace)::TensorSizeStride&lt;unsigned int, 4u&gt;, int, unsigned int)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(7.264), 'mean_duration_us': np.float64(7.264), 'median_duration_us': np.float64(7.264), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(7.264), 'max_duration_us': np.float64(7.264)}]</t>
         </is>
       </c>
-      <c r="AJ10" t="inlineStr">
+      <c r="AM10" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::(anonymous namespace)::CatArrayBatchedCopy&lt;at::...', 'stream': 7, 'mean_duration_us': np.float64(7.26)}]</t>
         </is>
       </c>
-      <c r="AK10" t="inlineStr"/>
-      <c r="AL10" t="b">
+      <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="b">
         <v>0</v>
       </c>
-      <c r="AM10" t="n">
+      <c r="AP10" t="n">
         <v>0.5928232777729626</v>
       </c>
-      <c r="AN10" t="n">
+      <c r="AQ10" t="n">
         <v>99.0075246096478</v>
       </c>
     </row>
@@ -3932,124 +6588,139 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>thread 5617 (python3)</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t>((768,), (4, 768), (768, 768), (), ())</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>('c10::BFloat16', 'c10::BFloat16', 'c10::BFloat16', 'Scalar', 'Scalar')</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>((1,), (151296, 1), (1, 768), (), ())</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>('', '', '', '1', '1')</t>
         </is>
       </c>
-      <c r="G11" t="n">
+      <c r="J11" t="n">
         <v>1256</v>
       </c>
-      <c r="H11" t="n">
+      <c r="K11" t="n">
         <v>1</v>
       </c>
-      <c r="I11" t="n">
+      <c r="L11" t="n">
         <v>31.331</v>
       </c>
-      <c r="J11" t="n">
+      <c r="M11" t="n">
         <v>31.331</v>
       </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="n">
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="n">
         <v>0.004721664</v>
       </c>
-      <c r="M11" t="n">
+      <c r="P11" t="n">
         <v>1.13818359375</v>
       </c>
-      <c r="N11" t="n">
+      <c r="Q11" t="n">
         <v>3.956241956241956</v>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>matrix_bf16</t>
         </is>
       </c>
-      <c r="P11" t="n">
+      <c r="S11" t="n">
         <v>0.1734973492333901</v>
       </c>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="n">
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="n">
         <v>0.6863974923339013</v>
       </c>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="n">
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="n">
         <v>6.87890625</v>
       </c>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="n">
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="n">
         <v>6.87890625</v>
       </c>
-      <c r="W11" t="n">
+      <c r="Z11" t="n">
         <v>31.331</v>
       </c>
-      <c r="X11" t="n">
+      <c r="AA11" t="n">
         <v>31.331</v>
       </c>
-      <c r="Y11" t="n">
+      <c r="AB11" t="n">
         <v>31.331</v>
       </c>
-      <c r="Z11" t="n">
+      <c r="AC11" t="n">
         <v>0.1734973492333901</v>
       </c>
-      <c r="AA11" t="n">
+      <c r="AD11" t="n">
         <v>0.1734973492333901</v>
       </c>
-      <c r="AB11" t="n">
+      <c r="AE11" t="n">
         <v>0.1734973492333901</v>
       </c>
-      <c r="AC11" t="n">
+      <c r="AF11" t="n">
         <v>0.6863974923339013</v>
       </c>
-      <c r="AD11" t="n">
+      <c r="AG11" t="n">
         <v>0.6863974923339013</v>
       </c>
-      <c r="AE11" t="n">
+      <c r="AH11" t="n">
         <v>0.6863974923339013</v>
       </c>
-      <c r="AF11" t="n">
+      <c r="AI11" t="n">
         <v>6.87890625</v>
       </c>
-      <c r="AG11" t="n">
+      <c r="AJ11" t="n">
         <v>6.87890625</v>
       </c>
-      <c r="AH11" t="n">
+      <c r="AK11" t="n">
         <v>6.87890625</v>
       </c>
-      <c r="AI11" t="inlineStr">
+      <c r="AL11" t="inlineStr">
         <is>
           <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_64x64_64x6_tn_align8&gt;(cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_64x64_64x6_tn_align8::Params)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(6.879), 'mean_duration_us': np.float64(6.879), 'median_duration_us': np.float64(6.879), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(6.879), 'max_duration_us': np.float64(6.879)}]</t>
         </is>
       </c>
-      <c r="AJ11" t="inlineStr">
+      <c r="AM11" t="inlineStr">
         <is>
           <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_80_tensorop_bf16_s16816gemm_relu_b...', 'stream': 7, 'mean_duration_us': np.float64(6.88)}]</t>
         </is>
       </c>
-      <c r="AK11" t="inlineStr">
+      <c r="AN11" t="inlineStr">
         <is>
           <t>{'M': 4, 'N': 768, 'K': 768, 'bias': True, 'stride_A': (151296, 1), 'stride_B': (1, 768), 'dtype_A_B': ('c10::BFloat16', 'c10::BFloat16'), 'B': 1}</t>
         </is>
       </c>
-      <c r="AL11" t="b">
+      <c r="AO11" t="b">
         <v>1</v>
       </c>
-      <c r="AM11" t="n">
+      <c r="AP11" t="n">
         <v>0.5614018308920443</v>
       </c>
-      <c r="AN11" t="n">
+      <c r="AQ11" t="n">
         <v>99.56892644053984</v>
       </c>
     </row>
@@ -4066,124 +6737,139 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>thread 5617 (python3)</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t>((4, 197, 768), (1, 197, 768), ())</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>('c10::BFloat16', 'c10::BFloat16', 'Scalar')</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>((151296, 768, 1), (151296, 768, 1), ())</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>('', '', '1')</t>
         </is>
       </c>
-      <c r="G12" t="n">
+      <c r="J12" t="n">
         <v>15</v>
       </c>
-      <c r="H12" t="n">
+      <c r="K12" t="n">
         <v>1</v>
       </c>
-      <c r="I12" t="n">
+      <c r="L12" t="n">
         <v>10.421</v>
       </c>
-      <c r="J12" t="n">
+      <c r="M12" t="n">
         <v>10.421</v>
       </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="n">
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="n">
         <v>0.000605184</v>
       </c>
-      <c r="M12" t="n">
+      <c r="P12" t="n">
         <v>2.59716796875</v>
       </c>
-      <c r="N12" t="n">
+      <c r="Q12" t="n">
         <v>0.2222222222222222</v>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>vector_bf16</t>
         </is>
       </c>
-      <c r="P12" t="n">
+      <c r="S12" t="n">
         <v>0.7210103734729494</v>
       </c>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="n">
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="n">
         <v>0.1602245274384332</v>
       </c>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="n">
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="n">
         <v>3.777099609375</v>
       </c>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="n">
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="n">
         <v>3.777099609375</v>
       </c>
-      <c r="W12" t="n">
+      <c r="Z12" t="n">
         <v>10.421</v>
       </c>
-      <c r="X12" t="n">
+      <c r="AA12" t="n">
         <v>10.421</v>
       </c>
-      <c r="Y12" t="n">
+      <c r="AB12" t="n">
         <v>10.421</v>
       </c>
-      <c r="Z12" t="n">
+      <c r="AC12" t="n">
         <v>0.7210103734729494</v>
       </c>
-      <c r="AA12" t="n">
+      <c r="AD12" t="n">
         <v>0.7210103734729494</v>
       </c>
-      <c r="AB12" t="n">
+      <c r="AE12" t="n">
         <v>0.7210103734729494</v>
       </c>
-      <c r="AC12" t="n">
+      <c r="AF12" t="n">
         <v>0.1602245274384332</v>
       </c>
-      <c r="AD12" t="n">
+      <c r="AG12" t="n">
         <v>0.1602245274384332</v>
       </c>
-      <c r="AE12" t="n">
+      <c r="AH12" t="n">
         <v>0.1602245274384332</v>
       </c>
-      <c r="AF12" t="n">
+      <c r="AI12" t="n">
         <v>3.777099609375</v>
       </c>
-      <c r="AG12" t="n">
+      <c r="AJ12" t="n">
         <v>3.777099609375</v>
       </c>
-      <c r="AH12" t="n">
+      <c r="AK12" t="n">
         <v>3.777099609375</v>
       </c>
-      <c r="AI12" t="inlineStr">
+      <c r="AL12" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(3.777), 'mean_duration_us': np.float64(3.777), 'median_duration_us': np.float64(3.777), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(3.777), 'max_duration_us': np.float64(3.777)}]</t>
         </is>
       </c>
-      <c r="AJ12" t="inlineStr">
+      <c r="AM12" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(3.78)}]</t>
         </is>
       </c>
-      <c r="AK12" t="inlineStr">
+      <c r="AN12" t="inlineStr">
         <is>
           <t>{'shape_in1': (4, 197, 768), 'shape_in2': (1, 197, 768), 'dtype_in1_in2_out': ('c10::BFloat16', 'c10::BFloat16', None), 'stride_input1': (151296, 768, 1), 'stride_input2': (151296, 768, 1), 'stride_output': None}</t>
         </is>
       </c>
-      <c r="AL12" t="b">
+      <c r="AO12" t="b">
         <v>1</v>
       </c>
-      <c r="AM12" t="n">
+      <c r="AP12" t="n">
         <v>0.3082569465407019</v>
       </c>
-      <c r="AN12" t="n">
+      <c r="AQ12" t="n">
         <v>99.87718338708055</v>
       </c>
     </row>
@@ -4200,94 +6886,109 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>thread 5617 (python3)</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t>((4, 768),)</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>('c10::BFloat16',)</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>((768, 1),)</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>('',)</t>
         </is>
       </c>
-      <c r="G13" t="n">
+      <c r="J13" t="n">
         <v>1258</v>
       </c>
-      <c r="H13" t="n">
+      <c r="K13" t="n">
         <v>1</v>
       </c>
-      <c r="I13" t="n">
+      <c r="L13" t="n">
         <v>12.47</v>
       </c>
-      <c r="J13" t="n">
+      <c r="M13" t="n">
         <v>12.47</v>
       </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr"/>
-      <c r="T13" t="n">
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="n">
         <v>1.5048828125</v>
       </c>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="n">
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="n">
         <v>1.5048828125</v>
       </c>
-      <c r="W13" t="n">
+      <c r="Z13" t="n">
         <v>12.47</v>
       </c>
-      <c r="X13" t="n">
+      <c r="AA13" t="n">
         <v>12.47</v>
       </c>
-      <c r="Y13" t="n">
+      <c r="AB13" t="n">
         <v>12.47</v>
       </c>
-      <c r="Z13" t="inlineStr"/>
-      <c r="AA13" t="inlineStr"/>
-      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="inlineStr"/>
-      <c r="AF13" t="n">
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="inlineStr"/>
+      <c r="AH13" t="inlineStr"/>
+      <c r="AI13" t="n">
         <v>1.5048828125</v>
       </c>
-      <c r="AG13" t="n">
+      <c r="AJ13" t="n">
         <v>1.5048828125</v>
       </c>
-      <c r="AH13" t="n">
+      <c r="AK13" t="n">
         <v>1.5048828125</v>
       </c>
-      <c r="AI13" t="inlineStr">
+      <c r="AL13" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::tanh_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::tanh_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(1.505), 'mean_duration_us': np.float64(1.505), 'median_duration_us': np.float64(1.505), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(1.505), 'max_duration_us': np.float64(1.505)}]</t>
         </is>
       </c>
-      <c r="AJ13" t="inlineStr">
+      <c r="AM13" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::ta...', 'stream': 7, 'mean_duration_us': np.float64(1.5)}]</t>
         </is>
       </c>
-      <c r="AK13" t="inlineStr"/>
-      <c r="AL13" t="b">
+      <c r="AN13" t="inlineStr"/>
+      <c r="AO13" t="b">
         <v>0</v>
       </c>
-      <c r="AM13" t="n">
+      <c r="AP13" t="n">
         <v>0.1228166129194549</v>
       </c>
-      <c r="AN13" t="n">
+      <c r="AQ13" t="n">
         <v>100</v>
       </c>
     </row>
@@ -4302,191 +7003,206 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK5"/>
+  <dimension ref="A1:AN5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>param: M</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>param: N</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>param: K</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>param: bias</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>param: stride_A</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>param: stride_B</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>param: dtype_A_B</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>param: B</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>GFLOPS_first</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Data Moved (MB)_first</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>FLOPS/Byte_first</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>TB/s_mean</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>TB/s_median</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>TB/s_std</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>TB/s_min</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>TB/s_max</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>TFLOPS/s_mean</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>TFLOPS/s_median</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>TFLOPS/s_std</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>TFLOPS/s_min</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>TFLOPS/s_max</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>process_name_first</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>process_label_first</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>thread_name_first</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Compute Spec</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>kernel_details__summarize_kernel_stats</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>trunc_kernel_details</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Input Dims_first</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Input type_first</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Input Strides_first</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Concrete Inputs_first</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_mean</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_median</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_std</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_min</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_max</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_sum</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>name_count</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>UID_first</t>
         </is>
@@ -4579,61 +7295,76 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>thread 5617 (python3)</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>matrix_bf16</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_128x64_64x6_tn_align8&gt;(cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_128x64_64x6_tn_align8::Params)', 'stream': 7, 'count': 48, 'total_duration_us': np.float64(399.136), 'mean_duration_us': np.float64(8.315333333333333), 'median_duration_us': np.float64(8.256), 'std_dev_duration_us': np.float64(0.13305517861231703), 'min_duration_us': np.float64(8.128), 'max_duration_us': np.float64(8.64)}]</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_80_tensorop_bf16_s16816gemm_relu_b...', 'stream': 7, 'mean_duration_us': np.float64(8.32)}]</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>[[768], [788, 768], [768, 768], [], []]</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>['c10::BFloat16', 'c10::BFloat16', 'c10::BFloat16', 'Scalar', 'Scalar']</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>[[1], [768, 1], [1, 768], [], []]</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>['', '', '', '1', '1']</t>
         </is>
       </c>
-      <c r="AD2" t="n">
+      <c r="AG2" t="n">
         <v>8.315348307291666</v>
       </c>
-      <c r="AE2" t="n">
+      <c r="AH2" t="n">
         <v>8.256103515625</v>
       </c>
-      <c r="AF2" t="n">
+      <c r="AI2" t="n">
         <v>0.1344482499064346</v>
       </c>
-      <c r="AG2" t="n">
+      <c r="AJ2" t="n">
         <v>8.1279296875</v>
       </c>
-      <c r="AH2" t="n">
+      <c r="AK2" t="n">
         <v>8.639892578125</v>
       </c>
-      <c r="AI2" t="n">
+      <c r="AL2" t="n">
         <v>399.13671875</v>
       </c>
-      <c r="AJ2" t="n">
+      <c r="AM2" t="n">
         <v>48</v>
       </c>
-      <c r="AK2" t="n">
+      <c r="AN2" t="n">
         <v>30</v>
       </c>
     </row>
@@ -4724,61 +7455,76 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>thread 5617 (python3)</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>matrix_bf16</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>[{'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'count': 12, 'total_duration_us': np.float64(166.59), 'mean_duration_us': np.float64(13.8825), 'median_duration_us': np.float64(13.8875), 'std_dev_duration_us': np.float64(0.10183278777813505), 'min_duration_us': np.float64(13.76), 'max_duration_us': np.float64(14.176)}]</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>[{'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warp...', 'stream': 7, 'mean_duration_us': np.float64(13.88)}]</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>[[3072], [788, 768], [768, 3072], [], []]</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>['c10::BFloat16', 'c10::BFloat16', 'c10::BFloat16', 'Scalar', 'Scalar']</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>[[1], [768, 1], [1, 768], [], []]</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
         <is>
           <t>['', '', '', '1', '1']</t>
         </is>
       </c>
-      <c r="AD3" t="n">
+      <c r="AG3" t="n">
         <v>13.88246663411458</v>
       </c>
-      <c r="AE3" t="n">
+      <c r="AH3" t="n">
         <v>13.887451171875</v>
       </c>
-      <c r="AF3" t="n">
+      <c r="AI3" t="n">
         <v>0.1063651301764554</v>
       </c>
-      <c r="AG3" t="n">
+      <c r="AJ3" t="n">
         <v>13.760009765625</v>
       </c>
-      <c r="AH3" t="n">
+      <c r="AK3" t="n">
         <v>14.176025390625</v>
       </c>
-      <c r="AI3" t="n">
+      <c r="AL3" t="n">
         <v>166.589599609375</v>
       </c>
-      <c r="AJ3" t="n">
+      <c r="AM3" t="n">
         <v>12</v>
       </c>
-      <c r="AK3" t="n">
+      <c r="AN3" t="n">
         <v>104</v>
       </c>
     </row>
@@ -4869,61 +7615,76 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>thread 5617 (python3)</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>matrix_bf16</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>[{'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x64x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'count': 12, 'total_duration_us': np.float64(162.43200000000002), 'mean_duration_us': np.float64(13.536000000000001), 'median_duration_us': np.float64(13.488), 'std_dev_duration_us': np.float64(0.16983128883296716), 'min_duration_us': np.float64(13.344), 'max_duration_us': np.float64(13.952)}]</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>[{'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x64x64_warpg...', 'stream': 7, 'mean_duration_us': np.float64(13.54)}]</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>[[768], [788, 3072], [3072, 768], [], []]</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>['c10::BFloat16', 'c10::BFloat16', 'c10::BFloat16', 'Scalar', 'Scalar']</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>[[1], [3072, 1], [1, 3072], [], []]</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
         <is>
           <t>['', '', '', '1', '1']</t>
         </is>
       </c>
-      <c r="AD4" t="n">
+      <c r="AG4" t="n">
         <v>13.53594970703125</v>
       </c>
-      <c r="AE4" t="n">
+      <c r="AH4" t="n">
         <v>13.4879150390625</v>
       </c>
-      <c r="AF4" t="n">
+      <c r="AI4" t="n">
         <v>0.1773776572326171</v>
       </c>
-      <c r="AG4" t="n">
+      <c r="AJ4" t="n">
         <v>13.343994140625</v>
       </c>
-      <c r="AH4" t="n">
+      <c r="AK4" t="n">
         <v>13.951904296875</v>
       </c>
-      <c r="AI4" t="n">
+      <c r="AL4" t="n">
         <v>162.431396484375</v>
       </c>
-      <c r="AJ4" t="n">
+      <c r="AM4" t="n">
         <v>12</v>
       </c>
-      <c r="AK4" t="n">
+      <c r="AN4" t="n">
         <v>114</v>
       </c>
     </row>
@@ -5010,59 +7771,74 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>thread 5617 (python3)</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>matrix_bf16</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_64x64_64x6_tn_align8&gt;(cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_64x64_64x6_tn_align8::Params)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(6.879), 'mean_duration_us': np.float64(6.879), 'median_duration_us': np.float64(6.879), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(6.879), 'max_duration_us': np.float64(6.879)}]</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_80_tensorop_bf16_s16816gemm_relu_b...', 'stream': 7, 'mean_duration_us': np.float64(6.88)}]</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>[[768], [4, 768], [768, 768], [], []]</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>['c10::BFloat16', 'c10::BFloat16', 'c10::BFloat16', 'Scalar', 'Scalar']</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>[[1], [151296, 1], [1, 768], [], []]</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
         <is>
           <t>['', '', '', '1', '1']</t>
         </is>
       </c>
-      <c r="AD5" t="n">
-        <v>6.87890625</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>6.87890625</v>
-      </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="n">
         <v>6.87890625</v>
       </c>
       <c r="AH5" t="n">
         <v>6.87890625</v>
       </c>
-      <c r="AI5" t="n">
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="n">
         <v>6.87890625</v>
       </c>
-      <c r="AJ5" t="n">
+      <c r="AK5" t="n">
+        <v>6.87890625</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>6.87890625</v>
+      </c>
+      <c r="AM5" t="n">
         <v>1</v>
       </c>
-      <c r="AK5" t="n">
+      <c r="AN5" t="n">
         <v>1256</v>
       </c>
     </row>
@@ -5077,201 +7853,216 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM2"/>
+  <dimension ref="A1:AP2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>param: B</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>param: N_Q</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>param: H_Q</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>param: N_KV</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>param: H_KV</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>param: d_h_qk</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>param: d_h_v</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>param: dropout</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>param: causal</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>param: flash_impl</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>GFLOPS_first</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Data Moved (MB)_first</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>FLOPS/Byte_first</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>TB/s_mean</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>TB/s_median</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>TB/s_std</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>TB/s_min</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>TB/s_max</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>TFLOPS/s_mean</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>TFLOPS/s_median</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>TFLOPS/s_std</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>TFLOPS/s_min</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>TFLOPS/s_max</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>process_name_first</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>process_label_first</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>thread_name_first</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Compute Spec</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>kernel_details__summarize_kernel_stats</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>trunc_kernel_details</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Input Dims_first</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Input type_first</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>Input Strides_first</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>Concrete Inputs_first</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_mean</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_median</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_std</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_min</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_max</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_sum</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>name_count</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>UID_first</t>
         </is>
@@ -5372,59 +8163,74 @@
       <c r="X2" t="n">
         <v>47.61178099819627</v>
       </c>
-      <c r="Y2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>python3</t>
+        </is>
+      </c>
       <c r="Z2" t="inlineStr">
         <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>thread 5617 (python3)</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr">
+        <is>
           <t>[{'name': 'void pytorch_flash::flash_fwd_kernel&lt;pytorch_flash::Flash_fwd_kernel_traits&lt;64, 128, 128, 4, false, false, cutlass::bfloat16_t, pytorch_flash::Flash_kernel_traits&lt;64, 128, 128, 4, cutlass::bfloat16_t&gt; &gt;, false, false, false, false, false, true, false&gt;(pytorch_flash::Flash_fwd_params)', 'stream': 7, 'count': 12, 'total_duration_us': np.float64(122.848), 'mean_duration_us': np.float64(10.237333333333334), 'median_duration_us': np.float64(10.224), 'std_dev_duration_us': np.float64(0.21878045819699932), 'min_duration_us': np.float64(10.016), 'max_duration_us': np.float64(10.848)}]</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>[{'name': 'void pytorch_flash::flash_fwd_kernel&lt;pytorch_flash::Flash_fwd_ke...', 'stream': 7, 'mean_duration_us': np.float64(10.24)}]</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>[[4, 12, 197, 64], [4, 12, 197, 64], [4, 12, 197, 64], [], [], [], []]</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>['c10::BFloat16', 'c10::BFloat16', 'c10::BFloat16', 'Scalar', 'Scalar', 'Scalar', 'Scalar']</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>[[151296, 64, 768, 1], [151296, 64, 768, 1], [151296, 64, 768, 1], [], [], [], []]</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
         <is>
           <t>['', '', '', '0.', 'False', 'False', '0.125']</t>
         </is>
       </c>
-      <c r="AF2" t="n">
+      <c r="AI2" t="n">
         <v>10.23734537760417</v>
       </c>
-      <c r="AG2" t="n">
+      <c r="AJ2" t="n">
         <v>10.2239990234375</v>
       </c>
-      <c r="AH2" t="n">
+      <c r="AK2" t="n">
         <v>0.228442528412397</v>
       </c>
-      <c r="AI2" t="n">
+      <c r="AL2" t="n">
         <v>10.01611328125</v>
       </c>
-      <c r="AJ2" t="n">
+      <c r="AM2" t="n">
         <v>10.847900390625</v>
       </c>
-      <c r="AK2" t="n">
+      <c r="AN2" t="n">
         <v>122.84814453125</v>
       </c>
-      <c r="AL2" t="n">
+      <c r="AO2" t="n">
         <v>12</v>
       </c>
-      <c r="AM2" t="n">
+      <c r="AP2" t="n">
         <v>61</v>
       </c>
     </row>
@@ -5439,216 +8245,231 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP2"/>
+  <dimension ref="A1:AS2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>param: convNd</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>param: input_shape</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>param: filter_shape</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>param: dtype_input_weight</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>param: input_stride</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>param: weight_stride</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>param: bias</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>param: stride</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>param: padding</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>param: dilation</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>param: transposed_conv</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>param: output_padding</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>param: groups</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>GFLOPS_first</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Data Moved (MB)_first</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>FLOPS/Byte_first</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>TB/s_mean</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>TB/s_median</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>TB/s_std</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>TB/s_min</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>TB/s_max</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>TFLOPS/s_mean</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>TFLOPS/s_median</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>TFLOPS/s_std</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>TFLOPS/s_min</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>TFLOPS/s_max</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>process_name_first</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>process_label_first</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>thread_name_first</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Compute Spec</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>kernel_details__summarize_kernel_stats</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>trunc_kernel_details</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>Input Dims_first</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>Input type_first</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>Input Strides_first</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>Concrete Inputs_first</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_mean</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_median</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_std</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_min</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_max</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_sum</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>name_count</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>UID_first</t>
         </is>
@@ -5762,59 +8583,74 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>thread 5617 (python3)</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
           <t>matrix_bf16</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>[{'name': 'Memset (Device)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(2.272), 'mean_duration_us': np.float64(2.272), 'median_duration_us': np.float64(2.272), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(2.272), 'max_duration_us': np.float64(2.272)}, {'name': 'void cudnn::engines_precompiled::nchwToNhwcKernel&lt;__nv_bfloat16, __nv_bfloat16, float, false, true, (cudnnKernelDataType_t)0&gt;(cudnn::engines_precompiled::nchw2nhwc_params_t&lt;float&gt;, __nv_bfloat16 const*, __nv_bfloat16*)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(10.464), 'mean_duration_us': np.float64(10.464), 'median_duration_us': np.float64(10.464), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(10.464), 'max_duration_us': np.float64(10.464)}, {'name': 'Memset (Device)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(2.112), 'mean_duration_us': np.float64(2.112), 'median_duration_us': np.float64(2.112), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(2.112), 'max_duration_us': np.float64(2.112)}, {'name': 'void cudnn::engines_precompiled::nchwToNhwcKernel&lt;__nv_bfloat16, __nv_bfloat16, float, false, true, (cudnnKernelDataType_t)0&gt;(cudnn::engines_precompiled::nchw2nhwc_params_t&lt;float&gt;, __nv_bfloat16 const*, __nv_bfloat16*)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(10.4), 'mean_duration_us': np.float64(10.4), 'median_duration_us': np.float64(10.4), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(10.4), 'max_duration_us': np.float64(10.4)}, {'name': 'void cutlass__5x_cudnn::Kernel&lt;cutlass_tensorop_bf16_s16816fprop_optimized_bf16_256x64_32x4_nhwc_align8&gt;(cutlass_tensorop_bf16_s16816fprop_optimized_bf16_256x64_32x4_nhwc_align8::Params)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(98.176), 'mean_duration_us': np.float64(98.176), 'median_duration_us': np.float64(98.176), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(98.176), 'max_duration_us': np.float64(98.176)}, {'name': 'void cudnn::engines_precompiled::nhwcToNchwKernel&lt;__nv_bfloat16, __nv_bfloat16, float, true, false, (cudnnKernelDataType_t)0&gt;(cudnn::engines_precompiled::nhwc2nchw_params_t&lt;float&gt;, __nv_bfloat16 const*, __nv_bfloat16*)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(2.208), 'mean_duration_us': np.float64(2.208), 'median_duration_us': np.float64(2.208), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(2.208), 'max_duration_us': np.float64(2.208)}, {'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(3.968), 'mean_duration_us': np.float64(3.968), 'median_duration_us': np.float64(3.968), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(3.968), 'max_duration_us': np.float64(3.968)}]</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>[{'name': 'Memset (Device)', 'stream': 7, 'mean_duration_us': np.float64(2.27)}, {'name': 'void cudnn::engines_precompiled::nchwToNhwcKernel&lt;__nv_bfloat16,...', 'stream': 7, 'mean_duration_us': np.float64(10.46)}, {'name': 'Memset (Device)', 'stream': 7, 'mean_duration_us': np.float64(2.11)}, {'name': 'void cudnn::engines_precompiled::nchwToNhwcKernel&lt;__nv_bfloat16,...', 'stream': 7, 'mean_duration_us': np.float64(10.4)}, {'name': 'void cutlass__5x_cudnn::Kernel&lt;cutlass_tensorop_bf16_s16816fprop...', 'stream': 7, 'mean_duration_us': np.float64(98.18)}, {'name': 'void cudnn::engines_precompiled::nhwcToNchwKernel&lt;__nv_bfloat16,...', 'stream': 7, 'mean_duration_us': np.float64(2.21)}, {'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(3.97)}]</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
         <is>
           <t>[[4, 3, 224, 224], [768, 3, 16, 16], [768], [], [], [], [], [], []]</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
         <is>
           <t>['c10::BFloat16', 'c10::BFloat16', 'c10::BFloat16', 'ScalarList', 'ScalarList', 'ScalarList', 'Scalar', 'ScalarList', 'Scalar']</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AJ2" t="inlineStr">
         <is>
           <t>[[150528, 50176, 224, 1], [768, 256, 16, 1], [1], [], [], [], [], [], []]</t>
         </is>
       </c>
-      <c r="AH2" t="inlineStr">
+      <c r="AK2" t="inlineStr">
         <is>
           <t>['', '', '', '[16, 16]', '[0, 0]', '[1, 1]', 'False', '[0, 0]', '1']</t>
         </is>
       </c>
-      <c r="AI2" t="n">
-        <v>129.60009765625</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>129.60009765625</v>
-      </c>
-      <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="n">
         <v>129.60009765625</v>
       </c>
       <c r="AM2" t="n">
         <v>129.60009765625</v>
       </c>
-      <c r="AN2" t="n">
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="n">
         <v>129.60009765625</v>
       </c>
-      <c r="AO2" t="n">
+      <c r="AP2" t="n">
+        <v>129.60009765625</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>129.60009765625</v>
+      </c>
+      <c r="AR2" t="n">
         <v>1</v>
       </c>
-      <c r="AP2" t="n">
+      <c r="AS2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -5829,181 +8665,196 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI4"/>
+  <dimension ref="A1:AL4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>param: shape_in1</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>param: shape_in2</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>param: dtype_in1_in2_out</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>param: stride_input1</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>param: stride_input2</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>param: stride_output</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>GFLOPS_first</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Data Moved (MB)_first</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>FLOPS/Byte_first</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>TB/s_mean</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>TB/s_median</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>TB/s_std</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>TB/s_min</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>TB/s_max</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>TFLOPS/s_mean</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>TFLOPS/s_median</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>TFLOPS/s_std</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>TFLOPS/s_min</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>TFLOPS/s_max</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>process_name_first</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>process_label_first</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>thread_name_first</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
         <is>
           <t>Compute Spec</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>kernel_details__summarize_kernel_stats</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>trunc_kernel_details</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Input Dims_first</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Input type_first</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Input Strides_first</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Concrete Inputs_first</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_mean</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_median</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_std</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_min</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_max</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_sum</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>name_count</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>UID_first</t>
         </is>
@@ -6040,11 +8891,7 @@
           <t>(151296, 768, 1)</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
         <v>0.000605184</v>
       </c>
@@ -6086,61 +8933,76 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>thread 5617 (python3)</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
           <t>vector_bf16</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 7, 'count': 24, 'total_duration_us': np.float64(53.536), 'mean_duration_us': np.float64(2.2306666666666666), 'median_duration_us': np.float64(2.2245), 'std_dev_duration_us': np.float64(0.033798011118341686), 'min_duration_us': np.float64(2.176), 'max_duration_us': np.float64(2.304)}]</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CU...', 'stream': 7, 'mean_duration_us': np.float64(2.23)}]</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>[[4, 197, 768], [4, 197, 768], []]</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>['c10::BFloat16', 'c10::BFloat16', 'Scalar']</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>[[151296, 768, 1], [151296, 768, 1], []]</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>['', '', '1']</t>
         </is>
       </c>
-      <c r="AB2" t="n">
+      <c r="AE2" t="n">
         <v>2.230662027994792</v>
       </c>
-      <c r="AC2" t="n">
+      <c r="AF2" t="n">
         <v>2.2244873046875</v>
       </c>
-      <c r="AD2" t="n">
+      <c r="AG2" t="n">
         <v>0.03450867810431143</v>
       </c>
-      <c r="AE2" t="n">
+      <c r="AH2" t="n">
         <v>2.176025390625</v>
       </c>
-      <c r="AF2" t="n">
+      <c r="AI2" t="n">
         <v>2.303955078125</v>
       </c>
-      <c r="AG2" t="n">
+      <c r="AJ2" t="n">
         <v>53.535888671875</v>
       </c>
-      <c r="AH2" t="n">
+      <c r="AK2" t="n">
         <v>24</v>
       </c>
-      <c r="AI2" t="n">
+      <c r="AL2" t="n">
         <v>90</v>
       </c>
     </row>
@@ -6175,11 +9037,7 @@
           <t>(768, 1, 1, 1)</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>0.000602112</v>
       </c>
@@ -6217,59 +9075,74 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>thread 5617 (python3)</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
           <t>vector_bf16</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(3.968), 'mean_duration_us': np.float64(3.968), 'median_duration_us': np.float64(3.968), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(3.968), 'max_duration_us': np.float64(3.968)}]</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(3.97)}]</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>[[4, 768, 14, 14], [1, 768, 1, 1], []]</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>['c10::BFloat16', 'c10::BFloat16', 'Scalar']</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>[[150528, 196, 14, 1], [768, 1, 1, 1], []]</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>['', '', '1']</t>
         </is>
       </c>
-      <c r="AB3" t="n">
-        <v>3.968017578125</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>3.968017578125</v>
-      </c>
-      <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="n">
         <v>3.968017578125</v>
       </c>
       <c r="AF3" t="n">
         <v>3.968017578125</v>
       </c>
-      <c r="AG3" t="n">
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="n">
         <v>3.968017578125</v>
       </c>
-      <c r="AH3" t="n">
+      <c r="AI3" t="n">
+        <v>3.968017578125</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>3.968017578125</v>
+      </c>
+      <c r="AK3" t="n">
         <v>1</v>
       </c>
-      <c r="AI3" t="n">
+      <c r="AL3" t="n">
         <v>7</v>
       </c>
     </row>
@@ -6304,11 +9177,7 @@
           <t>(151296, 768, 1)</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>0.000605184</v>
       </c>
@@ -6346,59 +9215,74 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>thread 5617 (python3)</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
           <t>vector_bf16</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(3.777), 'mean_duration_us': np.float64(3.777), 'median_duration_us': np.float64(3.777), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(3.777), 'max_duration_us': np.float64(3.777)}]</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(3.78)}]</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>[[4, 197, 768], [1, 197, 768], []]</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>['c10::BFloat16', 'c10::BFloat16', 'Scalar']</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>[[151296, 768, 1], [151296, 768, 1], []]</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>['', '', '1']</t>
         </is>
       </c>
-      <c r="AB4" t="n">
-        <v>3.777099609375</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>3.777099609375</v>
-      </c>
-      <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="n">
         <v>3.777099609375</v>
       </c>
       <c r="AF4" t="n">
         <v>3.777099609375</v>
       </c>
-      <c r="AG4" t="n">
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="n">
         <v>3.777099609375</v>
       </c>
-      <c r="AH4" t="n">
+      <c r="AI4" t="n">
+        <v>3.777099609375</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>3.777099609375</v>
+      </c>
+      <c r="AK4" t="n">
         <v>1</v>
       </c>
-      <c r="AI4" t="n">
+      <c r="AL4" t="n">
         <v>15</v>
       </c>
     </row>

--- a/tests/traces/h100/Falconsai_nsfw_image_detection__1016002_perf_report.xlsx
+++ b/tests/traces/h100/Falconsai_nsfw_image_detection__1016002_perf_report.xlsx
@@ -868,7 +868,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 7, 'count': 25, 'total_duration_us': np.float64(111.20100000000001), 'mean_duration_us': np.float64(4.448040000000001), 'median_duration_us': np.float64(4.448), 'std_dev_duration_us': np.float64(0.10934037863479323), 'min_duration_us': np.float64(4.256), 'max_duration_us': np.float64(4.64)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 7, 'gpu_op_uid': 4048, 'count': 25, 'total_duration_us': np.float64(111.20100000000001), 'mean_duration_us': np.float64(4.448040000000001), 'median_duration_us': np.float64(4.448), 'std_dev_duration_us': np.float64(0.10934037863479323), 'min_duration_us': np.float64(4.256), 'max_duration_us': np.float64(4.64)}]</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 7, 'count': 25, 'total_duration_us': np.float64(111.20100000000001), 'mean_duration_us': np.float64(4.448040000000001), 'median_duration_us': np.float64(4.448), 'std_dev_duration_us': np.float64(0.10934037863479323), 'min_duration_us': np.float64(4.256), 'max_duration_us': np.float64(4.64)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 7, 'gpu_op_uid': 4048, 'count': 25, 'total_duration_us': np.float64(111.20100000000001), 'mean_duration_us': np.float64(4.448040000000001), 'median_duration_us': np.float64(4.448), 'std_dev_duration_us': np.float64(0.10934037863479323), 'min_duration_us': np.float64(4.256), 'max_duration_us': np.float64(4.64)}]</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -5380,7 +5380,7 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_128x64_64x6_tn_align8&gt;(cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_128x64_64x6_tn_align8::Params)', 'stream': 7, 'count': 48, 'total_duration_us': np.float64(399.136), 'mean_duration_us': np.float64(8.315333333333333), 'median_duration_us': np.float64(8.256), 'std_dev_duration_us': np.float64(0.13305517861231703), 'min_duration_us': np.float64(8.128), 'max_duration_us': np.float64(8.64)}]</t>
+          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_128x64_64x6_tn_align8&gt;(cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_128x64_64x6_tn_align8::Params)', 'stream': 7, 'gpu_op_uid': 4056, 'count': 48, 'total_duration_us': np.float64(399.136), 'mean_duration_us': np.float64(8.315333333333333), 'median_duration_us': np.float64(8.256), 'std_dev_duration_us': np.float64(0.13305517861231703), 'min_duration_us': np.float64(8.128), 'max_duration_us': np.float64(8.64)}]</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
@@ -5537,7 +5537,7 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>[{'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'count': 12, 'total_duration_us': np.float64(166.59), 'mean_duration_us': np.float64(13.8825), 'median_duration_us': np.float64(13.8875), 'std_dev_duration_us': np.float64(0.10183278777813505), 'min_duration_us': np.float64(13.76), 'max_duration_us': np.float64(14.176)}]</t>
+          <t>[{'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'gpu_op_uid': 4108, 'count': 12, 'total_duration_us': np.float64(166.59), 'mean_duration_us': np.float64(13.8825), 'median_duration_us': np.float64(13.8875), 'std_dev_duration_us': np.float64(0.10183278777813505), 'min_duration_us': np.float64(13.76), 'max_duration_us': np.float64(14.176)}]</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>[{'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x64x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'count': 12, 'total_duration_us': np.float64(162.43200000000002), 'mean_duration_us': np.float64(13.536000000000001), 'median_duration_us': np.float64(13.488), 'std_dev_duration_us': np.float64(0.16983128883296716), 'min_duration_us': np.float64(13.344), 'max_duration_us': np.float64(13.952)}]</t>
+          <t>[{'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x64x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'gpu_op_uid': 4124, 'count': 12, 'total_duration_us': np.float64(162.43200000000002), 'mean_duration_us': np.float64(13.536000000000001), 'median_duration_us': np.float64(13.488), 'std_dev_duration_us': np.float64(0.16983128883296716), 'min_duration_us': np.float64(13.344), 'max_duration_us': np.float64(13.952)}]</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
@@ -5843,7 +5843,7 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>[{'name': 'Memset (Device)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(2.272), 'mean_duration_us': np.float64(2.272), 'median_duration_us': np.float64(2.272), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(2.272), 'max_duration_us': np.float64(2.272)}, {'name': 'void cudnn::engines_precompiled::nchwToNhwcKernel&lt;__nv_bfloat16, __nv_bfloat16, float, false, true, (cudnnKernelDataType_t)0&gt;(cudnn::engines_precompiled::nchw2nhwc_params_t&lt;float&gt;, __nv_bfloat16 const*, __nv_bfloat16*)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(10.464), 'mean_duration_us': np.float64(10.464), 'median_duration_us': np.float64(10.464), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(10.464), 'max_duration_us': np.float64(10.464)}, {'name': 'Memset (Device)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(2.112), 'mean_duration_us': np.float64(2.112), 'median_duration_us': np.float64(2.112), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(2.112), 'max_duration_us': np.float64(2.112)}, {'name': 'void cudnn::engines_precompiled::nchwToNhwcKernel&lt;__nv_bfloat16, __nv_bfloat16, float, false, true, (cudnnKernelDataType_t)0&gt;(cudnn::engines_precompiled::nchw2nhwc_params_t&lt;float&gt;, __nv_bfloat16 const*, __nv_bfloat16*)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(10.4), 'mean_duration_us': np.float64(10.4), 'median_duration_us': np.float64(10.4), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(10.4), 'max_duration_us': np.float64(10.4)}, {'name': 'void cutlass__5x_cudnn::Kernel&lt;cutlass_tensorop_bf16_s16816fprop_optimized_bf16_256x64_32x4_nhwc_align8&gt;(cutlass_tensorop_bf16_s16816fprop_optimized_bf16_256x64_32x4_nhwc_align8::Params)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(98.176), 'mean_duration_us': np.float64(98.176), 'median_duration_us': np.float64(98.176), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(98.176), 'max_duration_us': np.float64(98.176)}, {'name': 'void cudnn::engines_precompiled::nhwcToNchwKernel&lt;__nv_bfloat16, __nv_bfloat16, float, true, false, (cudnnKernelDataType_t)0&gt;(cudnn::engines_precompiled::nhwc2nchw_params_t&lt;float&gt;, __nv_bfloat16 const*, __nv_bfloat16*)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(2.208), 'mean_duration_us': np.float64(2.208), 'median_duration_us': np.float64(2.208), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(2.208), 'max_duration_us': np.float64(2.208)}, {'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(3.968), 'mean_duration_us': np.float64(3.968), 'median_duration_us': np.float64(3.968), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(3.968), 'max_duration_us': np.float64(3.968)}]</t>
+          <t>[{'name': 'Memset (Device)', 'stream': 7, 'gpu_op_uid': 4006, 'count': 1, 'total_duration_us': np.float64(2.272), 'mean_duration_us': np.float64(2.272), 'median_duration_us': np.float64(2.272), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(2.272), 'max_duration_us': np.float64(2.272)}, {'name': 'void cudnn::engines_precompiled::nchwToNhwcKernel&lt;__nv_bfloat16, __nv_bfloat16, float, false, true, (cudnnKernelDataType_t)0&gt;(cudnn::engines_precompiled::nchw2nhwc_params_t&lt;float&gt;, __nv_bfloat16 const*, __nv_bfloat16*)', 'stream': 7, 'gpu_op_uid': 4010, 'count': 1, 'total_duration_us': np.float64(10.464), 'mean_duration_us': np.float64(10.464), 'median_duration_us': np.float64(10.464), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(10.464), 'max_duration_us': np.float64(10.464)}, {'name': 'Memset (Device)', 'stream': 7, 'gpu_op_uid': 4014, 'count': 1, 'total_duration_us': np.float64(2.112), 'mean_duration_us': np.float64(2.112), 'median_duration_us': np.float64(2.112), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(2.112), 'max_duration_us': np.float64(2.112)}, {'name': 'void cudnn::engines_precompiled::nchwToNhwcKernel&lt;__nv_bfloat16, __nv_bfloat16, float, false, true, (cudnnKernelDataType_t)0&gt;(cudnn::engines_precompiled::nchw2nhwc_params_t&lt;float&gt;, __nv_bfloat16 const*, __nv_bfloat16*)', 'stream': 7, 'gpu_op_uid': 4018, 'count': 1, 'total_duration_us': np.float64(10.4), 'mean_duration_us': np.float64(10.4), 'median_duration_us': np.float64(10.4), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(10.4), 'max_duration_us': np.float64(10.4)}, {'name': 'void cutlass__5x_cudnn::Kernel&lt;cutlass_tensorop_bf16_s16816fprop_optimized_bf16_256x64_32x4_nhwc_align8&gt;(cutlass_tensorop_bf16_s16816fprop_optimized_bf16_256x64_32x4_nhwc_align8::Params)', 'stream': 7, 'gpu_op_uid': 4026, 'count': 1, 'total_duration_us': np.float64(98.176), 'mean_duration_us': np.float64(98.176), 'median_duration_us': np.float64(98.176), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(98.176), 'max_duration_us': np.float64(98.176)}, {'name': 'void cudnn::engines_precompiled::nhwcToNchwKernel&lt;__nv_bfloat16, __nv_bfloat16, float, true, false, (cudnnKernelDataType_t)0&gt;(cudnn::engines_precompiled::nhwc2nchw_params_t&lt;float&gt;, __nv_bfloat16 const*, __nv_bfloat16*)', 'stream': 7, 'gpu_op_uid': 4032, 'count': 1, 'total_duration_us': np.float64(2.208), 'mean_duration_us': np.float64(2.208), 'median_duration_us': np.float64(2.208), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(2.208), 'max_duration_us': np.float64(2.208)}, {'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1})', 'stream': 7, 'gpu_op_uid': 4036, 'count': 1, 'total_duration_us': np.float64(3.968), 'mean_duration_us': np.float64(3.968), 'median_duration_us': np.float64(3.968), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(3.968), 'max_duration_us': np.float64(3.968)}]</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
@@ -5996,7 +5996,7 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>[{'name': 'void pytorch_flash::flash_fwd_kernel&lt;pytorch_flash::Flash_fwd_kernel_traits&lt;64, 128, 128, 4, false, false, cutlass::bfloat16_t, pytorch_flash::Flash_kernel_traits&lt;64, 128, 128, 4, cutlass::bfloat16_t&gt; &gt;, false, false, false, false, false, true, false&gt;(pytorch_flash::Flash_fwd_params)', 'stream': 7, 'count': 12, 'total_duration_us': np.float64(122.848), 'mean_duration_us': np.float64(10.237333333333334), 'median_duration_us': np.float64(10.224), 'std_dev_duration_us': np.float64(0.21878045819699932), 'min_duration_us': np.float64(10.016), 'max_duration_us': np.float64(10.848)}]</t>
+          <t>[{'name': 'void pytorch_flash::flash_fwd_kernel&lt;pytorch_flash::Flash_fwd_kernel_traits&lt;64, 128, 128, 4, false, false, cutlass::bfloat16_t, pytorch_flash::Flash_kernel_traits&lt;64, 128, 128, 4, cutlass::bfloat16_t&gt; &gt;, false, false, false, false, false, true, false&gt;(pytorch_flash::Flash_fwd_params)', 'stream': 7, 'gpu_op_uid': 4080, 'count': 12, 'total_duration_us': np.float64(122.848), 'mean_duration_us': np.float64(10.237333333333334), 'median_duration_us': np.float64(10.224), 'std_dev_duration_us': np.float64(0.21878045819699932), 'min_duration_us': np.float64(10.016), 'max_duration_us': np.float64(10.848)}]</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
@@ -6153,7 +6153,7 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 7, 'count': 25, 'total_duration_us': np.float64(111.20100000000001), 'mean_duration_us': np.float64(4.448040000000001), 'median_duration_us': np.float64(4.448), 'std_dev_duration_us': np.float64(0.10934037863479323), 'min_duration_us': np.float64(4.256), 'max_duration_us': np.float64(4.64)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 7, 'gpu_op_uid': 4048, 'count': 25, 'total_duration_us': np.float64(111.20100000000001), 'mean_duration_us': np.float64(4.448040000000001), 'median_duration_us': np.float64(4.448), 'std_dev_duration_us': np.float64(0.10934037863479323), 'min_duration_us': np.float64(4.256), 'max_duration_us': np.float64(4.64)}]</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -6280,7 +6280,7 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::GeluCUDAKernelImpl(at::TensorIteratorBase&amp;, at::native::GeluType)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::GeluCUDAKernelImpl(at::TensorIteratorBase&amp;, at::native::GeluType)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 12, 'total_duration_us': np.float64(60.541999999999994), 'mean_duration_us': np.float64(5.045166666666666), 'median_duration_us': np.float64(5.0555), 'std_dev_duration_us': np.float64(0.037739972914080884), 'min_duration_us': np.float64(4.991), 'max_duration_us': np.float64(5.12)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::GeluCUDAKernelImpl(at::TensorIteratorBase&amp;, at::native::GeluType)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::GeluCUDAKernelImpl(at::TensorIteratorBase&amp;, at::native::GeluType)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'gpu_op_uid': 4112, 'count': 12, 'total_duration_us': np.float64(60.541999999999994), 'mean_duration_us': np.float64(5.045166666666666), 'median_duration_us': np.float64(5.0555), 'std_dev_duration_us': np.float64(0.037739972914080884), 'min_duration_us': np.float64(4.991), 'max_duration_us': np.float64(5.12)}]</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
@@ -6433,7 +6433,7 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 7, 'count': 24, 'total_duration_us': np.float64(53.536), 'mean_duration_us': np.float64(2.2306666666666666), 'median_duration_us': np.float64(2.2245), 'std_dev_duration_us': np.float64(0.033798011118341686), 'min_duration_us': np.float64(2.176), 'max_duration_us': np.float64(2.304)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 7, 'gpu_op_uid': 4092, 'count': 24, 'total_duration_us': np.float64(53.536), 'mean_duration_us': np.float64(2.2306666666666666), 'median_duration_us': np.float64(2.2245), 'std_dev_duration_us': np.float64(0.033798011118341686), 'min_duration_us': np.float64(2.176), 'max_duration_us': np.float64(2.304)}]</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -6556,7 +6556,7 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::CatArrayBatchedCopy&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 3, 64, 64&gt;(at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;*, at::native::(anonymous namespace)::CatArrInputTensorMetadata&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 64, 64&gt;, at::native::(anonymous namespace)::TensorSizeStride&lt;unsigned int, 4u&gt;, int, unsigned int)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(7.264), 'mean_duration_us': np.float64(7.264), 'median_duration_us': np.float64(7.264), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(7.264), 'max_duration_us': np.float64(7.264)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::CatArrayBatchedCopy&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 3, 64, 64&gt;(at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;*, at::native::(anonymous namespace)::CatArrInputTensorMetadata&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 64, 64&gt;, at::native::(anonymous namespace)::TensorSizeStride&lt;unsigned int, 4u&gt;, int, unsigned int)', 'stream': 7, 'gpu_op_uid': 4040, 'count': 1, 'total_duration_us': np.float64(7.264), 'mean_duration_us': np.float64(7.264), 'median_duration_us': np.float64(7.264), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(7.264), 'max_duration_us': np.float64(7.264)}]</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -6701,7 +6701,7 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_64x64_64x6_tn_align8&gt;(cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_64x64_64x6_tn_align8::Params)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(6.879), 'mean_duration_us': np.float64(6.879), 'median_duration_us': np.float64(6.879), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(6.879), 'max_duration_us': np.float64(6.879)}]</t>
+          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_64x64_64x6_tn_align8&gt;(cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_64x64_64x6_tn_align8::Params)', 'stream': 7, 'gpu_op_uid': 5064, 'count': 1, 'total_duration_us': np.float64(6.879), 'mean_duration_us': np.float64(6.879), 'median_duration_us': np.float64(6.879), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(6.879), 'max_duration_us': np.float64(6.879)}]</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
@@ -6850,7 +6850,7 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(3.777), 'mean_duration_us': np.float64(3.777), 'median_duration_us': np.float64(3.777), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(3.777), 'max_duration_us': np.float64(3.777)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1})', 'stream': 7, 'gpu_op_uid': 4044, 'count': 1, 'total_duration_us': np.float64(3.777), 'mean_duration_us': np.float64(3.777), 'median_duration_us': np.float64(3.777), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(3.777), 'max_duration_us': np.float64(3.777)}]</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -6973,7 +6973,7 @@
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::tanh_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::tanh_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(1.505), 'mean_duration_us': np.float64(1.505), 'median_duration_us': np.float64(1.505), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(1.505), 'max_duration_us': np.float64(1.505)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::tanh_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::tanh_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'gpu_op_uid': 5068, 'count': 1, 'total_duration_us': np.float64(1.505), 'mean_duration_us': np.float64(1.505), 'median_duration_us': np.float64(1.505), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(1.505), 'max_duration_us': np.float64(1.505)}]</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -7315,7 +7315,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_128x64_64x6_tn_align8&gt;(cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_128x64_64x6_tn_align8::Params)', 'stream': 7, 'count': 48, 'total_duration_us': np.float64(399.136), 'mean_duration_us': np.float64(8.315333333333333), 'median_duration_us': np.float64(8.256), 'std_dev_duration_us': np.float64(0.13305517861231703), 'min_duration_us': np.float64(8.128), 'max_duration_us': np.float64(8.64)}]</t>
+          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_128x64_64x6_tn_align8&gt;(cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_128x64_64x6_tn_align8::Params)', 'stream': 7, 'gpu_op_uid': 4056, 'count': 48, 'total_duration_us': np.float64(399.136), 'mean_duration_us': np.float64(8.315333333333333), 'median_duration_us': np.float64(8.256), 'std_dev_duration_us': np.float64(0.13305517861231703), 'min_duration_us': np.float64(8.128), 'max_duration_us': np.float64(8.64)}]</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -7475,7 +7475,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>[{'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'count': 12, 'total_duration_us': np.float64(166.59), 'mean_duration_us': np.float64(13.8825), 'median_duration_us': np.float64(13.8875), 'std_dev_duration_us': np.float64(0.10183278777813505), 'min_duration_us': np.float64(13.76), 'max_duration_us': np.float64(14.176)}]</t>
+          <t>[{'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'gpu_op_uid': 4108, 'count': 12, 'total_duration_us': np.float64(166.59), 'mean_duration_us': np.float64(13.8825), 'median_duration_us': np.float64(13.8875), 'std_dev_duration_us': np.float64(0.10183278777813505), 'min_duration_us': np.float64(13.76), 'max_duration_us': np.float64(14.176)}]</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -7635,7 +7635,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>[{'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x64x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'count': 12, 'total_duration_us': np.float64(162.43200000000002), 'mean_duration_us': np.float64(13.536000000000001), 'median_duration_us': np.float64(13.488), 'std_dev_duration_us': np.float64(0.16983128883296716), 'min_duration_us': np.float64(13.344), 'max_duration_us': np.float64(13.952)}]</t>
+          <t>[{'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x64x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'gpu_op_uid': 4124, 'count': 12, 'total_duration_us': np.float64(162.43200000000002), 'mean_duration_us': np.float64(13.536000000000001), 'median_duration_us': np.float64(13.488), 'std_dev_duration_us': np.float64(0.16983128883296716), 'min_duration_us': np.float64(13.344), 'max_duration_us': np.float64(13.952)}]</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -7791,7 +7791,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_64x64_64x6_tn_align8&gt;(cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_64x64_64x6_tn_align8::Params)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(6.879), 'mean_duration_us': np.float64(6.879), 'median_duration_us': np.float64(6.879), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(6.879), 'max_duration_us': np.float64(6.879)}]</t>
+          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_64x64_64x6_tn_align8&gt;(cutlass_80_tensorop_bf16_s16816gemm_relu_bf16_64x64_64x6_tn_align8::Params)', 'stream': 7, 'gpu_op_uid': 5064, 'count': 1, 'total_duration_us': np.float64(6.879), 'mean_duration_us': np.float64(6.879), 'median_duration_us': np.float64(6.879), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(6.879), 'max_duration_us': np.float64(6.879)}]</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -8181,7 +8181,7 @@
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>[{'name': 'void pytorch_flash::flash_fwd_kernel&lt;pytorch_flash::Flash_fwd_kernel_traits&lt;64, 128, 128, 4, false, false, cutlass::bfloat16_t, pytorch_flash::Flash_kernel_traits&lt;64, 128, 128, 4, cutlass::bfloat16_t&gt; &gt;, false, false, false, false, false, true, false&gt;(pytorch_flash::Flash_fwd_params)', 'stream': 7, 'count': 12, 'total_duration_us': np.float64(122.848), 'mean_duration_us': np.float64(10.237333333333334), 'median_duration_us': np.float64(10.224), 'std_dev_duration_us': np.float64(0.21878045819699932), 'min_duration_us': np.float64(10.016), 'max_duration_us': np.float64(10.848)}]</t>
+          <t>[{'name': 'void pytorch_flash::flash_fwd_kernel&lt;pytorch_flash::Flash_fwd_kernel_traits&lt;64, 128, 128, 4, false, false, cutlass::bfloat16_t, pytorch_flash::Flash_kernel_traits&lt;64, 128, 128, 4, cutlass::bfloat16_t&gt; &gt;, false, false, false, false, false, true, false&gt;(pytorch_flash::Flash_fwd_params)', 'stream': 7, 'gpu_op_uid': 4080, 'count': 12, 'total_duration_us': np.float64(122.848), 'mean_duration_us': np.float64(10.237333333333334), 'median_duration_us': np.float64(10.224), 'std_dev_duration_us': np.float64(0.21878045819699932), 'min_duration_us': np.float64(10.016), 'max_duration_us': np.float64(10.848)}]</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -8603,7 +8603,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>[{'name': 'Memset (Device)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(2.272), 'mean_duration_us': np.float64(2.272), 'median_duration_us': np.float64(2.272), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(2.272), 'max_duration_us': np.float64(2.272)}, {'name': 'void cudnn::engines_precompiled::nchwToNhwcKernel&lt;__nv_bfloat16, __nv_bfloat16, float, false, true, (cudnnKernelDataType_t)0&gt;(cudnn::engines_precompiled::nchw2nhwc_params_t&lt;float&gt;, __nv_bfloat16 const*, __nv_bfloat16*)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(10.464), 'mean_duration_us': np.float64(10.464), 'median_duration_us': np.float64(10.464), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(10.464), 'max_duration_us': np.float64(10.464)}, {'name': 'Memset (Device)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(2.112), 'mean_duration_us': np.float64(2.112), 'median_duration_us': np.float64(2.112), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(2.112), 'max_duration_us': np.float64(2.112)}, {'name': 'void cudnn::engines_precompiled::nchwToNhwcKernel&lt;__nv_bfloat16, __nv_bfloat16, float, false, true, (cudnnKernelDataType_t)0&gt;(cudnn::engines_precompiled::nchw2nhwc_params_t&lt;float&gt;, __nv_bfloat16 const*, __nv_bfloat16*)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(10.4), 'mean_duration_us': np.float64(10.4), 'median_duration_us': np.float64(10.4), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(10.4), 'max_duration_us': np.float64(10.4)}, {'name': 'void cutlass__5x_cudnn::Kernel&lt;cutlass_tensorop_bf16_s16816fprop_optimized_bf16_256x64_32x4_nhwc_align8&gt;(cutlass_tensorop_bf16_s16816fprop_optimized_bf16_256x64_32x4_nhwc_align8::Params)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(98.176), 'mean_duration_us': np.float64(98.176), 'median_duration_us': np.float64(98.176), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(98.176), 'max_duration_us': np.float64(98.176)}, {'name': 'void cudnn::engines_precompiled::nhwcToNchwKernel&lt;__nv_bfloat16, __nv_bfloat16, float, true, false, (cudnnKernelDataType_t)0&gt;(cudnn::engines_precompiled::nhwc2nchw_params_t&lt;float&gt;, __nv_bfloat16 const*, __nv_bfloat16*)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(2.208), 'mean_duration_us': np.float64(2.208), 'median_duration_us': np.float64(2.208), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(2.208), 'max_duration_us': np.float64(2.208)}, {'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(3.968), 'mean_duration_us': np.float64(3.968), 'median_duration_us': np.float64(3.968), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(3.968), 'max_duration_us': np.float64(3.968)}]</t>
+          <t>[{'name': 'Memset (Device)', 'stream': 7, 'gpu_op_uid': 4006, 'count': 1, 'total_duration_us': np.float64(2.272), 'mean_duration_us': np.float64(2.272), 'median_duration_us': np.float64(2.272), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(2.272), 'max_duration_us': np.float64(2.272)}, {'name': 'void cudnn::engines_precompiled::nchwToNhwcKernel&lt;__nv_bfloat16, __nv_bfloat16, float, false, true, (cudnnKernelDataType_t)0&gt;(cudnn::engines_precompiled::nchw2nhwc_params_t&lt;float&gt;, __nv_bfloat16 const*, __nv_bfloat16*)', 'stream': 7, 'gpu_op_uid': 4010, 'count': 1, 'total_duration_us': np.float64(10.464), 'mean_duration_us': np.float64(10.464), 'median_duration_us': np.float64(10.464), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(10.464), 'max_duration_us': np.float64(10.464)}, {'name': 'Memset (Device)', 'stream': 7, 'gpu_op_uid': 4014, 'count': 1, 'total_duration_us': np.float64(2.112), 'mean_duration_us': np.float64(2.112), 'median_duration_us': np.float64(2.112), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(2.112), 'max_duration_us': np.float64(2.112)}, {'name': 'void cudnn::engines_precompiled::nchwToNhwcKernel&lt;__nv_bfloat16, __nv_bfloat16, float, false, true, (cudnnKernelDataType_t)0&gt;(cudnn::engines_precompiled::nchw2nhwc_params_t&lt;float&gt;, __nv_bfloat16 const*, __nv_bfloat16*)', 'stream': 7, 'gpu_op_uid': 4018, 'count': 1, 'total_duration_us': np.float64(10.4), 'mean_duration_us': np.float64(10.4), 'median_duration_us': np.float64(10.4), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(10.4), 'max_duration_us': np.float64(10.4)}, {'name': 'void cutlass__5x_cudnn::Kernel&lt;cutlass_tensorop_bf16_s16816fprop_optimized_bf16_256x64_32x4_nhwc_align8&gt;(cutlass_tensorop_bf16_s16816fprop_optimized_bf16_256x64_32x4_nhwc_align8::Params)', 'stream': 7, 'gpu_op_uid': 4026, 'count': 1, 'total_duration_us': np.float64(98.176), 'mean_duration_us': np.float64(98.176), 'median_duration_us': np.float64(98.176), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(98.176), 'max_duration_us': np.float64(98.176)}, {'name': 'void cudnn::engines_precompiled::nhwcToNchwKernel&lt;__nv_bfloat16, __nv_bfloat16, float, true, false, (cudnnKernelDataType_t)0&gt;(cudnn::engines_precompiled::nhwc2nchw_params_t&lt;float&gt;, __nv_bfloat16 const*, __nv_bfloat16*)', 'stream': 7, 'gpu_op_uid': 4032, 'count': 1, 'total_duration_us': np.float64(2.208), 'mean_duration_us': np.float64(2.208), 'median_duration_us': np.float64(2.208), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(2.208), 'max_duration_us': np.float64(2.208)}, {'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1})', 'stream': 7, 'gpu_op_uid': 4036, 'count': 1, 'total_duration_us': np.float64(3.968), 'mean_duration_us': np.float64(3.968), 'median_duration_us': np.float64(3.968), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(3.968), 'max_duration_us': np.float64(3.968)}]</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 7, 'count': 24, 'total_duration_us': np.float64(53.536), 'mean_duration_us': np.float64(2.2306666666666666), 'median_duration_us': np.float64(2.2245), 'std_dev_duration_us': np.float64(0.033798011118341686), 'min_duration_us': np.float64(2.176), 'max_duration_us': np.float64(2.304)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 7, 'gpu_op_uid': 4092, 'count': 24, 'total_duration_us': np.float64(53.536), 'mean_duration_us': np.float64(2.2306666666666666), 'median_duration_us': np.float64(2.2245), 'std_dev_duration_us': np.float64(0.033798011118341686), 'min_duration_us': np.float64(2.176), 'max_duration_us': np.float64(2.304)}]</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -9095,7 +9095,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(3.968), 'mean_duration_us': np.float64(3.968), 'median_duration_us': np.float64(3.968), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(3.968), 'max_duration_us': np.float64(3.968)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1})', 'stream': 7, 'gpu_op_uid': 4036, 'count': 1, 'total_duration_us': np.float64(3.968), 'mean_duration_us': np.float64(3.968), 'median_duration_us': np.float64(3.968), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(3.968), 'max_duration_us': np.float64(3.968)}]</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -9235,7 +9235,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(3.777), 'mean_duration_us': np.float64(3.777), 'median_duration_us': np.float64(3.777), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(3.777), 'max_duration_us': np.float64(3.777)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1})', 'stream': 7, 'gpu_op_uid': 4044, 'count': 1, 'total_duration_us': np.float64(3.777), 'mean_duration_us': np.float64(3.777), 'median_duration_us': np.float64(3.777), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(3.777), 'max_duration_us': np.float64(3.777)}]</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
